--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-07.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-05 00:18:01</t>
+          <t>2026-05-05 02:26:21</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-05 00:18:01</t>
+          <t>2026-05-05 02:26:21</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G4" t="n">
         <v>2.1</v>
@@ -1154,13 +1154,13 @@
         <v>4.8</v>
       </c>
       <c r="I4" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="J4" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K4" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1178,7 +1178,7 @@
         <v>1.52</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-05 00:18:01</t>
+          <t>2026-05-05 02:26:21</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
         <v>1.4</v>
       </c>
       <c r="I5" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="J5" t="n">
         <v>5.2</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-05 00:18:01</t>
+          <t>2026-05-05 02:26:21</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-07.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-05 02:26:21</t>
+          <t>2026-05-05 04:34:24</t>
         </is>
       </c>
     </row>
@@ -942,31 +942,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>National Bank</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ismaily</t>
+          <t>ZED FC</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.66</v>
+        <v>1.99</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>4.8</v>
       </c>
       <c r="I3" t="n">
-        <v>14.5</v>
+        <v>5.4</v>
       </c>
       <c r="J3" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K3" t="n">
-        <v>950</v>
+        <v>3.4</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -981,10 +981,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.12</v>
+        <v>2.66</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-05 02:26:21</t>
+          <t>2026-05-05 04:34:24</t>
         </is>
       </c>
     </row>
@@ -1136,31 +1136,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>National Bank</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ZED FC</t>
+          <t>Ismaily</t>
         </is>
       </c>
       <c r="F4" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" t="n">
         <v>2.04</v>
       </c>
-      <c r="G4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="H4" t="n">
-        <v>4.8</v>
-      </c>
       <c r="I4" t="n">
-        <v>4.9</v>
+        <v>14.5</v>
       </c>
       <c r="J4" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="K4" t="n">
-        <v>3.3</v>
+        <v>950</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1175,10 +1175,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.66</v>
+        <v>2.12</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-05 02:26:21</t>
+          <t>2026-05-05 04:34:24</t>
         </is>
       </c>
     </row>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-05 02:26:21</t>
+          <t>2026-05-05 04:34:24</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-07.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-05 04:34:24</t>
+          <t>2026-05-05 06:43:40</t>
         </is>
       </c>
     </row>
@@ -951,13 +951,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I3" t="n">
         <v>5.4</v>
@@ -966,7 +966,7 @@
         <v>3.1</v>
       </c>
       <c r="K3" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -981,10 +981,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-05 04:34:24</t>
+          <t>2026-05-05 06:43:40</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="G4" t="n">
         <v>2</v>
@@ -1154,10 +1154,10 @@
         <v>2.04</v>
       </c>
       <c r="I4" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="J4" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K4" t="n">
         <v>950</v>
@@ -1178,7 +1178,7 @@
         <v>1.56</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-05 04:34:24</t>
+          <t>2026-05-05 06:43:40</t>
         </is>
       </c>
     </row>
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="G5" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="H5" t="n">
         <v>1.4</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-05 04:34:24</t>
+          <t>2026-05-05 06:43:40</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-07.xlsx
@@ -757,10 +757,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="G2" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
         <v>3.7</v>
@@ -769,10 +769,10 @@
         <v>6</v>
       </c>
       <c r="J2" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="K2" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-05 06:43:40</t>
+          <t>2026-05-05 08:54:04</t>
         </is>
       </c>
     </row>
@@ -942,31 +942,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>National Bank</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ZED FC</t>
+          <t>Ismaily</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="G3" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H3" t="n">
-        <v>4.7</v>
+        <v>1.97</v>
       </c>
       <c r="I3" t="n">
-        <v>5.4</v>
+        <v>16.5</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="K3" t="n">
-        <v>3.35</v>
+        <v>950</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -981,10 +981,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.68</v>
+        <v>2.26</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-05 06:43:40</t>
+          <t>2026-05-05 08:54:04</t>
         </is>
       </c>
     </row>
@@ -1136,31 +1136,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>National Bank</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ismaily</t>
+          <t>ZED FC</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.75</v>
+        <v>1.99</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="H4" t="n">
-        <v>2.04</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
-        <v>13</v>
+        <v>5.5</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K4" t="n">
-        <v>950</v>
+        <v>3.4</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1175,10 +1175,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.24</v>
+        <v>2.62</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-05 06:43:40</t>
+          <t>2026-05-05 08:54:04</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="G5" t="n">
         <v>9.6</v>
       </c>
       <c r="H5" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="I5" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="J5" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="K5" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-05 06:43:40</t>
+          <t>2026-05-05 08:54:04</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-07.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-05 08:54:04</t>
+          <t>2026-05-05 11:04:01</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="G3" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="H3" t="n">
-        <v>1.97</v>
+        <v>5.7</v>
       </c>
       <c r="I3" t="n">
-        <v>16.5</v>
+        <v>7.4</v>
       </c>
       <c r="J3" t="n">
-        <v>2.92</v>
+        <v>3.3</v>
       </c>
       <c r="K3" t="n">
-        <v>950</v>
+        <v>3.85</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -981,10 +981,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-05 08:54:04</t>
+          <t>2026-05-05 11:04:01</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-05 08:54:04</t>
+          <t>2026-05-05 11:04:01</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
         <v>7.4</v>
       </c>
       <c r="G5" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="H5" t="n">
         <v>1.36</v>
@@ -1372,7 +1372,7 @@
         <v>3.05</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-05 08:54:04</t>
+          <t>2026-05-05 11:04:01</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH5"/>
+  <dimension ref="A1:BH9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,34 +757,34 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="H2" t="n">
         <v>3.7</v>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>110</v>
       </c>
       <c r="J2" t="n">
-        <v>2.26</v>
+        <v>1.49</v>
       </c>
       <c r="K2" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="P2" t="n">
         <v>1.26</v>
@@ -793,141 +793,141 @@
         <v>3</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-05 11:04:01</t>
+          <t>2026-05-05 13:13:41</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,191 +937,191 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>National Bank</t>
+          <t>Paradou</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ismaily</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.75</v>
+        <v>1.04</v>
       </c>
       <c r="G3" t="n">
-        <v>1.92</v>
+        <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="I3" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="K3" t="n">
-        <v>3.85</v>
+        <v>950</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P3" t="n">
-        <v>1.58</v>
+        <v>1.24</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.36</v>
+        <v>1.02</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-05 11:04:01</t>
+          <t>2026-05-05 13:13:41</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,378 +1131,1154 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ZED FC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.99</v>
+        <v>1.04</v>
       </c>
       <c r="G4" t="n">
-        <v>2.02</v>
+        <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="I4" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="K4" t="n">
-        <v>3.4</v>
+        <v>950</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P4" t="n">
-        <v>1.52</v>
+        <v>1.24</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.62</v>
+        <v>1.36</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-05 11:04:01</t>
+          <t>2026-05-05 13:13:41</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Finnish Ykkosliiga</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PK-35 RY</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>MP</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>2026-05-05 13:13:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Egyptian Premier</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Haras El Hodood</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>ZED FC</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>2026-05-05 13:13:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Egyptian Premier</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>National Bank</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Ismaily</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="H7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="I7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>2026-05-05 13:13:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>Saudi Professional League</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>15:00:00</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Al-Shabab (KSA)</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Al Nassr</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="F8" t="n">
         <v>7.4</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G8" t="n">
         <v>10.5</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H8" t="n">
         <v>1.36</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I8" t="n">
         <v>1.45</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J8" t="n">
         <v>5.5</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K8" t="n">
         <v>6.8</v>
       </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
         <v>3.05</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="Q8" t="n">
         <v>1.39</v>
       </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>2026-05-05 11:04:01</t>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>2026-05-05 13:13:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Algerian Ligue 1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>MC Oran</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>ASO Chlef</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K9" t="n">
+        <v>950</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>2026-05-05 13:13:41</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH9"/>
+  <dimension ref="A1:BH10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="G2" t="n">
         <v>3.1</v>
@@ -766,10 +766,10 @@
         <v>3.7</v>
       </c>
       <c r="I2" t="n">
-        <v>110</v>
+        <v>6</v>
       </c>
       <c r="J2" t="n">
-        <v>1.49</v>
+        <v>1.95</v>
       </c>
       <c r="K2" t="n">
         <v>3.05</v>
@@ -781,13 +781,13 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="O2" t="n">
         <v>1.7</v>
       </c>
       <c r="P2" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q2" t="n">
         <v>3</v>
@@ -805,7 +805,7 @@
         <v>1.56</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="W2" t="n">
         <v>1.47</v>
@@ -865,7 +865,7 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
         <v>1.16</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-05 13:13:41</t>
+          <t>2026-05-05 15:23:41</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K3" t="n">
         <v>950</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-05 13:13:41</t>
+          <t>2026-05-05 15:23:41</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K4" t="n">
         <v>950</v>
@@ -1172,19 +1172,19 @@
         <v>1.25</v>
       </c>
       <c r="O4" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P4" t="n">
         <v>1.24</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="R4" t="n">
         <v>1.12</v>
       </c>
       <c r="S4" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T4" t="n">
         <v>1.01</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-05 13:13:41</t>
+          <t>2026-05-05 15:23:41</t>
         </is>
       </c>
     </row>
@@ -1339,170 +1339,170 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="G5" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="H5" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="I5" t="n">
         <v>5.5</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K5" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P5" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-05 13:13:41</t>
+          <t>2026-05-05 15:23:41</t>
         </is>
       </c>
     </row>
@@ -1533,170 +1533,170 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="G6" t="n">
         <v>1.98</v>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="I6" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="J6" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K6" t="n">
         <v>3.45</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="P6" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Q6" t="n">
         <v>2.62</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-05 13:13:41</t>
+          <t>2026-05-05 15:23:41</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="G7" t="n">
         <v>1.92</v>
@@ -1742,19 +1742,19 @@
         <v>3.3</v>
       </c>
       <c r="K7" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="P7" t="n">
         <v>1.58</v>
@@ -1763,141 +1763,141 @@
         <v>2.36</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-05 13:13:41</t>
+          <t>2026-05-05 15:23:41</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Turkish 1 Lig</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,378 +1907,572 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Al-Shabab (KSA)</t>
+          <t>Corum Belediyespor</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Keciorengucu</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>7.4</v>
+        <v>1.66</v>
       </c>
       <c r="G8" t="n">
-        <v>10.5</v>
+        <v>1.78</v>
       </c>
       <c r="H8" t="n">
-        <v>1.36</v>
+        <v>5.1</v>
       </c>
       <c r="I8" t="n">
-        <v>1.45</v>
+        <v>6.6</v>
       </c>
       <c r="J8" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="K8" t="n">
-        <v>6.8</v>
+        <v>4.6</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P8" t="n">
-        <v>3.05</v>
+        <v>2.14</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.39</v>
+        <v>1.65</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-05 13:13:41</t>
+          <t>2026-05-05 15:23:41</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Saudi Professional League</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Al-Shabab (KSA)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Al Nassr</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>8</v>
+      </c>
+      <c r="G9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="J9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="K9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V9" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X9" t="n">
+        <v>55</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>65</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>48</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>100</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>18</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>2026-05-05 15:23:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Algerian Ligue 1</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>16:00:00</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>MC Oran</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>ASO Chlef</t>
         </is>
       </c>
-      <c r="F9" t="n">
+      <c r="F10" t="n">
         <v>1.04</v>
       </c>
-      <c r="G9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H9" t="n">
+      <c r="G10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H10" t="n">
         <v>1.04</v>
       </c>
-      <c r="I9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="K9" t="n">
+      <c r="I10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K10" t="n">
         <v>950</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>2026-05-05 13:13:41</t>
+      <c r="Q10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>2026-05-05 15:23:41</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH10"/>
+  <dimension ref="A1:BH14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -766,10 +766,10 @@
         <v>3.7</v>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>970</v>
       </c>
       <c r="J2" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="K2" t="n">
         <v>3.05</v>
@@ -805,7 +805,7 @@
         <v>1.56</v>
       </c>
       <c r="V2" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W2" t="n">
         <v>1.47</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-05 15:23:41</t>
+          <t>2026-05-05 16:03:36</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-05 15:23:41</t>
+          <t>2026-05-05 16:03:36</t>
         </is>
       </c>
     </row>
@@ -1308,14 +1308,14 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-05 15:23:41</t>
+          <t>2026-05-05 16:03:36</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Finnish Ykkosliiga</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,36 +1325,36 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PK-35 RY</t>
+          <t>FK Tukums 2000</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.78</v>
+        <v>1.04</v>
       </c>
       <c r="G5" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>2.14</v>
       </c>
       <c r="I5" t="n">
-        <v>5.5</v>
+        <v>870</v>
       </c>
       <c r="J5" t="n">
-        <v>3.35</v>
+        <v>2.18</v>
       </c>
       <c r="K5" t="n">
-        <v>4.2</v>
+        <v>950</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1363,22 +1363,22 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="O5" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="P5" t="n">
-        <v>1.84</v>
+        <v>1.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.96</v>
+        <v>1.27</v>
       </c>
       <c r="R5" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>1.28</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1387,10 +1387,10 @@
         <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1502,14 +1502,14 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-05 15:23:41</t>
+          <t>2026-05-05 16:03:36</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Finnish Ykkosliiga</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,184 +1519,184 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>PK-35 RY</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ZED FC</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
       <c r="G6" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="H6" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="J6" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="K6" t="n">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>2.54</v>
+        <v>1.85</v>
       </c>
       <c r="O6" t="n">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="P6" t="n">
-        <v>1.53</v>
+        <v>1.84</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.62</v>
+        <v>1.96</v>
       </c>
       <c r="R6" t="n">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="S6" t="n">
-        <v>5.5</v>
+        <v>3</v>
       </c>
       <c r="T6" t="n">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W6" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X6" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>5.6</v>
+        <v>1.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AV6" t="n">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW6" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AY6" t="n">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6" t="n">
-        <v>23</v>
+        <v>1.03</v>
       </c>
       <c r="BA6" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BC6" t="n">
-        <v>23</v>
+        <v>1.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-05 15:23:41</t>
+          <t>2026-05-05 16:03:36</t>
         </is>
       </c>
     </row>
@@ -1718,186 +1718,186 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>National Bank</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ismaily</t>
+          <t>ZED FC</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="G7" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="H7" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="I7" t="n">
-        <v>7.4</v>
+        <v>5.8</v>
       </c>
       <c r="J7" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="K7" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N7" t="n">
-        <v>1.58</v>
+        <v>2.54</v>
       </c>
       <c r="O7" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="P7" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.36</v>
+        <v>2.62</v>
       </c>
       <c r="R7" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="V7" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="W7" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="X7" t="n">
-        <v>13.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y7" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>170</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>300</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>210</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>32</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB7" t="n">
         <v>21</v>
       </c>
-      <c r="Z7" t="n">
-        <v>65</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>34</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>38</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>28</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>2.4</v>
-      </c>
       <c r="BC7" t="n">
-        <v>2.42</v>
+        <v>23</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.52</v>
+        <v>10</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.62</v>
+        <v>11.5</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.62</v>
+        <v>20</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.62</v>
+        <v>11.5</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-05 15:23:41</t>
+          <t>2026-05-05 16:03:36</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Turkish 1 Lig</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1912,56 +1912,56 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Corum Belediyespor</t>
+          <t>National Bank</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Keciorengucu</t>
+          <t>Ismaily</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="G8" t="n">
-        <v>1.78</v>
+        <v>1.92</v>
       </c>
       <c r="H8" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="I8" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="J8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S8" t="n">
         <v>4</v>
       </c>
-      <c r="K8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.66</v>
-      </c>
       <c r="T8" t="n">
         <v>1.01</v>
       </c>
@@ -1969,55 +1969,55 @@
         <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="W8" t="n">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA8" t="n">
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AE8" t="n">
         <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AI8" t="n">
         <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM8" t="n">
         <v>1000</v>
@@ -2029,69 +2029,69 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.03</v>
+        <v>2.18</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.03</v>
+        <v>2.52</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.03</v>
+        <v>2.62</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.03</v>
+        <v>2.02</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.03</v>
+        <v>2.12</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.03</v>
+        <v>2.62</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.03</v>
+        <v>2.18</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.03</v>
+        <v>2.22</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.03</v>
+        <v>2.44</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.03</v>
+        <v>2.62</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.03</v>
+        <v>2.4</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.03</v>
+        <v>2.42</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.03</v>
+        <v>2.52</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.03</v>
+        <v>2.62</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-05 15:23:41</t>
+          <t>2026-05-05 16:03:36</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,108 +2101,108 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Al-Shabab (KSA)</t>
+          <t>FK Auda</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>SC Grobina</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>8</v>
+        <v>1.4</v>
       </c>
       <c r="G9" t="n">
-        <v>10.5</v>
+        <v>1.55</v>
       </c>
       <c r="H9" t="n">
-        <v>1.33</v>
+        <v>2.9</v>
       </c>
       <c r="I9" t="n">
-        <v>1.42</v>
+        <v>870</v>
       </c>
       <c r="J9" t="n">
-        <v>5.7</v>
+        <v>2.88</v>
       </c>
       <c r="K9" t="n">
-        <v>6.8</v>
+        <v>950</v>
       </c>
       <c r="L9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="R9" t="n">
         <v>1.18</v>
       </c>
-      <c r="M9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="P9" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.76</v>
-      </c>
       <c r="S9" t="n">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="T9" t="n">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="U9" t="n">
         <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>3.35</v>
+        <v>1.06</v>
       </c>
       <c r="W9" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="X9" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
         <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
         <v>1000</v>
@@ -2211,7 +2211,7 @@
         <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
         <v>1000</v>
@@ -2223,256 +2223,1032 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.71</v>
+        <v>1.03</v>
       </c>
       <c r="AQ9" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.6</v>
+        <v>1.03</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.61</v>
+        <v>1.03</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.72</v>
+        <v>1.03</v>
       </c>
       <c r="AU9" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.6</v>
+        <v>1.03</v>
       </c>
       <c r="AW9" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.77</v>
+        <v>1.03</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.7</v>
+        <v>1.03</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.67</v>
+        <v>1.03</v>
       </c>
       <c r="BA9" t="n">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.77</v>
+        <v>1.03</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.77</v>
+        <v>1.03</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.73</v>
+        <v>1.03</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.77</v>
+        <v>1.03</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.77</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.77</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-05 15:23:41</t>
+          <t>2026-05-05 16:03:36</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Turkish 1 Lig</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Corum Belediyespor</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Keciorengucu</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="H10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:03:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Saudi Professional League</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Al-Shabab (KSA)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Al Nassr</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>8</v>
+      </c>
+      <c r="G11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="K11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="P11" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V11" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>55</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>46</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:03:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>Algerian Ligue 1</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>16:00:00</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>MC Oran</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>ASO Chlef</t>
         </is>
       </c>
-      <c r="F10" t="n">
+      <c r="F12" t="n">
         <v>1.04</v>
       </c>
-      <c r="G10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H10" t="n">
+      <c r="G12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H12" t="n">
         <v>1.04</v>
       </c>
-      <c r="I10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="K10" t="n">
+      <c r="I12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K12" t="n">
         <v>950</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>2026-05-05 15:23:41</t>
+      <c r="Q12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:03:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>CA Platense</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Penarol</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:03:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Mirassol</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>LDU</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="H14" t="n">
+        <v>7</v>
+      </c>
+      <c r="I14" t="n">
+        <v>8</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>310</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>160</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>230</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>260</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>10</v>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:03:36</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH14"/>
+  <dimension ref="A1:BH18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -781,13 +781,13 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="O2" t="n">
         <v>1.7</v>
       </c>
       <c r="P2" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Q2" t="n">
         <v>3</v>
@@ -802,10 +802,10 @@
         <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="V2" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="W2" t="n">
         <v>1.47</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
@@ -1178,13 +1178,13 @@
         <v>1.24</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="R4" t="n">
         <v>1.12</v>
       </c>
       <c r="S4" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T4" t="n">
         <v>1.01</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.84</v>
+        <v>2.12</v>
       </c>
       <c r="O5" t="n">
         <v>1.27</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
@@ -1696,14 +1696,14 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1718,186 +1718,186 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>FK Auda</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ZED FC</t>
+          <t>SC Grobina</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="G7" t="n">
-        <v>1.97</v>
+        <v>1.61</v>
       </c>
       <c r="H7" t="n">
-        <v>5.2</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>5.8</v>
+        <v>970</v>
       </c>
       <c r="J7" t="n">
-        <v>3.2</v>
+        <v>1.09</v>
       </c>
       <c r="K7" t="n">
-        <v>3.45</v>
+        <v>950</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>2.54</v>
+        <v>1.3</v>
       </c>
       <c r="O7" t="n">
-        <v>1.55</v>
+        <v>1.22</v>
       </c>
       <c r="P7" t="n">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="Q7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W7" t="n">
         <v>2.62</v>
       </c>
-      <c r="R7" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W7" t="n">
-        <v>2.02</v>
-      </c>
       <c r="X7" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AR7" t="n">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="AS7" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AT7" t="n">
-        <v>5.6</v>
+        <v>1.03</v>
       </c>
       <c r="AU7" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AV7" t="n">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW7" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AX7" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AY7" t="n">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7" t="n">
-        <v>23</v>
+        <v>1.03</v>
       </c>
       <c r="BA7" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="BB7" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BC7" t="n">
-        <v>23</v>
+        <v>1.03</v>
       </c>
       <c r="BD7" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="BE7" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="BF7" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Turkish 1 Lig</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1912,31 +1912,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>National Bank</t>
+          <t>Corum Belediyespor</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ismaily</t>
+          <t>Keciorengucu</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="G8" t="n">
-        <v>1.92</v>
+        <v>1.81</v>
       </c>
       <c r="H8" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="I8" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="J8" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="K8" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
@@ -1945,79 +1945,79 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.58</v>
+        <v>2.14</v>
       </c>
       <c r="O8" t="n">
-        <v>1.46</v>
+        <v>1.24</v>
       </c>
       <c r="P8" t="n">
-        <v>1.58</v>
+        <v>2.14</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.36</v>
+        <v>1.65</v>
       </c>
       <c r="R8" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>1.66</v>
       </c>
       <c r="T8" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="U8" t="n">
         <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="W8" t="n">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="X8" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
         <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
         <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
         <v>1000</v>
@@ -2029,69 +2029,69 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.18</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AR8" t="n">
-        <v>2.52</v>
+        <v>1.03</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.62</v>
+        <v>1.03</v>
       </c>
       <c r="AT8" t="n">
-        <v>2.02</v>
+        <v>1.03</v>
       </c>
       <c r="AU8" t="n">
-        <v>2.12</v>
+        <v>1.03</v>
       </c>
       <c r="AV8" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW8" t="n">
-        <v>2.62</v>
+        <v>1.03</v>
       </c>
       <c r="AX8" t="n">
-        <v>2.18</v>
+        <v>1.03</v>
       </c>
       <c r="AY8" t="n">
-        <v>2.22</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8" t="n">
-        <v>2.44</v>
+        <v>1.03</v>
       </c>
       <c r="BA8" t="n">
-        <v>2.62</v>
+        <v>1.03</v>
       </c>
       <c r="BB8" t="n">
-        <v>2.4</v>
+        <v>1.03</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.42</v>
+        <v>1.03</v>
       </c>
       <c r="BD8" t="n">
-        <v>2.52</v>
+        <v>1.03</v>
       </c>
       <c r="BE8" t="n">
-        <v>2.62</v>
+        <v>1.03</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.62</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.62</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2106,186 +2106,186 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FK Auda</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SC Grobina</t>
+          <t>ZED FC</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.4</v>
+        <v>1.81</v>
       </c>
       <c r="G9" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="I9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O9" t="n">
         <v>1.55</v>
       </c>
-      <c r="H9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="I9" t="n">
-        <v>870</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="K9" t="n">
-        <v>950</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.22</v>
-      </c>
       <c r="P9" t="n">
-        <v>1.26</v>
+        <v>1.53</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.22</v>
+        <v>2.62</v>
       </c>
       <c r="R9" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S9" t="n">
-        <v>1.22</v>
+        <v>5.5</v>
       </c>
       <c r="T9" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="V9" t="n">
-        <v>1.06</v>
+        <v>1.19</v>
       </c>
       <c r="W9" t="n">
-        <v>2.8</v>
+        <v>2.08</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.03</v>
+        <v>34</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.03</v>
+        <v>24</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.03</v>
+        <v>23</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Turkish 1 Lig</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2300,56 +2300,56 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Corum Belediyespor</t>
+          <t>National Bank</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Keciorengucu</t>
+          <t>Ismaily</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="G10" t="n">
-        <v>1.78</v>
+        <v>1.92</v>
       </c>
       <c r="H10" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="I10" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="J10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S10" t="n">
         <v>4</v>
       </c>
-      <c r="K10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.66</v>
-      </c>
       <c r="T10" t="n">
         <v>1.01</v>
       </c>
@@ -2357,55 +2357,55 @@
         <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="W10" t="n">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA10" t="n">
         <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AE10" t="n">
         <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AI10" t="n">
         <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM10" t="n">
         <v>1000</v>
@@ -2417,62 +2417,62 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.03</v>
+        <v>2.18</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.03</v>
+        <v>2.52</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.03</v>
+        <v>2.62</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.03</v>
+        <v>2.02</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.03</v>
+        <v>2.12</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.03</v>
+        <v>2.62</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.03</v>
+        <v>2.18</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.03</v>
+        <v>2.22</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.03</v>
+        <v>2.44</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.03</v>
+        <v>2.62</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.03</v>
+        <v>2.4</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.03</v>
+        <v>2.42</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.03</v>
+        <v>2.52</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.03</v>
+        <v>2.62</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
@@ -2521,13 +2521,13 @@
         <v>6.8</v>
       </c>
       <c r="L11" t="n">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="M11" t="n">
         <v>1.02</v>
       </c>
       <c r="N11" t="n">
-        <v>3.05</v>
+        <v>7</v>
       </c>
       <c r="O11" t="n">
         <v>1.12</v>
@@ -2539,16 +2539,16 @@
         <v>1.39</v>
       </c>
       <c r="R11" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="S11" t="n">
-        <v>1.39</v>
+        <v>1.93</v>
       </c>
       <c r="T11" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="U11" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="V11" t="n">
         <v>3.35</v>
@@ -2557,116 +2557,116 @@
         <v>1.1</v>
       </c>
       <c r="X11" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="Y11" t="n">
-        <v>20</v>
+        <v>15.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>18</v>
+        <v>13.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AC11" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE11" t="n">
-        <v>19</v>
+        <v>14.5</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AG11" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI11" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.38</v>
+        <v>5.8</v>
       </c>
       <c r="AQ11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR11" t="n">
         <v>10</v>
       </c>
-      <c r="AR11" t="n">
-        <v>1.41</v>
-      </c>
       <c r="AS11" t="n">
-        <v>1.31</v>
+        <v>10.5</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.38</v>
+        <v>5.9</v>
       </c>
       <c r="AU11" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.41</v>
+        <v>9.6</v>
       </c>
       <c r="AW11" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.41</v>
+        <v>6.4</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.37</v>
+        <v>5.7</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.41</v>
+        <v>5.3</v>
       </c>
       <c r="BA11" t="n">
-        <v>18.5</v>
+        <v>5.5</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.41</v>
+        <v>6.6</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.41</v>
+        <v>6.4</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.41</v>
+        <v>6.2</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.41</v>
+        <v>6.4</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.41</v>
+        <v>6.4</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.41</v>
+        <v>3.05</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
@@ -2715,159 +2715,159 @@
         <v>950</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P12" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q12" t="n">
         <v>1.01</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CA Platense</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Penarol</t>
+          <t>Shakhtar</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="P13" t="n">
-        <v>1.24</v>
+        <v>2.12</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AO13" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BG13" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,184 +3071,960 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>LDU</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.61</v>
+        <v>1.94</v>
       </c>
       <c r="G14" t="n">
-        <v>1.63</v>
+        <v>1.96</v>
       </c>
       <c r="H14" t="n">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="I14" t="n">
-        <v>8</v>
+        <v>4.5</v>
       </c>
       <c r="J14" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K14" t="n">
         <v>3.95</v>
       </c>
-      <c r="K14" t="n">
-        <v>4.3</v>
-      </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="P14" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T14" t="n">
-        <v>2.14</v>
+        <v>1.82</v>
       </c>
       <c r="U14" t="n">
-        <v>1.75</v>
+        <v>2.12</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="X14" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="Z14" t="n">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="AA14" t="n">
-        <v>310</v>
+        <v>95</v>
       </c>
       <c r="AB14" t="n">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="AE14" t="n">
-        <v>160</v>
+        <v>60</v>
       </c>
       <c r="AF14" t="n">
-        <v>8.6</v>
+        <v>12</v>
       </c>
       <c r="AG14" t="n">
         <v>10.5</v>
       </c>
       <c r="AH14" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>29</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>14</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>13</v>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>2026-05-05 18:14:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>UEFA Europa League</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Nottm Forest</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I15" t="n">
+        <v>5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="X15" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>19</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>32</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>65</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>50</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>60</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>17</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>100</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>11</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>75</v>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>2026-05-05 18:14:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>UEFA Europa League</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="H16" t="n">
+        <v>5</v>
+      </c>
+      <c r="I16" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="X16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>90</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>32</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>60</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>42</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>36</v>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>2026-05-05 18:14:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>CA Platense</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Penarol</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>2026-05-05 18:14:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Mirassol</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>LDU</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="H18" t="n">
+        <v>7</v>
+      </c>
+      <c r="I18" t="n">
+        <v>8</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>310</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>160</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH18" t="n">
         <v>28</v>
       </c>
-      <c r="AI14" t="n">
+      <c r="AI18" t="n">
         <v>150</v>
       </c>
-      <c r="AJ14" t="n">
+      <c r="AJ18" t="n">
         <v>15</v>
       </c>
-      <c r="AK14" t="n">
+      <c r="AK18" t="n">
         <v>970</v>
       </c>
-      <c r="AL14" t="n">
+      <c r="AL18" t="n">
         <v>48</v>
       </c>
-      <c r="AM14" t="n">
+      <c r="AM18" t="n">
         <v>230</v>
       </c>
-      <c r="AN14" t="n">
+      <c r="AN18" t="n">
         <v>11.5</v>
       </c>
-      <c r="AO14" t="n">
+      <c r="AO18" t="n">
         <v>260</v>
       </c>
-      <c r="AP14" t="n">
+      <c r="AP18" t="n">
         <v>11</v>
       </c>
-      <c r="AQ14" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AR14" t="n">
+      <c r="AQ18" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR18" t="n">
         <v>9</v>
       </c>
-      <c r="AS14" t="n">
+      <c r="AS18" t="n">
         <v>10</v>
       </c>
-      <c r="AT14" t="n">
+      <c r="AT18" t="n">
         <v>6</v>
       </c>
-      <c r="AU14" t="n">
+      <c r="AU18" t="n">
         <v>8.4</v>
       </c>
-      <c r="AV14" t="n">
+      <c r="AV18" t="n">
         <v>7.6</v>
       </c>
-      <c r="AW14" t="n">
+      <c r="AW18" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AX14" t="n">
+      <c r="AX18" t="n">
         <v>7.4</v>
       </c>
-      <c r="AY14" t="n">
+      <c r="AY18" t="n">
         <v>9</v>
       </c>
-      <c r="AZ14" t="n">
+      <c r="AZ18" t="n">
         <v>7.6</v>
       </c>
-      <c r="BA14" t="n">
+      <c r="BA18" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="BB14" t="n">
+      <c r="BB18" t="n">
         <v>13</v>
       </c>
-      <c r="BC14" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BD14" t="n">
+      <c r="BC18" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD18" t="n">
         <v>8.6</v>
       </c>
-      <c r="BE14" t="n">
+      <c r="BE18" t="n">
         <v>10</v>
       </c>
-      <c r="BF14" t="n">
+      <c r="BF18" t="n">
         <v>10</v>
       </c>
-      <c r="BG14" t="n">
+      <c r="BG18" t="n">
         <v>10</v>
       </c>
-      <c r="BH14" t="inlineStr">
-        <is>
-          <t>2026-05-05 16:03:36</t>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-07.xlsx
@@ -760,16 +760,16 @@
         <v>2.48</v>
       </c>
       <c r="G2" t="n">
-        <v>3.1</v>
+        <v>600</v>
       </c>
       <c r="H2" t="n">
         <v>3.7</v>
       </c>
       <c r="I2" t="n">
-        <v>970</v>
+        <v>990</v>
       </c>
       <c r="J2" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="K2" t="n">
         <v>3.05</v>
@@ -781,13 +781,13 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.3</v>
+        <v>1.84</v>
       </c>
       <c r="O2" t="n">
-        <v>1.7</v>
+        <v>1.42</v>
       </c>
       <c r="P2" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="Q2" t="n">
         <v>3</v>
@@ -799,7 +799,7 @@
         <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U2" t="n">
         <v>1.58</v>
@@ -808,7 +808,7 @@
         <v>1.19</v>
       </c>
       <c r="W2" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="X2" t="n">
         <v>7.2</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -954,16 +954,16 @@
         <v>1.04</v>
       </c>
       <c r="G3" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="H3" t="n">
         <v>1.04</v>
       </c>
       <c r="I3" t="n">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="J3" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K3" t="n">
         <v>950</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -1148,16 +1148,16 @@
         <v>1.04</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="H4" t="n">
         <v>1.04</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="J4" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K4" t="n">
         <v>950</v>
@@ -1178,13 +1178,13 @@
         <v>1.24</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="R4" t="n">
         <v>1.12</v>
       </c>
       <c r="S4" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="T4" t="n">
         <v>1.01</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -1342,16 +1342,16 @@
         <v>1.04</v>
       </c>
       <c r="G5" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="H5" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="I5" t="n">
         <v>870</v>
       </c>
       <c r="J5" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="K5" t="n">
         <v>950</v>
@@ -1378,7 +1378,7 @@
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1390,7 +1390,7 @@
         <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -1557,28 +1557,28 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="O6" t="n">
         <v>1.3</v>
       </c>
       <c r="P6" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="R6" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V6" t="n">
         <v>1.22</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -1733,13 +1733,13 @@
         <v>1.61</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>1.04</v>
       </c>
       <c r="I7" t="n">
-        <v>970</v>
+        <v>990</v>
       </c>
       <c r="J7" t="n">
-        <v>1.09</v>
+        <v>2.64</v>
       </c>
       <c r="K7" t="n">
         <v>950</v>
@@ -1751,13 +1751,13 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="O7" t="n">
         <v>1.22</v>
       </c>
       <c r="P7" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="Q7" t="n">
         <v>1.22</v>
@@ -1766,16 +1766,16 @@
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
         <v>2.62</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -1957,16 +1957,16 @@
         <v>1.65</v>
       </c>
       <c r="R8" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="S8" t="n">
-        <v>1.66</v>
+        <v>2.48</v>
       </c>
       <c r="T8" t="n">
         <v>1.64</v>
       </c>
       <c r="U8" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="V8" t="n">
         <v>1.17</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="G9" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="H9" t="n">
         <v>5.6</v>
@@ -2127,7 +2127,7 @@
         <v>6.4</v>
       </c>
       <c r="J9" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K9" t="n">
         <v>3.55</v>
@@ -2166,7 +2166,7 @@
         <v>1.19</v>
       </c>
       <c r="W9" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="X9" t="n">
         <v>8.800000000000001</v>
@@ -2229,7 +2229,7 @@
         <v>12.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AS9" t="n">
         <v>12</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="G10" t="n">
         <v>1.92</v>
@@ -2324,7 +2324,7 @@
         <v>3.3</v>
       </c>
       <c r="K10" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2333,16 +2333,16 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.58</v>
+        <v>2.14</v>
       </c>
       <c r="O10" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="P10" t="n">
         <v>1.58</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="R10" t="n">
         <v>1.16</v>
@@ -2351,10 +2351,10 @@
         <v>4</v>
       </c>
       <c r="T10" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U10" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V10" t="n">
         <v>1.15</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -2545,7 +2545,7 @@
         <v>1.93</v>
       </c>
       <c r="T11" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U11" t="n">
         <v>2.18</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -2700,13 +2700,13 @@
         <v>1.04</v>
       </c>
       <c r="G12" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="H12" t="n">
         <v>1.04</v>
       </c>
       <c r="I12" t="n">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="J12" t="n">
         <v>1.01</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
         <v>1.6</v>
       </c>
       <c r="G13" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="H13" t="n">
         <v>6</v>
@@ -2906,7 +2906,7 @@
         <v>4.4</v>
       </c>
       <c r="K13" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
@@ -2924,7 +2924,7 @@
         <v>2.12</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="R13" t="n">
         <v>1.43</v>
@@ -2933,7 +2933,7 @@
         <v>3.1</v>
       </c>
       <c r="T13" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="U13" t="n">
         <v>1.99</v>
@@ -2942,7 +2942,7 @@
         <v>1.17</v>
       </c>
       <c r="W13" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="X13" t="n">
         <v>17</v>
@@ -2960,7 +2960,7 @@
         <v>9</v>
       </c>
       <c r="AC13" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AD13" t="n">
         <v>24</v>
@@ -2969,16 +2969,16 @@
         <v>95</v>
       </c>
       <c r="AF13" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AG13" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AH13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI13" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AJ13" t="n">
         <v>15</v>
@@ -2987,7 +2987,7 @@
         <v>16.5</v>
       </c>
       <c r="AL13" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="AM13" t="n">
         <v>150</v>
@@ -2996,19 +2996,19 @@
         <v>8.4</v>
       </c>
       <c r="AO13" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AP13" t="n">
         <v>15.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AR13" t="n">
-        <v>44</v>
+        <v>16.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AT13" t="n">
         <v>8.199999999999999</v>
@@ -3017,10 +3017,10 @@
         <v>9</v>
       </c>
       <c r="AV13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW13" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AX13" t="n">
         <v>8.6</v>
@@ -3032,7 +3032,7 @@
         <v>20</v>
       </c>
       <c r="BA13" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BB13" t="n">
         <v>13</v>
@@ -3044,7 +3044,7 @@
         <v>30</v>
       </c>
       <c r="BE13" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="BF13" t="n">
         <v>7.8</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -3133,7 +3133,7 @@
         <v>2.12</v>
       </c>
       <c r="V14" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W14" t="n">
         <v>2.04</v>
@@ -3148,7 +3148,7 @@
         <v>34</v>
       </c>
       <c r="AA14" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AB14" t="n">
         <v>9.6</v>
@@ -3157,10 +3157,10 @@
         <v>8.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF14" t="n">
         <v>12</v>
@@ -3178,7 +3178,7 @@
         <v>22</v>
       </c>
       <c r="AK14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL14" t="n">
         <v>36</v>
@@ -3202,7 +3202,7 @@
         <v>29</v>
       </c>
       <c r="AS14" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AT14" t="n">
         <v>8.800000000000001</v>
@@ -3214,19 +3214,19 @@
         <v>15.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AX14" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY14" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ14" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BB14" t="n">
         <v>19.5</v>
@@ -3238,17 +3238,17 @@
         <v>30</v>
       </c>
       <c r="BE14" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BF14" t="n">
         <v>11.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -3297,31 +3297,31 @@
         <v>4.1</v>
       </c>
       <c r="L15" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M15" t="n">
         <v>1.07</v>
       </c>
       <c r="N15" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="O15" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P15" t="n">
         <v>1.96</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="R15" t="n">
         <v>1.36</v>
       </c>
       <c r="S15" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T15" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="U15" t="n">
         <v>2</v>
@@ -3345,10 +3345,10 @@
         <v>120</v>
       </c>
       <c r="AB15" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC15" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD15" t="n">
         <v>19.5</v>
@@ -3363,7 +3363,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AH15" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AI15" t="n">
         <v>75</v>
@@ -3399,10 +3399,10 @@
         <v>65</v>
       </c>
       <c r="AT15" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU15" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV15" t="n">
         <v>18</v>
@@ -3411,7 +3411,7 @@
         <v>50</v>
       </c>
       <c r="AX15" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY15" t="n">
         <v>9.4</v>
@@ -3420,10 +3420,10 @@
         <v>19</v>
       </c>
       <c r="BA15" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BB15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BC15" t="n">
         <v>17.5</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -3473,16 +3473,16 @@
         </is>
       </c>
       <c r="F16" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="G16" t="n">
         <v>1.85</v>
       </c>
-      <c r="G16" t="n">
-        <v>1.87</v>
-      </c>
       <c r="H16" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I16" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J16" t="n">
         <v>3.8</v>
@@ -3491,19 +3491,19 @@
         <v>3.85</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M16" t="n">
         <v>1.08</v>
       </c>
       <c r="N16" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="O16" t="n">
         <v>1.36</v>
       </c>
       <c r="P16" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q16" t="n">
         <v>2.08</v>
@@ -3515,25 +3515,25 @@
         <v>3.85</v>
       </c>
       <c r="T16" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="U16" t="n">
         <v>1.95</v>
       </c>
       <c r="V16" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W16" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X16" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Y16" t="n">
         <v>16</v>
       </c>
       <c r="Z16" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AA16" t="n">
         <v>130</v>
@@ -3554,16 +3554,16 @@
         <v>10.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH16" t="n">
         <v>22</v>
       </c>
       <c r="AI16" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ16" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AK16" t="n">
         <v>20</v>
@@ -3575,7 +3575,7 @@
         <v>130</v>
       </c>
       <c r="AN16" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AO16" t="n">
         <v>90</v>
@@ -3584,7 +3584,7 @@
         <v>12</v>
       </c>
       <c r="AQ16" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AR16" t="n">
         <v>32</v>
@@ -3599,7 +3599,7 @@
         <v>7.6</v>
       </c>
       <c r="AV16" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AW16" t="n">
         <v>60</v>
@@ -3611,13 +3611,13 @@
         <v>9.6</v>
       </c>
       <c r="AZ16" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA16" t="n">
         <v>36</v>
       </c>
       <c r="BB16" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BC16" t="n">
         <v>18.5</v>
@@ -3629,14 +3629,14 @@
         <v>42</v>
       </c>
       <c r="BF16" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BG16" t="n">
         <v>36</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -3667,170 +3667,170 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="P17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V17" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="BG17" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="G18" t="n">
         <v>1.63</v>
@@ -3876,19 +3876,19 @@
         <v>3.95</v>
       </c>
       <c r="K18" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M18" t="n">
         <v>1.08</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="P18" t="n">
         <v>1.78</v>
@@ -3897,10 +3897,10 @@
         <v>2.1</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="T18" t="n">
         <v>2.14</v>
@@ -3909,34 +3909,34 @@
         <v>1.75</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="X18" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="Z18" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA18" t="n">
-        <v>310</v>
+        <v>290</v>
       </c>
       <c r="AB18" t="n">
         <v>7.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD18" t="n">
         <v>29</v>
       </c>
       <c r="AE18" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AF18" t="n">
         <v>8.6</v>
@@ -3948,61 +3948,61 @@
         <v>28</v>
       </c>
       <c r="AI18" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AJ18" t="n">
         <v>15</v>
       </c>
       <c r="AK18" t="n">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="AL18" t="n">
         <v>48</v>
       </c>
       <c r="AM18" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AN18" t="n">
         <v>11.5</v>
       </c>
       <c r="AO18" t="n">
-        <v>260</v>
+        <v>220</v>
       </c>
       <c r="AP18" t="n">
         <v>11</v>
       </c>
       <c r="AQ18" t="n">
-        <v>7.4</v>
+        <v>17</v>
       </c>
       <c r="AR18" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AT18" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU18" t="n">
         <v>8.4</v>
       </c>
       <c r="AV18" t="n">
+        <v>24</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AX18" t="n">
         <v>7.6</v>
       </c>
-      <c r="AW18" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>7.4</v>
-      </c>
       <c r="AY18" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ18" t="n">
-        <v>7.6</v>
+        <v>24</v>
       </c>
       <c r="BA18" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BB18" t="n">
         <v>13</v>
@@ -4011,20 +4011,20 @@
         <v>16.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>8.6</v>
+        <v>34</v>
       </c>
       <c r="BE18" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BF18" t="n">
         <v>10</v>
       </c>
       <c r="BG18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-07.xlsx
@@ -760,16 +760,16 @@
         <v>2.48</v>
       </c>
       <c r="G2" t="n">
-        <v>600</v>
+        <v>3.1</v>
       </c>
       <c r="H2" t="n">
         <v>3.7</v>
       </c>
       <c r="I2" t="n">
-        <v>990</v>
+        <v>5.3</v>
       </c>
       <c r="J2" t="n">
-        <v>1.85</v>
+        <v>2.36</v>
       </c>
       <c r="K2" t="n">
         <v>3.05</v>
@@ -787,7 +787,7 @@
         <v>1.42</v>
       </c>
       <c r="P2" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q2" t="n">
         <v>3</v>
@@ -802,13 +802,13 @@
         <v>1.11</v>
       </c>
       <c r="U2" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="V2" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="W2" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="X2" t="n">
         <v>7.2</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -954,13 +954,13 @@
         <v>1.04</v>
       </c>
       <c r="G3" t="n">
-        <v>600</v>
+        <v>990</v>
       </c>
       <c r="H3" t="n">
         <v>1.04</v>
       </c>
       <c r="I3" t="n">
-        <v>870</v>
+        <v>1000</v>
       </c>
       <c r="J3" t="n">
         <v>1.04</v>
@@ -990,13 +990,13 @@
         <v>1.12</v>
       </c>
       <c r="S3" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="T3" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U3" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V3" t="n">
         <v>1.01</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -1148,13 +1148,13 @@
         <v>1.04</v>
       </c>
       <c r="G4" t="n">
-        <v>600</v>
+        <v>990</v>
       </c>
       <c r="H4" t="n">
         <v>1.04</v>
       </c>
       <c r="I4" t="n">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J4" t="n">
         <v>1.04</v>
@@ -1184,13 +1184,13 @@
         <v>1.12</v>
       </c>
       <c r="S4" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V4" t="n">
         <v>1.01</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
         <v>2.1</v>
       </c>
       <c r="I5" t="n">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J5" t="n">
         <v>2.1</v>
@@ -1366,25 +1366,25 @@
         <v>2.12</v>
       </c>
       <c r="O5" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="P5" t="n">
         <v>1.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V5" t="n">
         <v>1.01</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.96</v>
+        <v>2.72</v>
       </c>
       <c r="O6" t="n">
         <v>1.3</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -1739,10 +1739,10 @@
         <v>990</v>
       </c>
       <c r="J7" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="K7" t="n">
-        <v>950</v>
+        <v>80</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -1754,19 +1754,19 @@
         <v>1.25</v>
       </c>
       <c r="O7" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P7" t="n">
         <v>1.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="R7" t="n">
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T7" t="n">
         <v>1.11</v>
@@ -1781,116 +1781,116 @@
         <v>2.62</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>710</v>
       </c>
       <c r="AA7" t="n">
         <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AE7" t="n">
         <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>390</v>
       </c>
       <c r="AI7" t="n">
         <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>710</v>
       </c>
       <c r="AM7" t="n">
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO7" t="n">
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.03</v>
+        <v>1.28</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.03</v>
+        <v>2.86</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.03</v>
+        <v>1.28</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.03</v>
+        <v>1.28</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.03</v>
+        <v>1.28</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -1945,7 +1945,7 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="O8" t="n">
         <v>1.24</v>
@@ -1963,10 +1963,10 @@
         <v>2.48</v>
       </c>
       <c r="T8" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="U8" t="n">
-        <v>1.87</v>
+        <v>1.11</v>
       </c>
       <c r="V8" t="n">
         <v>1.17</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="G9" t="n">
         <v>1.89</v>
@@ -2241,7 +2241,7 @@
         <v>7</v>
       </c>
       <c r="AV9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW9" t="n">
         <v>11.5</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -2548,7 +2548,7 @@
         <v>1.68</v>
       </c>
       <c r="U11" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V11" t="n">
         <v>3.35</v>
@@ -2560,7 +2560,7 @@
         <v>42</v>
       </c>
       <c r="Y11" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z11" t="n">
         <v>12.5</v>
@@ -2611,7 +2611,7 @@
         <v>4.6</v>
       </c>
       <c r="AP11" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AQ11" t="n">
         <v>12</v>
@@ -2623,7 +2623,7 @@
         <v>10.5</v>
       </c>
       <c r="AT11" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AU11" t="n">
         <v>12.5</v>
@@ -2638,7 +2638,7 @@
         <v>6.4</v>
       </c>
       <c r="AY11" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AZ11" t="n">
         <v>5.3</v>
@@ -2650,10 +2650,10 @@
         <v>6.6</v>
       </c>
       <c r="BC11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD11" t="n">
         <v>6.4</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>6.2</v>
       </c>
       <c r="BE11" t="n">
         <v>6.4</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -2709,7 +2709,7 @@
         <v>870</v>
       </c>
       <c r="J12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="K12" t="n">
         <v>950</v>
@@ -2721,13 +2721,13 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="O12" t="n">
         <v>1.33</v>
       </c>
       <c r="P12" t="n">
-        <v>1.25</v>
+        <v>1.81</v>
       </c>
       <c r="Q12" t="n">
         <v>1.01</v>
@@ -2736,13 +2736,13 @@
         <v>1.12</v>
       </c>
       <c r="S12" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="T12" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U12" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V12" t="n">
         <v>1.01</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -2966,7 +2966,7 @@
         <v>24</v>
       </c>
       <c r="AE13" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AF13" t="n">
         <v>9.6</v>
@@ -3002,13 +3002,13 @@
         <v>15.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>16.5</v>
+        <v>44</v>
       </c>
       <c r="AS13" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AT13" t="n">
         <v>8.199999999999999</v>
@@ -3017,10 +3017,10 @@
         <v>9</v>
       </c>
       <c r="AV13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW13" t="n">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="AX13" t="n">
         <v>8.6</v>
@@ -3050,11 +3050,11 @@
         <v>7.8</v>
       </c>
       <c r="BG13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3172,7 @@
         <v>18.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ14" t="n">
         <v>22</v>
@@ -3214,16 +3214,16 @@
         <v>15.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AX14" t="n">
         <v>11</v>
       </c>
       <c r="AY14" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ14" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA14" t="n">
         <v>15.5</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -3279,10 +3279,10 @@
         </is>
       </c>
       <c r="F15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G15" t="n">
         <v>1.81</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1.82</v>
       </c>
       <c r="H15" t="n">
         <v>4.9</v>
@@ -3324,16 +3324,16 @@
         <v>1.92</v>
       </c>
       <c r="U15" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V15" t="n">
         <v>1.25</v>
       </c>
       <c r="W15" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="X15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Y15" t="n">
         <v>17</v>
@@ -3369,7 +3369,7 @@
         <v>75</v>
       </c>
       <c r="AJ15" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AK15" t="n">
         <v>19</v>
@@ -3387,7 +3387,7 @@
         <v>85</v>
       </c>
       <c r="AP15" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ15" t="n">
         <v>16</v>
@@ -3411,7 +3411,7 @@
         <v>50</v>
       </c>
       <c r="AX15" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AY15" t="n">
         <v>9.4</v>
@@ -3420,10 +3420,10 @@
         <v>19</v>
       </c>
       <c r="BA15" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BB15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC15" t="n">
         <v>17.5</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -3476,10 +3476,10 @@
         <v>1.84</v>
       </c>
       <c r="G16" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="H16" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="I16" t="n">
         <v>5.2</v>
@@ -3563,7 +3563,7 @@
         <v>75</v>
       </c>
       <c r="AJ16" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AK16" t="n">
         <v>20</v>
@@ -3596,10 +3596,10 @@
         <v>7.6</v>
       </c>
       <c r="AU16" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV16" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AW16" t="n">
         <v>60</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -3691,16 +3691,16 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="O17" t="n">
         <v>1.51</v>
       </c>
       <c r="P17" t="n">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.51</v>
+        <v>2.12</v>
       </c>
       <c r="R17" t="n">
         <v>1.18</v>
@@ -3709,10 +3709,10 @@
         <v>4.7</v>
       </c>
       <c r="T17" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U17" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V17" t="n">
         <v>1.24</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -3885,10 +3885,10 @@
         <v>1.08</v>
       </c>
       <c r="N18" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O18" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="P18" t="n">
         <v>1.78</v>
@@ -3897,10 +3897,10 @@
         <v>2.1</v>
       </c>
       <c r="R18" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="S18" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="T18" t="n">
         <v>2.14</v>
@@ -3927,7 +3927,7 @@
         <v>290</v>
       </c>
       <c r="AB18" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AC18" t="n">
         <v>9.4</v>
@@ -3975,10 +3975,10 @@
         <v>17</v>
       </c>
       <c r="AR18" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AS18" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AT18" t="n">
         <v>6.2</v>
@@ -3990,7 +3990,7 @@
         <v>24</v>
       </c>
       <c r="AW18" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AX18" t="n">
         <v>7.6</v>
@@ -4002,7 +4002,7 @@
         <v>24</v>
       </c>
       <c r="BA18" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BB18" t="n">
         <v>13</v>
@@ -4014,17 +4014,17 @@
         <v>34</v>
       </c>
       <c r="BE18" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BF18" t="n">
         <v>10</v>
       </c>
       <c r="BG18" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH18"/>
+  <dimension ref="A1:BH21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.48</v>
+        <v>2.32</v>
       </c>
       <c r="G2" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H2" t="n">
         <v>3.7</v>
       </c>
       <c r="I2" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="J2" t="n">
-        <v>2.36</v>
+        <v>2.16</v>
       </c>
       <c r="K2" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="L2" t="n">
         <v>1.68</v>
@@ -784,10 +784,10 @@
         <v>1.84</v>
       </c>
       <c r="O2" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="P2" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Q2" t="n">
         <v>3</v>
@@ -802,10 +802,10 @@
         <v>1.11</v>
       </c>
       <c r="U2" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="V2" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="W2" t="n">
         <v>1.48</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -978,13 +978,13 @@
         <v>1.25</v>
       </c>
       <c r="O3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P3" t="n">
         <v>1.24</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R3" t="n">
         <v>1.12</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
         <v>1.12</v>
       </c>
       <c r="S4" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T4" t="n">
         <v>1.11</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -1366,19 +1366,19 @@
         <v>2.12</v>
       </c>
       <c r="O5" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="P5" t="n">
         <v>1.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.28</v>
+        <v>1.05</v>
       </c>
       <c r="T5" t="n">
         <v>1.11</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -1696,14 +1696,14 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1718,186 +1718,186 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FK Auda</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SC Grobina</t>
+          <t>ZED FC</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.4</v>
+        <v>1.82</v>
       </c>
       <c r="G7" t="n">
-        <v>1.61</v>
+        <v>1.89</v>
       </c>
       <c r="H7" t="n">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="I7" t="n">
-        <v>990</v>
+        <v>6.4</v>
       </c>
       <c r="J7" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="K7" t="n">
-        <v>80</v>
+        <v>3.55</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N7" t="n">
-        <v>1.25</v>
+        <v>2.58</v>
       </c>
       <c r="O7" t="n">
-        <v>1.23</v>
+        <v>1.55</v>
       </c>
       <c r="P7" t="n">
-        <v>1.24</v>
+        <v>1.53</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.23</v>
+        <v>2.62</v>
       </c>
       <c r="R7" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S7" t="n">
-        <v>1.22</v>
+        <v>5.5</v>
       </c>
       <c r="T7" t="n">
-        <v>1.11</v>
+        <v>2.26</v>
       </c>
       <c r="U7" t="n">
-        <v>1.11</v>
+        <v>1.69</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="W7" t="n">
-        <v>2.62</v>
+        <v>2.12</v>
       </c>
       <c r="X7" t="n">
-        <v>85</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y7" t="n">
-        <v>110</v>
+        <v>16.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>710</v>
+        <v>44</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AB7" t="n">
-        <v>38</v>
+        <v>6.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="AD7" t="n">
-        <v>380</v>
+        <v>25</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF7" t="n">
-        <v>30</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG7" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="AH7" t="n">
-        <v>390</v>
+        <v>28</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AJ7" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>300</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>210</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR7" t="n">
         <v>36</v>
       </c>
-      <c r="AK7" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>710</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>60</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AS7" t="n">
-        <v>1.28</v>
+        <v>12</v>
       </c>
       <c r="AT7" t="n">
-        <v>2.86</v>
+        <v>5.6</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AV7" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.28</v>
+        <v>11.5</v>
       </c>
       <c r="AX7" t="n">
-        <v>3.75</v>
+        <v>8.6</v>
       </c>
       <c r="AY7" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ7" t="n">
+        <v>24</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BE7" t="n">
         <v>12</v>
       </c>
-      <c r="BA7" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.28</v>
-      </c>
       <c r="BF7" t="n">
-        <v>2.1</v>
+        <v>20</v>
       </c>
       <c r="BG7" t="n">
-        <v>8.4</v>
+        <v>12</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Turkish 1 Lig</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1912,186 +1912,186 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Corum Belediyespor</t>
+          <t>National Bank</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Keciorengucu</t>
+          <t>Ismaily</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.66</v>
+        <v>1.96</v>
       </c>
       <c r="G8" t="n">
-        <v>1.81</v>
+        <v>2.18</v>
       </c>
       <c r="H8" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="I8" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="J8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>4.6</v>
+        <v>3.55</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="M8" t="n">
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="O8" t="n">
-        <v>1.24</v>
+        <v>1.47</v>
       </c>
       <c r="P8" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="X8" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AU8" t="n">
         <v>2.14</v>
       </c>
-      <c r="Q8" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AV8" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.03</v>
+        <v>2.74</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.03</v>
+        <v>2.32</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.03</v>
+        <v>2.32</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.03</v>
+        <v>2.52</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.03</v>
+        <v>2.74</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.03</v>
+        <v>2.54</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.03</v>
+        <v>2.64</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.03</v>
+        <v>2.74</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2106,186 +2106,186 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>FK Auda</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ZED FC</t>
+          <t>SC Grobina</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.81</v>
+        <v>1.4</v>
       </c>
       <c r="G9" t="n">
-        <v>1.89</v>
+        <v>1.61</v>
       </c>
       <c r="H9" t="n">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="I9" t="n">
-        <v>6.4</v>
+        <v>990</v>
       </c>
       <c r="J9" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="K9" t="n">
-        <v>3.55</v>
+        <v>80</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>2.58</v>
+        <v>1.24</v>
       </c>
       <c r="O9" t="n">
-        <v>1.55</v>
+        <v>1.23</v>
       </c>
       <c r="P9" t="n">
-        <v>1.53</v>
+        <v>1.24</v>
       </c>
       <c r="Q9" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W9" t="n">
         <v>2.62</v>
       </c>
-      <c r="R9" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="W9" t="n">
-        <v>2.12</v>
-      </c>
       <c r="X9" t="n">
-        <v>8.800000000000001</v>
+        <v>85</v>
       </c>
       <c r="Y9" t="n">
-        <v>16.5</v>
+        <v>110</v>
       </c>
       <c r="Z9" t="n">
-        <v>44</v>
+        <v>710</v>
       </c>
       <c r="AA9" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>6.2</v>
+        <v>38</v>
       </c>
       <c r="AC9" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="AD9" t="n">
-        <v>25</v>
+        <v>380</v>
       </c>
       <c r="AE9" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>9.800000000000001</v>
+        <v>30</v>
       </c>
       <c r="AG9" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="AH9" t="n">
-        <v>28</v>
+        <v>390</v>
       </c>
       <c r="AI9" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="AK9" t="n">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="AL9" t="n">
+        <v>710</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN9" t="n">
         <v>60</v>
       </c>
-      <c r="AM9" t="n">
-        <v>300</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>23</v>
-      </c>
       <c r="AO9" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>7.6</v>
+        <v>4.6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>12.5</v>
+        <v>8.4</v>
       </c>
       <c r="AR9" t="n">
-        <v>36</v>
+        <v>1.27</v>
       </c>
       <c r="AS9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ9" t="n">
         <v>12</v>
       </c>
-      <c r="AT9" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>22</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>24</v>
-      </c>
       <c r="BA9" t="n">
-        <v>11.5</v>
+        <v>1.28</v>
       </c>
       <c r="BB9" t="n">
-        <v>19.5</v>
+        <v>7.4</v>
       </c>
       <c r="BC9" t="n">
-        <v>23</v>
+        <v>9.6</v>
       </c>
       <c r="BD9" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>12</v>
+        <v>1.28</v>
       </c>
       <c r="BF9" t="n">
-        <v>20</v>
+        <v>2.18</v>
       </c>
       <c r="BG9" t="n">
-        <v>12</v>
+        <v>8.4</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Turkish 1 Lig</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2300,31 +2300,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>National Bank</t>
+          <t>Corum Belediyespor</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ismaily</t>
+          <t>Keciorengucu</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="G10" t="n">
-        <v>1.92</v>
+        <v>1.81</v>
       </c>
       <c r="H10" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="I10" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="J10" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2333,79 +2333,79 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P10" t="n">
         <v>2.14</v>
       </c>
-      <c r="O10" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.58</v>
-      </c>
       <c r="Q10" t="n">
-        <v>2.36</v>
+        <v>1.65</v>
       </c>
       <c r="R10" t="n">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>2.48</v>
       </c>
       <c r="T10" t="n">
-        <v>1.11</v>
+        <v>1.7</v>
       </c>
       <c r="U10" t="n">
         <v>1.11</v>
       </c>
       <c r="V10" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="W10" t="n">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="X10" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
         <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD10" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AE10" t="n">
         <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AG10" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AI10" t="n">
         <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL10" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM10" t="n">
         <v>1000</v>
@@ -2417,62 +2417,62 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.18</v>
+        <v>1.03</v>
       </c>
       <c r="AQ10" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AR10" t="n">
-        <v>2.52</v>
+        <v>1.03</v>
       </c>
       <c r="AS10" t="n">
-        <v>2.62</v>
+        <v>1.03</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.02</v>
+        <v>1.03</v>
       </c>
       <c r="AU10" t="n">
-        <v>2.12</v>
+        <v>1.03</v>
       </c>
       <c r="AV10" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW10" t="n">
-        <v>2.62</v>
+        <v>1.03</v>
       </c>
       <c r="AX10" t="n">
-        <v>2.18</v>
+        <v>1.03</v>
       </c>
       <c r="AY10" t="n">
-        <v>2.22</v>
+        <v>1.03</v>
       </c>
       <c r="AZ10" t="n">
-        <v>2.44</v>
+        <v>1.03</v>
       </c>
       <c r="BA10" t="n">
-        <v>2.62</v>
+        <v>1.03</v>
       </c>
       <c r="BB10" t="n">
-        <v>2.4</v>
+        <v>1.03</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.42</v>
+        <v>1.03</v>
       </c>
       <c r="BD10" t="n">
-        <v>2.52</v>
+        <v>1.03</v>
       </c>
       <c r="BE10" t="n">
-        <v>2.62</v>
+        <v>1.03</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.62</v>
+        <v>1.01</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.62</v>
+        <v>1.01</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
         <v>6.8</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="M11" t="n">
         <v>1.02</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
         <v>1.94</v>
       </c>
       <c r="U13" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V13" t="n">
         <v>1.17</v>
@@ -3002,10 +3002,10 @@
         <v>15.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AR13" t="n">
-        <v>44</v>
+        <v>16.5</v>
       </c>
       <c r="AS13" t="n">
         <v>19</v>
@@ -3017,10 +3017,10 @@
         <v>9</v>
       </c>
       <c r="AV13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW13" t="n">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="AX13" t="n">
         <v>8.6</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -3279,16 +3279,16 @@
         </is>
       </c>
       <c r="F15" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="G15" t="n">
         <v>1.8</v>
       </c>
-      <c r="G15" t="n">
-        <v>1.81</v>
-      </c>
       <c r="H15" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I15" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J15" t="n">
         <v>4</v>
@@ -3315,7 +3315,7 @@
         <v>1.98</v>
       </c>
       <c r="R15" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S15" t="n">
         <v>3.6</v>
@@ -3324,13 +3324,13 @@
         <v>1.92</v>
       </c>
       <c r="U15" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V15" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W15" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="X15" t="n">
         <v>15</v>
@@ -3342,7 +3342,7 @@
         <v>38</v>
       </c>
       <c r="AA15" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AB15" t="n">
         <v>8.6</v>
@@ -3393,7 +3393,7 @@
         <v>16</v>
       </c>
       <c r="AR15" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AS15" t="n">
         <v>65</v>
@@ -3429,7 +3429,7 @@
         <v>17.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE15" t="n">
         <v>100</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
         <v>3.8</v>
       </c>
       <c r="K16" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L16" t="n">
         <v>1.44</v>
@@ -3518,7 +3518,7 @@
         <v>1.97</v>
       </c>
       <c r="U16" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V16" t="n">
         <v>1.23</v>
@@ -3608,7 +3608,7 @@
         <v>9.4</v>
       </c>
       <c r="AY16" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ16" t="n">
         <v>19.5</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -3667,19 +3667,19 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="G17" t="n">
-        <v>2.64</v>
+        <v>2.52</v>
       </c>
       <c r="H17" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="I17" t="n">
         <v>5.1</v>
       </c>
       <c r="J17" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="K17" t="n">
         <v>3.75</v>
@@ -3691,7 +3691,7 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="O17" t="n">
         <v>1.51</v>
@@ -3700,7 +3700,7 @@
         <v>1.43</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R17" t="n">
         <v>1.18</v>
@@ -3715,10 +3715,10 @@
         <v>1.11</v>
       </c>
       <c r="V17" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="W17" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="X17" t="n">
         <v>10.5</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -3867,16 +3867,16 @@
         <v>1.63</v>
       </c>
       <c r="H18" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="I18" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J18" t="n">
         <v>3.95</v>
       </c>
       <c r="K18" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
@@ -3924,7 +3924,7 @@
         <v>60</v>
       </c>
       <c r="AA18" t="n">
-        <v>290</v>
+        <v>260</v>
       </c>
       <c r="AB18" t="n">
         <v>7.2</v>
@@ -3936,7 +3936,7 @@
         <v>29</v>
       </c>
       <c r="AE18" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AF18" t="n">
         <v>8.6</v>
@@ -3954,7 +3954,7 @@
         <v>15</v>
       </c>
       <c r="AK18" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL18" t="n">
         <v>48</v>
@@ -3972,10 +3972,10 @@
         <v>11</v>
       </c>
       <c r="AQ18" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="AS18" t="n">
         <v>13.5</v>
@@ -3990,7 +3990,7 @@
         <v>24</v>
       </c>
       <c r="AW18" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AX18" t="n">
         <v>7.6</v>
@@ -3999,10 +3999,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ18" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="BA18" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BB18" t="n">
         <v>13</v>
@@ -4011,20 +4011,602 @@
         <v>16.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BE18" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BF18" t="n">
         <v>10</v>
       </c>
       <c r="BG18" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Coquimbo Unido</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Universitario de Deportes</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="X19" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>2026-05-06 00:47:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Ind Medellin</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G20" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>36</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>140</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>85</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>100</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>120</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>21</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>2026-05-06 00:47:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>23:00:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Junior FC Barranquilla</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Cerro Porteno</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K21" t="n">
+        <v>950</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-07.xlsx
@@ -757,19 +757,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G2" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="H2" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="J2" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="K2" t="n">
         <v>3.35</v>
@@ -781,13 +781,13 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="O2" t="n">
         <v>1.47</v>
       </c>
       <c r="P2" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Q2" t="n">
         <v>3</v>
@@ -796,19 +796,19 @@
         <v>1.12</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T2" t="n">
         <v>1.11</v>
       </c>
       <c r="U2" t="n">
-        <v>1.61</v>
+        <v>1.11</v>
       </c>
       <c r="V2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W2" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="X2" t="n">
         <v>7.2</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-06 00:47:57</t>
+          <t>2026-05-06 02:59:05</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-06 00:47:57</t>
+          <t>2026-05-06 02:59:05</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-06 00:47:57</t>
+          <t>2026-05-06 02:59:05</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-06 00:47:57</t>
+          <t>2026-05-06 02:59:05</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
         <v>1.78</v>
       </c>
       <c r="G6" t="n">
-        <v>1.96</v>
+        <v>1.84</v>
       </c>
       <c r="H6" t="n">
         <v>5</v>
@@ -1545,7 +1545,7 @@
         <v>5.5</v>
       </c>
       <c r="J6" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="K6" t="n">
         <v>4.2</v>
@@ -1557,16 +1557,16 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="O6" t="n">
         <v>1.3</v>
       </c>
       <c r="P6" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="R6" t="n">
         <v>1.27</v>
@@ -1584,7 +1584,7 @@
         <v>1.22</v>
       </c>
       <c r="W6" t="n">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-06 00:47:57</t>
+          <t>2026-05-06 02:59:05</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="G7" t="n">
         <v>1.89</v>
       </c>
       <c r="H7" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="I7" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="J7" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="K7" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -1751,16 +1751,16 @@
         <v>1.12</v>
       </c>
       <c r="N7" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="O7" t="n">
         <v>1.55</v>
       </c>
       <c r="P7" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="R7" t="n">
         <v>1.19</v>
@@ -1769,28 +1769,28 @@
         <v>5.5</v>
       </c>
       <c r="T7" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="U7" t="n">
         <v>1.69</v>
       </c>
       <c r="V7" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W7" t="n">
         <v>2.12</v>
       </c>
       <c r="X7" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y7" t="n">
         <v>16.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AA7" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AB7" t="n">
         <v>6.2</v>
@@ -1799,98 +1799,98 @@
         <v>8</v>
       </c>
       <c r="AD7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE7" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AF7" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AG7" t="n">
         <v>11</v>
       </c>
       <c r="AH7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI7" t="n">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="AJ7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL7" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AM7" t="n">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="AN7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO7" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AP7" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AQ7" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AR7" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AS7" t="n">
         <v>12</v>
       </c>
       <c r="AT7" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AU7" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW7" t="n">
         <v>11.5</v>
       </c>
       <c r="AX7" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AY7" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA7" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BB7" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="BC7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD7" t="n">
-        <v>10.5</v>
+        <v>50</v>
       </c>
       <c r="BE7" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BF7" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BG7" t="n">
         <v>12</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-06 00:47:57</t>
+          <t>2026-05-06 02:59:05</t>
         </is>
       </c>
     </row>
@@ -1921,170 +1921,170 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.96</v>
+        <v>2.32</v>
       </c>
       <c r="G8" t="n">
-        <v>2.18</v>
+        <v>2.56</v>
       </c>
       <c r="H8" t="n">
-        <v>4.8</v>
+        <v>3.65</v>
       </c>
       <c r="I8" t="n">
-        <v>5.9</v>
+        <v>4.2</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="K8" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="L8" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O8" t="n">
         <v>1.51</v>
       </c>
-      <c r="M8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.47</v>
-      </c>
       <c r="P8" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="R8" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="S8" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="T8" t="n">
         <v>1.11</v>
       </c>
       <c r="U8" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="W8" t="n">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="X8" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>18</v>
+        <v>13.5</v>
       </c>
       <c r="Z8" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ8" t="n">
         <v>50</v>
       </c>
-      <c r="AA8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC8" t="n">
+      <c r="AK8" t="n">
+        <v>48</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>90</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AX8" t="n">
         <v>10</v>
       </c>
-      <c r="AD8" t="n">
-        <v>29</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AS8" t="n">
+      <c r="AY8" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BC8" t="n">
         <v>2.74</v>
       </c>
-      <c r="AT8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>18</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>2.54</v>
-      </c>
       <c r="BD8" t="n">
-        <v>2.64</v>
+        <v>2.82</v>
       </c>
       <c r="BE8" t="n">
-        <v>2.74</v>
+        <v>2.92</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.74</v>
+        <v>2.92</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.74</v>
+        <v>2.92</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-06 00:47:57</t>
+          <t>2026-05-06 02:59:05</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
         <v>1.4</v>
       </c>
       <c r="G9" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="H9" t="n">
         <v>1.04</v>
@@ -2127,7 +2127,7 @@
         <v>990</v>
       </c>
       <c r="J9" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="K9" t="n">
         <v>80</v>
@@ -2205,7 +2205,7 @@
         <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK9" t="n">
         <v>65</v>
@@ -2217,25 +2217,25 @@
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AO9" t="n">
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AQ9" t="n">
         <v>8.4</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AS9" t="n">
         <v>1.28</v>
       </c>
       <c r="AT9" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="AU9" t="n">
         <v>6.6</v>
@@ -2247,7 +2247,7 @@
         <v>1.28</v>
       </c>
       <c r="AX9" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AY9" t="n">
         <v>10</v>
@@ -2271,14 +2271,14 @@
         <v>1.28</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="BG9" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-06 00:47:57</t>
+          <t>2026-05-06 02:59:05</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-06 00:47:57</t>
+          <t>2026-05-06 02:59:05</t>
         </is>
       </c>
     </row>
@@ -2503,13 +2503,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G11" t="n">
         <v>10.5</v>
       </c>
       <c r="H11" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="I11" t="n">
         <v>1.42</v>
@@ -2533,7 +2533,7 @@
         <v>1.12</v>
       </c>
       <c r="P11" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="Q11" t="n">
         <v>1.39</v>
@@ -2548,7 +2548,7 @@
         <v>1.68</v>
       </c>
       <c r="U11" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V11" t="n">
         <v>3.35</v>
@@ -2560,7 +2560,7 @@
         <v>42</v>
       </c>
       <c r="Y11" t="n">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="Z11" t="n">
         <v>12.5</v>
@@ -2584,34 +2584,34 @@
         <v>110</v>
       </c>
       <c r="AG11" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AH11" t="n">
         <v>24</v>
       </c>
       <c r="AI11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ11" t="n">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="AK11" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AL11" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AM11" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN11" t="n">
         <v>100</v>
       </c>
       <c r="AO11" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="AP11" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AQ11" t="n">
         <v>12</v>
@@ -2623,7 +2623,7 @@
         <v>10.5</v>
       </c>
       <c r="AT11" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AU11" t="n">
         <v>12.5</v>
@@ -2635,38 +2635,38 @@
         <v>11.5</v>
       </c>
       <c r="AX11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY11" t="n">
         <v>6.4</v>
       </c>
-      <c r="AY11" t="n">
-        <v>5.8</v>
-      </c>
       <c r="AZ11" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BA11" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BC11" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BD11" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BE11" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BF11" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BG11" t="n">
         <v>3.05</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-06 00:47:57</t>
+          <t>2026-05-06 02:59:05</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-06 00:47:57</t>
+          <t>2026-05-06 02:59:05</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="G13" t="n">
         <v>1.64</v>
@@ -2999,16 +2999,16 @@
         <v>100</v>
       </c>
       <c r="AP13" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ13" t="n">
         <v>20</v>
       </c>
       <c r="AR13" t="n">
-        <v>16.5</v>
+        <v>44</v>
       </c>
       <c r="AS13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AT13" t="n">
         <v>8.199999999999999</v>
@@ -3020,7 +3020,7 @@
         <v>21</v>
       </c>
       <c r="AW13" t="n">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="AX13" t="n">
         <v>8.6</v>
@@ -3050,11 +3050,11 @@
         <v>7.8</v>
       </c>
       <c r="BG13" t="n">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-06 00:47:57</t>
+          <t>2026-05-06 02:59:05</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="G14" t="n">
         <v>1.96</v>
@@ -3094,7 +3094,7 @@
         <v>4.2</v>
       </c>
       <c r="I14" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J14" t="n">
         <v>3.85</v>
@@ -3190,7 +3190,7 @@
         <v>13</v>
       </c>
       <c r="AO14" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP14" t="n">
         <v>13.5</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-06 00:47:57</t>
+          <t>2026-05-06 02:59:05</t>
         </is>
       </c>
     </row>
@@ -3279,10 +3279,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="G15" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="H15" t="n">
         <v>5</v>
@@ -3309,7 +3309,7 @@
         <v>1.33</v>
       </c>
       <c r="P15" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="Q15" t="n">
         <v>1.98</v>
@@ -3330,7 +3330,7 @@
         <v>1.24</v>
       </c>
       <c r="W15" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="X15" t="n">
         <v>15</v>
@@ -3342,7 +3342,7 @@
         <v>38</v>
       </c>
       <c r="AA15" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB15" t="n">
         <v>8.6</v>
@@ -3354,7 +3354,7 @@
         <v>19.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF15" t="n">
         <v>10.5</v>
@@ -3393,7 +3393,7 @@
         <v>16</v>
       </c>
       <c r="AR15" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AS15" t="n">
         <v>65</v>
@@ -3405,25 +3405,25 @@
         <v>8.6</v>
       </c>
       <c r="AV15" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AW15" t="n">
         <v>50</v>
       </c>
       <c r="AX15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY15" t="n">
         <v>9.6</v>
       </c>
-      <c r="AY15" t="n">
-        <v>9.4</v>
-      </c>
       <c r="AZ15" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BA15" t="n">
         <v>60</v>
       </c>
       <c r="BB15" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BC15" t="n">
         <v>17.5</v>
@@ -3438,11 +3438,11 @@
         <v>11</v>
       </c>
       <c r="BG15" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-06 00:47:57</t>
+          <t>2026-05-06 02:59:05</t>
         </is>
       </c>
     </row>
@@ -3476,19 +3476,19 @@
         <v>1.84</v>
       </c>
       <c r="G16" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="H16" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="I16" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J16" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K16" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L16" t="n">
         <v>1.44</v>
@@ -3515,13 +3515,13 @@
         <v>3.85</v>
       </c>
       <c r="T16" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="U16" t="n">
         <v>1.96</v>
       </c>
       <c r="V16" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W16" t="n">
         <v>2.16</v>
@@ -3533,7 +3533,7 @@
         <v>16</v>
       </c>
       <c r="Z16" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA16" t="n">
         <v>130</v>
@@ -3560,7 +3560,7 @@
         <v>22</v>
       </c>
       <c r="AI16" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AJ16" t="n">
         <v>19.5</v>
@@ -3599,7 +3599,7 @@
         <v>7.8</v>
       </c>
       <c r="AV16" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AW16" t="n">
         <v>60</v>
@@ -3617,7 +3617,7 @@
         <v>36</v>
       </c>
       <c r="BB16" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BC16" t="n">
         <v>18.5</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-06 00:47:57</t>
+          <t>2026-05-06 02:59:05</t>
         </is>
       </c>
     </row>
@@ -3667,170 +3667,170 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.97</v>
+        <v>2.14</v>
       </c>
       <c r="G17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N17" t="n">
         <v>2.52</v>
       </c>
-      <c r="H17" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="I17" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="K17" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N17" t="n">
-        <v>2.18</v>
-      </c>
       <c r="O17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P17" t="n">
         <v>1.51</v>
       </c>
-      <c r="P17" t="n">
-        <v>1.43</v>
-      </c>
       <c r="Q17" t="n">
-        <v>2.14</v>
+        <v>2.6</v>
       </c>
       <c r="R17" t="n">
         <v>1.18</v>
       </c>
       <c r="S17" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="T17" t="n">
-        <v>1.11</v>
+        <v>2.12</v>
       </c>
       <c r="U17" t="n">
-        <v>1.11</v>
+        <v>1.74</v>
       </c>
       <c r="V17" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="W17" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="X17" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>240</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>140</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AX17" t="n">
         <v>10.5</v>
       </c>
-      <c r="Y17" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AC17" t="n">
+      <c r="AY17" t="n">
         <v>10</v>
       </c>
-      <c r="AD17" t="n">
-        <v>27</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>46</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>46</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>85</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>2.34</v>
-      </c>
       <c r="AZ17" t="n">
-        <v>2.52</v>
+        <v>20</v>
       </c>
       <c r="BA17" t="n">
-        <v>2.72</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB17" t="n">
-        <v>2.56</v>
+        <v>7.4</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.56</v>
+        <v>7.4</v>
       </c>
       <c r="BD17" t="n">
-        <v>2.64</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE17" t="n">
-        <v>2.72</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.72</v>
+        <v>7.4</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.72</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-06 00:47:57</t>
+          <t>2026-05-06 02:59:05</t>
         </is>
       </c>
     </row>
@@ -3861,22 +3861,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="G18" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="H18" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="I18" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="J18" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="K18" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
@@ -3885,146 +3885,146 @@
         <v>1.08</v>
       </c>
       <c r="N18" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="O18" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="P18" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R18" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S18" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="T18" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="U18" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="V18" t="n">
         <v>1.14</v>
       </c>
       <c r="W18" t="n">
-        <v>2.58</v>
+        <v>2.82</v>
       </c>
       <c r="X18" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z18" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AA18" t="n">
-        <v>260</v>
+        <v>350</v>
       </c>
       <c r="AB18" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AC18" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD18" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AE18" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AF18" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG18" t="n">
         <v>10.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AI18" t="n">
-        <v>140</v>
+        <v>210</v>
       </c>
       <c r="AJ18" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AK18" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AL18" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AM18" t="n">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="AN18" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AO18" t="n">
-        <v>220</v>
+        <v>260</v>
       </c>
       <c r="AP18" t="n">
         <v>11</v>
       </c>
       <c r="AQ18" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AR18" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AS18" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="AT18" t="n">
         <v>6.2</v>
       </c>
       <c r="AU18" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV18" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AW18" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AX18" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AY18" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ18" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="BA18" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BB18" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BD18" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BE18" t="n">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="BF18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BG18" t="n">
         <v>10</v>
       </c>
-      <c r="BG18" t="n">
-        <v>13.5</v>
-      </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-06 00:47:57</t>
+          <t>2026-05-06 02:59:05</t>
         </is>
       </c>
     </row>
@@ -4079,10 +4079,10 @@
         <v>1.12</v>
       </c>
       <c r="N19" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="O19" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="P19" t="n">
         <v>1.53</v>
@@ -4091,7 +4091,7 @@
         <v>2.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S19" t="n">
         <v>5.1</v>
@@ -4142,19 +4142,19 @@
         <v>24</v>
       </c>
       <c r="AI19" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ19" t="n">
         <v>34</v>
       </c>
       <c r="AK19" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL19" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM19" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AN19" t="n">
         <v>32</v>
@@ -4163,7 +4163,7 @@
         <v>120</v>
       </c>
       <c r="AP19" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ19" t="n">
         <v>9.4</v>
@@ -4172,7 +4172,7 @@
         <v>18</v>
       </c>
       <c r="AS19" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AT19" t="n">
         <v>6.2</v>
@@ -4184,7 +4184,7 @@
         <v>15</v>
       </c>
       <c r="AW19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AX19" t="n">
         <v>11</v>
@@ -4196,29 +4196,29 @@
         <v>19.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB19" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BC19" t="n">
         <v>21</v>
       </c>
       <c r="BD19" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="BE19" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF19" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG19" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-06 00:47:57</t>
+          <t>2026-05-06 02:59:05</t>
         </is>
       </c>
     </row>
@@ -4249,13 +4249,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="G20" t="n">
         <v>5.1</v>
       </c>
       <c r="H20" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="I20" t="n">
         <v>2.12</v>
@@ -4267,7 +4267,7 @@
         <v>3.7</v>
       </c>
       <c r="L20" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M20" t="n">
         <v>1.1</v>
@@ -4279,10 +4279,10 @@
         <v>1.43</v>
       </c>
       <c r="P20" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="R20" t="n">
         <v>1.24</v>
@@ -4297,7 +4297,7 @@
         <v>1.83</v>
       </c>
       <c r="V20" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="W20" t="n">
         <v>1.24</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-06 00:47:57</t>
+          <t>2026-05-06 02:59:05</t>
         </is>
       </c>
     </row>
@@ -4443,13 +4443,13 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="G21" t="n">
         <v>1000</v>
       </c>
       <c r="H21" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="I21" t="n">
         <v>1000</v>
@@ -4482,7 +4482,7 @@
         <v>1.18</v>
       </c>
       <c r="S21" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="T21" t="n">
         <v>1.01</v>
@@ -4551,52 +4551,52 @@
         <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF21" t="n">
         <v>1.01</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-06 00:47:57</t>
+          <t>2026-05-06 02:59:05</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-07.xlsx
@@ -769,7 +769,7 @@
         <v>5.5</v>
       </c>
       <c r="J2" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="K2" t="n">
         <v>3.35</v>
@@ -781,7 +781,7 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="O2" t="n">
         <v>1.47</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
         <v>1.04</v>
       </c>
       <c r="G4" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="H4" t="n">
         <v>1.04</v>
@@ -1157,7 +1157,7 @@
         <v>990</v>
       </c>
       <c r="J4" t="n">
-        <v>1.04</v>
+        <v>2.28</v>
       </c>
       <c r="K4" t="n">
         <v>950</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
         <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N5" t="n">
         <v>2.12</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
         <v>1.78</v>
       </c>
       <c r="G6" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="H6" t="n">
         <v>5</v>
@@ -1554,13 +1554,13 @@
         <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>2.74</v>
+        <v>3.55</v>
       </c>
       <c r="O6" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="P6" t="n">
         <v>1.89</v>
@@ -1569,134 +1569,134 @@
         <v>1.96</v>
       </c>
       <c r="R6" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="T6" t="n">
-        <v>1.11</v>
+        <v>1.9</v>
       </c>
       <c r="U6" t="n">
-        <v>1.11</v>
+        <v>1.96</v>
       </c>
       <c r="V6" t="n">
         <v>1.22</v>
       </c>
       <c r="W6" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -1727,16 +1727,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="G7" t="n">
         <v>1.89</v>
       </c>
       <c r="H7" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I7" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J7" t="n">
         <v>3.35</v>
@@ -1745,28 +1745,28 @@
         <v>3.6</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="M7" t="n">
         <v>1.12</v>
       </c>
       <c r="N7" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="O7" t="n">
         <v>1.55</v>
       </c>
       <c r="P7" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="R7" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S7" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="T7" t="n">
         <v>2.28</v>
@@ -1802,7 +1802,7 @@
         <v>24</v>
       </c>
       <c r="AE7" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AF7" t="n">
         <v>9.4</v>
@@ -1811,7 +1811,7 @@
         <v>11</v>
       </c>
       <c r="AH7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AI7" t="n">
         <v>130</v>
@@ -1826,7 +1826,7 @@
         <v>65</v>
       </c>
       <c r="AM7" t="n">
-        <v>320</v>
+        <v>250</v>
       </c>
       <c r="AN7" t="n">
         <v>22</v>
@@ -1856,7 +1856,7 @@
         <v>21</v>
       </c>
       <c r="AW7" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AX7" t="n">
         <v>8.4</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -1921,103 +1921,103 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.32</v>
+        <v>2.04</v>
       </c>
       <c r="G8" t="n">
-        <v>2.56</v>
+        <v>2.26</v>
       </c>
       <c r="H8" t="n">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="I8" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="J8" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="K8" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="L8" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="M8" t="n">
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>2.3</v>
+        <v>2.66</v>
       </c>
       <c r="O8" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="P8" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="R8" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="S8" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="T8" t="n">
         <v>1.11</v>
       </c>
       <c r="U8" t="n">
-        <v>1.67</v>
+        <v>1.11</v>
       </c>
       <c r="V8" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="W8" t="n">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="X8" t="n">
         <v>10.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>13.5</v>
+        <v>17</v>
       </c>
       <c r="Z8" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="AA8" t="n">
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC8" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AD8" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AE8" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AF8" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AG8" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AI8" t="n">
         <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AK8" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AL8" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AM8" t="n">
         <v>1000</v>
@@ -2029,62 +2029,62 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="AQ8" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="AT8" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="AU8" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AW8" t="n">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="AX8" t="n">
-        <v>10</v>
+        <v>2.44</v>
       </c>
       <c r="AY8" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="AZ8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BB8" t="n">
         <v>2.66</v>
       </c>
-      <c r="BA8" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>2.76</v>
-      </c>
       <c r="BC8" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BD8" t="n">
         <v>2.74</v>
       </c>
-      <c r="BD8" t="n">
-        <v>2.82</v>
-      </c>
       <c r="BE8" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -2121,16 +2121,16 @@
         <v>1.6</v>
       </c>
       <c r="H9" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I9" t="n">
         <v>990</v>
       </c>
       <c r="J9" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="K9" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2181,7 +2181,7 @@
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AC9" t="n">
         <v>26</v>
@@ -2193,7 +2193,7 @@
         <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AG9" t="n">
         <v>30</v>
@@ -2205,7 +2205,7 @@
         <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AK9" t="n">
         <v>65</v>
@@ -2217,46 +2217,46 @@
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="AO9" t="n">
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>4.8</v>
+        <v>1.31</v>
       </c>
       <c r="AQ9" t="n">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AT9" t="n">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV9" t="n">
-        <v>16</v>
+        <v>1.32</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AX9" t="n">
-        <v>4.1</v>
+        <v>1.26</v>
       </c>
       <c r="AY9" t="n">
         <v>10</v>
       </c>
       <c r="AZ9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="BB9" t="n">
         <v>7.4</v>
@@ -2268,17 +2268,17 @@
         <v>14.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="BG9" t="n">
-        <v>8.6</v>
+        <v>13</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -2321,40 +2321,40 @@
         <v>6.6</v>
       </c>
       <c r="J10" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="K10" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M10" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>2.26</v>
+        <v>4.3</v>
       </c>
       <c r="O10" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P10" t="n">
         <v>2.14</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="R10" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="S10" t="n">
-        <v>2.48</v>
+        <v>2.88</v>
       </c>
       <c r="T10" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="U10" t="n">
-        <v>1.11</v>
+        <v>2.1</v>
       </c>
       <c r="V10" t="n">
         <v>1.17</v>
@@ -2363,116 +2363,116 @@
         <v>2.24</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="BD10" t="n">
         <v>1.03</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BG10" t="n">
         <v>1.01</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -2533,34 +2533,34 @@
         <v>1.12</v>
       </c>
       <c r="P11" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="R11" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="S11" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="T11" t="n">
         <v>1.68</v>
       </c>
       <c r="U11" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V11" t="n">
         <v>3.35</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X11" t="n">
         <v>42</v>
       </c>
       <c r="Y11" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z11" t="n">
         <v>12.5</v>
@@ -2599,10 +2599,10 @@
         <v>120</v>
       </c>
       <c r="AL11" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AM11" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AN11" t="n">
         <v>100</v>
@@ -2611,7 +2611,7 @@
         <v>4.1</v>
       </c>
       <c r="AP11" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AQ11" t="n">
         <v>12</v>
@@ -2623,7 +2623,7 @@
         <v>10.5</v>
       </c>
       <c r="AT11" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU11" t="n">
         <v>12.5</v>
@@ -2635,38 +2635,38 @@
         <v>11.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ11" t="n">
         <v>6.4</v>
       </c>
-      <c r="AZ11" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BA11" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BB11" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BC11" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD11" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BE11" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BF11" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BG11" t="n">
         <v>3.05</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -2891,16 +2891,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="G13" t="n">
         <v>1.64</v>
       </c>
       <c r="H13" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I13" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J13" t="n">
         <v>4.4</v>
@@ -2909,7 +2909,7 @@
         <v>4.6</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M13" t="n">
         <v>1.06</v>
@@ -2960,13 +2960,13 @@
         <v>9</v>
       </c>
       <c r="AC13" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD13" t="n">
         <v>24</v>
       </c>
       <c r="AE13" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AF13" t="n">
         <v>9.6</v>
@@ -2987,7 +2987,7 @@
         <v>16.5</v>
       </c>
       <c r="AL13" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AM13" t="n">
         <v>150</v>
@@ -2996,10 +2996,10 @@
         <v>8.4</v>
       </c>
       <c r="AO13" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AP13" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AQ13" t="n">
         <v>20</v>
@@ -3044,7 +3044,7 @@
         <v>30</v>
       </c>
       <c r="BE13" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BF13" t="n">
         <v>7.8</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -3115,7 +3115,7 @@
         <v>1.31</v>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q14" t="n">
         <v>1.92</v>
@@ -3130,7 +3130,7 @@
         <v>1.82</v>
       </c>
       <c r="U14" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V14" t="n">
         <v>1.29</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -3282,19 +3282,19 @@
         <v>1.8</v>
       </c>
       <c r="G15" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="H15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I15" t="n">
         <v>5</v>
-      </c>
-      <c r="I15" t="n">
-        <v>5.1</v>
       </c>
       <c r="J15" t="n">
         <v>4</v>
       </c>
       <c r="K15" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L15" t="n">
         <v>1.41</v>
@@ -3303,37 +3303,37 @@
         <v>1.07</v>
       </c>
       <c r="N15" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O15" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P15" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="R15" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S15" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="T15" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="U15" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V15" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W15" t="n">
         <v>2.22</v>
       </c>
       <c r="X15" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Y15" t="n">
         <v>17</v>
@@ -3351,7 +3351,7 @@
         <v>9</v>
       </c>
       <c r="AD15" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AE15" t="n">
         <v>65</v>
@@ -3366,19 +3366,19 @@
         <v>19.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ15" t="n">
         <v>18.5</v>
       </c>
       <c r="AK15" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL15" t="n">
         <v>38</v>
       </c>
       <c r="AM15" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN15" t="n">
         <v>12</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -3479,7 +3479,7 @@
         <v>1.85</v>
       </c>
       <c r="H16" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I16" t="n">
         <v>5.1</v>
@@ -3488,7 +3488,7 @@
         <v>3.85</v>
       </c>
       <c r="K16" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L16" t="n">
         <v>1.44</v>
@@ -3515,13 +3515,13 @@
         <v>3.85</v>
       </c>
       <c r="T16" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="U16" t="n">
         <v>1.96</v>
       </c>
       <c r="V16" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W16" t="n">
         <v>2.16</v>
@@ -3539,10 +3539,10 @@
         <v>130</v>
       </c>
       <c r="AB16" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AC16" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AD16" t="n">
         <v>20</v>
@@ -3608,16 +3608,16 @@
         <v>9.4</v>
       </c>
       <c r="AY16" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ16" t="n">
         <v>19.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BB16" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BC16" t="n">
         <v>18.5</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -3781,7 +3781,7 @@
         <v>9.4</v>
       </c>
       <c r="AR17" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AS17" t="n">
         <v>8.800000000000001</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -3861,10 +3861,10 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="G18" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="H18" t="n">
         <v>7.6</v>
@@ -3873,13 +3873,13 @@
         <v>9</v>
       </c>
       <c r="J18" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="K18" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M18" t="n">
         <v>1.08</v>
@@ -3888,13 +3888,13 @@
         <v>3.35</v>
       </c>
       <c r="O18" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P18" t="n">
         <v>1.79</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="R18" t="n">
         <v>1.3</v>
@@ -3903,16 +3903,16 @@
         <v>3.9</v>
       </c>
       <c r="T18" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="U18" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="V18" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="W18" t="n">
-        <v>2.82</v>
+        <v>2.72</v>
       </c>
       <c r="X18" t="n">
         <v>14.5</v>
@@ -3924,7 +3924,7 @@
         <v>75</v>
       </c>
       <c r="AA18" t="n">
-        <v>350</v>
+        <v>330</v>
       </c>
       <c r="AB18" t="n">
         <v>8</v>
@@ -3948,7 +3948,7 @@
         <v>30</v>
       </c>
       <c r="AI18" t="n">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="AJ18" t="n">
         <v>13.5</v>
@@ -3966,13 +3966,13 @@
         <v>10</v>
       </c>
       <c r="AO18" t="n">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="AP18" t="n">
         <v>11</v>
       </c>
       <c r="AQ18" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AR18" t="n">
         <v>50</v>
@@ -3984,10 +3984,10 @@
         <v>6.2</v>
       </c>
       <c r="AU18" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AV18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW18" t="n">
         <v>10</v>
@@ -3996,13 +3996,13 @@
         <v>7.2</v>
       </c>
       <c r="AY18" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ18" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="BA18" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BB18" t="n">
         <v>11.5</v>
@@ -4011,7 +4011,7 @@
         <v>16</v>
       </c>
       <c r="BD18" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BE18" t="n">
         <v>10</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G19" t="n">
         <v>2.42</v>
@@ -4088,7 +4088,7 @@
         <v>1.53</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="R19" t="n">
         <v>1.2</v>
@@ -4106,7 +4106,7 @@
         <v>1.29</v>
       </c>
       <c r="W19" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="X19" t="n">
         <v>9.199999999999999</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -4255,10 +4255,10 @@
         <v>5.1</v>
       </c>
       <c r="H20" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="I20" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="J20" t="n">
         <v>3.25</v>
@@ -4282,7 +4282,7 @@
         <v>1.67</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="R20" t="n">
         <v>1.24</v>
@@ -4297,10 +4297,10 @@
         <v>1.83</v>
       </c>
       <c r="V20" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="W20" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="X20" t="n">
         <v>11.5</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -4455,10 +4455,10 @@
         <v>1000</v>
       </c>
       <c r="J21" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K21" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L21" t="n">
         <v>1.01</v>
@@ -4482,7 +4482,7 @@
         <v>1.18</v>
       </c>
       <c r="S21" t="n">
-        <v>1.02</v>
+        <v>1.44</v>
       </c>
       <c r="T21" t="n">
         <v>1.01</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-07.xlsx
@@ -781,13 +781,13 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="O2" t="n">
-        <v>1.47</v>
+        <v>1.75</v>
       </c>
       <c r="P2" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Q2" t="n">
         <v>3</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G3" t="n">
         <v>990</v>
@@ -960,10 +960,10 @@
         <v>1.04</v>
       </c>
       <c r="I3" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J3" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="K3" t="n">
         <v>950</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
         <v>990</v>
       </c>
       <c r="J4" t="n">
-        <v>2.28</v>
+        <v>2.52</v>
       </c>
       <c r="K4" t="n">
         <v>950</v>
@@ -1169,22 +1169,22 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="O4" t="n">
         <v>1.35</v>
       </c>
       <c r="P4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.35</v>
+        <v>1.94</v>
       </c>
       <c r="R4" t="n">
         <v>1.12</v>
       </c>
       <c r="S4" t="n">
-        <v>1.35</v>
+        <v>1.95</v>
       </c>
       <c r="T4" t="n">
         <v>1.11</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -1339,19 +1339,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.04</v>
+        <v>1.52</v>
       </c>
       <c r="G5" t="n">
         <v>1.94</v>
       </c>
       <c r="H5" t="n">
-        <v>2.1</v>
+        <v>1.04</v>
       </c>
       <c r="I5" t="n">
         <v>990</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1</v>
+        <v>1.09</v>
       </c>
       <c r="K5" t="n">
         <v>950</v>
@@ -1369,7 +1369,7 @@
         <v>1.31</v>
       </c>
       <c r="P5" t="n">
-        <v>1.25</v>
+        <v>1.48</v>
       </c>
       <c r="Q5" t="n">
         <v>1.31</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
         <v>1.83</v>
       </c>
       <c r="G7" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="H7" t="n">
         <v>5.4</v>
@@ -1742,7 +1742,7 @@
         <v>3.35</v>
       </c>
       <c r="K7" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L7" t="n">
         <v>1.49</v>
@@ -1769,7 +1769,7 @@
         <v>5.4</v>
       </c>
       <c r="T7" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="U7" t="n">
         <v>1.69</v>
@@ -1778,10 +1778,10 @@
         <v>1.2</v>
       </c>
       <c r="W7" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="X7" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y7" t="n">
         <v>16.5</v>
@@ -1808,7 +1808,7 @@
         <v>9.4</v>
       </c>
       <c r="AG7" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH7" t="n">
         <v>30</v>
@@ -1817,7 +1817,7 @@
         <v>130</v>
       </c>
       <c r="AJ7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK7" t="n">
         <v>26</v>
@@ -1841,7 +1841,7 @@
         <v>12</v>
       </c>
       <c r="AR7" t="n">
-        <v>34</v>
+        <v>11.5</v>
       </c>
       <c r="AS7" t="n">
         <v>12</v>
@@ -1856,7 +1856,7 @@
         <v>21</v>
       </c>
       <c r="AW7" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AX7" t="n">
         <v>8.4</v>
@@ -1880,17 +1880,17 @@
         <v>50</v>
       </c>
       <c r="BE7" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BF7" t="n">
         <v>18</v>
       </c>
       <c r="BG7" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -1921,170 +1921,170 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="H8" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I8" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="J8" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K8" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N8" t="n">
-        <v>2.66</v>
+        <v>2.46</v>
       </c>
       <c r="O8" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="P8" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="R8" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="S8" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="T8" t="n">
         <v>1.11</v>
       </c>
       <c r="U8" t="n">
-        <v>1.11</v>
+        <v>1.75</v>
       </c>
       <c r="V8" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="W8" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="X8" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>140</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>27</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>140</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV8" t="n">
         <v>17</v>
       </c>
-      <c r="Z8" t="n">
-        <v>44</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>28</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>13</v>
-      </c>
       <c r="AW8" t="n">
-        <v>2.76</v>
+        <v>7.6</v>
       </c>
       <c r="AX8" t="n">
-        <v>2.44</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY8" t="n">
-        <v>2.4</v>
+        <v>9.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>2.6</v>
+        <v>19.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>2.84</v>
+        <v>8.4</v>
       </c>
       <c r="BB8" t="n">
-        <v>2.66</v>
+        <v>6.4</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.66</v>
+        <v>6.4</v>
       </c>
       <c r="BD8" t="n">
-        <v>2.74</v>
+        <v>7.4</v>
       </c>
       <c r="BE8" t="n">
-        <v>2.84</v>
+        <v>8</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.84</v>
+        <v>19.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.84</v>
+        <v>8</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -2121,13 +2121,13 @@
         <v>1.6</v>
       </c>
       <c r="H9" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="I9" t="n">
         <v>990</v>
       </c>
       <c r="J9" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="K9" t="n">
         <v>70</v>
@@ -2163,7 +2163,7 @@
         <v>1.11</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W9" t="n">
         <v>2.62</v>
@@ -2172,10 +2172,10 @@
         <v>85</v>
       </c>
       <c r="Y9" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="Z9" t="n">
-        <v>710</v>
+        <v>430</v>
       </c>
       <c r="AA9" t="n">
         <v>1000</v>
@@ -2184,10 +2184,10 @@
         <v>34</v>
       </c>
       <c r="AC9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AD9" t="n">
-        <v>380</v>
+        <v>240</v>
       </c>
       <c r="AE9" t="n">
         <v>1000</v>
@@ -2196,58 +2196,58 @@
         <v>25</v>
       </c>
       <c r="AG9" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AH9" t="n">
-        <v>390</v>
+        <v>260</v>
       </c>
       <c r="AI9" t="n">
         <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="AK9" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AL9" t="n">
-        <v>710</v>
+        <v>480</v>
       </c>
       <c r="AM9" t="n">
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="AO9" t="n">
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AQ9" t="n">
-        <v>11.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR9" t="n">
         <v>1.32</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AT9" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="AU9" t="n">
         <v>7.2</v>
       </c>
       <c r="AV9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW9" t="n">
         <v>1.32</v>
       </c>
-      <c r="AW9" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AX9" t="n">
-        <v>1.26</v>
+        <v>4.7</v>
       </c>
       <c r="AY9" t="n">
         <v>10</v>
@@ -2256,10 +2256,10 @@
         <v>13</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BB9" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC9" t="n">
         <v>9.6</v>
@@ -2268,17 +2268,17 @@
         <v>14.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="BG9" t="n">
-        <v>13</v>
+        <v>8.6</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -2309,16 +2309,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="G10" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="H10" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="I10" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J10" t="n">
         <v>3.65</v>
@@ -2339,37 +2339,37 @@
         <v>1.25</v>
       </c>
       <c r="P10" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="R10" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S10" t="n">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="T10" t="n">
         <v>1.76</v>
       </c>
       <c r="U10" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V10" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W10" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="X10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y10" t="n">
         <v>24</v>
       </c>
       <c r="Z10" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AA10" t="n">
         <v>150</v>
@@ -2378,10 +2378,10 @@
         <v>11.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE10" t="n">
         <v>80</v>
@@ -2393,7 +2393,7 @@
         <v>12</v>
       </c>
       <c r="AH10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI10" t="n">
         <v>75</v>
@@ -2402,7 +2402,7 @@
         <v>21</v>
       </c>
       <c r="AK10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL10" t="n">
         <v>38</v>
@@ -2411,10 +2411,10 @@
         <v>110</v>
       </c>
       <c r="AN10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AO10" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AP10" t="n">
         <v>14</v>
@@ -2435,7 +2435,7 @@
         <v>7.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AW10" t="n">
         <v>1.01</v>
@@ -2444,7 +2444,7 @@
         <v>8.6</v>
       </c>
       <c r="AY10" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AZ10" t="n">
         <v>14.5</v>
@@ -2453,7 +2453,7 @@
         <v>1.01</v>
       </c>
       <c r="BB10" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BC10" t="n">
         <v>13</v>
@@ -2465,14 +2465,14 @@
         <v>1.01</v>
       </c>
       <c r="BF10" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BG10" t="n">
         <v>1.01</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -2506,13 +2506,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="H11" t="n">
         <v>1.34</v>
       </c>
       <c r="I11" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="J11" t="n">
         <v>5.7</v>
@@ -2536,7 +2536,7 @@
         <v>3.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="R11" t="n">
         <v>1.86</v>
@@ -2551,7 +2551,7 @@
         <v>2.2</v>
       </c>
       <c r="V11" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="W11" t="n">
         <v>1.11</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -2894,13 +2894,13 @@
         <v>1.6</v>
       </c>
       <c r="G13" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="H13" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I13" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J13" t="n">
         <v>4.4</v>
@@ -2927,7 +2927,7 @@
         <v>1.84</v>
       </c>
       <c r="R13" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S13" t="n">
         <v>3.1</v>
@@ -2936,13 +2936,13 @@
         <v>1.94</v>
       </c>
       <c r="U13" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="V13" t="n">
         <v>1.17</v>
       </c>
       <c r="W13" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="X13" t="n">
         <v>17</v>
@@ -2957,13 +2957,13 @@
         <v>190</v>
       </c>
       <c r="AB13" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC13" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE13" t="n">
         <v>95</v>
@@ -2972,10 +2972,10 @@
         <v>9.6</v>
       </c>
       <c r="AG13" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AH13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI13" t="n">
         <v>90</v>
@@ -2987,7 +2987,7 @@
         <v>16.5</v>
       </c>
       <c r="AL13" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AM13" t="n">
         <v>150</v>
@@ -3008,7 +3008,7 @@
         <v>44</v>
       </c>
       <c r="AS13" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AT13" t="n">
         <v>8.199999999999999</v>
@@ -3020,10 +3020,10 @@
         <v>21</v>
       </c>
       <c r="AW13" t="n">
-        <v>75</v>
+        <v>19.5</v>
       </c>
       <c r="AX13" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY13" t="n">
         <v>9.4</v>
@@ -3032,7 +3032,7 @@
         <v>20</v>
       </c>
       <c r="BA13" t="n">
-        <v>18.5</v>
+        <v>65</v>
       </c>
       <c r="BB13" t="n">
         <v>13</v>
@@ -3044,17 +3044,17 @@
         <v>30</v>
       </c>
       <c r="BE13" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="BF13" t="n">
         <v>7.8</v>
       </c>
       <c r="BG13" t="n">
-        <v>75</v>
+        <v>17.5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -3088,22 +3088,22 @@
         <v>1.95</v>
       </c>
       <c r="G14" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="H14" t="n">
         <v>4.2</v>
       </c>
       <c r="I14" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J14" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K14" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M14" t="n">
         <v>1.06</v>
@@ -3118,7 +3118,7 @@
         <v>2.02</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="R14" t="n">
         <v>1.39</v>
@@ -3127,19 +3127,19 @@
         <v>3.3</v>
       </c>
       <c r="T14" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="U14" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V14" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W14" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="X14" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Y14" t="n">
         <v>16</v>
@@ -3151,13 +3151,13 @@
         <v>110</v>
       </c>
       <c r="AB14" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC14" t="n">
         <v>8.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE14" t="n">
         <v>55</v>
@@ -3202,7 +3202,7 @@
         <v>29</v>
       </c>
       <c r="AS14" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AT14" t="n">
         <v>8.800000000000001</v>
@@ -3214,10 +3214,10 @@
         <v>15.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>15.5</v>
+        <v>46</v>
       </c>
       <c r="AX14" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY14" t="n">
         <v>9.800000000000001</v>
@@ -3226,7 +3226,7 @@
         <v>17</v>
       </c>
       <c r="BA14" t="n">
-        <v>15.5</v>
+        <v>50</v>
       </c>
       <c r="BB14" t="n">
         <v>19.5</v>
@@ -3238,7 +3238,7 @@
         <v>30</v>
       </c>
       <c r="BE14" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BF14" t="n">
         <v>11.5</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -3279,10 +3279,10 @@
         </is>
       </c>
       <c r="F15" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="G15" t="n">
         <v>1.8</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1.81</v>
       </c>
       <c r="H15" t="n">
         <v>4.9</v>
@@ -3303,7 +3303,7 @@
         <v>1.07</v>
       </c>
       <c r="N15" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O15" t="n">
         <v>1.32</v>
@@ -3324,13 +3324,13 @@
         <v>1.9</v>
       </c>
       <c r="U15" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V15" t="n">
         <v>1.25</v>
       </c>
       <c r="W15" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="X15" t="n">
         <v>15.5</v>
@@ -3345,7 +3345,7 @@
         <v>120</v>
       </c>
       <c r="AB15" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC15" t="n">
         <v>9</v>
@@ -3363,7 +3363,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AH15" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AI15" t="n">
         <v>70</v>
@@ -3381,7 +3381,7 @@
         <v>110</v>
       </c>
       <c r="AN15" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AO15" t="n">
         <v>85</v>
@@ -3396,7 +3396,7 @@
         <v>32</v>
       </c>
       <c r="AS15" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="AT15" t="n">
         <v>8.199999999999999</v>
@@ -3405,16 +3405,16 @@
         <v>8.6</v>
       </c>
       <c r="AV15" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AW15" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AX15" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AY15" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ15" t="n">
         <v>18.5</v>
@@ -3426,7 +3426,7 @@
         <v>17.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BD15" t="n">
         <v>34</v>
@@ -3435,14 +3435,14 @@
         <v>100</v>
       </c>
       <c r="BF15" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="G16" t="n">
         <v>1.85</v>
       </c>
       <c r="H16" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I16" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K16" t="n">
         <v>3.85</v>
-      </c>
-      <c r="K16" t="n">
-        <v>3.9</v>
       </c>
       <c r="L16" t="n">
         <v>1.44</v>
@@ -3515,13 +3515,13 @@
         <v>3.85</v>
       </c>
       <c r="T16" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U16" t="n">
         <v>1.97</v>
       </c>
-      <c r="U16" t="n">
-        <v>1.96</v>
-      </c>
       <c r="V16" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W16" t="n">
         <v>2.16</v>
@@ -3533,7 +3533,7 @@
         <v>16</v>
       </c>
       <c r="Z16" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AA16" t="n">
         <v>130</v>
@@ -3542,7 +3542,7 @@
         <v>8.4</v>
       </c>
       <c r="AC16" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD16" t="n">
         <v>20</v>
@@ -3554,16 +3554,16 @@
         <v>10.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI16" t="n">
         <v>80</v>
       </c>
       <c r="AJ16" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AK16" t="n">
         <v>20</v>
@@ -3575,7 +3575,7 @@
         <v>130</v>
       </c>
       <c r="AN16" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AO16" t="n">
         <v>90</v>
@@ -3596,16 +3596,16 @@
         <v>7.6</v>
       </c>
       <c r="AU16" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV16" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AW16" t="n">
         <v>60</v>
       </c>
       <c r="AX16" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY16" t="n">
         <v>9.6</v>
@@ -3614,16 +3614,16 @@
         <v>19.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BB16" t="n">
         <v>18</v>
       </c>
       <c r="BC16" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BD16" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BE16" t="n">
         <v>42</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G17" t="n">
         <v>2.38</v>
@@ -3679,40 +3679,40 @@
         <v>4.5</v>
       </c>
       <c r="J17" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="K17" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N17" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="O17" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="P17" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="R17" t="n">
         <v>1.18</v>
       </c>
       <c r="S17" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="T17" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="U17" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="V17" t="n">
         <v>1.28</v>
@@ -3736,7 +3736,7 @@
         <v>7.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD17" t="n">
         <v>19</v>
@@ -3775,7 +3775,7 @@
         <v>140</v>
       </c>
       <c r="AP17" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AQ17" t="n">
         <v>9.4</v>
@@ -3784,7 +3784,7 @@
         <v>18</v>
       </c>
       <c r="AS17" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT17" t="n">
         <v>6</v>
@@ -3796,7 +3796,7 @@
         <v>15.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX17" t="n">
         <v>10.5</v>
@@ -3808,29 +3808,29 @@
         <v>20</v>
       </c>
       <c r="BA17" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BB17" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BC17" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BD17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BE17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BG17" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BF17" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -3861,16 +3861,16 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="G18" t="n">
         <v>1.58</v>
       </c>
       <c r="H18" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="I18" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J18" t="n">
         <v>4.1</v>
@@ -3894,7 +3894,7 @@
         <v>1.79</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R18" t="n">
         <v>1.3</v>
@@ -3906,7 +3906,7 @@
         <v>2.2</v>
       </c>
       <c r="U18" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V18" t="n">
         <v>1.13</v>
@@ -3951,13 +3951,13 @@
         <v>190</v>
       </c>
       <c r="AJ18" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AK18" t="n">
         <v>970</v>
       </c>
       <c r="AL18" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM18" t="n">
         <v>240</v>
@@ -3978,13 +3978,13 @@
         <v>50</v>
       </c>
       <c r="AS18" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AT18" t="n">
         <v>6.2</v>
       </c>
       <c r="AU18" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AV18" t="n">
         <v>25</v>
@@ -3993,16 +3993,16 @@
         <v>10</v>
       </c>
       <c r="AX18" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY18" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ18" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="BA18" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BB18" t="n">
         <v>11.5</v>
@@ -4014,7 +4014,7 @@
         <v>36</v>
       </c>
       <c r="BE18" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF18" t="n">
         <v>8.6</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -4055,19 +4055,19 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="G19" t="n">
         <v>2.42</v>
       </c>
       <c r="H19" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="I19" t="n">
         <v>4.5</v>
       </c>
       <c r="J19" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="K19" t="n">
         <v>3.4</v>
@@ -4079,7 +4079,7 @@
         <v>1.12</v>
       </c>
       <c r="N19" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="O19" t="n">
         <v>1.5</v>
@@ -4205,7 +4205,7 @@
         <v>21</v>
       </c>
       <c r="BD19" t="n">
-        <v>44</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE19" t="n">
         <v>9.199999999999999</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -4255,7 +4255,7 @@
         <v>5.1</v>
       </c>
       <c r="H20" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="I20" t="n">
         <v>2.1</v>
@@ -4264,7 +4264,7 @@
         <v>3.25</v>
       </c>
       <c r="K20" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L20" t="n">
         <v>1.43</v>
@@ -4342,10 +4342,10 @@
         <v>140</v>
       </c>
       <c r="AK20" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AL20" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AM20" t="n">
         <v>180</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -4467,7 +4467,7 @@
         <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="O21" t="n">
         <v>1.43</v>
@@ -4476,13 +4476,13 @@
         <v>1.25</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="R21" t="n">
         <v>1.18</v>
       </c>
       <c r="S21" t="n">
-        <v>1.44</v>
+        <v>1.02</v>
       </c>
       <c r="T21" t="n">
         <v>1.01</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH21"/>
+  <dimension ref="A1:BH23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -760,19 +760,19 @@
         <v>2.34</v>
       </c>
       <c r="G2" t="n">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="H2" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="I2" t="n">
         <v>5.5</v>
       </c>
       <c r="J2" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="K2" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="L2" t="n">
         <v>1.68</v>
@@ -784,10 +784,10 @@
         <v>1.85</v>
       </c>
       <c r="O2" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="P2" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Q2" t="n">
         <v>3</v>
@@ -805,10 +805,10 @@
         <v>1.11</v>
       </c>
       <c r="V2" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W2" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="X2" t="n">
         <v>7.2</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-06 07:21:25</t>
+          <t>2026-05-06 09:33:28</t>
         </is>
       </c>
     </row>
@@ -957,16 +957,16 @@
         <v>990</v>
       </c>
       <c r="H3" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I3" t="n">
         <v>990</v>
       </c>
       <c r="J3" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K3" t="n">
-        <v>950</v>
+        <v>6.8</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-06 07:21:25</t>
+          <t>2026-05-06 09:33:28</t>
         </is>
       </c>
     </row>
@@ -1169,13 +1169,13 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="O4" t="n">
         <v>1.35</v>
       </c>
       <c r="P4" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q4" t="n">
         <v>1.94</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-06 07:21:25</t>
+          <t>2026-05-06 09:33:28</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
         <v>990</v>
       </c>
       <c r="J5" t="n">
-        <v>1.09</v>
+        <v>2.1</v>
       </c>
       <c r="K5" t="n">
         <v>950</v>
@@ -1502,14 +1502,14 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-06 07:21:25</t>
+          <t>2026-05-06 09:33:28</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Finnish Ykkosliiga</t>
+          <t>Serbian First League</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,191 +1519,191 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PK-35 RY</t>
+          <t>FK Borac Cacak</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>FK Graficar</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="G6" t="n">
-        <v>1.85</v>
+        <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="I6" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="K6" t="n">
-        <v>4.2</v>
+        <v>950</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
       </c>
       <c r="M6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N6" t="n">
         <v>1.07</v>
       </c>
-      <c r="N6" t="n">
-        <v>3.55</v>
-      </c>
       <c r="O6" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="P6" t="n">
-        <v>1.89</v>
+        <v>1.07</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="R6" t="n">
-        <v>1.34</v>
+        <v>1.07</v>
       </c>
       <c r="S6" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="T6" t="n">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>3.45</v>
+        <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AV6" t="n">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AY6" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="BC6" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>3.45</v>
+        <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-06 07:21:25</t>
+          <t>2026-05-06 09:33:28</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Serbian First League</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,191 +1713,191 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>FK Dubocica</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ZED FC</t>
+          <t>FK FAP</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="G7" t="n">
-        <v>1.87</v>
+        <v>200</v>
       </c>
       <c r="H7" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="I7" t="n">
-        <v>5.9</v>
+        <v>200</v>
       </c>
       <c r="J7" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="K7" t="n">
-        <v>3.55</v>
+        <v>200</v>
       </c>
       <c r="L7" t="n">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>2.66</v>
+        <v>1.07</v>
       </c>
       <c r="O7" t="n">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="P7" t="n">
-        <v>1.57</v>
+        <v>1.07</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.58</v>
+        <v>1.01</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="S7" t="n">
-        <v>5.4</v>
+        <v>1.41</v>
       </c>
       <c r="T7" t="n">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="U7" t="n">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AR7" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS7" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AU7" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV7" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AW7" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BA7" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BD7" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-06 07:21:25</t>
+          <t>2026-05-06 09:33:28</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Finnish Ykkosliiga</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,184 +1907,184 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>National Bank</t>
+          <t>PK-35 RY</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ismaily</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="G8" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="H8" t="n">
+        <v>5</v>
+      </c>
+      <c r="I8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W8" t="n">
         <v>2.16</v>
       </c>
-      <c r="H8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I8" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.86</v>
-      </c>
       <c r="X8" t="n">
-        <v>9.800000000000001</v>
+        <v>16.5</v>
       </c>
       <c r="Y8" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>160</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ8" t="n">
         <v>13.5</v>
       </c>
-      <c r="Z8" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>140</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AC8" t="n">
+      <c r="AR8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY8" t="n">
         <v>7.8</v>
       </c>
-      <c r="AD8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>29</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>210</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>27</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>140</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY8" t="n">
+      <c r="AZ8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>14</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BF8" t="n">
         <v>9.4</v>
       </c>
-      <c r="AZ8" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>19.5</v>
-      </c>
       <c r="BG8" t="n">
-        <v>8</v>
+        <v>4.6</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-06 07:21:25</t>
+          <t>2026-05-06 09:33:28</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         <v>990</v>
       </c>
       <c r="J9" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="K9" t="n">
         <v>70</v>
@@ -2235,7 +2235,7 @@
         <v>1.32</v>
       </c>
       <c r="AT9" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="AU9" t="n">
         <v>7.2</v>
@@ -2247,7 +2247,7 @@
         <v>1.32</v>
       </c>
       <c r="AX9" t="n">
-        <v>4.7</v>
+        <v>1.26</v>
       </c>
       <c r="AY9" t="n">
         <v>10</v>
@@ -2271,14 +2271,14 @@
         <v>1.32</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="BG9" t="n">
         <v>8.6</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-06 07:21:25</t>
+          <t>2026-05-06 09:33:28</t>
         </is>
       </c>
     </row>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="G10" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="H10" t="n">
         <v>5</v>
@@ -2339,31 +2339,31 @@
         <v>1.25</v>
       </c>
       <c r="P10" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="R10" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S10" t="n">
         <v>2.66</v>
       </c>
       <c r="T10" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="U10" t="n">
         <v>2.12</v>
       </c>
       <c r="V10" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W10" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="X10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y10" t="n">
         <v>24</v>
@@ -2384,7 +2384,7 @@
         <v>24</v>
       </c>
       <c r="AE10" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AF10" t="n">
         <v>13</v>
@@ -2411,7 +2411,7 @@
         <v>110</v>
       </c>
       <c r="AN10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AO10" t="n">
         <v>80</v>
@@ -2441,13 +2441,13 @@
         <v>1.01</v>
       </c>
       <c r="AX10" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY10" t="n">
         <v>8</v>
       </c>
       <c r="AZ10" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA10" t="n">
         <v>1.01</v>
@@ -2472,14 +2472,14 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-06 07:21:25</t>
+          <t>2026-05-06 09:33:28</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,191 +2489,191 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Al-Shabab (KSA)</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>ZED FC</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>8.199999999999999</v>
+        <v>1.77</v>
       </c>
       <c r="G11" t="n">
-        <v>10</v>
+        <v>1.83</v>
       </c>
       <c r="H11" t="n">
-        <v>1.34</v>
+        <v>5.9</v>
       </c>
       <c r="I11" t="n">
-        <v>1.41</v>
+        <v>6.6</v>
       </c>
       <c r="J11" t="n">
-        <v>5.7</v>
+        <v>3.5</v>
       </c>
       <c r="K11" t="n">
-        <v>6.8</v>
+        <v>3.8</v>
       </c>
       <c r="L11" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V11" t="n">
         <v>1.18</v>
       </c>
-      <c r="M11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N11" t="n">
-        <v>7</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="P11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="U11" t="n">
+      <c r="W11" t="n">
         <v>2.2</v>
       </c>
-      <c r="V11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.11</v>
-      </c>
       <c r="X11" t="n">
-        <v>42</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>220</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>130</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>280</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>240</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BB11" t="n">
         <v>15.5</v>
       </c>
-      <c r="Z11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>46</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>16</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>110</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>34</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>27</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>270</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>120</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>100</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW11" t="n">
+      <c r="BC11" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>13</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BG11" t="n">
         <v>11.5</v>
       </c>
-      <c r="AX11" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>7</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>8</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>8</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>3.05</v>
-      </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-06 07:21:25</t>
+          <t>2026-05-06 09:33:28</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,191 +2683,191 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>National Bank</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Ismaily</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.04</v>
+        <v>1.98</v>
       </c>
       <c r="G12" t="n">
-        <v>600</v>
+        <v>2.14</v>
       </c>
       <c r="H12" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="I12" t="n">
-        <v>870</v>
+        <v>5.2</v>
       </c>
       <c r="J12" t="n">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="K12" t="n">
-        <v>950</v>
+        <v>3.4</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N12" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="O12" t="n">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="P12" t="n">
-        <v>1.81</v>
+        <v>1.57</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="R12" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="S12" t="n">
-        <v>1.05</v>
+        <v>4.9</v>
       </c>
       <c r="T12" t="n">
-        <v>1.11</v>
+        <v>2.08</v>
       </c>
       <c r="U12" t="n">
-        <v>1.11</v>
+        <v>1.77</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-06 07:21:25</t>
+          <t>2026-05-06 09:33:28</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Al-Shabab (KSA)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Shakhtar</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>1.63</v>
+        <v>10</v>
       </c>
       <c r="H13" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J13" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N13" t="n">
+        <v>7</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="P13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X13" t="n">
+        <v>42</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>46</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>110</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>34</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>27</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>270</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>120</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>100</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ13" t="n">
         <v>6.4</v>
       </c>
-      <c r="I13" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="J13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="K13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N13" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="X13" t="n">
-        <v>17</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>22</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>190</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>95</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>15</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>120</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>20</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>44</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>17</v>
-      </c>
-      <c r="AT13" t="n">
+      <c r="BA13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC13" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AU13" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>65</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>13</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BD13" t="n">
-        <v>30</v>
+        <v>7.8</v>
       </c>
       <c r="BE13" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="BF13" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BG13" t="n">
-        <v>17.5</v>
+        <v>3.05</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-06 07:21:25</t>
+          <t>2026-05-06 09:33:28</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3076,186 +3076,186 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.95</v>
+        <v>1.04</v>
       </c>
       <c r="G14" t="n">
-        <v>1.98</v>
+        <v>600</v>
       </c>
       <c r="H14" t="n">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="I14" t="n">
-        <v>4.5</v>
+        <v>870</v>
       </c>
       <c r="J14" t="n">
-        <v>3.8</v>
+        <v>1.03</v>
       </c>
       <c r="K14" t="n">
-        <v>3.9</v>
+        <v>950</v>
       </c>
       <c r="L14" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>4</v>
+        <v>1.1</v>
       </c>
       <c r="O14" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="P14" t="n">
-        <v>2.02</v>
+        <v>1.81</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="R14" t="n">
-        <v>1.39</v>
+        <v>1.12</v>
       </c>
       <c r="S14" t="n">
-        <v>3.3</v>
+        <v>1.05</v>
       </c>
       <c r="T14" t="n">
-        <v>1.81</v>
+        <v>1.11</v>
       </c>
       <c r="U14" t="n">
-        <v>2.16</v>
+        <v>1.11</v>
       </c>
       <c r="V14" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ14" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AR14" t="n">
-        <v>29</v>
+        <v>1.03</v>
       </c>
       <c r="AS14" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AT14" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AU14" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AV14" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW14" t="n">
-        <v>46</v>
+        <v>1.03</v>
       </c>
       <c r="AX14" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY14" t="n">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AZ14" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="BA14" t="n">
-        <v>50</v>
+        <v>1.03</v>
       </c>
       <c r="BB14" t="n">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC14" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD14" t="n">
-        <v>30</v>
+        <v>1.03</v>
       </c>
       <c r="BE14" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="BF14" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-06 07:21:25</t>
+          <t>2026-05-06 09:33:28</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3270,55 +3270,55 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nottm Forest</t>
+          <t>Shakhtar</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.79</v>
+        <v>1.6</v>
       </c>
       <c r="G15" t="n">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="H15" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="I15" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="J15" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="K15" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="L15" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="M15" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N15" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O15" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="P15" t="n">
-        <v>1.99</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.96</v>
+        <v>1.78</v>
       </c>
       <c r="R15" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="S15" t="n">
-        <v>3.5</v>
+        <v>2.96</v>
       </c>
       <c r="T15" t="n">
         <v>1.9</v>
@@ -3327,129 +3327,129 @@
         <v>2.04</v>
       </c>
       <c r="V15" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="W15" t="n">
-        <v>2.24</v>
+        <v>2.58</v>
       </c>
       <c r="X15" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="Z15" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="AA15" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="AB15" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AC15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD15" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AE15" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="AF15" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG15" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AH15" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AI15" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AJ15" t="n">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="AK15" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AL15" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM15" t="n">
         <v>110</v>
       </c>
       <c r="AN15" t="n">
-        <v>11.5</v>
+        <v>8</v>
       </c>
       <c r="AO15" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AP15" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AR15" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="AS15" t="n">
-        <v>90</v>
+        <v>17</v>
       </c>
       <c r="AT15" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU15" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV15" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AW15" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AX15" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AY15" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ15" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BB15" t="n">
-        <v>17.5</v>
+        <v>13</v>
       </c>
       <c r="BC15" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BE15" t="n">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="BF15" t="n">
-        <v>10.5</v>
+        <v>7.2</v>
       </c>
       <c r="BG15" t="n">
-        <v>65</v>
+        <v>16</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-06 07:21:25</t>
+          <t>2026-05-06 09:33:28</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3464,186 +3464,186 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="G16" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="H16" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="I16" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="J16" t="n">
         <v>3.8</v>
       </c>
       <c r="K16" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L16" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="M16" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="N16" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="O16" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="P16" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.08</v>
+        <v>1.91</v>
       </c>
       <c r="R16" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="S16" t="n">
-        <v>3.85</v>
+        <v>3.35</v>
       </c>
       <c r="T16" t="n">
-        <v>1.96</v>
+        <v>1.81</v>
       </c>
       <c r="U16" t="n">
-        <v>1.97</v>
+        <v>2.16</v>
       </c>
       <c r="V16" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="W16" t="n">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="X16" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Y16" t="n">
         <v>16</v>
       </c>
       <c r="Z16" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AA16" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AB16" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC16" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AF16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG16" t="n">
         <v>10.5</v>
       </c>
-      <c r="AG16" t="n">
-        <v>10</v>
-      </c>
       <c r="AH16" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AJ16" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AK16" t="n">
         <v>20</v>
       </c>
       <c r="AL16" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AM16" t="n">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="AN16" t="n">
         <v>13</v>
       </c>
       <c r="AO16" t="n">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="AP16" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AQ16" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>29</v>
+      </c>
+      <c r="AS16" t="n">
         <v>15</v>
       </c>
-      <c r="AR16" t="n">
-        <v>32</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>40</v>
-      </c>
       <c r="AT16" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU16" t="n">
         <v>8</v>
       </c>
       <c r="AV16" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AX16" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AY16" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ16" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>50</v>
+      </c>
+      <c r="BB16" t="n">
         <v>19.5</v>
       </c>
-      <c r="BA16" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>18</v>
-      </c>
       <c r="BC16" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="BE16" t="n">
+        <v>15</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BG16" t="n">
         <v>42</v>
       </c>
-      <c r="BF16" t="n">
-        <v>12</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>36</v>
-      </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-06 07:21:25</t>
+          <t>2026-05-06 09:33:28</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,191 +3653,191 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>CA Platense</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Penarol</t>
+          <t>Nottm Forest</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.16</v>
+        <v>1.79</v>
       </c>
       <c r="G17" t="n">
-        <v>2.38</v>
+        <v>1.8</v>
       </c>
       <c r="H17" t="n">
-        <v>3.9</v>
+        <v>4.9</v>
       </c>
       <c r="I17" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="J17" t="n">
-        <v>2.92</v>
+        <v>4.1</v>
       </c>
       <c r="K17" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="L17" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M17" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="N17" t="n">
-        <v>2.48</v>
+        <v>3.95</v>
       </c>
       <c r="O17" t="n">
-        <v>1.56</v>
+        <v>1.32</v>
       </c>
       <c r="P17" t="n">
-        <v>1.49</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.68</v>
+        <v>1.96</v>
       </c>
       <c r="R17" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="S17" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="T17" t="n">
-        <v>2.18</v>
+        <v>1.9</v>
       </c>
       <c r="U17" t="n">
-        <v>1.72</v>
+        <v>2.04</v>
       </c>
       <c r="V17" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="W17" t="n">
-        <v>1.72</v>
+        <v>2.24</v>
       </c>
       <c r="X17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC17" t="n">
         <v>9</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>30</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>130</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>7.4</v>
       </c>
       <c r="AD17" t="n">
         <v>19</v>
       </c>
       <c r="AE17" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AF17" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>12.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH17" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AI17" t="n">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="AJ17" t="n">
-        <v>34</v>
+        <v>18.5</v>
       </c>
       <c r="AK17" t="n">
-        <v>34</v>
+        <v>18.5</v>
       </c>
       <c r="AL17" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>80</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AS17" t="n">
         <v>65</v>
       </c>
-      <c r="AM17" t="n">
-        <v>240</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>34</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>140</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AQ17" t="n">
+      <c r="AT17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY17" t="n">
         <v>9.4</v>
       </c>
-      <c r="AR17" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AX17" t="n">
+      <c r="AZ17" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>65</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>100</v>
+      </c>
+      <c r="BF17" t="n">
         <v>10.5</v>
       </c>
-      <c r="AY17" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>9</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BG17" t="n">
-        <v>9.199999999999999</v>
+        <v>65</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-06 07:21:25</t>
+          <t>2026-05-06 09:33:28</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,184 +3847,184 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>LDU</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="G18" t="n">
-        <v>1.58</v>
+        <v>1.84</v>
       </c>
       <c r="H18" t="n">
-        <v>7.2</v>
+        <v>5.1</v>
       </c>
       <c r="I18" t="n">
-        <v>8.800000000000001</v>
+        <v>5.2</v>
       </c>
       <c r="J18" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="K18" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="L18" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="M18" t="n">
         <v>1.08</v>
       </c>
       <c r="N18" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="O18" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P18" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="Q18" t="n">
         <v>2.08</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S18" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="T18" t="n">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="U18" t="n">
-        <v>1.73</v>
+        <v>1.97</v>
       </c>
       <c r="V18" t="n">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="W18" t="n">
-        <v>2.72</v>
+        <v>2.18</v>
       </c>
       <c r="X18" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="Y18" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="Z18" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE18" t="n">
         <v>75</v>
       </c>
-      <c r="AA18" t="n">
-        <v>330</v>
-      </c>
-      <c r="AB18" t="n">
+      <c r="AF18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>90</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>32</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU18" t="n">
         <v>8</v>
       </c>
-      <c r="AC18" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>32</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>150</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>190</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>14</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>970</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>240</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>10</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>240</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>50</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>8.6</v>
-      </c>
       <c r="AV18" t="n">
-        <v>25</v>
+        <v>18.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="AX18" t="n">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY18" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ18" t="n">
-        <v>25</v>
+        <v>19.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>11.5</v>
+        <v>36</v>
       </c>
       <c r="BB18" t="n">
-        <v>11.5</v>
+        <v>18</v>
       </c>
       <c r="BC18" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BD18" t="n">
         <v>36</v>
       </c>
       <c r="BE18" t="n">
-        <v>10.5</v>
+        <v>42</v>
       </c>
       <c r="BF18" t="n">
-        <v>8.6</v>
+        <v>12</v>
       </c>
       <c r="BG18" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-06 07:21:25</t>
+          <t>2026-05-06 09:33:28</t>
         </is>
       </c>
     </row>
@@ -4041,129 +4041,129 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>CA Platense</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Universitario de Deportes</t>
+          <t>Penarol</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G19" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="H19" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="I19" t="n">
         <v>4.5</v>
       </c>
       <c r="J19" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="K19" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L19" t="n">
         <v>1.49</v>
       </c>
       <c r="M19" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N19" t="n">
-        <v>2.58</v>
+        <v>2.48</v>
       </c>
       <c r="O19" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="P19" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.52</v>
+        <v>2.68</v>
       </c>
       <c r="R19" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="S19" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="T19" t="n">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="U19" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="V19" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W19" t="n">
         <v>1.73</v>
       </c>
       <c r="X19" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Y19" t="n">
         <v>11.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AA19" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AB19" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AE19" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AF19" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG19" t="n">
         <v>12.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI19" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AJ19" t="n">
         <v>34</v>
       </c>
       <c r="AK19" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AL19" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AM19" t="n">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="AN19" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AO19" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="AP19" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AQ19" t="n">
         <v>9.4</v>
@@ -4172,53 +4172,53 @@
         <v>18</v>
       </c>
       <c r="AS19" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT19" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AU19" t="n">
         <v>6.2</v>
       </c>
       <c r="AV19" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX19" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY19" t="n">
         <v>10</v>
       </c>
       <c r="AZ19" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA19" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BB19" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BC19" t="n">
-        <v>21</v>
+        <v>7.6</v>
       </c>
       <c r="BD19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BE19" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BG19" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BF19" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>9</v>
-      </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-06 07:21:25</t>
+          <t>2026-05-06 09:33:28</t>
         </is>
       </c>
     </row>
@@ -4235,184 +4235,184 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Ind Medellin</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>LDU</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>4.3</v>
+        <v>1.54</v>
       </c>
       <c r="G20" t="n">
-        <v>5.1</v>
+        <v>1.59</v>
       </c>
       <c r="H20" t="n">
-        <v>1.97</v>
+        <v>7.2</v>
       </c>
       <c r="I20" t="n">
-        <v>2.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="K20" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="L20" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="M20" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="N20" t="n">
-        <v>2.96</v>
+        <v>3.35</v>
       </c>
       <c r="O20" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="P20" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="R20" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="S20" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="U20" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="V20" t="n">
-        <v>1.91</v>
+        <v>1.12</v>
       </c>
       <c r="W20" t="n">
-        <v>1.25</v>
+        <v>2.68</v>
       </c>
       <c r="X20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>75</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>330</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>160</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>190</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>240</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>240</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>50</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>25</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>25</v>
+      </c>
+      <c r="BA20" t="n">
         <v>11.5</v>
       </c>
-      <c r="Y20" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>26</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD20" t="n">
+      <c r="BB20" t="n">
         <v>11.5</v>
       </c>
-      <c r="AE20" t="n">
-        <v>26</v>
-      </c>
-      <c r="AF20" t="n">
+      <c r="BC20" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD20" t="n">
         <v>36</v>
       </c>
-      <c r="AG20" t="n">
-        <v>20</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>140</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>75</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>90</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>120</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>22</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>21</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>16</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BE20" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BF20" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BG20" t="n">
-        <v>15.5</v>
+        <v>10</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-06 07:21:25</t>
+          <t>2026-05-06 09:33:28</t>
         </is>
       </c>
     </row>
@@ -4429,184 +4429,572 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Coquimbo Unido</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Universitario de Deportes</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="X21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>9</v>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>2026-05-06 09:33:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Ind Medellin</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G22" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S22" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V22" t="n">
+        <v>2</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>23</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>40</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>160</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>85</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>95</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>140</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>19</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>19</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>28</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>2026-05-06 09:33:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
           <t>23:00:00</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>Junior FC Barranquilla</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Cerro Porteno</t>
         </is>
       </c>
-      <c r="F21" t="n">
+      <c r="F23" t="n">
         <v>1.04</v>
       </c>
-      <c r="G21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H21" t="n">
+      <c r="G23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H23" t="n">
         <v>1.04</v>
       </c>
-      <c r="I21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J21" t="n">
+      <c r="I23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J23" t="n">
         <v>1.04</v>
       </c>
-      <c r="K21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N21" t="n">
+      <c r="K23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N23" t="n">
         <v>1.26</v>
       </c>
-      <c r="O21" t="n">
+      <c r="O23" t="n">
         <v>1.43</v>
       </c>
-      <c r="P21" t="n">
+      <c r="P23" t="n">
         <v>1.25</v>
       </c>
-      <c r="Q21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R21" t="n">
+      <c r="Q23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R23" t="n">
         <v>1.18</v>
       </c>
-      <c r="S21" t="n">
+      <c r="S23" t="n">
         <v>1.02</v>
       </c>
-      <c r="T21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH21" t="inlineStr">
-        <is>
-          <t>2026-05-06 07:21:25</t>
+      <c r="T23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>2026-05-06 09:33:28</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH23"/>
+  <dimension ref="A1:BH30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,37 +757,37 @@
         </is>
       </c>
       <c r="F2" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J2" t="n">
         <v>2.34</v>
       </c>
-      <c r="G2" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="H2" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="I2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2.3</v>
-      </c>
       <c r="K2" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="L2" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="N2" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="O2" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="P2" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Q2" t="n">
         <v>3</v>
@@ -799,19 +799,19 @@
         <v>6</v>
       </c>
       <c r="T2" t="n">
-        <v>1.11</v>
+        <v>2.14</v>
       </c>
       <c r="U2" t="n">
-        <v>1.11</v>
+        <v>1.61</v>
       </c>
       <c r="V2" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="W2" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="X2" t="n">
-        <v>7.2</v>
+        <v>970</v>
       </c>
       <c r="Y2" t="n">
         <v>1000</v>
@@ -868,59 +868,59 @@
         <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-06 09:33:28</t>
+          <t>2026-05-06 11:46:30</t>
         </is>
       </c>
     </row>
@@ -999,10 +999,10 @@
         <v>1.11</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-06 09:33:28</t>
+          <t>2026-05-06 11:46:30</t>
         </is>
       </c>
     </row>
@@ -1178,13 +1178,13 @@
         <v>1.24</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.94</v>
+        <v>1.35</v>
       </c>
       <c r="R4" t="n">
         <v>1.12</v>
       </c>
       <c r="S4" t="n">
-        <v>1.95</v>
+        <v>1.35</v>
       </c>
       <c r="T4" t="n">
         <v>1.11</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-06 09:33:28</t>
+          <t>2026-05-06 11:46:30</t>
         </is>
       </c>
     </row>
@@ -1339,170 +1339,170 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.52</v>
+        <v>1.83</v>
       </c>
       <c r="G5" t="n">
         <v>1.94</v>
       </c>
       <c r="H5" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="I5" t="n">
-        <v>990</v>
+        <v>5.6</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1</v>
+        <v>3.35</v>
       </c>
       <c r="K5" t="n">
-        <v>950</v>
+        <v>4.7</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="N5" t="n">
-        <v>2.12</v>
+        <v>3.05</v>
       </c>
       <c r="O5" t="n">
         <v>1.31</v>
       </c>
       <c r="P5" t="n">
-        <v>1.48</v>
+        <v>1.83</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.31</v>
+        <v>1.85</v>
       </c>
       <c r="R5" t="n">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="S5" t="n">
         <v>1.05</v>
       </c>
       <c r="T5" t="n">
-        <v>1.11</v>
+        <v>1.79</v>
       </c>
       <c r="U5" t="n">
-        <v>1.11</v>
+        <v>1.97</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="W5" t="n">
         <v>2.06</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA5" t="n">
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE5" t="n">
         <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM5" t="n">
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.03</v>
+        <v>2.9</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>2.96</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.03</v>
+        <v>3</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>3.05</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>3</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-06 09:33:28</t>
+          <t>2026-05-06 11:46:30</t>
         </is>
       </c>
     </row>
@@ -1533,19 +1533,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="H6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="J6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K6" t="n">
         <v>950</v>
@@ -1557,7 +1557,7 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="O6" t="n">
         <v>1.01</v>
@@ -1572,7 +1572,7 @@
         <v>1.07</v>
       </c>
       <c r="S6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="T6" t="n">
         <v>1.01</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-06 09:33:28</t>
+          <t>2026-05-06 11:46:30</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G7" t="n">
         <v>200</v>
       </c>
       <c r="H7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I7" t="n">
         <v>200</v>
       </c>
       <c r="J7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K7" t="n">
-        <v>200</v>
+        <v>950</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -1751,7 +1751,7 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="O7" t="n">
         <v>1.01</v>
@@ -1760,7 +1760,7 @@
         <v>1.07</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R7" t="n">
         <v>1.07</v>
@@ -1835,52 +1835,52 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF7" t="n">
         <v>1.01</v>
@@ -1890,14 +1890,14 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-06 09:33:28</t>
+          <t>2026-05-06 11:46:30</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Finnish Ykkosliiga</t>
+          <t>Finnish Kakkonen</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1912,186 +1912,186 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>PK-35 RY</t>
+          <t>SJK Akatemia 2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Huima</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.78</v>
+        <v>1.04</v>
       </c>
       <c r="G8" t="n">
-        <v>1.85</v>
+        <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="I8" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="K8" t="n">
-        <v>4.2</v>
+        <v>950</v>
       </c>
       <c r="L8" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>3.55</v>
+        <v>1.25</v>
       </c>
       <c r="O8" t="n">
-        <v>1.33</v>
+        <v>1.09</v>
       </c>
       <c r="P8" t="n">
-        <v>1.89</v>
+        <v>1.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.96</v>
+        <v>1.09</v>
       </c>
       <c r="R8" t="n">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="S8" t="n">
-        <v>3.5</v>
+        <v>1.09</v>
       </c>
       <c r="T8" t="n">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="U8" t="n">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR8" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AS8" t="n">
-        <v>3.45</v>
+        <v>1.03</v>
       </c>
       <c r="AT8" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU8" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AV8" t="n">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="AX8" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AY8" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="BB8" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="BC8" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD8" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="BE8" t="n">
-        <v>3.45</v>
+        <v>1.03</v>
       </c>
       <c r="BF8" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-06 09:33:28</t>
+          <t>2026-05-06 11:46:30</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Finnish Ykkosliiga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,191 +2101,191 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FK Auda</t>
+          <t>PK-35 RY</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SC Grobina</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.4</v>
+        <v>1.78</v>
       </c>
       <c r="G9" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="H9" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="I9" t="n">
-        <v>990</v>
+        <v>5.5</v>
       </c>
       <c r="J9" t="n">
-        <v>2.72</v>
+        <v>3.7</v>
       </c>
       <c r="K9" t="n">
-        <v>70</v>
+        <v>4.2</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N9" t="n">
-        <v>1.24</v>
+        <v>3.55</v>
       </c>
       <c r="O9" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="P9" t="n">
-        <v>1.24</v>
+        <v>1.89</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.23</v>
+        <v>1.96</v>
       </c>
       <c r="R9" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="S9" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="V9" t="n">
         <v>1.22</v>
       </c>
-      <c r="T9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.03</v>
-      </c>
       <c r="W9" t="n">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="X9" t="n">
-        <v>85</v>
+        <v>16.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="Z9" t="n">
-        <v>430</v>
+        <v>48</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB9" t="n">
-        <v>34</v>
+        <v>9.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>25</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD9" t="n">
-        <v>240</v>
+        <v>24</v>
       </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AF9" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="AG9" t="n">
-        <v>26</v>
+        <v>11.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>260</v>
+        <v>24</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ9" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="AK9" t="n">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="AL9" t="n">
-        <v>480</v>
+        <v>44</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN9" t="n">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.3</v>
+        <v>10.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>8.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.32</v>
+        <v>5</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.32</v>
+        <v>5.4</v>
       </c>
       <c r="AT9" t="n">
-        <v>3.45</v>
+        <v>6.4</v>
       </c>
       <c r="AU9" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AV9" t="n">
         <v>16</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.32</v>
+        <v>5.2</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.26</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY9" t="n">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="AZ9" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.32</v>
+        <v>5.2</v>
       </c>
       <c r="BB9" t="n">
-        <v>8.199999999999999</v>
+        <v>4.4</v>
       </c>
       <c r="BC9" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF9" t="n">
         <v>9.6</v>
       </c>
-      <c r="BD9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>2.38</v>
-      </c>
       <c r="BG9" t="n">
-        <v>8.6</v>
+        <v>5.3</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-06 09:33:28</t>
+          <t>2026-05-06 11:46:30</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Turkish 1 Lig</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,191 +2295,191 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Corum Belediyespor</t>
+          <t>DHJ El Jadida</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Keciorengucu</t>
+          <t>HUSA Agadir</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.69</v>
+        <v>2.06</v>
       </c>
       <c r="G10" t="n">
-        <v>1.84</v>
+        <v>4</v>
       </c>
       <c r="H10" t="n">
-        <v>5</v>
+        <v>2.48</v>
       </c>
       <c r="I10" t="n">
-        <v>6.4</v>
+        <v>3.65</v>
       </c>
       <c r="J10" t="n">
-        <v>3.65</v>
+        <v>2.56</v>
       </c>
       <c r="K10" t="n">
-        <v>4.5</v>
+        <v>950</v>
       </c>
       <c r="L10" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>4.3</v>
+        <v>1.34</v>
       </c>
       <c r="O10" t="n">
-        <v>1.25</v>
+        <v>1.56</v>
       </c>
       <c r="P10" t="n">
-        <v>2.14</v>
+        <v>1.34</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.67</v>
+        <v>2.62</v>
       </c>
       <c r="R10" t="n">
-        <v>1.45</v>
+        <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="T10" t="n">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="U10" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="W10" t="n">
-        <v>2.18</v>
+        <v>1.4</v>
       </c>
       <c r="X10" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD10" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AE10" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AG10" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI10" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AL10" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM10" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AQ10" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT10" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AU10" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV10" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX10" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AY10" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AZ10" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB10" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC10" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="BD10" t="n">
         <v>1.03</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF10" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG10" t="n">
         <v>1.01</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-06 09:33:28</t>
+          <t>2026-05-06 11:46:30</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Polish I Liga</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,191 +2489,191 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>LKS Lodz</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ZED FC</t>
+          <t>Pogon Grodzisk Mazowiecki</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="G11" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="H11" t="n">
-        <v>5.9</v>
+        <v>4.8</v>
       </c>
       <c r="I11" t="n">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="J11" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="K11" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="L11" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="N11" t="n">
-        <v>2.66</v>
+        <v>4.6</v>
       </c>
       <c r="O11" t="n">
-        <v>1.54</v>
+        <v>1.22</v>
       </c>
       <c r="P11" t="n">
-        <v>1.58</v>
+        <v>2.24</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.54</v>
+        <v>1.64</v>
       </c>
       <c r="R11" t="n">
-        <v>1.2</v>
+        <v>1.49</v>
       </c>
       <c r="S11" t="n">
-        <v>5.5</v>
+        <v>2.62</v>
       </c>
       <c r="T11" t="n">
-        <v>2.36</v>
+        <v>1.68</v>
       </c>
       <c r="U11" t="n">
-        <v>1.65</v>
+        <v>2.18</v>
       </c>
       <c r="V11" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="W11" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="X11" t="n">
-        <v>8.800000000000001</v>
+        <v>26</v>
       </c>
       <c r="Y11" t="n">
-        <v>16.5</v>
+        <v>27</v>
       </c>
       <c r="Z11" t="n">
         <v>55</v>
       </c>
       <c r="AA11" t="n">
-        <v>220</v>
+        <v>140</v>
       </c>
       <c r="AB11" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AC11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX11" t="n">
         <v>8.6</v>
       </c>
-      <c r="AD11" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>130</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>9</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>160</v>
-      </c>
-      <c r="AJ11" t="n">
+      <c r="AY11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>40</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD11" t="n">
         <v>20</v>
       </c>
-      <c r="AK11" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>280</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>240</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>22</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>50</v>
-      </c>
       <c r="BE11" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="BF11" t="n">
-        <v>16.5</v>
+        <v>7.2</v>
       </c>
       <c r="BG11" t="n">
-        <v>11.5</v>
+        <v>38</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-06 09:33:28</t>
+          <t>2026-05-06 11:46:30</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Romanian Liga II</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,191 +2683,191 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>National Bank</t>
+          <t>CSA Steaua Bucuresti</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ismaily</t>
+          <t>ACS Sepsi OSK</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.98</v>
+        <v>1.04</v>
       </c>
       <c r="G12" t="n">
-        <v>2.14</v>
+        <v>1000</v>
       </c>
       <c r="H12" t="n">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="I12" t="n">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="K12" t="n">
-        <v>3.4</v>
+        <v>1000</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>2.7</v>
+        <v>1.25</v>
       </c>
       <c r="O12" t="n">
-        <v>1.49</v>
+        <v>1.29</v>
       </c>
       <c r="P12" t="n">
-        <v>1.57</v>
+        <v>1.24</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.48</v>
+        <v>1.29</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="S12" t="n">
-        <v>4.9</v>
+        <v>1.29</v>
       </c>
       <c r="T12" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="U12" t="n">
-        <v>1.77</v>
+        <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="X12" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AD12" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE12" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AG12" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH12" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI12" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AL12" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM12" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AQ12" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AR12" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AS12" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AT12" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AU12" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV12" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="AW12" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AX12" t="n">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AZ12" t="n">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA12" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="BB12" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="BC12" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="BD12" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="BE12" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="BF12" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG12" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-06 09:33:28</t>
+          <t>2026-05-06 11:46:30</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Turkish 1 Lig</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Al-Shabab (KSA)</t>
+          <t>Bodrum Belediyesi Bodrumspor</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>8.199999999999999</v>
+        <v>2.24</v>
       </c>
       <c r="G13" t="n">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="H13" t="n">
-        <v>1.34</v>
+        <v>3.15</v>
       </c>
       <c r="I13" t="n">
-        <v>1.4</v>
+        <v>3.95</v>
       </c>
       <c r="J13" t="n">
-        <v>5.8</v>
+        <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>6.8</v>
+        <v>4.3</v>
       </c>
       <c r="L13" t="n">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="N13" t="n">
-        <v>7</v>
+        <v>3.65</v>
       </c>
       <c r="O13" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="P13" t="n">
-        <v>3.1</v>
+        <v>1.91</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.39</v>
+        <v>1.91</v>
       </c>
       <c r="R13" t="n">
-        <v>1.89</v>
+        <v>1.35</v>
       </c>
       <c r="S13" t="n">
-        <v>1.85</v>
+        <v>3.3</v>
       </c>
       <c r="T13" t="n">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="U13" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="V13" t="n">
-        <v>3.5</v>
+        <v>1.35</v>
       </c>
       <c r="W13" t="n">
-        <v>1.11</v>
+        <v>1.66</v>
       </c>
       <c r="X13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS13" t="n">
         <v>42</v>
       </c>
-      <c r="Y13" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Z13" t="n">
+      <c r="AT13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>28</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ13" t="n">
         <v>12.5</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="BA13" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>22</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>27</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>60</v>
+      </c>
+      <c r="BF13" t="n">
         <v>13.5</v>
       </c>
-      <c r="AB13" t="n">
-        <v>46</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>16</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>110</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>34</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>27</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>270</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>120</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>100</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>7</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>8</v>
-      </c>
       <c r="BG13" t="n">
-        <v>3.05</v>
+        <v>26</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-06 09:33:28</t>
+          <t>2026-05-06 11:46:30</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,191 +3071,191 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>FK Auda</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>SC Grobina</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.04</v>
+        <v>1.5</v>
       </c>
       <c r="G14" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="H14" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="I14" t="n">
+        <v>8</v>
+      </c>
+      <c r="J14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K14" t="n">
+        <v>5</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="X14" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA14" t="n">
         <v>600</v>
       </c>
-      <c r="H14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I14" t="n">
-        <v>870</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="K14" t="n">
-        <v>950</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1000</v>
-      </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM14" t="n">
-        <v>1000</v>
+        <v>350</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-06 09:33:28</t>
+          <t>2026-05-06 11:46:30</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>Turkish 1 Lig</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,36 +3265,36 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Corum Belediyespor</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Shakhtar</t>
+          <t>Keciorengucu</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="G15" t="n">
-        <v>1.63</v>
+        <v>1.82</v>
       </c>
       <c r="H15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I15" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="J15" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K15" t="n">
         <v>4.5</v>
-      </c>
-      <c r="K15" t="n">
-        <v>4.6</v>
       </c>
       <c r="L15" t="n">
         <v>1.3</v>
@@ -3303,153 +3303,153 @@
         <v>1.05</v>
       </c>
       <c r="N15" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="O15" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P15" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="R15" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="S15" t="n">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="T15" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="U15" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="V15" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="W15" t="n">
-        <v>2.58</v>
+        <v>2.22</v>
       </c>
       <c r="X15" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="Y15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z15" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AA15" t="n">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="AB15" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AD15" t="n">
         <v>24</v>
       </c>
       <c r="AE15" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AF15" t="n">
-        <v>9.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="AG15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AH15" t="n">
         <v>22</v>
       </c>
       <c r="AI15" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ15" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AK15" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AL15" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM15" t="n">
         <v>110</v>
       </c>
       <c r="AN15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>80</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY15" t="n">
         <v>8</v>
       </c>
-      <c r="AO15" t="n">
-        <v>90</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>20</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>44</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>17</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>65</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>9.4</v>
-      </c>
       <c r="AZ15" t="n">
-        <v>19.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>65</v>
+        <v>1.01</v>
       </c>
       <c r="BB15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BC15" t="n">
         <v>13</v>
       </c>
-      <c r="BC15" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BD15" t="n">
-        <v>30</v>
+        <v>1.03</v>
       </c>
       <c r="BE15" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BF15" t="n">
         <v>7.2</v>
       </c>
       <c r="BG15" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-06 09:33:28</t>
+          <t>2026-05-06 11:46:30</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,191 +3459,191 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>ZED FC</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="G16" t="n">
-        <v>1.96</v>
+        <v>1.78</v>
       </c>
       <c r="H16" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="I16" t="n">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="J16" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K16" t="n">
         <v>3.8</v>
       </c>
-      <c r="K16" t="n">
-        <v>3.9</v>
-      </c>
       <c r="L16" t="n">
-        <v>1.34</v>
+        <v>1.47</v>
       </c>
       <c r="M16" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="N16" t="n">
-        <v>3.95</v>
+        <v>2.68</v>
       </c>
       <c r="O16" t="n">
-        <v>1.31</v>
+        <v>1.54</v>
       </c>
       <c r="P16" t="n">
-        <v>2.02</v>
+        <v>1.58</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.91</v>
+        <v>2.56</v>
       </c>
       <c r="R16" t="n">
-        <v>1.39</v>
+        <v>1.2</v>
       </c>
       <c r="S16" t="n">
-        <v>3.35</v>
+        <v>5.4</v>
       </c>
       <c r="T16" t="n">
-        <v>1.81</v>
+        <v>2.4</v>
       </c>
       <c r="U16" t="n">
-        <v>2.16</v>
+        <v>1.62</v>
       </c>
       <c r="V16" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="W16" t="n">
-        <v>2.04</v>
+        <v>2.26</v>
       </c>
       <c r="X16" t="n">
-        <v>15</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y16" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="AA16" t="n">
-        <v>110</v>
+        <v>230</v>
       </c>
       <c r="AB16" t="n">
-        <v>9.800000000000001</v>
+        <v>6</v>
       </c>
       <c r="AC16" t="n">
         <v>8.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>17.5</v>
+        <v>27</v>
       </c>
       <c r="AE16" t="n">
-        <v>55</v>
+        <v>140</v>
       </c>
       <c r="AF16" t="n">
-        <v>12</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG16" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH16" t="n">
-        <v>18.5</v>
+        <v>32</v>
       </c>
       <c r="AI16" t="n">
-        <v>60</v>
+        <v>160</v>
       </c>
       <c r="AJ16" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AK16" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AL16" t="n">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="AM16" t="n">
-        <v>100</v>
+        <v>280</v>
       </c>
       <c r="AN16" t="n">
+        <v>19</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>260</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AQ16" t="n">
         <v>13</v>
       </c>
-      <c r="AO16" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP16" t="n">
+      <c r="AR16" t="n">
+        <v>42</v>
+      </c>
+      <c r="AS16" t="n">
         <v>13.5</v>
       </c>
-      <c r="AQ16" t="n">
+      <c r="AT16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW16" t="n">
         <v>14</v>
       </c>
-      <c r="AR16" t="n">
-        <v>29</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>15</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU16" t="n">
+      <c r="AX16" t="n">
         <v>8</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>46</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>11</v>
       </c>
       <c r="AY16" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ16" t="n">
-        <v>17</v>
+        <v>10.5</v>
       </c>
       <c r="BA16" t="n">
+        <v>14</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD16" t="n">
         <v>50</v>
       </c>
-      <c r="BB16" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>30</v>
-      </c>
       <c r="BE16" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BF16" t="n">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>42</v>
+        <v>13.5</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-06 09:33:28</t>
+          <t>2026-05-06 11:46:30</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,150 +3653,150 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>National Bank</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Nottm Forest</t>
+          <t>Ismaily</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.79</v>
+        <v>1.98</v>
       </c>
       <c r="G17" t="n">
-        <v>1.8</v>
+        <v>2.14</v>
       </c>
       <c r="H17" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="I17" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J17" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="K17" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="L17" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="N17" t="n">
-        <v>3.95</v>
+        <v>2.7</v>
       </c>
       <c r="O17" t="n">
-        <v>1.32</v>
+        <v>1.49</v>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>1.56</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.96</v>
+        <v>2.48</v>
       </c>
       <c r="R17" t="n">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="S17" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="T17" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="U17" t="n">
-        <v>2.04</v>
+        <v>1.76</v>
       </c>
       <c r="V17" t="n">
         <v>1.24</v>
       </c>
       <c r="W17" t="n">
-        <v>2.24</v>
+        <v>1.87</v>
       </c>
       <c r="X17" t="n">
-        <v>15.5</v>
+        <v>11</v>
       </c>
       <c r="Y17" t="n">
-        <v>17</v>
+        <v>13.5</v>
       </c>
       <c r="Z17" t="n">
         <v>36</v>
       </c>
       <c r="AA17" t="n">
+        <v>140</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI17" t="n">
         <v>120</v>
       </c>
-      <c r="AB17" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF17" t="n">
+      <c r="AJ17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>26</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>140</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ17" t="n">
         <v>10.5</v>
       </c>
-      <c r="AG17" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>80</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>16</v>
-      </c>
       <c r="AR17" t="n">
-        <v>32</v>
+        <v>6.6</v>
       </c>
       <c r="AS17" t="n">
-        <v>65</v>
+        <v>7.6</v>
       </c>
       <c r="AT17" t="n">
-        <v>8.199999999999999</v>
+        <v>5.9</v>
       </c>
       <c r="AU17" t="n">
-        <v>8.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AW17" t="n">
-        <v>50</v>
+        <v>7.4</v>
       </c>
       <c r="AX17" t="n">
         <v>9.800000000000001</v>
@@ -3805,39 +3805,39 @@
         <v>9.4</v>
       </c>
       <c r="AZ17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA17" t="n">
-        <v>65</v>
+        <v>7.6</v>
       </c>
       <c r="BB17" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BC17" t="n">
-        <v>17.5</v>
+        <v>6.4</v>
       </c>
       <c r="BD17" t="n">
-        <v>32</v>
+        <v>7.2</v>
       </c>
       <c r="BE17" t="n">
-        <v>100</v>
+        <v>7.8</v>
       </c>
       <c r="BF17" t="n">
-        <v>10.5</v>
+        <v>21</v>
       </c>
       <c r="BG17" t="n">
-        <v>65</v>
+        <v>7.6</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-06 09:33:28</t>
+          <t>2026-05-06 11:46:30</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,191 +3847,191 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Union de Touarga</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.83</v>
+        <v>1.04</v>
       </c>
       <c r="G18" t="n">
-        <v>1.84</v>
+        <v>1000</v>
       </c>
       <c r="H18" t="n">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="I18" t="n">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="J18" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="K18" t="n">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="L18" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>3.65</v>
+        <v>1.25</v>
       </c>
       <c r="O18" t="n">
         <v>1.36</v>
       </c>
       <c r="P18" t="n">
-        <v>1.87</v>
+        <v>1.24</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.08</v>
+        <v>1.36</v>
       </c>
       <c r="R18" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="S18" t="n">
-        <v>3.85</v>
+        <v>1.36</v>
       </c>
       <c r="T18" t="n">
-        <v>1.97</v>
+        <v>1.01</v>
       </c>
       <c r="U18" t="n">
-        <v>1.97</v>
+        <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="X18" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Z18" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AA18" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AC18" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD18" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AE18" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AG18" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AH18" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI18" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AL18" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM18" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AO18" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AQ18" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AR18" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="AS18" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AT18" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU18" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AV18" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW18" t="n">
-        <v>60</v>
+        <v>1.01</v>
       </c>
       <c r="AX18" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY18" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ18" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA18" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BB18" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BC18" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BD18" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BE18" t="n">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BF18" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BG18" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-06 09:33:28</t>
+          <t>2026-05-06 11:46:30</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,191 +4041,191 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CA Platense</t>
+          <t>Al-Shabab (KSA)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Penarol</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.16</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>2.38</v>
+        <v>10</v>
       </c>
       <c r="H19" t="n">
-        <v>3.9</v>
+        <v>1.33</v>
       </c>
       <c r="I19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J19" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K19" t="n">
+        <v>7</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="P19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="V19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X19" t="n">
+        <v>48</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>55</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>110</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>36</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>28</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>300</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>130</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>95</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>110</v>
+      </c>
+      <c r="AO19" t="n">
         <v>4.5</v>
       </c>
-      <c r="J19" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="K19" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="N19" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S19" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="X19" t="n">
-        <v>9</v>
-      </c>
-      <c r="Y19" t="n">
+      <c r="AP19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW19" t="n">
         <v>11.5</v>
       </c>
-      <c r="Z19" t="n">
-        <v>30</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>130</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD19" t="n">
+      <c r="AX19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AZ19" t="n">
         <v>19</v>
       </c>
-      <c r="AE19" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>240</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>34</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>140</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>20</v>
-      </c>
       <c r="BA19" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="BB19" t="n">
-        <v>7.6</v>
+        <v>5.3</v>
       </c>
       <c r="BC19" t="n">
-        <v>7.6</v>
+        <v>5.2</v>
       </c>
       <c r="BD19" t="n">
-        <v>8.6</v>
+        <v>5.1</v>
       </c>
       <c r="BE19" t="n">
-        <v>9.4</v>
+        <v>5.1</v>
       </c>
       <c r="BF19" t="n">
-        <v>7.6</v>
+        <v>5.1</v>
       </c>
       <c r="BG19" t="n">
-        <v>9.199999999999999</v>
+        <v>3</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-06 09:33:28</t>
+          <t>2026-05-06 11:46:30</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,191 +4235,191 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>LDU</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.54</v>
+        <v>1.04</v>
       </c>
       <c r="G20" t="n">
-        <v>1.59</v>
+        <v>600</v>
       </c>
       <c r="H20" t="n">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="I20" t="n">
-        <v>8.800000000000001</v>
+        <v>870</v>
       </c>
       <c r="J20" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="K20" t="n">
-        <v>4.5</v>
+        <v>950</v>
       </c>
       <c r="L20" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="M20" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>3.35</v>
+        <v>1.1</v>
       </c>
       <c r="O20" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="P20" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="S20" t="n">
-        <v>3.9</v>
+        <v>1.05</v>
       </c>
       <c r="T20" t="n">
-        <v>2.2</v>
+        <v>1.11</v>
       </c>
       <c r="U20" t="n">
-        <v>1.73</v>
+        <v>1.11</v>
       </c>
       <c r="V20" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>2.68</v>
+        <v>1.01</v>
       </c>
       <c r="X20" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Y20" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Z20" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AA20" t="n">
-        <v>330</v>
+        <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AC20" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD20" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AE20" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AF20" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AG20" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH20" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AI20" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AJ20" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AK20" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AL20" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM20" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AO20" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AQ20" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR20" t="n">
-        <v>50</v>
+        <v>1.03</v>
       </c>
       <c r="AS20" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AT20" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AU20" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AV20" t="n">
-        <v>25</v>
+        <v>1.03</v>
       </c>
       <c r="AW20" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AX20" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AY20" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AZ20" t="n">
-        <v>25</v>
+        <v>1.03</v>
       </c>
       <c r="BA20" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="BB20" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC20" t="n">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="BD20" t="n">
-        <v>36</v>
+        <v>1.03</v>
       </c>
       <c r="BE20" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="BF20" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG20" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-06 09:33:28</t>
+          <t>2026-05-06 11:46:30</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,191 +4429,191 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Universitario de Deportes</t>
+          <t>Shakhtar</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.14</v>
+        <v>1.6</v>
       </c>
       <c r="G21" t="n">
-        <v>2.42</v>
+        <v>1.63</v>
       </c>
       <c r="H21" t="n">
-        <v>3.8</v>
+        <v>6</v>
       </c>
       <c r="I21" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J21" t="n">
         <v>4.5</v>
       </c>
-      <c r="J21" t="n">
-        <v>2.98</v>
-      </c>
       <c r="K21" t="n">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="L21" t="n">
-        <v>1.49</v>
+        <v>1.28</v>
       </c>
       <c r="M21" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="N21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W21" t="n">
         <v>2.6</v>
       </c>
-      <c r="O21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S21" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.73</v>
-      </c>
       <c r="X21" t="n">
-        <v>9.199999999999999</v>
+        <v>19</v>
       </c>
       <c r="Y21" t="n">
-        <v>11.5</v>
+        <v>22</v>
       </c>
       <c r="Z21" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>200</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>42</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>65</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>17</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD21" t="n">
         <v>29</v>
       </c>
-      <c r="AA21" t="n">
-        <v>120</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD21" t="n">
+      <c r="BE21" t="n">
         <v>18.5</v>
       </c>
-      <c r="AE21" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>32</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>120</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BF21" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BG21" t="n">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-06 09:33:28</t>
+          <t>2026-05-06 11:46:30</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4623,378 +4623,1736 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Ind Medellin</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>4.8</v>
+        <v>1.94</v>
       </c>
       <c r="G22" t="n">
-        <v>5.6</v>
+        <v>1.96</v>
       </c>
       <c r="H22" t="n">
-        <v>1.84</v>
+        <v>4.4</v>
       </c>
       <c r="I22" t="n">
-        <v>1.99</v>
+        <v>4.5</v>
       </c>
       <c r="J22" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="K22" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L22" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="M22" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="N22" t="n">
-        <v>3</v>
+        <v>3.95</v>
       </c>
       <c r="O22" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="P22" t="n">
-        <v>1.68</v>
+        <v>2.02</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.26</v>
+        <v>1.9</v>
       </c>
       <c r="R22" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="S22" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="T22" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W22" t="n">
         <v>2.04</v>
       </c>
-      <c r="U22" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="V22" t="n">
-        <v>2</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.22</v>
-      </c>
       <c r="X22" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>29</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>46</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>50</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BF22" t="n">
         <v>11.5</v>
       </c>
-      <c r="Y22" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>11</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>23</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>15</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>26</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>40</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>22</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>160</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>85</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>95</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>140</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>19</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>19</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>28</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BG22" t="n">
-        <v>15.5</v>
+        <v>42</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-06 09:33:28</t>
+          <t>2026-05-06 11:46:30</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>UEFA Europa League</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Nottm Forest</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H23" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I23" t="n">
+        <v>5</v>
+      </c>
+      <c r="J23" t="n">
+        <v>4</v>
+      </c>
+      <c r="K23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N23" t="n">
+        <v>4</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W23" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="X23" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>32</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>65</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>50</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>60</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>100</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>65</v>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>2026-05-06 11:46:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>UEFA Europa League</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H24" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="X24" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>90</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>32</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>60</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>55</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>60</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>12</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>70</v>
+      </c>
+      <c r="BH24" t="inlineStr">
+        <is>
+          <t>2026-05-06 11:46:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Moroccan Botola Pro 1</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>FAR Rabat</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Olympic Safi</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="H25" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="I25" t="n">
+        <v>16</v>
+      </c>
+      <c r="J25" t="n">
+        <v>4</v>
+      </c>
+      <c r="K25" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W25" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="X25" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>34</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>60</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>46</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH25" t="inlineStr">
+        <is>
+          <t>2026-05-06 11:46:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>CONMEBOL Copa Libertadores</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>CA Platense</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Penarol</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="X26" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>240</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>140</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>27</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BH26" t="inlineStr">
+        <is>
+          <t>2026-05-06 11:46:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Mirassol</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>LDU</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="H27" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="I27" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J27" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W27" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="X27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>320</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>160</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>190</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>240</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>240</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>25</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>25</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>9</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>10</v>
+      </c>
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t>2026-05-06 11:46:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Coquimbo Unido</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Universitario de Deportes</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I28" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="X28" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t>2026-05-06 11:46:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Ind Medellin</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G29" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N29" t="n">
+        <v>3</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S29" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V29" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X29" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>23</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>40</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>160</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>85</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>95</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>140</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>19</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>28</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BH29" t="inlineStr">
+        <is>
+          <t>2026-05-06 11:46:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
         <is>
           <t>23:00:00</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>Junior FC Barranquilla</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Cerro Porteno</t>
         </is>
       </c>
-      <c r="F23" t="n">
+      <c r="F30" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J30" t="n">
         <v>1.04</v>
       </c>
-      <c r="G23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N23" t="n">
+      <c r="K30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N30" t="n">
         <v>1.26</v>
       </c>
-      <c r="O23" t="n">
+      <c r="O30" t="n">
         <v>1.43</v>
       </c>
-      <c r="P23" t="n">
+      <c r="P30" t="n">
         <v>1.25</v>
       </c>
-      <c r="Q23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R23" t="n">
+      <c r="Q30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R30" t="n">
         <v>1.18</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S30" t="n">
         <v>1.02</v>
       </c>
-      <c r="T23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH23" t="inlineStr">
-        <is>
-          <t>2026-05-06 09:33:28</t>
+      <c r="T30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH30" t="inlineStr">
+        <is>
+          <t>2026-05-06 11:46:30</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-07.xlsx
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.44</v>
+        <v>2.54</v>
       </c>
       <c r="G2" t="n">
-        <v>3.1</v>
+        <v>2.82</v>
       </c>
       <c r="H2" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="I2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J2" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="K2" t="n">
-        <v>3.15</v>
+        <v>2.72</v>
       </c>
       <c r="L2" t="n">
         <v>1.69</v>
@@ -781,16 +781,16 @@
         <v>1.16</v>
       </c>
       <c r="N2" t="n">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="O2" t="n">
         <v>1.69</v>
       </c>
       <c r="P2" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R2" t="n">
         <v>1.12</v>
@@ -802,13 +802,13 @@
         <v>2.14</v>
       </c>
       <c r="U2" t="n">
-        <v>1.61</v>
+        <v>1.34</v>
       </c>
       <c r="V2" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="W2" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="X2" t="n">
         <v>970</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-06 11:46:30</t>
+          <t>2026-05-06 14:02:42</t>
         </is>
       </c>
     </row>
@@ -951,170 +951,170 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.09</v>
+        <v>3.6</v>
       </c>
       <c r="G3" t="n">
-        <v>990</v>
+        <v>4.1</v>
       </c>
       <c r="H3" t="n">
-        <v>1.09</v>
+        <v>2.26</v>
       </c>
       <c r="I3" t="n">
-        <v>990</v>
+        <v>2.54</v>
       </c>
       <c r="J3" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>6.8</v>
+        <v>3.4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N3" t="n">
-        <v>1.25</v>
+        <v>2.56</v>
       </c>
       <c r="O3" t="n">
-        <v>1.02</v>
+        <v>1.52</v>
       </c>
       <c r="P3" t="n">
-        <v>1.24</v>
+        <v>1.53</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="R3" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="S3" t="n">
-        <v>1.48</v>
+        <v>4.8</v>
       </c>
       <c r="T3" t="n">
-        <v>1.11</v>
+        <v>2.08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.11</v>
+        <v>1.76</v>
       </c>
       <c r="V3" t="n">
-        <v>1.04</v>
+        <v>1.64</v>
       </c>
       <c r="W3" t="n">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-06 11:46:30</t>
+          <t>2026-05-06 14:02:42</t>
         </is>
       </c>
     </row>
@@ -1145,94 +1145,94 @@
         </is>
       </c>
       <c r="F4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>27</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="J4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V4" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="W4" t="n">
         <v>1.04</v>
       </c>
-      <c r="G4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I4" t="n">
-        <v>990</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="K4" t="n">
-        <v>950</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.01</v>
-      </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AF4" t="n">
         <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AJ4" t="n">
         <v>1000</v>
@@ -1250,65 +1250,65 @@
         <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.03</v>
+        <v>1.67</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.03</v>
+        <v>1.65</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.03</v>
+        <v>2.42</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.03</v>
+        <v>2.44</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.03</v>
+        <v>1.68</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.03</v>
+        <v>1.68</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.03</v>
+        <v>1.68</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.03</v>
+        <v>1.68</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-06 11:46:30</t>
+          <t>2026-05-06 14:02:42</t>
         </is>
       </c>
     </row>
@@ -1339,58 +1339,58 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.83</v>
+        <v>1.61</v>
       </c>
       <c r="G5" t="n">
-        <v>1.94</v>
+        <v>1.74</v>
       </c>
       <c r="H5" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="I5" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="J5" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M5" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="O5" t="n">
         <v>1.31</v>
       </c>
       <c r="P5" t="n">
-        <v>1.83</v>
+        <v>2.04</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="R5" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="S5" t="n">
-        <v>1.05</v>
+        <v>3.1</v>
       </c>
       <c r="T5" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="U5" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="V5" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="W5" t="n">
-        <v>2.06</v>
+        <v>2.34</v>
       </c>
       <c r="X5" t="n">
         <v>970</v>
@@ -1399,7 +1399,7 @@
         <v>970</v>
       </c>
       <c r="Z5" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AA5" t="n">
         <v>1000</v>
@@ -1408,101 +1408,101 @@
         <v>970</v>
       </c>
       <c r="AC5" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AD5" t="n">
         <v>21</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AF5" t="n">
         <v>970</v>
       </c>
       <c r="AG5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>970</v>
       </c>
-      <c r="AH5" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>26</v>
-      </c>
       <c r="AK5" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="AL5" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN5" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP5" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2.9</v>
+        <v>5.3</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AS5" t="n">
-        <v>3.35</v>
+        <v>2.98</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.45</v>
+        <v>8.6</v>
       </c>
       <c r="AV5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE5" t="n">
         <v>2.96</v>
       </c>
-      <c r="AW5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>3</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>3</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>3.35</v>
-      </c>
       <c r="BF5" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.3</v>
+        <v>2.94</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-06 11:46:30</t>
+          <t>2026-05-06 14:02:42</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1545,7 @@
         <v>250</v>
       </c>
       <c r="J6" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K6" t="n">
         <v>950</v>
@@ -1557,7 +1557,7 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="O6" t="n">
         <v>1.01</v>
@@ -1572,7 +1572,7 @@
         <v>1.07</v>
       </c>
       <c r="S6" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="T6" t="n">
         <v>1.01</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-06 11:46:30</t>
+          <t>2026-05-06 14:02:42</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
         <v>1.02</v>
       </c>
       <c r="G7" t="n">
-        <v>200</v>
+        <v>610</v>
       </c>
       <c r="H7" t="n">
         <v>1.02</v>
@@ -1739,7 +1739,7 @@
         <v>200</v>
       </c>
       <c r="J7" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K7" t="n">
         <v>950</v>
@@ -1751,7 +1751,7 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="O7" t="n">
         <v>1.01</v>
@@ -1760,7 +1760,7 @@
         <v>1.07</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R7" t="n">
         <v>1.07</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-06 11:46:30</t>
+          <t>2026-05-06 14:02:42</t>
         </is>
       </c>
     </row>
@@ -1924,16 +1924,16 @@
         <v>1.04</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H8" t="n">
         <v>1.04</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K8" t="n">
         <v>950</v>
@@ -1945,7 +1945,7 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O8" t="n">
         <v>1.09</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-06 11:46:30</t>
+          <t>2026-05-06 14:02:42</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
         <v>1.78</v>
       </c>
       <c r="G9" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="H9" t="n">
         <v>5</v>
@@ -2127,52 +2127,52 @@
         <v>5.5</v>
       </c>
       <c r="J9" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="K9" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M9" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="O9" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="P9" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="R9" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="S9" t="n">
         <v>3.55</v>
       </c>
       <c r="T9" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="U9" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="V9" t="n">
         <v>1.22</v>
       </c>
       <c r="W9" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="X9" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Z9" t="n">
         <v>48</v>
@@ -2181,7 +2181,7 @@
         <v>160</v>
       </c>
       <c r="AB9" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AC9" t="n">
         <v>9.800000000000001</v>
@@ -2229,10 +2229,10 @@
         <v>13</v>
       </c>
       <c r="AR9" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AT9" t="n">
         <v>6.4</v>
@@ -2244,7 +2244,7 @@
         <v>16</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AX9" t="n">
         <v>8.199999999999999</v>
@@ -2256,29 +2256,29 @@
         <v>15.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BC9" t="n">
         <v>15</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BF9" t="n">
-        <v>9.6</v>
+        <v>4.1</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-06 11:46:30</t>
+          <t>2026-05-06 14:02:42</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.06</v>
+        <v>3</v>
       </c>
       <c r="G10" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="H10" t="n">
-        <v>2.48</v>
+        <v>2.88</v>
       </c>
       <c r="I10" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="J10" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="K10" t="n">
-        <v>950</v>
+        <v>3.1</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2333,13 +2333,13 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.34</v>
+        <v>2.22</v>
       </c>
       <c r="O10" t="n">
         <v>1.56</v>
       </c>
       <c r="P10" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="Q10" t="n">
         <v>2.62</v>
@@ -2357,10 +2357,10 @@
         <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="W10" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-06 11:46:30</t>
+          <t>2026-05-06 14:02:42</t>
         </is>
       </c>
     </row>
@@ -2503,13 +2503,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="G11" t="n">
         <v>1.79</v>
       </c>
       <c r="H11" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="I11" t="n">
         <v>5.7</v>
@@ -2533,19 +2533,19 @@
         <v>1.22</v>
       </c>
       <c r="P11" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q11" t="n">
         <v>1.64</v>
       </c>
       <c r="R11" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S11" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="T11" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="U11" t="n">
         <v>2.18</v>
@@ -2560,7 +2560,7 @@
         <v>26</v>
       </c>
       <c r="Y11" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="Z11" t="n">
         <v>55</v>
@@ -2572,16 +2572,16 @@
         <v>13</v>
       </c>
       <c r="AC11" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AD11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE11" t="n">
         <v>75</v>
       </c>
       <c r="AF11" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG11" t="n">
         <v>12</v>
@@ -2593,7 +2593,7 @@
         <v>70</v>
       </c>
       <c r="AJ11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK11" t="n">
         <v>21</v>
@@ -2602,7 +2602,7 @@
         <v>40</v>
       </c>
       <c r="AM11" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN11" t="n">
         <v>10</v>
@@ -2617,25 +2617,25 @@
         <v>15.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AT11" t="n">
-        <v>7.8</v>
+        <v>3.6</v>
       </c>
       <c r="AU11" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV11" t="n">
         <v>14.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AX11" t="n">
-        <v>8.6</v>
+        <v>3.65</v>
       </c>
       <c r="AY11" t="n">
         <v>8.6</v>
@@ -2656,17 +2656,17 @@
         <v>20</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BF11" t="n">
         <v>7.2</v>
       </c>
       <c r="BG11" t="n">
-        <v>38</v>
+        <v>4.6</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-06 11:46:30</t>
+          <t>2026-05-06 14:02:42</t>
         </is>
       </c>
     </row>
@@ -2700,19 +2700,19 @@
         <v>1.04</v>
       </c>
       <c r="G12" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H12" t="n">
         <v>1.04</v>
       </c>
       <c r="I12" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K12" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -2736,7 +2736,7 @@
         <v>1.15</v>
       </c>
       <c r="S12" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T12" t="n">
         <v>1.01</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-06 11:46:30</t>
+          <t>2026-05-06 14:02:42</t>
         </is>
       </c>
     </row>
@@ -2894,10 +2894,10 @@
         <v>2.24</v>
       </c>
       <c r="G13" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="H13" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I13" t="n">
         <v>3.95</v>
@@ -2906,10 +2906,10 @@
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M13" t="n">
         <v>1.07</v>
@@ -2924,16 +2924,16 @@
         <v>1.91</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="R13" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S13" t="n">
         <v>3.3</v>
       </c>
       <c r="T13" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="U13" t="n">
         <v>2.1</v>
@@ -2942,10 +2942,10 @@
         <v>1.35</v>
       </c>
       <c r="W13" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="X13" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Y13" t="n">
         <v>16</v>
@@ -3008,7 +3008,7 @@
         <v>17.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="AT13" t="n">
         <v>7.6</v>
@@ -3020,7 +3020,7 @@
         <v>10.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="AX13" t="n">
         <v>11</v>
@@ -3032,29 +3032,29 @@
         <v>12.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BB13" t="n">
-        <v>22</v>
+        <v>1.03</v>
       </c>
       <c r="BC13" t="n">
         <v>18</v>
       </c>
       <c r="BD13" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BE13" t="n">
-        <v>60</v>
+        <v>1.01</v>
       </c>
       <c r="BF13" t="n">
         <v>13.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-06 11:46:30</t>
+          <t>2026-05-06 14:02:42</t>
         </is>
       </c>
     </row>
@@ -3118,13 +3118,13 @@
         <v>1.95</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="R14" t="n">
         <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="T14" t="n">
         <v>1.84</v>
@@ -3139,7 +3139,7 @@
         <v>2.68</v>
       </c>
       <c r="X14" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Y14" t="n">
         <v>25</v>
@@ -3181,7 +3181,7 @@
         <v>17</v>
       </c>
       <c r="AL14" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM14" t="n">
         <v>350</v>
@@ -3196,13 +3196,13 @@
         <v>5.7</v>
       </c>
       <c r="AQ14" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AR14" t="n">
         <v>7.2</v>
       </c>
       <c r="AS14" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT14" t="n">
         <v>7.2</v>
@@ -3211,7 +3211,7 @@
         <v>8.4</v>
       </c>
       <c r="AV14" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AW14" t="n">
         <v>7.6</v>
@@ -3226,7 +3226,7 @@
         <v>6</v>
       </c>
       <c r="BA14" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB14" t="n">
         <v>12</v>
@@ -3235,20 +3235,20 @@
         <v>13.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BE14" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF14" t="n">
         <v>4.2</v>
       </c>
       <c r="BG14" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-06 11:46:30</t>
+          <t>2026-05-06 14:02:42</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3282,7 @@
         <v>1.69</v>
       </c>
       <c r="G15" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="H15" t="n">
         <v>5</v>
@@ -3318,7 +3318,7 @@
         <v>1.45</v>
       </c>
       <c r="S15" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="T15" t="n">
         <v>1.75</v>
@@ -3357,7 +3357,7 @@
         <v>75</v>
       </c>
       <c r="AF15" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AG15" t="n">
         <v>12</v>
@@ -3399,7 +3399,7 @@
         <v>1.01</v>
       </c>
       <c r="AT15" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU15" t="n">
         <v>7.4</v>
@@ -3414,10 +3414,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AY15" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AZ15" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA15" t="n">
         <v>1.01</v>
@@ -3435,14 +3435,14 @@
         <v>1.01</v>
       </c>
       <c r="BF15" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BG15" t="n">
         <v>1.01</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-06 11:46:30</t>
+          <t>2026-05-06 14:02:42</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
         <v>1.75</v>
       </c>
       <c r="G16" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="H16" t="n">
         <v>6</v>
@@ -3488,34 +3488,34 @@
         <v>3.55</v>
       </c>
       <c r="K16" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L16" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M16" t="n">
         <v>1.12</v>
       </c>
       <c r="N16" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="O16" t="n">
         <v>1.54</v>
       </c>
       <c r="P16" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="R16" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S16" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="T16" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="U16" t="n">
         <v>1.62</v>
@@ -3527,7 +3527,7 @@
         <v>2.26</v>
       </c>
       <c r="X16" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="Y16" t="n">
         <v>16.5</v>
@@ -3539,13 +3539,13 @@
         <v>230</v>
       </c>
       <c r="AB16" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AC16" t="n">
         <v>8.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE16" t="n">
         <v>140</v>
@@ -3560,28 +3560,28 @@
         <v>32</v>
       </c>
       <c r="AI16" t="n">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="AJ16" t="n">
         <v>19</v>
       </c>
       <c r="AK16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL16" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AM16" t="n">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="AN16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO16" t="n">
         <v>260</v>
       </c>
       <c r="AP16" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AQ16" t="n">
         <v>13</v>
@@ -3590,7 +3590,7 @@
         <v>42</v>
       </c>
       <c r="AS16" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AT16" t="n">
         <v>5.5</v>
@@ -3602,7 +3602,7 @@
         <v>21</v>
       </c>
       <c r="AW16" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AX16" t="n">
         <v>8</v>
@@ -3614,7 +3614,7 @@
         <v>10.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BB16" t="n">
         <v>15.5</v>
@@ -3626,17 +3626,17 @@
         <v>50</v>
       </c>
       <c r="BE16" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BF16" t="n">
         <v>15.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-06 11:46:30</t>
+          <t>2026-05-06 14:02:42</t>
         </is>
       </c>
     </row>
@@ -3667,16 +3667,16 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="G17" t="n">
         <v>2.14</v>
       </c>
       <c r="H17" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="I17" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J17" t="n">
         <v>3.1</v>
@@ -3718,7 +3718,7 @@
         <v>1.24</v>
       </c>
       <c r="W17" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="X17" t="n">
         <v>11</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-06 11:46:30</t>
+          <t>2026-05-06 14:02:42</t>
         </is>
       </c>
     </row>
@@ -3864,19 +3864,19 @@
         <v>1.04</v>
       </c>
       <c r="G18" t="n">
-        <v>1000</v>
+        <v>1.57</v>
       </c>
       <c r="H18" t="n">
-        <v>1.04</v>
+        <v>2.84</v>
       </c>
       <c r="I18" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="J18" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="K18" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
@@ -3885,22 +3885,22 @@
         <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>1.25</v>
+        <v>1.97</v>
       </c>
       <c r="O18" t="n">
         <v>1.36</v>
       </c>
       <c r="P18" t="n">
-        <v>1.24</v>
+        <v>1.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.36</v>
+        <v>1.83</v>
       </c>
       <c r="R18" t="n">
         <v>1.18</v>
       </c>
       <c r="S18" t="n">
-        <v>1.36</v>
+        <v>1.83</v>
       </c>
       <c r="T18" t="n">
         <v>1.01</v>
@@ -3912,7 +3912,7 @@
         <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="X18" t="n">
         <v>1000</v>
@@ -3969,52 +3969,52 @@
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF18" t="n">
         <v>1.01</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-06 11:46:30</t>
+          <t>2026-05-06 14:02:42</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4064,7 @@
         <v>1.33</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="J19" t="n">
         <v>5.8</v>
@@ -4088,13 +4088,13 @@
         <v>3.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="R19" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="S19" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="T19" t="n">
         <v>1.67</v>
@@ -4103,7 +4103,7 @@
         <v>2.22</v>
       </c>
       <c r="V19" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="W19" t="n">
         <v>1.11</v>
@@ -4124,13 +4124,13 @@
         <v>55</v>
       </c>
       <c r="AC19" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AD19" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AE19" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AF19" t="n">
         <v>110</v>
@@ -4145,7 +4145,7 @@
         <v>28</v>
       </c>
       <c r="AJ19" t="n">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="AK19" t="n">
         <v>130</v>
@@ -4154,28 +4154,28 @@
         <v>95</v>
       </c>
       <c r="AM19" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN19" t="n">
         <v>100</v>
       </c>
-      <c r="AN19" t="n">
-        <v>110</v>
-      </c>
       <c r="AO19" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AP19" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AQ19" t="n">
         <v>13.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS19" t="n">
         <v>9.4</v>
       </c>
       <c r="AT19" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="AU19" t="n">
         <v>11</v>
@@ -4187,10 +4187,10 @@
         <v>11.5</v>
       </c>
       <c r="AX19" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="AY19" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="AZ19" t="n">
         <v>19</v>
@@ -4199,26 +4199,26 @@
         <v>19</v>
       </c>
       <c r="BB19" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BC19" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BD19" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BE19" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BF19" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BG19" t="n">
         <v>3</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-06 11:46:30</t>
+          <t>2026-05-06 14:02:42</t>
         </is>
       </c>
     </row>
@@ -4249,55 +4249,55 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.04</v>
+        <v>1.45</v>
       </c>
       <c r="G20" t="n">
-        <v>600</v>
+        <v>1.56</v>
       </c>
       <c r="H20" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="I20" t="n">
         <v>870</v>
       </c>
       <c r="J20" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="K20" t="n">
-        <v>950</v>
+        <v>50</v>
       </c>
       <c r="L20" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M20" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N20" t="n">
         <v>1.1</v>
       </c>
       <c r="O20" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="P20" t="n">
-        <v>1.9</v>
+        <v>1.24</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R20" t="n">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="S20" t="n">
         <v>1.05</v>
       </c>
       <c r="T20" t="n">
-        <v>1.11</v>
+        <v>2.2</v>
       </c>
       <c r="U20" t="n">
-        <v>1.11</v>
+        <v>1.67</v>
       </c>
       <c r="V20" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="W20" t="n">
         <v>1.01</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-06 11:46:30</t>
+          <t>2026-05-06 14:02:42</t>
         </is>
       </c>
     </row>
@@ -4446,10 +4446,10 @@
         <v>1.6</v>
       </c>
       <c r="G21" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="H21" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I21" t="n">
         <v>6.4</v>
@@ -4458,7 +4458,7 @@
         <v>4.5</v>
       </c>
       <c r="K21" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="L21" t="n">
         <v>1.28</v>
@@ -4470,25 +4470,25 @@
         <v>4.6</v>
       </c>
       <c r="O21" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P21" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="R21" t="n">
         <v>1.47</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="T21" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="U21" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="V21" t="n">
         <v>1.18</v>
@@ -4503,13 +4503,13 @@
         <v>22</v>
       </c>
       <c r="Z21" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AA21" t="n">
         <v>200</v>
       </c>
       <c r="AB21" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC21" t="n">
         <v>10.5</v>
@@ -4518,7 +4518,7 @@
         <v>23</v>
       </c>
       <c r="AE21" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AF21" t="n">
         <v>9.800000000000001</v>
@@ -4560,13 +4560,13 @@
         <v>42</v>
       </c>
       <c r="AS21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT21" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AU21" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV21" t="n">
         <v>21</v>
@@ -4578,13 +4578,13 @@
         <v>9</v>
       </c>
       <c r="AY21" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ21" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="BB21" t="n">
         <v>13</v>
@@ -4593,10 +4593,10 @@
         <v>14</v>
       </c>
       <c r="BD21" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BE21" t="n">
-        <v>18.5</v>
+        <v>14</v>
       </c>
       <c r="BF21" t="n">
         <v>7.2</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-06 11:46:30</t>
+          <t>2026-05-06 14:02:42</t>
         </is>
       </c>
     </row>
@@ -4637,22 +4637,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="G22" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="H22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I22" t="n">
         <v>4.4</v>
       </c>
-      <c r="I22" t="n">
-        <v>4.5</v>
-      </c>
       <c r="J22" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K22" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="L22" t="n">
         <v>1.34</v>
@@ -4661,7 +4661,7 @@
         <v>1.06</v>
       </c>
       <c r="N22" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O22" t="n">
         <v>1.31</v>
@@ -4679,19 +4679,19 @@
         <v>3.3</v>
       </c>
       <c r="T22" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U22" t="n">
         <v>2.16</v>
       </c>
       <c r="V22" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W22" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="X22" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Y22" t="n">
         <v>16</v>
@@ -4709,13 +4709,13 @@
         <v>8.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE22" t="n">
         <v>55</v>
       </c>
       <c r="AF22" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AG22" t="n">
         <v>10.5</v>
@@ -4736,7 +4736,7 @@
         <v>36</v>
       </c>
       <c r="AM22" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AN22" t="n">
         <v>13</v>
@@ -4748,13 +4748,13 @@
         <v>13.5</v>
       </c>
       <c r="AQ22" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AR22" t="n">
         <v>29</v>
       </c>
       <c r="AS22" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AT22" t="n">
         <v>8.800000000000001</v>
@@ -4769,7 +4769,7 @@
         <v>46</v>
       </c>
       <c r="AX22" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY22" t="n">
         <v>9.800000000000001</v>
@@ -4790,7 +4790,7 @@
         <v>30</v>
       </c>
       <c r="BE22" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BF22" t="n">
         <v>11.5</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-06 11:46:30</t>
+          <t>2026-05-06 14:02:42</t>
         </is>
       </c>
     </row>
@@ -4831,25 +4831,25 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="G23" t="n">
         <v>1.8</v>
       </c>
       <c r="H23" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I23" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J23" t="n">
         <v>4</v>
       </c>
       <c r="K23" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L23" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M23" t="n">
         <v>1.07</v>
@@ -4870,7 +4870,7 @@
         <v>1.38</v>
       </c>
       <c r="S23" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="T23" t="n">
         <v>1.9</v>
@@ -4879,7 +4879,7 @@
         <v>2.04</v>
       </c>
       <c r="V23" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W23" t="n">
         <v>2.24</v>
@@ -4891,7 +4891,7 @@
         <v>17</v>
       </c>
       <c r="Z23" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AA23" t="n">
         <v>120</v>
@@ -4924,7 +4924,7 @@
         <v>18.5</v>
       </c>
       <c r="AK23" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AL23" t="n">
         <v>36</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-06 11:46:30</t>
+          <t>2026-05-06 14:02:42</t>
         </is>
       </c>
     </row>
@@ -5025,31 +5025,31 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="G24" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="H24" t="n">
+        <v>5</v>
+      </c>
+      <c r="I24" t="n">
         <v>5.1</v>
-      </c>
-      <c r="I24" t="n">
-        <v>5.2</v>
       </c>
       <c r="J24" t="n">
         <v>3.85</v>
       </c>
       <c r="K24" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L24" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="M24" t="n">
         <v>1.08</v>
       </c>
       <c r="N24" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O24" t="n">
         <v>1.35</v>
@@ -5058,13 +5058,13 @@
         <v>1.9</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="R24" t="n">
         <v>1.35</v>
       </c>
       <c r="S24" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="T24" t="n">
         <v>1.96</v>
@@ -5073,10 +5073,10 @@
         <v>1.97</v>
       </c>
       <c r="V24" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W24" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="X24" t="n">
         <v>13</v>
@@ -5085,7 +5085,7 @@
         <v>16</v>
       </c>
       <c r="Z24" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA24" t="n">
         <v>130</v>
@@ -5151,7 +5151,7 @@
         <v>8</v>
       </c>
       <c r="AV24" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AW24" t="n">
         <v>60</v>
@@ -5160,7 +5160,7 @@
         <v>9.6</v>
       </c>
       <c r="AY24" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ24" t="n">
         <v>19.5</v>
@@ -5172,13 +5172,13 @@
         <v>17.5</v>
       </c>
       <c r="BC24" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BD24" t="n">
         <v>34</v>
       </c>
       <c r="BE24" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="BF24" t="n">
         <v>12</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-06 11:46:30</t>
+          <t>2026-05-06 14:02:42</t>
         </is>
       </c>
     </row>
@@ -5219,64 +5219,64 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="G25" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="H25" t="n">
-        <v>7.8</v>
+        <v>11</v>
       </c>
       <c r="I25" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="J25" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="K25" t="n">
-        <v>6.8</v>
+        <v>5.6</v>
       </c>
       <c r="L25" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M25" t="n">
         <v>1.08</v>
       </c>
       <c r="N25" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O25" t="n">
         <v>1.39</v>
       </c>
       <c r="P25" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R25" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S25" t="n">
         <v>3.7</v>
       </c>
       <c r="T25" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="U25" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="V25" t="n">
         <v>1.07</v>
       </c>
       <c r="W25" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="X25" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="Y25" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Z25" t="n">
         <v>1000</v>
@@ -5285,104 +5285,104 @@
         <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>6.6</v>
+        <v>970</v>
       </c>
       <c r="AC25" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AD25" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AE25" t="n">
         <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>7.2</v>
+        <v>970</v>
       </c>
       <c r="AG25" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AH25" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AI25" t="n">
         <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AK25" t="n">
         <v>22</v>
       </c>
       <c r="AL25" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM25" t="n">
         <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>9.6</v>
+        <v>970</v>
       </c>
       <c r="AO25" t="n">
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ25" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT25" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AU25" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV25" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX25" t="n">
-        <v>5.4</v>
+        <v>1.03</v>
       </c>
       <c r="AY25" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ25" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB25" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BC25" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF25" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG25" t="n">
         <v>1.01</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-06 11:46:30</t>
+          <t>2026-05-06 14:02:42</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="G26" t="n">
         <v>2.38</v>
@@ -5431,7 +5431,7 @@
         <v>3.2</v>
       </c>
       <c r="L26" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M26" t="n">
         <v>1.13</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-06 11:46:30</t>
+          <t>2026-05-06 14:02:42</t>
         </is>
       </c>
     </row>
@@ -5607,25 +5607,25 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="G27" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="H27" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="I27" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J27" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K27" t="n">
         <v>4.4</v>
       </c>
       <c r="L27" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="M27" t="n">
         <v>1.08</v>
@@ -5634,55 +5634,55 @@
         <v>3.3</v>
       </c>
       <c r="O27" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P27" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="R27" t="n">
         <v>1.3</v>
       </c>
       <c r="S27" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="T27" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="U27" t="n">
         <v>1.78</v>
       </c>
       <c r="V27" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W27" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="X27" t="n">
         <v>14.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z27" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AA27" t="n">
-        <v>320</v>
+        <v>290</v>
       </c>
       <c r="AB27" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC27" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AE27" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AF27" t="n">
         <v>8.199999999999999</v>
@@ -5694,22 +5694,22 @@
         <v>29</v>
       </c>
       <c r="AI27" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AJ27" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AK27" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="AL27" t="n">
         <v>48</v>
       </c>
       <c r="AM27" t="n">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="AN27" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AO27" t="n">
         <v>240</v>
@@ -5718,37 +5718,37 @@
         <v>11</v>
       </c>
       <c r="AQ27" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>9.4</v>
+        <v>50</v>
       </c>
       <c r="AS27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT27" t="n">
         <v>6.2</v>
       </c>
       <c r="AU27" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW27" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AX27" t="n">
         <v>7.4</v>
       </c>
       <c r="AY27" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB27" t="n">
         <v>11.5</v>
@@ -5760,17 +5760,17 @@
         <v>40</v>
       </c>
       <c r="BE27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BF27" t="n">
         <v>9</v>
       </c>
       <c r="BG27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-06 11:46:30</t>
+          <t>2026-05-06 14:02:42</t>
         </is>
       </c>
     </row>
@@ -5801,22 +5801,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G28" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H28" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="I28" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J28" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="K28" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L28" t="n">
         <v>1.49</v>
@@ -5852,7 +5852,7 @@
         <v>1.29</v>
       </c>
       <c r="W28" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="X28" t="n">
         <v>9.199999999999999</v>
@@ -5951,7 +5951,7 @@
         <v>21</v>
       </c>
       <c r="BD28" t="n">
-        <v>44</v>
+        <v>8.6</v>
       </c>
       <c r="BE28" t="n">
         <v>9.6</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-06 11:46:30</t>
+          <t>2026-05-06 14:02:42</t>
         </is>
       </c>
     </row>
@@ -5998,16 +5998,16 @@
         <v>4.8</v>
       </c>
       <c r="G29" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="H29" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="I29" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="J29" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K29" t="n">
         <v>3.7</v>
@@ -6043,7 +6043,7 @@
         <v>1.83</v>
       </c>
       <c r="V29" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="W29" t="n">
         <v>1.22</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-06 11:46:30</t>
+          <t>2026-05-06 14:02:42</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-05-06 11:46:30</t>
+          <t>2026-05-06 14:02:42</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH30"/>
+  <dimension ref="A1:BH32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,19 +757,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="G2" t="n">
-        <v>2.82</v>
+        <v>2.68</v>
       </c>
       <c r="H2" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="I2" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="J2" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="K2" t="n">
         <v>2.72</v>
@@ -778,40 +778,40 @@
         <v>1.69</v>
       </c>
       <c r="M2" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="O2" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="P2" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="R2" t="n">
         <v>1.12</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>3.15</v>
       </c>
       <c r="T2" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="U2" t="n">
         <v>1.34</v>
       </c>
       <c r="V2" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="W2" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="X2" t="n">
-        <v>970</v>
+        <v>6.6</v>
       </c>
       <c r="Y2" t="n">
         <v>1000</v>
@@ -868,59 +868,59 @@
         <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-06 14:02:42</t>
+          <t>2026-05-06 16:19:40</t>
         </is>
       </c>
     </row>
@@ -951,61 +951,61 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="G3" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="H3" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="I3" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="K3" t="n">
         <v>3.4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="M3" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N3" t="n">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="O3" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="P3" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="R3" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S3" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="T3" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="U3" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="V3" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W3" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="X3" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y3" t="n">
         <v>8.4</v>
@@ -1020,101 +1020,101 @@
         <v>12</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD3" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AE3" t="n">
         <v>38</v>
       </c>
       <c r="AF3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG3" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AH3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI3" t="n">
         <v>70</v>
       </c>
       <c r="AJ3" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AK3" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AL3" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN3" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AO3" t="n">
         <v>40</v>
       </c>
       <c r="AP3" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AR3" t="n">
         <v>10</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.8</v>
+        <v>26</v>
       </c>
       <c r="AT3" t="n">
-        <v>8.199999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="AU3" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AV3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.8</v>
+        <v>24</v>
       </c>
       <c r="AX3" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AY3" t="n">
         <v>13</v>
       </c>
       <c r="AZ3" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BF3" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-06 14:02:42</t>
+          <t>2026-05-06 16:19:40</t>
         </is>
       </c>
     </row>
@@ -1145,91 +1145,91 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>11.5</v>
+        <v>19.5</v>
       </c>
       <c r="G4" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H4" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="I4" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="J4" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="K4" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="M4" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="N4" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="P4" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.34</v>
+        <v>2.1</v>
       </c>
       <c r="R4" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="S4" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="T4" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U4" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="V4" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="W4" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>970</v>
+        <v>5.6</v>
       </c>
       <c r="Z4" t="n">
-        <v>970</v>
+        <v>6.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>970</v>
+        <v>8.6</v>
       </c>
       <c r="AB4" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AC4" t="n">
         <v>970</v>
       </c>
       <c r="AD4" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AF4" t="n">
         <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AH4" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AI4" t="n">
         <v>130</v>
@@ -1250,65 +1250,65 @@
         <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>970</v>
+        <v>8.4</v>
       </c>
       <c r="AP4" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AQ4" t="n">
         <v>4.3</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="AT4" t="n">
         <v>6.4</v>
       </c>
       <c r="AU4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AV4" t="n">
         <v>10.5</v>
       </c>
-      <c r="AV4" t="n">
-        <v>5</v>
-      </c>
       <c r="AW4" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.67</v>
+        <v>7.2</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.65</v>
+        <v>7</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2.42</v>
+        <v>6.8</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.44</v>
+        <v>7</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.68</v>
+        <v>7.4</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.68</v>
+        <v>7.4</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.68</v>
+        <v>7.4</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.68</v>
+        <v>7.4</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.68</v>
+        <v>7.4</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-06 14:02:42</t>
+          <t>2026-05-06 16:19:40</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="G5" t="n">
         <v>1.74</v>
       </c>
       <c r="H5" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="I5" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K5" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L5" t="n">
         <v>1.3</v>
@@ -1363,28 +1363,28 @@
         <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O5" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="P5" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q5" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="T5" t="n">
         <v>1.81</v>
       </c>
-      <c r="R5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.86</v>
-      </c>
       <c r="U5" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="V5" t="n">
         <v>1.2</v>
@@ -1402,107 +1402,107 @@
         <v>55</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AB5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC5" t="n">
         <v>970</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>11.5</v>
       </c>
       <c r="AD5" t="n">
         <v>21</v>
       </c>
       <c r="AE5" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AF5" t="n">
         <v>970</v>
       </c>
       <c r="AG5" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AH5" t="n">
         <v>25</v>
       </c>
       <c r="AI5" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ5" t="n">
         <v>970</v>
       </c>
       <c r="AK5" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AL5" t="n">
         <v>40</v>
       </c>
       <c r="AM5" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN5" t="n">
         <v>10.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AP5" t="n">
         <v>15</v>
       </c>
       <c r="AQ5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV5" t="n">
         <v>5.3</v>
       </c>
-      <c r="AR5" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>5.4</v>
-      </c>
       <c r="AW5" t="n">
-        <v>5.4</v>
+        <v>3.35</v>
       </c>
       <c r="AX5" t="n">
         <v>6.8</v>
       </c>
       <c r="AY5" t="n">
-        <v>7.8</v>
+        <v>4.3</v>
       </c>
       <c r="AZ5" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.3</v>
+        <v>3.35</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BC5" t="n">
-        <v>11.5</v>
+        <v>5.1</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-06 14:02:42</t>
+          <t>2026-05-06 16:19:40</t>
         </is>
       </c>
     </row>
@@ -1572,7 +1572,7 @@
         <v>1.07</v>
       </c>
       <c r="S6" t="n">
-        <v>1.05</v>
+        <v>1.44</v>
       </c>
       <c r="T6" t="n">
         <v>1.01</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-06 14:02:42</t>
+          <t>2026-05-06 16:19:40</t>
         </is>
       </c>
     </row>
@@ -1718,28 +1718,28 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FK Dubocica</t>
+          <t>SU Dinamo Jug</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FK FAP</t>
+          <t>FK Usce Novi Beograd</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="G7" t="n">
-        <v>610</v>
+        <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="I7" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="K7" t="n">
         <v>950</v>
@@ -1751,22 +1751,22 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="O7" t="n">
         <v>1.01</v>
       </c>
       <c r="P7" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Q7" t="n">
         <v>1.01</v>
       </c>
       <c r="R7" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="S7" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="T7" t="n">
         <v>1.01</v>
@@ -1890,14 +1890,14 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-06 14:02:42</t>
+          <t>2026-05-06 16:19:40</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Finnish Kakkonen</t>
+          <t>Serbian First League</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,27 +1907,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SJK Akatemia 2</t>
+          <t>Tekstilac Odzaci</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Huima</t>
+          <t>Fk Smederevo</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="G8" t="n">
         <v>110</v>
       </c>
       <c r="H8" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="I8" t="n">
         <v>110</v>
@@ -1945,22 +1945,22 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.26</v>
+        <v>2.72</v>
       </c>
       <c r="O8" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="P8" t="n">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="R8" t="n">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
       <c r="S8" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
@@ -2084,14 +2084,14 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-06 14:02:42</t>
+          <t>2026-05-06 16:19:40</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Finnish Ykkosliiga</t>
+          <t>Serbian First League</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,191 +2101,191 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>PK-35 RY</t>
+          <t>FK Dubocica</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>FK FAP</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.78</v>
+        <v>1.02</v>
       </c>
       <c r="G9" t="n">
-        <v>1.85</v>
+        <v>610</v>
       </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>1.02</v>
       </c>
       <c r="I9" t="n">
-        <v>5.5</v>
+        <v>610</v>
       </c>
       <c r="J9" t="n">
-        <v>3.6</v>
+        <v>1.03</v>
       </c>
       <c r="K9" t="n">
-        <v>4</v>
+        <v>950</v>
       </c>
       <c r="L9" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>3.4</v>
+        <v>1.02</v>
       </c>
       <c r="O9" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="P9" t="n">
-        <v>1.85</v>
+        <v>1.07</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="R9" t="n">
-        <v>1.31</v>
+        <v>1.07</v>
       </c>
       <c r="S9" t="n">
-        <v>3.55</v>
+        <v>1.41</v>
       </c>
       <c r="T9" t="n">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="U9" t="n">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ9" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AR9" t="n">
-        <v>5.2</v>
+        <v>1.03</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.7</v>
+        <v>1.03</v>
       </c>
       <c r="AT9" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AV9" t="n">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.5</v>
+        <v>1.03</v>
       </c>
       <c r="AX9" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AY9" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AZ9" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.5</v>
+        <v>1.03</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="BC9" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.2</v>
+        <v>1.03</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.6</v>
+        <v>1.03</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-06 14:02:42</t>
+          <t>2026-05-06 16:19:40</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Moroccan Botola Pro 1</t>
+          <t>Finnish Kakkonen</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2300,31 +2300,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>DHJ El Jadida</t>
+          <t>SJK Akatemia 2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>HUSA Agadir</t>
+          <t>Huima</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>1.04</v>
       </c>
       <c r="G10" t="n">
-        <v>3.45</v>
+        <v>380</v>
       </c>
       <c r="H10" t="n">
-        <v>2.88</v>
+        <v>1.04</v>
       </c>
       <c r="I10" t="n">
-        <v>3.25</v>
+        <v>290</v>
       </c>
       <c r="J10" t="n">
-        <v>2.5</v>
+        <v>1.03</v>
       </c>
       <c r="K10" t="n">
-        <v>3.1</v>
+        <v>950</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2333,22 +2333,22 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>2.22</v>
+        <v>1.02</v>
       </c>
       <c r="O10" t="n">
-        <v>1.56</v>
+        <v>1.08</v>
       </c>
       <c r="P10" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.62</v>
+        <v>1.08</v>
       </c>
       <c r="R10" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="S10" t="n">
-        <v>2.62</v>
+        <v>1.08</v>
       </c>
       <c r="T10" t="n">
         <v>1.01</v>
@@ -2357,10 +2357,10 @@
         <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -2472,14 +2472,14 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-06 14:02:42</t>
+          <t>2026-05-06 16:19:40</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Polish I Liga</t>
+          <t>Finnish Ykkosliiga</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2494,186 +2494,186 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LKS Lodz</t>
+          <t>PK-35 RY</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pogon Grodzisk Mazowiecki</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="G11" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="H11" t="n">
         <v>5</v>
       </c>
       <c r="I11" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="J11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K11" t="n">
         <v>4.1</v>
       </c>
-      <c r="K11" t="n">
-        <v>4.8</v>
-      </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M11" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="N11" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="O11" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="V11" t="n">
         <v>1.22</v>
       </c>
-      <c r="P11" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.21</v>
-      </c>
       <c r="W11" t="n">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="X11" t="n">
-        <v>26</v>
+        <v>15.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AA11" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AB11" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AC11" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD11" t="n">
         <v>24</v>
       </c>
       <c r="AE11" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AF11" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AG11" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH11" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK11" t="n">
         <v>23</v>
       </c>
-      <c r="AI11" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>21</v>
-      </c>
       <c r="AL11" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AM11" t="n">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="AN11" t="n">
-        <v>10</v>
+        <v>970</v>
       </c>
       <c r="AO11" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="AP11" t="n">
-        <v>15.5</v>
+        <v>10.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>15.5</v>
+        <v>4.9</v>
       </c>
       <c r="AR11" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF11" t="n">
         <v>4.5</v>
       </c>
-      <c r="AS11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>40</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>13</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>12</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BG11" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-06 14:02:42</t>
+          <t>2026-05-06 16:19:40</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Romanian Liga II</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2688,31 +2688,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CSA Steaua Bucuresti</t>
+          <t>DHJ El Jadida</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ACS Sepsi OSK</t>
+          <t>HUSA Agadir</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="G12" t="n">
-        <v>110</v>
+        <v>3.45</v>
       </c>
       <c r="H12" t="n">
-        <v>1.04</v>
+        <v>2.88</v>
       </c>
       <c r="I12" t="n">
-        <v>110</v>
+        <v>3.25</v>
       </c>
       <c r="J12" t="n">
-        <v>1.02</v>
+        <v>2.52</v>
       </c>
       <c r="K12" t="n">
-        <v>950</v>
+        <v>3.1</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -2721,22 +2721,22 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.25</v>
+        <v>2.42</v>
       </c>
       <c r="O12" t="n">
-        <v>1.29</v>
+        <v>1.59</v>
       </c>
       <c r="P12" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.29</v>
+        <v>2.62</v>
       </c>
       <c r="R12" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>1.3</v>
+        <v>2.62</v>
       </c>
       <c r="T12" t="n">
         <v>1.01</v>
@@ -2745,10 +2745,10 @@
         <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -2860,14 +2860,14 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-06 14:02:42</t>
+          <t>2026-05-06 16:19:40</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Turkish 1 Lig</t>
+          <t>Polish I Liga</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Bodrum Belediyesi Bodrumspor</t>
+          <t>LKS Lodz</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Pogon Grodzisk Mazowiecki</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.24</v>
+        <v>1.63</v>
       </c>
       <c r="G13" t="n">
-        <v>2.46</v>
+        <v>1.79</v>
       </c>
       <c r="H13" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="I13" t="n">
-        <v>3.95</v>
+        <v>5.7</v>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="K13" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="L13" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="N13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="X13" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>140</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX13" t="n">
         <v>3.65</v>
       </c>
-      <c r="O13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="X13" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>29</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>23</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>46</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>11</v>
-      </c>
       <c r="AY13" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ13" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="BC13" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BF13" t="n">
-        <v>13.5</v>
+        <v>7.2</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-06 14:02:42</t>
+          <t>2026-05-06 16:19:40</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Romanian Liga II</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,184 +3071,184 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>FK Auda</t>
+          <t>CSA Steaua Bucuresti</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SC Grobina</t>
+          <t>ACS Sepsi OSK</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.5</v>
+        <v>1.04</v>
       </c>
       <c r="G14" t="n">
-        <v>1.59</v>
+        <v>570</v>
       </c>
       <c r="H14" t="n">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="I14" t="n">
-        <v>8</v>
+        <v>570</v>
       </c>
       <c r="J14" t="n">
-        <v>4</v>
+        <v>1.02</v>
       </c>
       <c r="K14" t="n">
-        <v>5</v>
+        <v>950</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>3.6</v>
+        <v>1.26</v>
       </c>
       <c r="O14" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="P14" t="n">
-        <v>1.95</v>
+        <v>1.24</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.73</v>
+        <v>1.27</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>1.15</v>
       </c>
       <c r="S14" t="n">
-        <v>2.72</v>
+        <v>1.27</v>
       </c>
       <c r="T14" t="n">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="U14" t="n">
-        <v>1.91</v>
+        <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>2.68</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>5.7</v>
+        <v>1.03</v>
       </c>
       <c r="AQ14" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AR14" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AS14" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AT14" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AU14" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV14" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AW14" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AX14" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="AY14" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AZ14" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="BA14" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="BB14" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="BC14" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD14" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="BE14" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="BF14" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-06 14:02:42</t>
+          <t>2026-05-06 16:19:40</t>
         </is>
       </c>
     </row>
@@ -3270,186 +3270,186 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Corum Belediyespor</t>
+          <t>Bodrum Belediyesi Bodrumspor</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Keciorengucu</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.69</v>
+        <v>2.24</v>
       </c>
       <c r="G15" t="n">
-        <v>1.81</v>
+        <v>2.46</v>
       </c>
       <c r="H15" t="n">
-        <v>5</v>
+        <v>3.25</v>
       </c>
       <c r="I15" t="n">
-        <v>5.8</v>
+        <v>3.75</v>
       </c>
       <c r="J15" t="n">
-        <v>3.95</v>
+        <v>3.3</v>
       </c>
       <c r="K15" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="L15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O15" t="n">
         <v>1.3</v>
       </c>
-      <c r="M15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N15" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.25</v>
-      </c>
       <c r="P15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U15" t="n">
         <v>2.14</v>
       </c>
-      <c r="Q15" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.12</v>
-      </c>
       <c r="V15" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="W15" t="n">
-        <v>2.22</v>
+        <v>1.68</v>
       </c>
       <c r="X15" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="Y15" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="Z15" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="AA15" t="n">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="AB15" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD15" t="n">
-        <v>24</v>
+        <v>17.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="AF15" t="n">
-        <v>13.5</v>
+        <v>18.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AH15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI15" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AJ15" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="AK15" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="AL15" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AM15" t="n">
         <v>110</v>
       </c>
       <c r="AN15" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP15" t="n">
         <v>10.5</v>
       </c>
-      <c r="AO15" t="n">
-        <v>80</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>14</v>
-      </c>
       <c r="AQ15" t="n">
-        <v>15.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT15" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AU15" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV15" t="n">
-        <v>15.5</v>
+        <v>10.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AX15" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AY15" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AZ15" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF15" t="n">
         <v>13.5</v>
       </c>
-      <c r="BC15" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>7</v>
-      </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-06 14:02:42</t>
+          <t>2026-05-06 16:19:40</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Turkish 1 Lig</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3464,186 +3464,186 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Corum Belediyespor</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ZED FC</t>
+          <t>Keciorengucu</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="G16" t="n">
         <v>1.79</v>
       </c>
       <c r="H16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I16" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="J16" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="K16" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="L16" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="M16" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="N16" t="n">
-        <v>2.62</v>
+        <v>4.3</v>
       </c>
       <c r="O16" t="n">
-        <v>1.54</v>
+        <v>1.25</v>
       </c>
       <c r="P16" t="n">
-        <v>1.55</v>
+        <v>2.16</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.58</v>
+        <v>1.74</v>
       </c>
       <c r="R16" t="n">
-        <v>1.19</v>
+        <v>1.45</v>
       </c>
       <c r="S16" t="n">
-        <v>5.5</v>
+        <v>2.88</v>
       </c>
       <c r="T16" t="n">
-        <v>2.44</v>
+        <v>1.75</v>
       </c>
       <c r="U16" t="n">
-        <v>1.62</v>
+        <v>2.12</v>
       </c>
       <c r="V16" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="W16" t="n">
         <v>2.26</v>
       </c>
       <c r="X16" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="Y16" t="n">
-        <v>16.5</v>
+        <v>24</v>
       </c>
       <c r="Z16" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AA16" t="n">
-        <v>230</v>
+        <v>150</v>
       </c>
       <c r="AB16" t="n">
-        <v>5.9</v>
+        <v>11.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="AD16" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AE16" t="n">
-        <v>140</v>
+        <v>80</v>
       </c>
       <c r="AF16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>80</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX16" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AG16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>200</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>19</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>290</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>20</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>260</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>8</v>
-      </c>
-      <c r="AQ16" t="n">
+      <c r="AY16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BC16" t="n">
         <v>13</v>
       </c>
-      <c r="AR16" t="n">
-        <v>42</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>14</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>22</v>
-      </c>
       <c r="BD16" t="n">
-        <v>50</v>
+        <v>1.03</v>
       </c>
       <c r="BE16" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BF16" t="n">
-        <v>15.5</v>
+        <v>7</v>
       </c>
       <c r="BG16" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-06 14:02:42</t>
+          <t>2026-05-06 16:19:40</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3658,186 +3658,186 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>National Bank</t>
+          <t>FK Auda</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ismaily</t>
+          <t>SC Grobina</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>1.48</v>
       </c>
       <c r="G17" t="n">
-        <v>2.14</v>
+        <v>1.56</v>
       </c>
       <c r="H17" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="I17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K17" t="n">
         <v>5.1</v>
       </c>
-      <c r="J17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>3.4</v>
-      </c>
       <c r="L17" t="n">
         <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="N17" t="n">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="O17" t="n">
-        <v>1.49</v>
+        <v>1.26</v>
       </c>
       <c r="P17" t="n">
-        <v>1.56</v>
+        <v>2.04</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.48</v>
+        <v>1.77</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2</v>
+        <v>1.41</v>
       </c>
       <c r="S17" t="n">
-        <v>4.8</v>
+        <v>2.96</v>
       </c>
       <c r="T17" t="n">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="U17" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="V17" t="n">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="W17" t="n">
-        <v>1.88</v>
+        <v>2.8</v>
       </c>
       <c r="X17" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>26</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>320</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC17" t="n">
         <v>11</v>
       </c>
-      <c r="Y17" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA17" t="n">
+      <c r="AD17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE17" t="n">
         <v>140</v>
       </c>
-      <c r="AB17" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD17" t="n">
+      <c r="AF17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>200</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ17" t="n">
         <v>21</v>
       </c>
-      <c r="AE17" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>220</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>26</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>140</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AQ17" t="n">
+      <c r="AR17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS17" t="n">
         <v>10.5</v>
       </c>
-      <c r="AR17" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AS17" t="n">
+      <c r="AT17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AX17" t="n">
         <v>7.6</v>
       </c>
-      <c r="AT17" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AY17" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ17" t="n">
         <v>20</v>
       </c>
       <c r="BA17" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="BB17" t="n">
-        <v>20</v>
+        <v>11.5</v>
       </c>
       <c r="BC17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF17" t="n">
         <v>6.4</v>
       </c>
-      <c r="BD17" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>21</v>
-      </c>
       <c r="BG17" t="n">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-06 14:02:42</t>
+          <t>2026-05-06 16:19:40</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Moroccan Botola Pro 1</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,191 +3847,191 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>National Bank</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Union de Touarga</t>
+          <t>Ismaily</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.04</v>
+        <v>1.88</v>
       </c>
       <c r="G18" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>2.84</v>
+        <v>5.2</v>
       </c>
       <c r="I18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2</v>
+      </c>
+      <c r="X18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>190</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI18" t="n">
         <v>140</v>
       </c>
-      <c r="J18" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="K18" t="n">
-        <v>950</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N18" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W18" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>1000</v>
-      </c>
       <c r="AJ18" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK18" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL18" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM18" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AN18" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AO18" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-06 14:02:42</t>
+          <t>2026-05-06 16:19:40</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,191 +4041,191 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Al-Shabab (KSA)</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>ZED FC</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>8.199999999999999</v>
+        <v>1.97</v>
       </c>
       <c r="G19" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="H19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I19" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="X19" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>220</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>250</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>26</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>170</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>25</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD19" t="n">
         <v>10</v>
       </c>
-      <c r="H19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="J19" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="K19" t="n">
-        <v>7</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N19" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="P19" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="V19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X19" t="n">
-        <v>48</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>55</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>16</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>16</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>110</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>36</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>28</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>290</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>130</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>95</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>100</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>11</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW19" t="n">
+      <c r="BE19" t="n">
         <v>11.5</v>
       </c>
-      <c r="AX19" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>19</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BF19" t="n">
-        <v>5.9</v>
+        <v>21</v>
       </c>
       <c r="BG19" t="n">
-        <v>3</v>
+        <v>11.5</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-06 14:02:42</t>
+          <t>2026-05-06 16:19:40</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,72 +4235,72 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Union de Touarga</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="G20" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="H20" t="n">
-        <v>1.1</v>
+        <v>4.7</v>
       </c>
       <c r="I20" t="n">
-        <v>870</v>
+        <v>12</v>
       </c>
       <c r="J20" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="K20" t="n">
-        <v>50</v>
+        <v>5.7</v>
       </c>
       <c r="L20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="O20" t="n">
         <v>1.37</v>
       </c>
-      <c r="M20" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.35</v>
-      </c>
       <c r="P20" t="n">
-        <v>1.24</v>
+        <v>1.63</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.02</v>
+        <v>2</v>
       </c>
       <c r="R20" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="S20" t="n">
-        <v>1.05</v>
+        <v>2</v>
       </c>
       <c r="T20" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="U20" t="n">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="V20" t="n">
         <v>1.09</v>
       </c>
       <c r="W20" t="n">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="X20" t="n">
         <v>1000</v>
@@ -4412,14 +4412,14 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-06 14:02:42</t>
+          <t>2026-05-06 16:19:40</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,191 +4429,191 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Al-Shabab (KSA)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Shakhtar</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>1.62</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="J21" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K21" t="n">
+        <v>7</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N21" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="P21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="V21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X21" t="n">
+        <v>48</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>48</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>110</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>36</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>27</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>290</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>130</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>100</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AP21" t="n">
         <v>6.2</v>
       </c>
-      <c r="I21" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="J21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K21" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N21" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="W21" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="X21" t="n">
+      <c r="AQ21" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>36</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AZ21" t="n">
         <v>19</v>
       </c>
-      <c r="Y21" t="n">
-        <v>22</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>50</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>200</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>15</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>8</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>85</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>20</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>42</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>15</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>65</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>19.5</v>
-      </c>
       <c r="BA21" t="n">
-        <v>65</v>
+        <v>19</v>
       </c>
       <c r="BB21" t="n">
-        <v>13</v>
+        <v>6.8</v>
       </c>
       <c r="BC21" t="n">
-        <v>14</v>
+        <v>6.8</v>
       </c>
       <c r="BD21" t="n">
-        <v>30</v>
+        <v>6.6</v>
       </c>
       <c r="BE21" t="n">
-        <v>14</v>
+        <v>6.6</v>
       </c>
       <c r="BF21" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BG21" t="n">
-        <v>65</v>
+        <v>3</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-06 14:02:42</t>
+          <t>2026-05-06 16:19:40</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4628,186 +4628,186 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.95</v>
+        <v>1.45</v>
       </c>
       <c r="G22" t="n">
-        <v>1.98</v>
+        <v>1.55</v>
       </c>
       <c r="H22" t="n">
-        <v>4.2</v>
+        <v>2.98</v>
       </c>
       <c r="I22" t="n">
-        <v>4.4</v>
+        <v>870</v>
       </c>
       <c r="J22" t="n">
         <v>3.85</v>
       </c>
       <c r="K22" t="n">
-        <v>3.95</v>
+        <v>50</v>
       </c>
       <c r="L22" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="M22" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N22" t="n">
-        <v>4</v>
+        <v>1.1</v>
       </c>
       <c r="O22" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="P22" t="n">
-        <v>2.02</v>
+        <v>1.69</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="R22" t="n">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="S22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X22" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>42</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX22" t="n">
         <v>3.3</v>
       </c>
-      <c r="T22" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="U22" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W22" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="X22" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>22</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>20</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>13</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>29</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>46</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AY22" t="n">
-        <v>9.800000000000001</v>
+        <v>3.6</v>
       </c>
       <c r="AZ22" t="n">
-        <v>17</v>
+        <v>4.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="BB22" t="n">
-        <v>19.5</v>
+        <v>3.85</v>
       </c>
       <c r="BC22" t="n">
-        <v>17.5</v>
+        <v>4.1</v>
       </c>
       <c r="BD22" t="n">
-        <v>30</v>
+        <v>4.7</v>
       </c>
       <c r="BE22" t="n">
-        <v>14.5</v>
+        <v>5.1</v>
       </c>
       <c r="BF22" t="n">
-        <v>11.5</v>
+        <v>3.55</v>
       </c>
       <c r="BG22" t="n">
-        <v>42</v>
+        <v>5.1</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-06 14:02:42</t>
+          <t>2026-05-06 16:19:40</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4822,148 +4822,148 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Nottm Forest</t>
+          <t>Shakhtar</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.78</v>
+        <v>1.61</v>
       </c>
       <c r="G23" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="H23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I23" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="J23" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="K23" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="L23" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="M23" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N23" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O23" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="P23" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="R23" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="S23" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="T23" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U23" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V23" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="W23" t="n">
-        <v>2.24</v>
+        <v>2.6</v>
       </c>
       <c r="X23" t="n">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="Y23" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="Z23" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="AA23" t="n">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="AB23" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AC23" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AE23" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AF23" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AG23" t="n">
         <v>10.5</v>
       </c>
-      <c r="AG23" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AH23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI23" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AJ23" t="n">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="AK23" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AL23" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AM23" t="n">
         <v>110</v>
       </c>
       <c r="AN23" t="n">
-        <v>12</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO23" t="n">
         <v>85</v>
       </c>
       <c r="AP23" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AQ23" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>44</v>
+      </c>
+      <c r="AS23" t="n">
         <v>16</v>
       </c>
-      <c r="AR23" t="n">
-        <v>32</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>65</v>
-      </c>
       <c r="AT23" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU23" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV23" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AW23" t="n">
-        <v>50</v>
+        <v>14.5</v>
       </c>
       <c r="AX23" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY23" t="n">
         <v>9.6</v>
@@ -4972,36 +4972,36 @@
         <v>19</v>
       </c>
       <c r="BA23" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BB23" t="n">
-        <v>17.5</v>
+        <v>13</v>
       </c>
       <c r="BC23" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="BD23" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BE23" t="n">
-        <v>100</v>
+        <v>15.5</v>
       </c>
       <c r="BF23" t="n">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="BG23" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-06 14:02:42</t>
+          <t>2026-05-06 16:19:40</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5016,186 +5016,186 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.84</v>
+        <v>2.02</v>
       </c>
       <c r="G24" t="n">
-        <v>1.85</v>
+        <v>2.06</v>
       </c>
       <c r="H24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I24" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="J24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K24" t="n">
         <v>3.85</v>
       </c>
-      <c r="K24" t="n">
-        <v>3.9</v>
-      </c>
       <c r="L24" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="M24" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="N24" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="O24" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="P24" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q24" t="n">
         <v>1.9</v>
       </c>
-      <c r="Q24" t="n">
-        <v>2.06</v>
-      </c>
       <c r="R24" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="S24" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="T24" t="n">
-        <v>1.96</v>
+        <v>1.81</v>
       </c>
       <c r="U24" t="n">
-        <v>1.97</v>
+        <v>2.16</v>
       </c>
       <c r="V24" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="W24" t="n">
-        <v>2.16</v>
+        <v>1.94</v>
       </c>
       <c r="X24" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="Y24" t="n">
         <v>16</v>
       </c>
       <c r="Z24" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AA24" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AB24" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AC24" t="n">
         <v>8.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AF24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG24" t="n">
         <v>10.5</v>
       </c>
-      <c r="AG24" t="n">
-        <v>10</v>
-      </c>
       <c r="AH24" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK24" t="n">
         <v>21</v>
       </c>
-      <c r="AI24" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>19</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>20</v>
-      </c>
       <c r="AL24" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AM24" t="n">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="AN24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>27</v>
+      </c>
+      <c r="AS24" t="n">
         <v>13</v>
       </c>
-      <c r="AO24" t="n">
-        <v>90</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>32</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>40</v>
-      </c>
       <c r="AT24" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AU24" t="n">
         <v>8</v>
       </c>
       <c r="AV24" t="n">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="AW24" t="n">
-        <v>60</v>
+        <v>13.5</v>
       </c>
       <c r="AX24" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AY24" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ24" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB24" t="n">
         <v>19.5</v>
       </c>
-      <c r="BA24" t="n">
-        <v>55</v>
-      </c>
-      <c r="BB24" t="n">
+      <c r="BC24" t="n">
         <v>17.5</v>
       </c>
-      <c r="BC24" t="n">
-        <v>18.5</v>
-      </c>
       <c r="BD24" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BE24" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="BF24" t="n">
         <v>12</v>
       </c>
       <c r="BG24" t="n">
-        <v>70</v>
+        <v>12</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-06 14:02:42</t>
+          <t>2026-05-06 16:19:40</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Moroccan Botola Pro 1</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,191 +5205,191 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Nottm Forest</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.37</v>
+        <v>1.79</v>
       </c>
       <c r="G25" t="n">
-        <v>1.45</v>
+        <v>1.8</v>
       </c>
       <c r="H25" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I25" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J25" t="n">
+        <v>4</v>
+      </c>
+      <c r="K25" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N25" t="n">
+        <v>4</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W25" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="X25" t="n">
         <v>15.5</v>
       </c>
-      <c r="J25" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K25" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N25" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W25" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="X25" t="n">
-        <v>970</v>
-      </c>
       <c r="Y25" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>80</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR25" t="n">
         <v>32</v>
       </c>
-      <c r="Z25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>55</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>44</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>970</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>970</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AS25" t="n">
-        <v>1.03</v>
+        <v>65</v>
       </c>
       <c r="AT25" t="n">
-        <v>4.8</v>
+        <v>8.4</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.03</v>
+        <v>50</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.03</v>
+        <v>60</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.03</v>
+        <v>32</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.03</v>
+        <v>95</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.01</v>
+        <v>65</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-06 14:02:42</t>
+          <t>2026-05-06 16:19:40</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,191 +5399,191 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>CA Platense</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Penarol</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.16</v>
+        <v>1.82</v>
       </c>
       <c r="G26" t="n">
-        <v>2.38</v>
+        <v>1.83</v>
       </c>
       <c r="H26" t="n">
+        <v>5</v>
+      </c>
+      <c r="I26" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J26" t="n">
         <v>3.9</v>
       </c>
-      <c r="I26" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J26" t="n">
-        <v>2.92</v>
-      </c>
       <c r="K26" t="n">
-        <v>3.2</v>
+        <v>3.95</v>
       </c>
       <c r="L26" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="M26" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="N26" t="n">
-        <v>2.48</v>
+        <v>3.7</v>
       </c>
       <c r="O26" t="n">
-        <v>1.56</v>
+        <v>1.35</v>
       </c>
       <c r="P26" t="n">
-        <v>1.49</v>
+        <v>1.9</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.68</v>
+        <v>2.08</v>
       </c>
       <c r="R26" t="n">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="S26" t="n">
-        <v>5.5</v>
+        <v>3.75</v>
       </c>
       <c r="T26" t="n">
-        <v>2.18</v>
+        <v>1.97</v>
       </c>
       <c r="U26" t="n">
-        <v>1.72</v>
+        <v>1.98</v>
       </c>
       <c r="V26" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="W26" t="n">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="X26" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Y26" t="n">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="Z26" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="AA26" t="n">
         <v>130</v>
       </c>
       <c r="AB26" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC26" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AE26" t="n">
         <v>75</v>
       </c>
       <c r="AF26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN26" t="n">
         <v>13</v>
       </c>
-      <c r="AG26" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>240</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>34</v>
-      </c>
       <c r="AO26" t="n">
-        <v>140</v>
+        <v>90</v>
       </c>
       <c r="AP26" t="n">
-        <v>7.2</v>
+        <v>12</v>
       </c>
       <c r="AQ26" t="n">
-        <v>9.4</v>
+        <v>15</v>
       </c>
       <c r="AR26" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="AS26" t="n">
-        <v>9.199999999999999</v>
+        <v>40</v>
       </c>
       <c r="AT26" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="AU26" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV26" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>8.6</v>
+        <v>60</v>
       </c>
       <c r="AX26" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AY26" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ26" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="BB26" t="n">
-        <v>27</v>
+        <v>17.5</v>
       </c>
       <c r="BC26" t="n">
-        <v>7.6</v>
+        <v>18.5</v>
       </c>
       <c r="BD26" t="n">
-        <v>8.6</v>
+        <v>36</v>
       </c>
       <c r="BE26" t="n">
-        <v>9.4</v>
+        <v>42</v>
       </c>
       <c r="BF26" t="n">
-        <v>7.6</v>
+        <v>12</v>
       </c>
       <c r="BG26" t="n">
-        <v>9.199999999999999</v>
+        <v>75</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-06 14:02:42</t>
+          <t>2026-05-06 16:19:40</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,184 +5593,184 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>LDU</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.57</v>
+        <v>1.37</v>
       </c>
       <c r="G27" t="n">
-        <v>1.61</v>
+        <v>1.46</v>
       </c>
       <c r="H27" t="n">
-        <v>6.8</v>
+        <v>10</v>
       </c>
       <c r="I27" t="n">
-        <v>8.199999999999999</v>
+        <v>15.5</v>
       </c>
       <c r="J27" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K27" t="n">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="L27" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="M27" t="n">
         <v>1.08</v>
       </c>
       <c r="N27" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="O27" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P27" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R27" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="S27" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="T27" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W27" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="X27" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>32</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>55</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>44</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AV27" t="n">
         <v>2.16</v>
       </c>
-      <c r="U27" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W27" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="X27" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>65</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>290</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>29</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>140</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>180</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>11</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>240</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>50</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>24</v>
-      </c>
       <c r="AW27" t="n">
-        <v>10.5</v>
+        <v>2.24</v>
       </c>
       <c r="AX27" t="n">
-        <v>7.4</v>
+        <v>3.85</v>
       </c>
       <c r="AY27" t="n">
-        <v>9.199999999999999</v>
+        <v>3.2</v>
       </c>
       <c r="AZ27" t="n">
-        <v>24</v>
+        <v>2.14</v>
       </c>
       <c r="BA27" t="n">
-        <v>11</v>
+        <v>2.24</v>
       </c>
       <c r="BB27" t="n">
-        <v>11.5</v>
+        <v>4.9</v>
       </c>
       <c r="BC27" t="n">
-        <v>16</v>
+        <v>2.02</v>
       </c>
       <c r="BD27" t="n">
-        <v>40</v>
+        <v>2.18</v>
       </c>
       <c r="BE27" t="n">
-        <v>11</v>
+        <v>2.24</v>
       </c>
       <c r="BF27" t="n">
-        <v>9</v>
+        <v>2.76</v>
       </c>
       <c r="BG27" t="n">
-        <v>11</v>
+        <v>2.24</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-06 14:02:42</t>
+          <t>2026-05-06 16:19:40</t>
         </is>
       </c>
     </row>
@@ -5787,27 +5787,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>CA Platense</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Universitario de Deportes</t>
+          <t>Penarol</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="G28" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="H28" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="I28" t="n">
         <v>4.4</v>
@@ -5816,100 +5816,100 @@
         <v>3</v>
       </c>
       <c r="K28" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="L28" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="M28" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N28" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q28" t="n">
         <v>2.6</v>
       </c>
-      <c r="O28" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="P28" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>2.5</v>
-      </c>
       <c r="R28" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="T28" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="U28" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="V28" t="n">
         <v>1.29</v>
       </c>
       <c r="W28" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="X28" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Y28" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z28" t="n">
         <v>29</v>
       </c>
       <c r="AA28" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AB28" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AC28" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD28" t="n">
         <v>18.5</v>
       </c>
       <c r="AE28" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AF28" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG28" t="n">
         <v>12</v>
       </c>
       <c r="AH28" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AI28" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AJ28" t="n">
         <v>34</v>
       </c>
       <c r="AK28" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AL28" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AM28" t="n">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="AN28" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AO28" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="AP28" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AQ28" t="n">
         <v>9.4</v>
@@ -5918,53 +5918,53 @@
         <v>18</v>
       </c>
       <c r="AS28" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT28" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AU28" t="n">
         <v>6.2</v>
       </c>
       <c r="AV28" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AX28" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY28" t="n">
         <v>10</v>
       </c>
       <c r="AZ28" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA28" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB28" t="n">
-        <v>7.6</v>
+        <v>27</v>
       </c>
       <c r="BC28" t="n">
-        <v>21</v>
+        <v>8.6</v>
       </c>
       <c r="BD28" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF28" t="n">
         <v>8.6</v>
       </c>
-      <c r="BE28" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BG28" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-06 14:02:42</t>
+          <t>2026-05-06 16:19:40</t>
         </is>
       </c>
     </row>
@@ -5981,184 +5981,184 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Ind Medellin</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>LDU</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>4.8</v>
+        <v>1.61</v>
       </c>
       <c r="G29" t="n">
-        <v>5.5</v>
+        <v>1.63</v>
       </c>
       <c r="H29" t="n">
-        <v>1.87</v>
+        <v>6.8</v>
       </c>
       <c r="I29" t="n">
-        <v>1.96</v>
+        <v>7.6</v>
       </c>
       <c r="J29" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="K29" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="L29" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="M29" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N29" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="O29" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="P29" t="n">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.26</v>
+        <v>2.12</v>
       </c>
       <c r="R29" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S29" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="T29" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="U29" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="V29" t="n">
-        <v>2.04</v>
+        <v>1.15</v>
       </c>
       <c r="W29" t="n">
-        <v>1.22</v>
+        <v>2.58</v>
       </c>
       <c r="X29" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>290</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>180</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>190</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>23</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>24</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>14</v>
+      </c>
+      <c r="BB29" t="n">
         <v>11.5</v>
       </c>
-      <c r="Y29" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>11</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>23</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>15</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>24</v>
-      </c>
-      <c r="AF29" t="n">
+      <c r="BC29" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD29" t="n">
         <v>40</v>
       </c>
-      <c r="AG29" t="n">
-        <v>22</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>160</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>85</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>95</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>140</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>19</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>28</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BE29" t="n">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="BF29" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BG29" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-06 14:02:42</t>
+          <t>2026-05-06 16:19:40</t>
         </is>
       </c>
     </row>
@@ -6175,184 +6175,572 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Coquimbo Unido</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Universitario de Deportes</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H30" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I30" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N30" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="X30" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BH30" t="inlineStr">
+        <is>
+          <t>2026-05-06 16:19:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Ind Medellin</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>5</v>
+      </c>
+      <c r="G31" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N31" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S31" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V31" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X31" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>23</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>42</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>160</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>90</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>95</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>140</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BH31" t="inlineStr">
+        <is>
+          <t>2026-05-06 16:19:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
           <t>23:00:00</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>Junior FC Barranquilla</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>Cerro Porteno</t>
         </is>
       </c>
-      <c r="F30" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="G30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H30" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="I30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J30" t="n">
+      <c r="F32" t="n">
         <v>1.04</v>
       </c>
-      <c r="K30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N30" t="n">
+      <c r="G32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N32" t="n">
         <v>1.26</v>
       </c>
-      <c r="O30" t="n">
+      <c r="O32" t="n">
         <v>1.43</v>
       </c>
-      <c r="P30" t="n">
+      <c r="P32" t="n">
         <v>1.25</v>
       </c>
-      <c r="Q30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R30" t="n">
+      <c r="Q32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R32" t="n">
         <v>1.18</v>
       </c>
-      <c r="S30" t="n">
+      <c r="S32" t="n">
         <v>1.02</v>
       </c>
-      <c r="T30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V30" t="n">
+      <c r="T32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V32" t="n">
         <v>1.02</v>
       </c>
-      <c r="W30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH30" t="inlineStr">
-        <is>
-          <t>2026-05-06 14:02:42</t>
+      <c r="W32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>2026-05-06 16:19:40</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-07.xlsx
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="G2" t="n">
         <v>2.68</v>
@@ -769,7 +769,7 @@
         <v>5.4</v>
       </c>
       <c r="J2" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="K2" t="n">
         <v>2.72</v>
@@ -784,7 +784,7 @@
         <v>1.92</v>
       </c>
       <c r="O2" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="P2" t="n">
         <v>1.26</v>
@@ -865,7 +865,7 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AQ2" t="n">
         <v>1.18</v>
@@ -913,14 +913,14 @@
         <v>1.18</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.18</v>
+        <v>1.55</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.18</v>
+        <v>1.55</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -954,13 +954,13 @@
         <v>3.4</v>
       </c>
       <c r="G3" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="H3" t="n">
         <v>2.3</v>
       </c>
       <c r="I3" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="J3" t="n">
         <v>2.98</v>
@@ -969,7 +969,7 @@
         <v>3.4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="M3" t="n">
         <v>1.12</v>
@@ -981,10 +981,10 @@
         <v>1.5</v>
       </c>
       <c r="P3" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="R3" t="n">
         <v>1.2</v>
@@ -1005,49 +1005,49 @@
         <v>1.35</v>
       </c>
       <c r="X3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="Y3" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="Z3" t="n">
-        <v>970</v>
+        <v>38</v>
       </c>
       <c r="AA3" t="n">
-        <v>40</v>
+        <v>900</v>
       </c>
       <c r="AB3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>13.5</v>
+        <v>21</v>
       </c>
       <c r="AE3" t="n">
-        <v>38</v>
+        <v>110</v>
       </c>
       <c r="AF3" t="n">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="AG3" t="n">
         <v>970</v>
       </c>
       <c r="AH3" t="n">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="AI3" t="n">
-        <v>70</v>
+        <v>460</v>
       </c>
       <c r="AJ3" t="n">
-        <v>90</v>
+        <v>900</v>
       </c>
       <c r="AK3" t="n">
-        <v>70</v>
+        <v>440</v>
       </c>
       <c r="AL3" t="n">
-        <v>95</v>
+        <v>460</v>
       </c>
       <c r="AM3" t="n">
         <v>200</v>
@@ -1056,10 +1056,10 @@
         <v>90</v>
       </c>
       <c r="AO3" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="AP3" t="n">
-        <v>7.2</v>
+        <v>4.6</v>
       </c>
       <c r="AQ3" t="n">
         <v>5.9</v>
@@ -1071,7 +1071,7 @@
         <v>26</v>
       </c>
       <c r="AT3" t="n">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="AU3" t="n">
         <v>6.2</v>
@@ -1083,38 +1083,38 @@
         <v>24</v>
       </c>
       <c r="AX3" t="n">
-        <v>5</v>
+        <v>10.5</v>
       </c>
       <c r="AY3" t="n">
         <v>13</v>
       </c>
       <c r="AZ3" t="n">
-        <v>5.3</v>
+        <v>11.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.7</v>
+        <v>7.8</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.7</v>
+        <v>8</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.6</v>
+        <v>7.8</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.7</v>
+        <v>8</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.9</v>
+        <v>8.6</v>
       </c>
       <c r="BF3" t="n">
-        <v>5.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG3" t="n">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -1151,10 +1151,10 @@
         <v>32</v>
       </c>
       <c r="H4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="J4" t="n">
         <v>5.4</v>
@@ -1166,19 +1166,19 @@
         <v>1.47</v>
       </c>
       <c r="M4" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N4" t="n">
         <v>3.05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="P4" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R4" t="n">
         <v>1.24</v>
@@ -1190,10 +1190,10 @@
         <v>3.4</v>
       </c>
       <c r="U4" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V4" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="W4" t="n">
         <v>1.03</v>
@@ -1208,31 +1208,31 @@
         <v>6.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AB4" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AC4" t="n">
-        <v>970</v>
+        <v>29</v>
       </c>
       <c r="AD4" t="n">
         <v>14.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>23</v>
+        <v>90</v>
       </c>
       <c r="AF4" t="n">
         <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>120</v>
+        <v>460</v>
       </c>
       <c r="AH4" t="n">
-        <v>90</v>
+        <v>380</v>
       </c>
       <c r="AI4" t="n">
-        <v>130</v>
+        <v>450</v>
       </c>
       <c r="AJ4" t="n">
         <v>1000</v>
@@ -1250,7 +1250,7 @@
         <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AP4" t="n">
         <v>10</v>
@@ -1265,7 +1265,7 @@
         <v>6.4</v>
       </c>
       <c r="AT4" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AU4" t="n">
         <v>12.5</v>
@@ -1274,41 +1274,41 @@
         <v>10.5</v>
       </c>
       <c r="AW4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB4" t="n">
         <v>5.6</v>
       </c>
-      <c r="AX4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BC4" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BD4" t="n">
-        <v>7.4</v>
+        <v>4.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF4" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG4" t="n">
         <v>6.2</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -1366,13 +1366,13 @@
         <v>4.1</v>
       </c>
       <c r="O5" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P5" t="n">
         <v>2.06</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="R5" t="n">
         <v>1.41</v>
@@ -1393,13 +1393,13 @@
         <v>2.34</v>
       </c>
       <c r="X5" t="n">
-        <v>970</v>
+        <v>90</v>
       </c>
       <c r="Y5" t="n">
         <v>970</v>
       </c>
       <c r="Z5" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AA5" t="n">
         <v>170</v>
@@ -1408,34 +1408,34 @@
         <v>11</v>
       </c>
       <c r="AC5" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AD5" t="n">
         <v>21</v>
       </c>
       <c r="AE5" t="n">
-        <v>85</v>
+        <v>400</v>
       </c>
       <c r="AF5" t="n">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="AH5" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="AI5" t="n">
-        <v>80</v>
+        <v>320</v>
       </c>
       <c r="AJ5" t="n">
-        <v>970</v>
+        <v>48</v>
       </c>
       <c r="AK5" t="n">
-        <v>970</v>
+        <v>65</v>
       </c>
       <c r="AL5" t="n">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="AM5" t="n">
         <v>130</v>
@@ -1444,65 +1444,65 @@
         <v>10.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>95</v>
+        <v>160</v>
       </c>
       <c r="AP5" t="n">
-        <v>15</v>
+        <v>7.6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="AR5" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.94</v>
+        <v>4.1</v>
       </c>
       <c r="AT5" t="n">
         <v>7.6</v>
       </c>
       <c r="AU5" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="AV5" t="n">
-        <v>5.3</v>
+        <v>10.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>3.35</v>
+        <v>7</v>
       </c>
       <c r="AX5" t="n">
         <v>6.8</v>
       </c>
       <c r="AY5" t="n">
-        <v>4.3</v>
+        <v>5.8</v>
       </c>
       <c r="AZ5" t="n">
-        <v>5.5</v>
+        <v>11.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>3.35</v>
+        <v>7</v>
       </c>
       <c r="BB5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BD5" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.94</v>
+        <v>4.1</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.9</v>
+        <v>7</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="G6" t="n">
         <v>200</v>
       </c>
       <c r="H6" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="I6" t="n">
         <v>250</v>
       </c>
       <c r="J6" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K6" t="n">
-        <v>950</v>
+        <v>100</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1581,122 +1581,122 @@
         <v>1.01</v>
       </c>
       <c r="V6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE6" t="n">
         <v>1.01</v>
       </c>
-      <c r="W6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>1.03</v>
-      </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -1727,19 +1727,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>1.87</v>
       </c>
       <c r="H7" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="J7" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="K7" t="n">
         <v>950</v>
@@ -1751,22 +1751,22 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P7" t="n">
         <v>1.07</v>
       </c>
-      <c r="O7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Q7" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="R7" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="S7" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="T7" t="n">
         <v>1.01</v>
@@ -1778,119 +1778,119 @@
         <v>1.01</v>
       </c>
       <c r="W7" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE7" t="n">
         <v>1.01</v>
       </c>
-      <c r="X7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.03</v>
-      </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="G8" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="H8" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="I8" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J8" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K8" t="n">
-        <v>950</v>
+        <v>100</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
@@ -1945,7 +1945,7 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>2.72</v>
+        <v>1.02</v>
       </c>
       <c r="O8" t="n">
         <v>1.01</v>
@@ -1960,7 +1960,7 @@
         <v>1.07</v>
       </c>
       <c r="S8" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
@@ -1969,122 +1969,122 @@
         <v>1.01</v>
       </c>
       <c r="V8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE8" t="n">
         <v>1.01</v>
       </c>
-      <c r="W8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.03</v>
-      </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.02</v>
+        <v>1.62</v>
       </c>
       <c r="G9" t="n">
-        <v>610</v>
+        <v>3.5</v>
       </c>
       <c r="H9" t="n">
-        <v>1.02</v>
+        <v>2.74</v>
       </c>
       <c r="I9" t="n">
-        <v>610</v>
+        <v>44</v>
       </c>
       <c r="J9" t="n">
-        <v>1.03</v>
+        <v>2.84</v>
       </c>
       <c r="K9" t="n">
-        <v>950</v>
+        <v>44</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2139,19 +2139,19 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="O9" t="n">
         <v>1.01</v>
       </c>
       <c r="P9" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Q9" t="n">
         <v>1.01</v>
       </c>
       <c r="R9" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="S9" t="n">
         <v>1.41</v>
@@ -2163,122 +2163,122 @@
         <v>1.01</v>
       </c>
       <c r="V9" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X9" t="n">
+        <v>90</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE9" t="n">
         <v>1.01</v>
       </c>
-      <c r="W9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>1.03</v>
-      </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="G10" t="n">
+        <v>95</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="I10" t="n">
+        <v>90</v>
+      </c>
+      <c r="J10" t="n">
         <v>1.04</v>
       </c>
-      <c r="G10" t="n">
-        <v>380</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I10" t="n">
-        <v>290</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1.03</v>
-      </c>
       <c r="K10" t="n">
-        <v>950</v>
+        <v>70</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2357,122 +2357,122 @@
         <v>1.01</v>
       </c>
       <c r="V10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE10" t="n">
         <v>1.01</v>
       </c>
-      <c r="W10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.03</v>
-      </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
         <v>1.78</v>
       </c>
       <c r="G11" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="H11" t="n">
         <v>5</v>
@@ -2515,7 +2515,7 @@
         <v>5.5</v>
       </c>
       <c r="J11" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K11" t="n">
         <v>4.1</v>
@@ -2533,7 +2533,7 @@
         <v>1.35</v>
       </c>
       <c r="P11" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="Q11" t="n">
         <v>2.02</v>
@@ -2554,7 +2554,7 @@
         <v>1.22</v>
       </c>
       <c r="W11" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="X11" t="n">
         <v>15.5</v>
@@ -2563,10 +2563,10 @@
         <v>19.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="AA11" t="n">
-        <v>160</v>
+        <v>900</v>
       </c>
       <c r="AB11" t="n">
         <v>9</v>
@@ -2575,10 +2575,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD11" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="AE11" t="n">
-        <v>90</v>
+        <v>400</v>
       </c>
       <c r="AF11" t="n">
         <v>12</v>
@@ -2590,7 +2590,7 @@
         <v>24</v>
       </c>
       <c r="AI11" t="n">
-        <v>90</v>
+        <v>320</v>
       </c>
       <c r="AJ11" t="n">
         <v>22</v>
@@ -2599,25 +2599,25 @@
         <v>23</v>
       </c>
       <c r="AL11" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AM11" t="n">
-        <v>140</v>
+        <v>390</v>
       </c>
       <c r="AN11" t="n">
-        <v>970</v>
+        <v>29</v>
       </c>
       <c r="AO11" t="n">
-        <v>110</v>
+        <v>310</v>
       </c>
       <c r="AP11" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4.9</v>
+        <v>8.4</v>
       </c>
       <c r="AR11" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AS11" t="n">
         <v>6.2</v>
@@ -2626,34 +2626,34 @@
         <v>7</v>
       </c>
       <c r="AU11" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="AV11" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="AW11" t="n">
         <v>6</v>
       </c>
       <c r="AX11" t="n">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="AY11" t="n">
-        <v>4.1</v>
+        <v>5.8</v>
       </c>
       <c r="AZ11" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BA11" t="n">
         <v>6</v>
       </c>
       <c r="BB11" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="BC11" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BD11" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BE11" t="n">
         <v>6.2</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -2739,19 +2739,19 @@
         <v>2.62</v>
       </c>
       <c r="T12" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="U12" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="V12" t="n">
         <v>1.45</v>
       </c>
       <c r="W12" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y12" t="n">
         <v>1000</v>
@@ -2760,7 +2760,7 @@
         <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB12" t="n">
         <v>1000</v>
@@ -2787,7 +2787,7 @@
         <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK12" t="n">
         <v>1000</v>
@@ -2805,62 +2805,62 @@
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -2891,19 +2891,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="G13" t="n">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="H13" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="I13" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="J13" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K13" t="n">
         <v>4.8</v>
@@ -2915,61 +2915,61 @@
         <v>1.04</v>
       </c>
       <c r="N13" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="O13" t="n">
         <v>1.22</v>
       </c>
       <c r="P13" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="S13" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="T13" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="U13" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V13" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="W13" t="n">
-        <v>2.26</v>
+        <v>2.46</v>
       </c>
       <c r="X13" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="Y13" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="Z13" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AA13" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AB13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AC13" t="n">
         <v>11</v>
       </c>
       <c r="AD13" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AE13" t="n">
-        <v>75</v>
+        <v>320</v>
       </c>
       <c r="AF13" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AG13" t="n">
         <v>12</v>
@@ -2978,83 +2978,83 @@
         <v>23</v>
       </c>
       <c r="AI13" t="n">
-        <v>70</v>
+        <v>250</v>
       </c>
       <c r="AJ13" t="n">
         <v>21</v>
       </c>
       <c r="AK13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL13" t="n">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="AM13" t="n">
-        <v>100</v>
+        <v>320</v>
       </c>
       <c r="AN13" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO13" t="n">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="AP13" t="n">
-        <v>15.5</v>
+        <v>4.8</v>
       </c>
       <c r="AQ13" t="n">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="AT13" t="n">
-        <v>3.55</v>
+        <v>6.2</v>
       </c>
       <c r="AU13" t="n">
-        <v>8.800000000000001</v>
+        <v>5.1</v>
       </c>
       <c r="AV13" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="AX13" t="n">
-        <v>3.65</v>
+        <v>6.2</v>
       </c>
       <c r="AY13" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AZ13" t="n">
         <v>13.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="BB13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BC13" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BD13" t="n">
         <v>20</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="BF13" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.6</v>
+        <v>42</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.04</v>
+        <v>2.3</v>
       </c>
       <c r="G14" t="n">
-        <v>570</v>
+        <v>90</v>
       </c>
       <c r="H14" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="I14" t="n">
-        <v>570</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
-        <v>1.02</v>
+        <v>2.52</v>
       </c>
       <c r="K14" t="n">
-        <v>950</v>
+        <v>70</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
@@ -3112,19 +3112,19 @@
         <v>1.26</v>
       </c>
       <c r="O14" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P14" t="n">
         <v>1.24</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="R14" t="n">
         <v>1.15</v>
       </c>
       <c r="S14" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="T14" t="n">
         <v>1.01</v>
@@ -3133,122 +3133,122 @@
         <v>1.01</v>
       </c>
       <c r="V14" t="n">
+        <v>2</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE14" t="n">
         <v>1.01</v>
       </c>
-      <c r="W14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>1.03</v>
-      </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -3285,10 +3285,10 @@
         <v>2.46</v>
       </c>
       <c r="H15" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I15" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J15" t="n">
         <v>3.3</v>
@@ -3297,7 +3297,7 @@
         <v>3.9</v>
       </c>
       <c r="L15" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
         <v>1.07</v>
@@ -3327,7 +3327,7 @@
         <v>2.14</v>
       </c>
       <c r="V15" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W15" t="n">
         <v>1.68</v>
@@ -3342,10 +3342,10 @@
         <v>29</v>
       </c>
       <c r="AA15" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AB15" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AC15" t="n">
         <v>9.800000000000001</v>
@@ -3354,7 +3354,7 @@
         <v>17.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AF15" t="n">
         <v>18.5</v>
@@ -3369,13 +3369,13 @@
         <v>60</v>
       </c>
       <c r="AJ15" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AK15" t="n">
         <v>32</v>
       </c>
       <c r="AL15" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AM15" t="n">
         <v>110</v>
@@ -3396,7 +3396,7 @@
         <v>17.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AT15" t="n">
         <v>7.6</v>
@@ -3408,7 +3408,7 @@
         <v>10.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AX15" t="n">
         <v>11</v>
@@ -3420,29 +3420,29 @@
         <v>12.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BB15" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BC15" t="n">
         <v>18</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BF15" t="n">
         <v>13.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -3476,16 +3476,16 @@
         <v>1.68</v>
       </c>
       <c r="G16" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="H16" t="n">
         <v>5</v>
       </c>
       <c r="I16" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J16" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="K16" t="n">
         <v>4.5</v>
@@ -3509,7 +3509,7 @@
         <v>1.74</v>
       </c>
       <c r="R16" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S16" t="n">
         <v>2.88</v>
@@ -3524,58 +3524,58 @@
         <v>1.21</v>
       </c>
       <c r="W16" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="X16" t="n">
         <v>22</v>
       </c>
       <c r="Y16" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="Z16" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="AA16" t="n">
-        <v>150</v>
+        <v>900</v>
       </c>
       <c r="AB16" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AC16" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD16" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="AE16" t="n">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AF16" t="n">
         <v>13</v>
       </c>
       <c r="AG16" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="AI16" t="n">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AJ16" t="n">
-        <v>21</v>
+        <v>900</v>
       </c>
       <c r="AK16" t="n">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="AL16" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AM16" t="n">
-        <v>110</v>
+        <v>580</v>
       </c>
       <c r="AN16" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO16" t="n">
         <v>80</v>
@@ -3587,10 +3587,10 @@
         <v>15.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AT16" t="n">
         <v>7.6</v>
@@ -3602,7 +3602,7 @@
         <v>15.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AX16" t="n">
         <v>8.800000000000001</v>
@@ -3614,7 +3614,7 @@
         <v>14.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BB16" t="n">
         <v>13.5</v>
@@ -3623,20 +3623,20 @@
         <v>13</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BF16" t="n">
         <v>7</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -3667,112 +3667,112 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="G17" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="H17" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="I17" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="J17" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K17" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L17" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M17" t="n">
         <v>1.05</v>
       </c>
       <c r="N17" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="O17" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="P17" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="R17" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="S17" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="T17" t="n">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="U17" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="V17" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="W17" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="X17" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Y17" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="Z17" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AA17" t="n">
-        <v>320</v>
+        <v>630</v>
       </c>
       <c r="AB17" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC17" t="n">
         <v>11</v>
       </c>
       <c r="AD17" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AE17" t="n">
-        <v>140</v>
+        <v>320</v>
       </c>
       <c r="AF17" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AG17" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH17" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="AI17" t="n">
-        <v>130</v>
+        <v>330</v>
       </c>
       <c r="AJ17" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AK17" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL17" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AM17" t="n">
-        <v>190</v>
+        <v>450</v>
       </c>
       <c r="AN17" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AO17" t="n">
-        <v>200</v>
+        <v>650</v>
       </c>
       <c r="AP17" t="n">
         <v>14.5</v>
@@ -3781,56 +3781,56 @@
         <v>21</v>
       </c>
       <c r="AR17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS17" t="n">
         <v>10</v>
       </c>
-      <c r="AS17" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AT17" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AU17" t="n">
         <v>9</v>
       </c>
       <c r="AV17" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AW17" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AX17" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AY17" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AZ17" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BA17" t="n">
         <v>10.5</v>
       </c>
       <c r="BB17" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BC17" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BD17" t="n">
         <v>28</v>
       </c>
       <c r="BE17" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF17" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG17" t="n">
         <v>11</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -3924,7 +3924,7 @@
         <v>44</v>
       </c>
       <c r="AA18" t="n">
-        <v>190</v>
+        <v>900</v>
       </c>
       <c r="AB18" t="n">
         <v>6.8</v>
@@ -3936,7 +3936,7 @@
         <v>26</v>
       </c>
       <c r="AE18" t="n">
-        <v>120</v>
+        <v>260</v>
       </c>
       <c r="AF18" t="n">
         <v>11</v>
@@ -3948,7 +3948,7 @@
         <v>25</v>
       </c>
       <c r="AI18" t="n">
-        <v>140</v>
+        <v>540</v>
       </c>
       <c r="AJ18" t="n">
         <v>25</v>
@@ -3957,7 +3957,7 @@
         <v>27</v>
       </c>
       <c r="AL18" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AM18" t="n">
         <v>210</v>
@@ -3975,10 +3975,10 @@
         <v>13</v>
       </c>
       <c r="AR18" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AS18" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT18" t="n">
         <v>5.7</v>
@@ -4002,7 +4002,7 @@
         <v>20</v>
       </c>
       <c r="BA18" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB18" t="n">
         <v>20</v>
@@ -4014,17 +4014,17 @@
         <v>7.8</v>
       </c>
       <c r="BE18" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BF18" t="n">
         <v>19</v>
       </c>
       <c r="BG18" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -4055,16 +4055,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="G19" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H19" t="n">
         <v>4.7</v>
       </c>
       <c r="I19" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J19" t="n">
         <v>3.3</v>
@@ -4097,16 +4097,16 @@
         <v>5.8</v>
       </c>
       <c r="T19" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="U19" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="V19" t="n">
         <v>1.23</v>
       </c>
       <c r="W19" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="X19" t="n">
         <v>8.4</v>
@@ -4154,7 +4154,7 @@
         <v>65</v>
       </c>
       <c r="AM19" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AN19" t="n">
         <v>26</v>
@@ -4163,7 +4163,7 @@
         <v>170</v>
       </c>
       <c r="AP19" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AQ19" t="n">
         <v>10.5</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -4249,22 +4249,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="G20" t="n">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="H20" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="I20" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="J20" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K20" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="L20" t="n">
         <v>1.01</v>
@@ -4273,13 +4273,13 @@
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="O20" t="n">
         <v>1.37</v>
       </c>
       <c r="P20" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Q20" t="n">
         <v>2</v>
@@ -4297,10 +4297,10 @@
         <v>1.01</v>
       </c>
       <c r="V20" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="W20" t="n">
-        <v>2.66</v>
+        <v>2.96</v>
       </c>
       <c r="X20" t="n">
         <v>1000</v>
@@ -4351,13 +4351,13 @@
         <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AO20" t="n">
         <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AQ20" t="n">
         <v>1.03</v>
@@ -4369,10 +4369,10 @@
         <v>1.03</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AV20" t="n">
         <v>1.03</v>
@@ -4381,38 +4381,38 @@
         <v>1.03</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BA20" t="n">
         <v>1.03</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -4446,19 +4446,19 @@
         <v>8.199999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="I21" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="J21" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="K21" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="L21" t="n">
         <v>1.18</v>
@@ -4467,28 +4467,28 @@
         <v>1.02</v>
       </c>
       <c r="N21" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="O21" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P21" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="R21" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="S21" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="T21" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="U21" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="V21" t="n">
         <v>3.6</v>
@@ -4497,7 +4497,7 @@
         <v>1.11</v>
       </c>
       <c r="X21" t="n">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="Y21" t="n">
         <v>15.5</v>
@@ -4509,52 +4509,52 @@
         <v>13.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="AC21" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AD21" t="n">
         <v>12</v>
       </c>
       <c r="AE21" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>540</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>85</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>38</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>260</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>240</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>160</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>320</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>320</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AP21" t="n">
         <v>16</v>
       </c>
-      <c r="AF21" t="n">
-        <v>110</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>36</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>27</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>290</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>130</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>100</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>6.2</v>
-      </c>
       <c r="AQ21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR21" t="n">
         <v>10</v>
@@ -4563,50 +4563,50 @@
         <v>10.5</v>
       </c>
       <c r="AT21" t="n">
-        <v>36</v>
+        <v>8.4</v>
       </c>
       <c r="AU21" t="n">
         <v>11</v>
       </c>
       <c r="AV21" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AW21" t="n">
         <v>11.5</v>
       </c>
       <c r="AX21" t="n">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="AY21" t="n">
-        <v>6.2</v>
+        <v>16</v>
       </c>
       <c r="AZ21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA21" t="n">
         <v>19</v>
       </c>
       <c r="BB21" t="n">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC21" t="n">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="BD21" t="n">
-        <v>6.6</v>
+        <v>28</v>
       </c>
       <c r="BE21" t="n">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="BF21" t="n">
-        <v>6.6</v>
+        <v>10.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -4637,64 +4637,64 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="G22" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="H22" t="n">
-        <v>2.98</v>
+        <v>6.4</v>
       </c>
       <c r="I22" t="n">
-        <v>870</v>
+        <v>90</v>
       </c>
       <c r="J22" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="K22" t="n">
-        <v>50</v>
+        <v>6.2</v>
       </c>
       <c r="L22" t="n">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="M22" t="n">
         <v>1.07</v>
       </c>
       <c r="N22" t="n">
-        <v>1.1</v>
+        <v>3.15</v>
       </c>
       <c r="O22" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="P22" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.92</v>
+        <v>2.2</v>
       </c>
       <c r="R22" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>1.05</v>
+        <v>3.85</v>
       </c>
       <c r="T22" t="n">
-        <v>2.2</v>
+        <v>2.58</v>
       </c>
       <c r="U22" t="n">
-        <v>1.67</v>
+        <v>1.51</v>
       </c>
       <c r="V22" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="W22" t="n">
-        <v>1.01</v>
+        <v>2.9</v>
       </c>
       <c r="X22" t="n">
         <v>970</v>
       </c>
       <c r="Y22" t="n">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="Z22" t="n">
         <v>1000</v>
@@ -4703,37 +4703,37 @@
         <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AC22" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AD22" t="n">
-        <v>42</v>
+        <v>180</v>
       </c>
       <c r="AE22" t="n">
         <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>970</v>
+        <v>7</v>
       </c>
       <c r="AG22" t="n">
         <v>970</v>
       </c>
       <c r="AH22" t="n">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="AI22" t="n">
         <v>1000</v>
       </c>
       <c r="AJ22" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK22" t="n">
         <v>970</v>
       </c>
-      <c r="AK22" t="n">
-        <v>21</v>
-      </c>
       <c r="AL22" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AM22" t="n">
         <v>1000</v>
@@ -4745,62 +4745,62 @@
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BF22" t="n">
         <v>3.9</v>
       </c>
-      <c r="AQ22" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>3.55</v>
-      </c>
       <c r="BG22" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -4837,16 +4837,16 @@
         <v>1.62</v>
       </c>
       <c r="H23" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="I23" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J23" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K23" t="n">
         <v>4.5</v>
-      </c>
-      <c r="K23" t="n">
-        <v>4.6</v>
       </c>
       <c r="L23" t="n">
         <v>1.29</v>
@@ -4858,7 +4858,7 @@
         <v>4.5</v>
       </c>
       <c r="O23" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P23" t="n">
         <v>2.18</v>
@@ -4867,10 +4867,10 @@
         <v>1.79</v>
       </c>
       <c r="R23" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="T23" t="n">
         <v>1.89</v>
@@ -4879,34 +4879,34 @@
         <v>2.06</v>
       </c>
       <c r="V23" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="W23" t="n">
         <v>2.6</v>
       </c>
       <c r="X23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Y23" t="n">
         <v>23</v>
       </c>
       <c r="Z23" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AA23" t="n">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="AB23" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC23" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AE23" t="n">
-        <v>80</v>
+        <v>190</v>
       </c>
       <c r="AF23" t="n">
         <v>9.6</v>
@@ -4915,7 +4915,7 @@
         <v>10.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI23" t="n">
         <v>80</v>
@@ -4924,10 +4924,10 @@
         <v>15</v>
       </c>
       <c r="AK23" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL23" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AM23" t="n">
         <v>110</v>
@@ -4936,7 +4936,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AO23" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AP23" t="n">
         <v>16</v>
@@ -4945,10 +4945,10 @@
         <v>20</v>
       </c>
       <c r="AR23" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AS23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT23" t="n">
         <v>8.800000000000001</v>
@@ -4960,13 +4960,13 @@
         <v>21</v>
       </c>
       <c r="AW23" t="n">
-        <v>14.5</v>
+        <v>65</v>
       </c>
       <c r="AX23" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AY23" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ23" t="n">
         <v>19</v>
@@ -4975,16 +4975,16 @@
         <v>65</v>
       </c>
       <c r="BB23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BC23" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BD23" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BE23" t="n">
-        <v>15.5</v>
+        <v>36</v>
       </c>
       <c r="BF23" t="n">
         <v>7.4</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -5025,13 +5025,13 @@
         </is>
       </c>
       <c r="F24" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" t="n">
         <v>2.02</v>
       </c>
-      <c r="G24" t="n">
-        <v>2.06</v>
-      </c>
       <c r="H24" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I24" t="n">
         <v>4.2</v>
@@ -5043,55 +5043,55 @@
         <v>3.85</v>
       </c>
       <c r="L24" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="M24" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N24" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="O24" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P24" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="R24" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="S24" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="T24" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="U24" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V24" t="n">
         <v>1.31</v>
       </c>
       <c r="W24" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="X24" t="n">
         <v>15.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z24" t="n">
         <v>30</v>
       </c>
       <c r="AA24" t="n">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="AB24" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AC24" t="n">
         <v>8.4</v>
@@ -5103,13 +5103,13 @@
         <v>55</v>
       </c>
       <c r="AF24" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG24" t="n">
         <v>10.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AI24" t="n">
         <v>60</v>
@@ -5124,28 +5124,28 @@
         <v>36</v>
       </c>
       <c r="AM24" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AN24" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AO24" t="n">
         <v>55</v>
       </c>
       <c r="AP24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ24" t="n">
         <v>13.5</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>14.5</v>
       </c>
       <c r="AR24" t="n">
         <v>27</v>
       </c>
       <c r="AS24" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="AT24" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU24" t="n">
         <v>8</v>
@@ -5154,13 +5154,13 @@
         <v>15</v>
       </c>
       <c r="AW24" t="n">
-        <v>13.5</v>
+        <v>44</v>
       </c>
       <c r="AX24" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AY24" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ24" t="n">
         <v>16.5</v>
@@ -5172,23 +5172,23 @@
         <v>19.5</v>
       </c>
       <c r="BC24" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BD24" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE24" t="n">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="BF24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BG24" t="n">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -5219,13 +5219,13 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="G25" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="H25" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="I25" t="n">
         <v>5.1</v>
@@ -5246,22 +5246,22 @@
         <v>4</v>
       </c>
       <c r="O25" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P25" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="R25" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S25" t="n">
         <v>3.45</v>
       </c>
       <c r="T25" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="U25" t="n">
         <v>2.08</v>
@@ -5270,13 +5270,13 @@
         <v>1.24</v>
       </c>
       <c r="W25" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="X25" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y25" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Z25" t="n">
         <v>38</v>
@@ -5294,7 +5294,7 @@
         <v>19</v>
       </c>
       <c r="AE25" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF25" t="n">
         <v>10.5</v>
@@ -5303,31 +5303,31 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AH25" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI25" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ25" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK25" t="n">
         <v>18.5</v>
       </c>
-      <c r="AK25" t="n">
-        <v>18</v>
-      </c>
       <c r="AL25" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM25" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN25" t="n">
         <v>11.5</v>
       </c>
       <c r="AO25" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AP25" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AQ25" t="n">
         <v>16</v>
@@ -5345,7 +5345,7 @@
         <v>8.6</v>
       </c>
       <c r="AV25" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AW25" t="n">
         <v>50</v>
@@ -5360,19 +5360,19 @@
         <v>19</v>
       </c>
       <c r="BA25" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BB25" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BC25" t="n">
         <v>17</v>
       </c>
       <c r="BD25" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BE25" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="BF25" t="n">
         <v>10.5</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -5419,16 +5419,16 @@
         <v>1.83</v>
       </c>
       <c r="H26" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I26" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J26" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K26" t="n">
         <v>3.9</v>
-      </c>
-      <c r="K26" t="n">
-        <v>3.95</v>
       </c>
       <c r="L26" t="n">
         <v>1.43</v>
@@ -5443,7 +5443,7 @@
         <v>1.35</v>
       </c>
       <c r="P26" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q26" t="n">
         <v>2.08</v>
@@ -5458,19 +5458,19 @@
         <v>1.97</v>
       </c>
       <c r="U26" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="V26" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W26" t="n">
         <v>2.2</v>
       </c>
       <c r="X26" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Z26" t="n">
         <v>38</v>
@@ -5521,7 +5521,7 @@
         <v>90</v>
       </c>
       <c r="AP26" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ26" t="n">
         <v>15</v>
@@ -5536,10 +5536,10 @@
         <v>7.8</v>
       </c>
       <c r="AU26" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AV26" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AW26" t="n">
         <v>60</v>
@@ -5557,7 +5557,7 @@
         <v>55</v>
       </c>
       <c r="BB26" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BC26" t="n">
         <v>18.5</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -5637,7 +5637,7 @@
         <v>1.39</v>
       </c>
       <c r="P27" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="Q27" t="n">
         <v>2.1</v>
@@ -5652,7 +5652,7 @@
         <v>2.42</v>
       </c>
       <c r="U27" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="V27" t="n">
         <v>1.07</v>
@@ -5664,7 +5664,7 @@
         <v>970</v>
       </c>
       <c r="Y27" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="Z27" t="n">
         <v>1000</v>
@@ -5676,28 +5676,28 @@
         <v>970</v>
       </c>
       <c r="AC27" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AD27" t="n">
-        <v>55</v>
+        <v>180</v>
       </c>
       <c r="AE27" t="n">
         <v>1000</v>
       </c>
       <c r="AF27" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AG27" t="n">
         <v>970</v>
       </c>
       <c r="AH27" t="n">
-        <v>44</v>
+        <v>190</v>
       </c>
       <c r="AI27" t="n">
         <v>1000</v>
       </c>
       <c r="AJ27" t="n">
-        <v>970</v>
+        <v>180</v>
       </c>
       <c r="AK27" t="n">
         <v>970</v>
@@ -5709,68 +5709,68 @@
         <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AO27" t="n">
         <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>2.3</v>
+        <v>5.8</v>
       </c>
       <c r="AQ27" t="n">
-        <v>2.1</v>
+        <v>10.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>2.22</v>
+        <v>4.2</v>
       </c>
       <c r="AS27" t="n">
-        <v>2.24</v>
+        <v>4.2</v>
       </c>
       <c r="AT27" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AU27" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="AV27" t="n">
-        <v>2.16</v>
+        <v>4.2</v>
       </c>
       <c r="AW27" t="n">
-        <v>2.24</v>
+        <v>4.2</v>
       </c>
       <c r="AX27" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AY27" t="n">
-        <v>3.2</v>
+        <v>6.4</v>
       </c>
       <c r="AZ27" t="n">
-        <v>2.14</v>
+        <v>4</v>
       </c>
       <c r="BA27" t="n">
-        <v>2.24</v>
+        <v>4.2</v>
       </c>
       <c r="BB27" t="n">
-        <v>4.9</v>
+        <v>8.6</v>
       </c>
       <c r="BC27" t="n">
-        <v>2.02</v>
+        <v>6</v>
       </c>
       <c r="BD27" t="n">
-        <v>2.18</v>
+        <v>3.4</v>
       </c>
       <c r="BE27" t="n">
-        <v>2.24</v>
+        <v>3</v>
       </c>
       <c r="BF27" t="n">
-        <v>2.76</v>
+        <v>3.8</v>
       </c>
       <c r="BG27" t="n">
-        <v>2.24</v>
+        <v>8.6</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -5801,10 +5801,10 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G28" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H28" t="n">
         <v>3.9</v>
@@ -5816,37 +5816,37 @@
         <v>3</v>
       </c>
       <c r="K28" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L28" t="n">
         <v>1.48</v>
       </c>
       <c r="M28" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N28" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="O28" t="n">
         <v>1.54</v>
       </c>
       <c r="P28" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="R28" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S28" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="T28" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="U28" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="V28" t="n">
         <v>1.29</v>
@@ -5861,10 +5861,10 @@
         <v>11</v>
       </c>
       <c r="Z28" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="AA28" t="n">
-        <v>130</v>
+        <v>900</v>
       </c>
       <c r="AB28" t="n">
         <v>7.2</v>
@@ -5876,7 +5876,7 @@
         <v>18.5</v>
       </c>
       <c r="AE28" t="n">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AF28" t="n">
         <v>13</v>
@@ -5888,16 +5888,16 @@
         <v>26</v>
       </c>
       <c r="AI28" t="n">
-        <v>120</v>
+        <v>260</v>
       </c>
       <c r="AJ28" t="n">
-        <v>34</v>
+        <v>900</v>
       </c>
       <c r="AK28" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AL28" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AM28" t="n">
         <v>240</v>
@@ -5918,7 +5918,7 @@
         <v>18</v>
       </c>
       <c r="AS28" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT28" t="n">
         <v>6</v>
@@ -5930,7 +5930,7 @@
         <v>15.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX28" t="n">
         <v>10.5</v>
@@ -5942,29 +5942,29 @@
         <v>20</v>
       </c>
       <c r="BA28" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB28" t="n">
-        <v>27</v>
+        <v>8.4</v>
       </c>
       <c r="BC28" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD28" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BE28" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF28" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BG28" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -5995,22 +5995,22 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="G29" t="n">
         <v>1.63</v>
       </c>
       <c r="H29" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="I29" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J29" t="n">
         <v>4.1</v>
       </c>
       <c r="K29" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L29" t="n">
         <v>1.38</v>
@@ -6019,13 +6019,13 @@
         <v>1.08</v>
       </c>
       <c r="N29" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O29" t="n">
         <v>1.38</v>
       </c>
       <c r="P29" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q29" t="n">
         <v>2.12</v>
@@ -6061,7 +6061,7 @@
         <v>290</v>
       </c>
       <c r="AB29" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AC29" t="n">
         <v>9.199999999999999</v>
@@ -6079,16 +6079,16 @@
         <v>10.5</v>
       </c>
       <c r="AH29" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AI29" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="AJ29" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AK29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL29" t="n">
         <v>48</v>
@@ -6106,25 +6106,25 @@
         <v>11</v>
       </c>
       <c r="AQ29" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AR29" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AS29" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AT29" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AU29" t="n">
         <v>8.6</v>
       </c>
       <c r="AV29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW29" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AX29" t="n">
         <v>7.6</v>
@@ -6148,17 +6148,17 @@
         <v>40</v>
       </c>
       <c r="BE29" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BF29" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BG29" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -6189,7 +6189,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G30" t="n">
         <v>2.4</v>
@@ -6252,7 +6252,7 @@
         <v>29</v>
       </c>
       <c r="AA30" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB30" t="n">
         <v>7.6</v>
@@ -6330,7 +6330,7 @@
         <v>19.5</v>
       </c>
       <c r="BA30" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB30" t="n">
         <v>8.4</v>
@@ -6339,7 +6339,7 @@
         <v>21</v>
       </c>
       <c r="BD30" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="BE30" t="n">
         <v>9.6</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -6383,16 +6383,16 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="G31" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="H31" t="n">
         <v>1.82</v>
       </c>
       <c r="I31" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="J31" t="n">
         <v>3.5</v>
@@ -6416,7 +6416,7 @@
         <v>1.69</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="R31" t="n">
         <v>1.25</v>
@@ -6446,7 +6446,7 @@
         <v>11</v>
       </c>
       <c r="AA31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB31" t="n">
         <v>15</v>
@@ -6461,13 +6461,13 @@
         <v>24</v>
       </c>
       <c r="AF31" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AG31" t="n">
         <v>22</v>
       </c>
       <c r="AH31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI31" t="n">
         <v>50</v>
@@ -6515,7 +6515,7 @@
         <v>19.5</v>
       </c>
       <c r="AX31" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AY31" t="n">
         <v>17.5</v>
@@ -6524,29 +6524,29 @@
         <v>19.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BB31" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC31" t="n">
         <v>9.6</v>
       </c>
-      <c r="BC31" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BD31" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE31" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF31" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BG31" t="n">
         <v>14.5</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -6589,7 +6589,7 @@
         <v>1000</v>
       </c>
       <c r="J32" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="K32" t="n">
         <v>1000</v>
@@ -6601,28 +6601,28 @@
         <v>1.01</v>
       </c>
       <c r="N32" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O32" t="n">
         <v>1.43</v>
       </c>
       <c r="P32" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="R32" t="n">
         <v>1.18</v>
       </c>
       <c r="S32" t="n">
-        <v>1.02</v>
+        <v>2.5</v>
       </c>
       <c r="T32" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U32" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V32" t="n">
         <v>1.02</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH32"/>
+  <dimension ref="A1:BH34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,7 +772,7 @@
         <v>2.36</v>
       </c>
       <c r="K2" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="L2" t="n">
         <v>1.69</v>
@@ -781,10 +781,10 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="O2" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="P2" t="n">
         <v>1.26</v>
@@ -838,7 +838,7 @@
         <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH2" t="n">
         <v>1000</v>
@@ -868,49 +868,49 @@
         <v>3.25</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AY2" t="n">
         <v>1.18</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="BF2" t="n">
         <v>1.55</v>
@@ -920,14 +920,14 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-06 18:35:36</t>
+          <t>2026-05-06 19:03:29</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>Jordanian Premier League</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,191 +937,191 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Paradou</t>
+          <t>Al-Jazeera</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="G3" t="n">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="H3" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="I3" t="n">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="J3" t="n">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="K3" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="L3" t="n">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="M3" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>2.64</v>
+        <v>3.05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="P3" t="n">
-        <v>1.55</v>
+        <v>1.79</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.48</v>
+        <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="S3" t="n">
-        <v>5.1</v>
+        <v>3.35</v>
       </c>
       <c r="T3" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="U3" t="n">
         <v>2.04</v>
       </c>
-      <c r="U3" t="n">
-        <v>1.79</v>
-      </c>
       <c r="V3" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="W3" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="X3" t="n">
-        <v>9.4</v>
+        <v>90</v>
       </c>
       <c r="Y3" t="n">
-        <v>8</v>
+        <v>500</v>
       </c>
       <c r="Z3" t="n">
-        <v>38</v>
+        <v>970</v>
       </c>
       <c r="AA3" t="n">
         <v>900</v>
       </c>
       <c r="AB3" t="n">
-        <v>11</v>
+        <v>500</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.6</v>
+        <v>14</v>
       </c>
       <c r="AD3" t="n">
-        <v>21</v>
+        <v>500</v>
       </c>
       <c r="AE3" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AF3" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AG3" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AH3" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AI3" t="n">
-        <v>460</v>
+        <v>500</v>
       </c>
       <c r="AJ3" t="n">
         <v>900</v>
       </c>
       <c r="AK3" t="n">
-        <v>440</v>
+        <v>500</v>
       </c>
       <c r="AL3" t="n">
-        <v>460</v>
+        <v>500</v>
       </c>
       <c r="AM3" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AN3" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AO3" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AP3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW3" t="n">
         <v>4.6</v>
       </c>
-      <c r="AQ3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>26</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AU3" t="n">
+      <c r="AX3" t="n">
         <v>6.2</v>
       </c>
-      <c r="AV3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AY3" t="n">
-        <v>13</v>
+        <v>7.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>11.5</v>
+        <v>6</v>
       </c>
       <c r="BA3" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BB3" t="n">
-        <v>8</v>
+        <v>5.2</v>
       </c>
       <c r="BC3" t="n">
-        <v>7.8</v>
+        <v>4.7</v>
       </c>
       <c r="BD3" t="n">
-        <v>8</v>
+        <v>3.35</v>
       </c>
       <c r="BE3" t="n">
-        <v>8.6</v>
+        <v>3.55</v>
       </c>
       <c r="BF3" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BG3" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-06 18:35:36</t>
+          <t>2026-05-06 19:03:29</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>Serbian First League</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1136,103 +1136,103 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Tekstilac Odzaci</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Fk Smederevo</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>19.5</v>
+        <v>1.04</v>
       </c>
       <c r="G4" t="n">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="H4" t="n">
-        <v>1.25</v>
+        <v>1.04</v>
       </c>
       <c r="I4" t="n">
-        <v>1.29</v>
+        <v>100</v>
       </c>
       <c r="J4" t="n">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="K4" t="n">
-        <v>6.4</v>
+        <v>100</v>
       </c>
       <c r="L4" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>3.05</v>
+        <v>1.02</v>
       </c>
       <c r="O4" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="P4" t="n">
-        <v>1.68</v>
+        <v>1.07</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="R4" t="n">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
       <c r="S4" t="n">
-        <v>4.2</v>
+        <v>1.05</v>
       </c>
       <c r="T4" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>4.4</v>
+        <v>1.02</v>
       </c>
       <c r="W4" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
         <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>460</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>380</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>450</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
         <v>1000</v>
@@ -1250,72 +1250,72 @@
         <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="AR4" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU4" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AV4" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW4" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="AX4" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AY4" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AZ4" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="BA4" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.6</v>
+        <v>1.03</v>
       </c>
       <c r="BC4" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BE4" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
-        <v>8.800000000000001</v>
+        <v>1.02</v>
       </c>
       <c r="BG4" t="n">
-        <v>6.2</v>
+        <v>1.02</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-06 18:35:36</t>
+          <t>2026-05-06 19:03:29</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Serbian First League</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1330,179 +1330,179 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FK Tukums 2000</t>
+          <t>SU Dinamo Jug</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>FK Usce Novi Beograd</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.62</v>
+        <v>1.05</v>
       </c>
       <c r="G5" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>2.04</v>
       </c>
       <c r="I5" t="n">
-        <v>5.9</v>
+        <v>180</v>
       </c>
       <c r="J5" t="n">
-        <v>4.1</v>
+        <v>2.32</v>
       </c>
       <c r="K5" t="n">
-        <v>4.9</v>
+        <v>950</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>4.1</v>
+        <v>1.02</v>
       </c>
       <c r="O5" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="P5" t="n">
-        <v>2.06</v>
+        <v>1.07</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="R5" t="n">
-        <v>1.41</v>
+        <v>1.07</v>
       </c>
       <c r="S5" t="n">
-        <v>2.98</v>
+        <v>1.39</v>
       </c>
       <c r="T5" t="n">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>2.34</v>
+        <v>1.71</v>
       </c>
       <c r="X5" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>320</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>48</v>
+        <v>900</v>
       </c>
       <c r="AK5" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA5" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.9</v>
+        <v>1.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.5</v>
+        <v>1.1</v>
       </c>
       <c r="BG5" t="n">
-        <v>7</v>
+        <v>1.55</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-06 18:35:36</t>
+          <t>2026-05-06 19:03:29</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-06 18:35:36</t>
+          <t>2026-05-06 19:03:29</t>
         </is>
       </c>
     </row>
@@ -1718,31 +1718,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SU Dinamo Jug</t>
+          <t>FK Dubocica</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FK Usce Novi Beograd</t>
+          <t>FK FAP</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.05</v>
+        <v>1.62</v>
       </c>
       <c r="G7" t="n">
-        <v>1.87</v>
+        <v>44</v>
       </c>
       <c r="H7" t="n">
-        <v>2.04</v>
+        <v>2.74</v>
       </c>
       <c r="I7" t="n">
-        <v>180</v>
+        <v>44</v>
       </c>
       <c r="J7" t="n">
-        <v>2.32</v>
+        <v>2.84</v>
       </c>
       <c r="K7" t="n">
-        <v>950</v>
+        <v>44</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -1754,19 +1754,19 @@
         <v>1.02</v>
       </c>
       <c r="O7" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="P7" t="n">
         <v>1.07</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="R7" t="n">
         <v>1.07</v>
       </c>
       <c r="S7" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="T7" t="n">
         <v>1.01</v>
@@ -1775,13 +1775,13 @@
         <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="W7" t="n">
-        <v>2.14</v>
+        <v>1.65</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y7" t="n">
         <v>1000</v>
@@ -1796,7 +1796,7 @@
         <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AD7" t="n">
         <v>1000</v>
@@ -1835,7 +1835,7 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AQ7" t="n">
         <v>1.03</v>
@@ -1883,21 +1883,21 @@
         <v>1.01</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="BG7" t="n">
         <v>1.55</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-06 18:35:36</t>
+          <t>2026-05-06 19:03:29</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Serbian First League</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1912,103 +1912,103 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Tekstilac Odzaci</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Fk Smederevo</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.04</v>
+        <v>19.5</v>
       </c>
       <c r="G8" t="n">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="H8" t="n">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="I8" t="n">
-        <v>100</v>
+        <v>1.29</v>
       </c>
       <c r="J8" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="K8" t="n">
-        <v>100</v>
+        <v>6.4</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N8" t="n">
-        <v>1.02</v>
+        <v>3.05</v>
       </c>
       <c r="O8" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="P8" t="n">
-        <v>1.07</v>
+        <v>1.68</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="R8" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="S8" t="n">
-        <v>1.05</v>
+        <v>4.2</v>
       </c>
       <c r="T8" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="U8" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="V8" t="n">
-        <v>1.02</v>
+        <v>4.4</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AF8" t="n">
         <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>460</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>450</v>
       </c>
       <c r="AJ8" t="n">
         <v>1000</v>
@@ -2026,72 +2026,72 @@
         <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.02</v>
+        <v>9</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.02</v>
+        <v>6.2</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-06 18:35:36</t>
+          <t>2026-05-06 19:03:29</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Serbian First League</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2106,186 +2106,186 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FK Dubocica</t>
+          <t>Paradou</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FK FAP</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.62</v>
+        <v>3.4</v>
       </c>
       <c r="G9" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="H9" t="n">
-        <v>2.74</v>
+        <v>2.3</v>
       </c>
       <c r="I9" t="n">
-        <v>44</v>
+        <v>2.6</v>
       </c>
       <c r="J9" t="n">
-        <v>2.84</v>
+        <v>2.98</v>
       </c>
       <c r="K9" t="n">
-        <v>44</v>
+        <v>3.4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N9" t="n">
-        <v>1.09</v>
+        <v>2.64</v>
       </c>
       <c r="O9" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="P9" t="n">
-        <v>1.09</v>
+        <v>1.55</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="R9" t="n">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="S9" t="n">
-        <v>1.41</v>
+        <v>5.1</v>
       </c>
       <c r="T9" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="V9" t="n">
-        <v>1.19</v>
+        <v>1.63</v>
       </c>
       <c r="W9" t="n">
-        <v>1.51</v>
+        <v>1.33</v>
       </c>
       <c r="X9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF9" t="n">
         <v>90</v>
       </c>
-      <c r="Y9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>42</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1000</v>
-      </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>460</v>
       </c>
       <c r="AJ9" t="n">
         <v>900</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>440</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>460</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP9" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.03</v>
+        <v>26</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.03</v>
+        <v>24</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.55</v>
+        <v>7.2</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-06 18:35:36</t>
+          <t>2026-05-06 19:03:29</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Finnish Kakkonen</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,191 +2295,191 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>SJK Akatemia 2</t>
+          <t>FK Tukums 2000</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Huima</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.07</v>
+        <v>1.62</v>
       </c>
       <c r="G10" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="H10" t="n">
+        <v>5</v>
+      </c>
+      <c r="I10" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="X10" t="n">
+        <v>90</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>120</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>170</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>400</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>36</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>44</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>320</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL10" t="n">
         <v>95</v>
       </c>
-      <c r="H10" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="I10" t="n">
-        <v>90</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="K10" t="n">
-        <v>70</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>1000</v>
-      </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.05</v>
+        <v>7.8</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.05</v>
+        <v>8</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-06 18:35:36</t>
+          <t>2026-05-06 19:03:29</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Finnish Ykkosliiga</t>
+          <t>Finnish Kakkonen</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2494,186 +2494,186 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>PK-35 RY</t>
+          <t>SJK Akatemia 2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Huima</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.78</v>
+        <v>1.08</v>
       </c>
       <c r="G11" t="n">
-        <v>1.82</v>
+        <v>95</v>
       </c>
       <c r="H11" t="n">
-        <v>5</v>
+        <v>1.07</v>
       </c>
       <c r="I11" t="n">
-        <v>5.5</v>
+        <v>90</v>
       </c>
       <c r="J11" t="n">
-        <v>3.65</v>
+        <v>1.04</v>
       </c>
       <c r="K11" t="n">
-        <v>4.1</v>
+        <v>70</v>
       </c>
       <c r="L11" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="M11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="O11" t="n">
         <v>1.08</v>
       </c>
-      <c r="N11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.35</v>
-      </c>
       <c r="P11" t="n">
-        <v>1.83</v>
+        <v>1.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.02</v>
+        <v>1.08</v>
       </c>
       <c r="R11" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="S11" t="n">
-        <v>3.55</v>
+        <v>1.08</v>
       </c>
       <c r="T11" t="n">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="U11" t="n">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>1.22</v>
+        <v>1.02</v>
       </c>
       <c r="W11" t="n">
-        <v>2.22</v>
+        <v>1.02</v>
       </c>
       <c r="X11" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD11" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI11" t="n">
-        <v>320</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
-        <v>390</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>310</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ11" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AR11" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AT11" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AU11" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="AV11" t="n">
-        <v>5.7</v>
+        <v>1.03</v>
       </c>
       <c r="AW11" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AX11" t="n">
-        <v>5.6</v>
+        <v>1.03</v>
       </c>
       <c r="AY11" t="n">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="AZ11" t="n">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="BA11" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="BB11" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="BC11" t="n">
-        <v>5.6</v>
+        <v>1.03</v>
       </c>
       <c r="BD11" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="BE11" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.5</v>
+        <v>1.05</v>
       </c>
       <c r="BG11" t="n">
-        <v>6.2</v>
+        <v>1.05</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-06 18:35:36</t>
+          <t>2026-05-06 19:03:29</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Moroccan Botola Pro 1</t>
+          <t>Finnish Ykkosliiga</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2688,186 +2688,186 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>DHJ El Jadida</t>
+          <t>PK-35 RY</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>HUSA Agadir</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>1.78</v>
       </c>
       <c r="G12" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="H12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N12" t="n">
         <v>3.45</v>
       </c>
-      <c r="H12" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="I12" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N12" t="n">
-        <v>2.42</v>
-      </c>
       <c r="O12" t="n">
-        <v>1.59</v>
+        <v>1.35</v>
       </c>
       <c r="P12" t="n">
-        <v>1.36</v>
+        <v>1.85</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.62</v>
+        <v>2.02</v>
       </c>
       <c r="R12" t="n">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="S12" t="n">
-        <v>2.62</v>
+        <v>3.55</v>
       </c>
       <c r="T12" t="n">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="U12" t="n">
-        <v>1.35</v>
+        <v>1.94</v>
       </c>
       <c r="V12" t="n">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
       <c r="W12" t="n">
-        <v>1.41</v>
+        <v>2.22</v>
       </c>
       <c r="X12" t="n">
-        <v>90</v>
+        <v>15.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AA12" t="n">
         <v>900</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD12" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AJ12" t="n">
-        <v>900</v>
+        <v>22</v>
       </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>390</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AP12" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.06</v>
+        <v>8.4</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.06</v>
+        <v>7.4</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.06</v>
+        <v>7.4</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.06</v>
+        <v>7</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.06</v>
+        <v>4.9</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.06</v>
+        <v>6.2</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.06</v>
+        <v>7</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.06</v>
+        <v>5.6</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.06</v>
+        <v>5.8</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.06</v>
+        <v>6.2</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.06</v>
+        <v>7</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.06</v>
+        <v>9</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.06</v>
+        <v>6.2</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.06</v>
+        <v>7.2</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.06</v>
+        <v>7.2</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.55</v>
+        <v>4.9</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.55</v>
+        <v>7.2</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-06 18:35:36</t>
+          <t>2026-05-06 19:03:29</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Polish I Liga</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2882,186 +2882,186 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LKS Lodz</t>
+          <t>DHJ El Jadida</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pogon Grodzisk Mazowiecki</t>
+          <t>HUSA Agadir</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="G13" t="n">
-        <v>1.68</v>
+        <v>3.45</v>
       </c>
       <c r="H13" t="n">
-        <v>5.7</v>
+        <v>2.88</v>
       </c>
       <c r="I13" t="n">
-        <v>6.6</v>
+        <v>3.25</v>
       </c>
       <c r="J13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X13" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP13" t="n">
         <v>4.2</v>
       </c>
-      <c r="K13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="X13" t="n">
-        <v>40</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>28</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>120</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>150</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>27</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>320</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>250</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>19</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>320</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>120</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>4.8</v>
-      </c>
       <c r="AQ13" t="n">
-        <v>11.5</v>
+        <v>1.06</v>
       </c>
       <c r="AR13" t="n">
-        <v>5.5</v>
+        <v>1.06</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.9</v>
+        <v>1.06</v>
       </c>
       <c r="AT13" t="n">
-        <v>6.2</v>
+        <v>1.06</v>
       </c>
       <c r="AU13" t="n">
-        <v>5.1</v>
+        <v>1.06</v>
       </c>
       <c r="AV13" t="n">
-        <v>17</v>
+        <v>1.06</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.6</v>
+        <v>1.06</v>
       </c>
       <c r="AX13" t="n">
-        <v>6.2</v>
+        <v>1.06</v>
       </c>
       <c r="AY13" t="n">
-        <v>8.4</v>
+        <v>1.06</v>
       </c>
       <c r="AZ13" t="n">
-        <v>13.5</v>
+        <v>1.06</v>
       </c>
       <c r="BA13" t="n">
-        <v>5.6</v>
+        <v>1.06</v>
       </c>
       <c r="BB13" t="n">
-        <v>12</v>
+        <v>1.06</v>
       </c>
       <c r="BC13" t="n">
-        <v>11.5</v>
+        <v>1.06</v>
       </c>
       <c r="BD13" t="n">
-        <v>20</v>
+        <v>1.06</v>
       </c>
       <c r="BE13" t="n">
-        <v>5.8</v>
+        <v>1.06</v>
       </c>
       <c r="BF13" t="n">
-        <v>6.6</v>
+        <v>1.55</v>
       </c>
       <c r="BG13" t="n">
-        <v>42</v>
+        <v>1.55</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-06 18:35:36</t>
+          <t>2026-05-06 19:03:29</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Romanian Liga II</t>
+          <t>Polish I Liga</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3076,186 +3076,186 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CSA Steaua Bucuresti</t>
+          <t>LKS Lodz</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ACS Sepsi OSK</t>
+          <t>Pogon Grodzisk Mazowiecki</t>
         </is>
       </c>
       <c r="F14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H14" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="I14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P14" t="n">
         <v>2.3</v>
       </c>
-      <c r="G14" t="n">
-        <v>90</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="I14" t="n">
-        <v>2</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="K14" t="n">
-        <v>70</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.24</v>
-      </c>
       <c r="Q14" t="n">
-        <v>1.28</v>
+        <v>1.63</v>
       </c>
       <c r="R14" t="n">
-        <v>1.15</v>
+        <v>1.52</v>
       </c>
       <c r="S14" t="n">
-        <v>1.28</v>
+        <v>2.58</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="V14" t="n">
-        <v>2</v>
+        <v>1.17</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>2.46</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM14" t="n">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.05</v>
+        <v>6.6</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.05</v>
+        <v>42</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-06 18:35:36</t>
+          <t>2026-05-06 19:03:29</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Turkish 1 Lig</t>
+          <t>Romanian Liga II</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,191 +3265,191 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Bodrum Belediyesi Bodrumspor</t>
+          <t>CSA Steaua Bucuresti</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>ACS Sepsi OSK</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="G15" t="n">
-        <v>2.46</v>
+        <v>90</v>
       </c>
       <c r="H15" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="I15" t="n">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
-        <v>3.3</v>
+        <v>2.52</v>
       </c>
       <c r="K15" t="n">
-        <v>3.9</v>
+        <v>70</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N15" t="n">
-        <v>3.7</v>
+        <v>1.25</v>
       </c>
       <c r="O15" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="P15" t="n">
-        <v>1.91</v>
+        <v>1.24</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.92</v>
+        <v>1.28</v>
       </c>
       <c r="R15" t="n">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="S15" t="n">
-        <v>3.3</v>
+        <v>1.28</v>
       </c>
       <c r="T15" t="n">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="U15" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>1.37</v>
+        <v>2</v>
       </c>
       <c r="W15" t="n">
-        <v>1.68</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Z15" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC15" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD15" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH15" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI15" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM15" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ15" t="n">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AR15" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS15" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="AT15" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AU15" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AV15" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="AX15" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AY15" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AZ15" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="BB15" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC15" t="n">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF15" t="n">
-        <v>13.5</v>
+        <v>1.05</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.6</v>
+        <v>1.05</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-06 18:35:36</t>
+          <t>2026-05-06 19:03:29</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Turkish 1 Lig</t>
+          <t>Jordanian Premier League</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,191 +3459,191 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:45:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Corum Belediyespor</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Keciorengucu</t>
+          <t>Al Buqaa</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="G16" t="n">
-        <v>1.76</v>
+        <v>2.44</v>
       </c>
       <c r="H16" t="n">
-        <v>5</v>
+        <v>2.92</v>
       </c>
       <c r="I16" t="n">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="J16" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="K16" t="n">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>4.3</v>
+        <v>1.77</v>
       </c>
       <c r="O16" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="P16" t="n">
-        <v>2.16</v>
+        <v>1.77</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="R16" t="n">
-        <v>1.46</v>
+        <v>1.18</v>
       </c>
       <c r="S16" t="n">
-        <v>2.88</v>
+        <v>1.72</v>
       </c>
       <c r="T16" t="n">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="U16" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="W16" t="n">
-        <v>2.28</v>
+        <v>1.69</v>
       </c>
       <c r="X16" t="n">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="Y16" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="Z16" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD16" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AE16" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH16" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AI16" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AM16" t="n">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AQ16" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR16" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AS16" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AT16" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU16" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV16" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW16" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AX16" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AY16" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA16" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB16" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC16" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BD16" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE16" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BF16" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BG16" t="n">
-        <v>9</v>
+        <v>1.55</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-06 18:35:36</t>
+          <t>2026-05-06 19:03:29</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Turkish 1 Lig</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3658,186 +3658,186 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>FK Auda</t>
+          <t>Bodrum Belediyesi Bodrumspor</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SC Grobina</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.44</v>
+        <v>2.26</v>
       </c>
       <c r="G17" t="n">
-        <v>1.52</v>
+        <v>2.46</v>
       </c>
       <c r="H17" t="n">
-        <v>7.8</v>
+        <v>3.3</v>
       </c>
       <c r="I17" t="n">
-        <v>9.6</v>
+        <v>3.7</v>
       </c>
       <c r="J17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="X17" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS17" t="n">
         <v>4.5</v>
       </c>
-      <c r="K17" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N17" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W17" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="X17" t="n">
-        <v>17</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>32</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>160</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>630</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC17" t="n">
+      <c r="AT17" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX17" t="n">
         <v>11</v>
       </c>
-      <c r="AD17" t="n">
-        <v>34</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>320</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>48</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>330</v>
-      </c>
-      <c r="AJ17" t="n">
+      <c r="AY17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BF17" t="n">
         <v>13.5</v>
       </c>
-      <c r="AK17" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>450</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>8</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>650</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>21</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>26</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>11</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>22</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>11</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>14</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>28</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>11</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BG17" t="n">
-        <v>11</v>
+        <v>4.6</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-06 18:35:36</t>
+          <t>2026-05-06 19:03:29</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Turkish 1 Lig</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3852,179 +3852,179 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>National Bank</t>
+          <t>Corum Belediyespor</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ismaily</t>
+          <t>Keciorengucu</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="H18" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="I18" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="J18" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="K18" t="n">
-        <v>3.45</v>
+        <v>4.6</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M18" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>2.72</v>
+        <v>4.3</v>
       </c>
       <c r="O18" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="P18" t="n">
-        <v>1.55</v>
+        <v>2.16</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.5</v>
+        <v>1.74</v>
       </c>
       <c r="R18" t="n">
-        <v>1.2</v>
+        <v>1.46</v>
       </c>
       <c r="S18" t="n">
-        <v>4.8</v>
+        <v>2.88</v>
       </c>
       <c r="T18" t="n">
-        <v>2.1</v>
+        <v>1.76</v>
       </c>
       <c r="U18" t="n">
-        <v>1.76</v>
+        <v>2.12</v>
       </c>
       <c r="V18" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="W18" t="n">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="X18" t="n">
-        <v>9.6</v>
+        <v>22</v>
       </c>
       <c r="Y18" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="Z18" t="n">
-        <v>44</v>
+        <v>120</v>
       </c>
       <c r="AA18" t="n">
         <v>900</v>
       </c>
       <c r="AB18" t="n">
-        <v>6.8</v>
+        <v>10</v>
       </c>
       <c r="AC18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>170</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>80</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY18" t="n">
         <v>7.8</v>
       </c>
-      <c r="AD18" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>260</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>540</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>120</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>210</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>23</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>190</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>9.4</v>
-      </c>
       <c r="AZ18" t="n">
-        <v>20</v>
+        <v>14.5</v>
       </c>
       <c r="BA18" t="n">
         <v>8.6</v>
       </c>
       <c r="BB18" t="n">
-        <v>20</v>
+        <v>13.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="BD18" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BE18" t="n">
         <v>9</v>
       </c>
       <c r="BF18" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="BG18" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-06 18:35:36</t>
+          <t>2026-05-06 19:03:29</t>
         </is>
       </c>
     </row>
@@ -4046,186 +4046,186 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>National Bank</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ZED FC</t>
+          <t>Ismaily</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
       <c r="G19" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="H19" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="I19" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="J19" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="K19" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L19" t="n">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="M19" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="N19" t="n">
-        <v>2.56</v>
+        <v>2.72</v>
       </c>
       <c r="O19" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="P19" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S19" t="n">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="T19" t="n">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="U19" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="V19" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="W19" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="X19" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="Y19" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Z19" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AA19" t="n">
-        <v>150</v>
+        <v>900</v>
       </c>
       <c r="AB19" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AC19" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AE19" t="n">
-        <v>110</v>
+        <v>260</v>
       </c>
       <c r="AF19" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AG19" t="n">
         <v>11.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AI19" t="n">
-        <v>220</v>
+        <v>540</v>
       </c>
       <c r="AJ19" t="n">
         <v>25</v>
       </c>
       <c r="AK19" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AL19" t="n">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="AM19" t="n">
-        <v>240</v>
+        <v>210</v>
       </c>
       <c r="AN19" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AO19" t="n">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="AP19" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD19" t="n">
         <v>8</v>
       </c>
-      <c r="AQ19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>18</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>25</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>11</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>25</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>10</v>
-      </c>
       <c r="BE19" t="n">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="BF19" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BG19" t="n">
-        <v>11.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-06 18:35:36</t>
+          <t>2026-05-06 19:03:29</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Moroccan Botola Pro 1</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,191 +4235,191 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Union de Touarga</t>
+          <t>ZED FC</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.39</v>
+        <v>1.96</v>
       </c>
       <c r="G20" t="n">
-        <v>1.51</v>
+        <v>2.04</v>
       </c>
       <c r="H20" t="n">
-        <v>6.8</v>
+        <v>4.7</v>
       </c>
       <c r="I20" t="n">
-        <v>14.5</v>
+        <v>5.2</v>
       </c>
       <c r="J20" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="K20" t="n">
-        <v>6.2</v>
+        <v>3.45</v>
       </c>
       <c r="L20" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="M20" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N20" t="n">
-        <v>1.64</v>
+        <v>2.56</v>
       </c>
       <c r="O20" t="n">
-        <v>1.37</v>
+        <v>1.57</v>
       </c>
       <c r="P20" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="Q20" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="R20" t="n">
         <v>1.18</v>
       </c>
       <c r="S20" t="n">
-        <v>2</v>
+        <v>5.8</v>
       </c>
       <c r="T20" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="U20" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="V20" t="n">
-        <v>1.07</v>
+        <v>1.23</v>
       </c>
       <c r="W20" t="n">
-        <v>2.96</v>
+        <v>1.96</v>
       </c>
       <c r="X20" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="Y20" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z20" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA20" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB20" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="AC20" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE20" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF20" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG20" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI20" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK20" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL20" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM20" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AN20" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="AO20" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.02</v>
+        <v>8</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.02</v>
+        <v>5.8</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.02</v>
+        <v>7</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.02</v>
+        <v>9.4</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.02</v>
+        <v>10.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.02</v>
+        <v>25</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.02</v>
+        <v>18.5</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.02</v>
+        <v>25</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.02</v>
+        <v>10</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.02</v>
+        <v>11.5</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.05</v>
+        <v>21</v>
       </c>
       <c r="BG20" t="n">
-        <v>3.9</v>
+        <v>11.5</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-06 18:35:36</t>
+          <t>2026-05-06 19:03:29</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,191 +4429,191 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Al-Shabab (KSA)</t>
+          <t>FK Auda</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>SC Grobina</t>
         </is>
       </c>
       <c r="F21" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="H21" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="I21" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K21" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="X21" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>32</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>160</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>630</v>
+      </c>
+      <c r="AB21" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="G21" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="H21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="J21" t="n">
-        <v>6</v>
-      </c>
-      <c r="K21" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N21" t="n">
+      <c r="AC21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>36</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>320</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>48</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>330</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>450</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>650</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>26</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX21" t="n">
         <v>7.2</v>
       </c>
-      <c r="O21" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="P21" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="S21" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="V21" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X21" t="n">
-        <v>95</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>100</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>540</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>85</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>38</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>260</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>240</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>160</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>320</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>320</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS21" t="n">
+      <c r="AY21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA21" t="n">
         <v>10.5</v>
       </c>
-      <c r="AT21" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU21" t="n">
+      <c r="BB21" t="n">
         <v>11</v>
       </c>
-      <c r="AV21" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>16</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>19</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BC21" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="BD21" t="n">
         <v>28</v>
       </c>
       <c r="BE21" t="n">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="BF21" t="n">
-        <v>10.5</v>
+        <v>6.6</v>
       </c>
       <c r="BG21" t="n">
-        <v>3.45</v>
+        <v>11</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-06 18:35:36</t>
+          <t>2026-05-06 19:03:29</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4623,78 +4623,78 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Union de Touarga</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="G22" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="H22" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I22" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K22" t="n">
         <v>6.4</v>
       </c>
-      <c r="I22" t="n">
-        <v>90</v>
-      </c>
-      <c r="J22" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="K22" t="n">
-        <v>6.2</v>
-      </c>
       <c r="L22" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>3.15</v>
+        <v>1.64</v>
       </c>
       <c r="O22" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="P22" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="R22" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="S22" t="n">
-        <v>3.85</v>
+        <v>2</v>
       </c>
       <c r="T22" t="n">
-        <v>2.58</v>
+        <v>1.01</v>
       </c>
       <c r="U22" t="n">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="V22" t="n">
         <v>1.07</v>
       </c>
       <c r="W22" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="X22" t="n">
-        <v>970</v>
+        <v>90</v>
       </c>
       <c r="Y22" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="Z22" t="n">
         <v>1000</v>
@@ -4703,111 +4703,111 @@
         <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AC22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN22" t="n">
         <v>42</v>
       </c>
-      <c r="AD22" t="n">
-        <v>180</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>7</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>120</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>970</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>970</v>
-      </c>
       <c r="AO22" t="n">
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>6.2</v>
+        <v>1.02</v>
       </c>
       <c r="AQ22" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="AR22" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AS22" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="AT22" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="AU22" t="n">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="AV22" t="n">
-        <v>5.3</v>
+        <v>4.2</v>
       </c>
       <c r="AW22" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="AX22" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="AY22" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AZ22" t="n">
-        <v>5.3</v>
+        <v>1.03</v>
       </c>
       <c r="BA22" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="BB22" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BC22" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="BE22" t="n">
-        <v>5.5</v>
+        <v>1.03</v>
       </c>
       <c r="BF22" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BG22" t="n">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-06 18:35:36</t>
+          <t>2026-05-06 19:03:29</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,191 +4817,191 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Al-Shabab (KSA)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Shakhtar</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.61</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>1.62</v>
+        <v>9.4</v>
       </c>
       <c r="H23" t="n">
-        <v>6.4</v>
+        <v>1.34</v>
       </c>
       <c r="I23" t="n">
-        <v>6.6</v>
+        <v>1.38</v>
       </c>
       <c r="J23" t="n">
-        <v>4.4</v>
+        <v>5.9</v>
       </c>
       <c r="K23" t="n">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="L23" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="M23" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="N23" t="n">
-        <v>4.5</v>
+        <v>7.4</v>
       </c>
       <c r="O23" t="n">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="P23" t="n">
-        <v>2.18</v>
+        <v>3.15</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.79</v>
+        <v>1.42</v>
       </c>
       <c r="R23" t="n">
-        <v>1.46</v>
+        <v>1.89</v>
       </c>
       <c r="S23" t="n">
-        <v>2.92</v>
+        <v>1.88</v>
       </c>
       <c r="T23" t="n">
-        <v>1.89</v>
+        <v>1.66</v>
       </c>
       <c r="U23" t="n">
-        <v>2.06</v>
+        <v>2.26</v>
       </c>
       <c r="V23" t="n">
-        <v>1.17</v>
+        <v>3.6</v>
       </c>
       <c r="W23" t="n">
-        <v>2.6</v>
+        <v>1.11</v>
       </c>
       <c r="X23" t="n">
-        <v>20</v>
+        <v>95</v>
       </c>
       <c r="Y23" t="n">
-        <v>23</v>
+        <v>15.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>55</v>
+        <v>12.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>200</v>
+        <v>13.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>9.800000000000001</v>
+        <v>100</v>
       </c>
       <c r="AC23" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>540</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>75</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>38</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>260</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>240</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>390</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>320</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>320</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR23" t="n">
         <v>10</v>
       </c>
-      <c r="AD23" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>190</v>
-      </c>
-      <c r="AF23" t="n">
+      <c r="AS23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>19</v>
+      </c>
+      <c r="BB23" t="n">
         <v>9.6</v>
       </c>
-      <c r="AG23" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>15</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>90</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>20</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>38</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>15</v>
-      </c>
-      <c r="AT23" t="n">
+      <c r="BC23" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD23" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AU23" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>65</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>65</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>14</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>14</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>30</v>
-      </c>
       <c r="BE23" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="BF23" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="BG23" t="n">
-        <v>70</v>
+        <v>3.45</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-06 18:35:36</t>
+          <t>2026-05-06 19:03:29</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5016,186 +5016,186 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2</v>
+        <v>1.38</v>
       </c>
       <c r="G24" t="n">
-        <v>2.02</v>
+        <v>1.5</v>
       </c>
       <c r="H24" t="n">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="I24" t="n">
-        <v>4.2</v>
+        <v>19.5</v>
       </c>
       <c r="J24" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="K24" t="n">
-        <v>3.85</v>
+        <v>6.6</v>
       </c>
       <c r="L24" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="M24" t="n">
         <v>1.07</v>
       </c>
       <c r="N24" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S24" t="n">
         <v>3.85</v>
       </c>
-      <c r="O24" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.6</v>
-      </c>
       <c r="T24" t="n">
-        <v>1.83</v>
+        <v>2.58</v>
       </c>
       <c r="U24" t="n">
-        <v>2.14</v>
+        <v>1.51</v>
       </c>
       <c r="V24" t="n">
-        <v>1.31</v>
+        <v>1.08</v>
       </c>
       <c r="W24" t="n">
-        <v>1.98</v>
+        <v>2.94</v>
       </c>
       <c r="X24" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="Y24" t="n">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="Z24" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AA24" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>9.6</v>
+        <v>970</v>
       </c>
       <c r="AC24" t="n">
-        <v>8.4</v>
+        <v>42</v>
       </c>
       <c r="AD24" t="n">
-        <v>16.5</v>
+        <v>180</v>
       </c>
       <c r="AE24" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>12.5</v>
+        <v>7</v>
       </c>
       <c r="AG24" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AH24" t="n">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="AI24" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ24" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AK24" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AL24" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AM24" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AO24" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>13</v>
+        <v>6.2</v>
       </c>
       <c r="AQ24" t="n">
-        <v>13.5</v>
+        <v>5.5</v>
       </c>
       <c r="AR24" t="n">
-        <v>27</v>
+        <v>4.2</v>
       </c>
       <c r="AS24" t="n">
-        <v>28</v>
+        <v>4.2</v>
       </c>
       <c r="AT24" t="n">
-        <v>8.800000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="AU24" t="n">
-        <v>8</v>
+        <v>5.8</v>
       </c>
       <c r="AV24" t="n">
-        <v>15</v>
+        <v>5.2</v>
       </c>
       <c r="AW24" t="n">
-        <v>44</v>
+        <v>4.2</v>
       </c>
       <c r="AX24" t="n">
-        <v>11</v>
+        <v>4.8</v>
       </c>
       <c r="AY24" t="n">
-        <v>9.6</v>
+        <v>6.4</v>
       </c>
       <c r="AZ24" t="n">
-        <v>16.5</v>
+        <v>6</v>
       </c>
       <c r="BA24" t="n">
-        <v>48</v>
+        <v>4.2</v>
       </c>
       <c r="BB24" t="n">
-        <v>19.5</v>
+        <v>4.5</v>
       </c>
       <c r="BC24" t="n">
-        <v>19</v>
+        <v>4.3</v>
       </c>
       <c r="BD24" t="n">
-        <v>32</v>
+        <v>3.35</v>
       </c>
       <c r="BE24" t="n">
-        <v>75</v>
+        <v>3.9</v>
       </c>
       <c r="BF24" t="n">
-        <v>13</v>
+        <v>4.1</v>
       </c>
       <c r="BG24" t="n">
-        <v>46</v>
+        <v>6.6</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-06 18:35:36</t>
+          <t>2026-05-06 19:03:29</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5210,55 +5210,55 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Nottm Forest</t>
+          <t>Shakhtar</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="G25" t="n">
-        <v>1.82</v>
+        <v>1.63</v>
       </c>
       <c r="H25" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="I25" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="J25" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="K25" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="L25" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="M25" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N25" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O25" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="P25" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.94</v>
+        <v>1.79</v>
       </c>
       <c r="R25" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="S25" t="n">
-        <v>3.45</v>
+        <v>2.94</v>
       </c>
       <c r="T25" t="n">
         <v>1.88</v>
@@ -5267,129 +5267,129 @@
         <v>2.08</v>
       </c>
       <c r="V25" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="W25" t="n">
-        <v>2.2</v>
+        <v>2.58</v>
       </c>
       <c r="X25" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>200</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>190</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ25" t="n">
         <v>15</v>
       </c>
-      <c r="Y25" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>38</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>120</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>19</v>
-      </c>
       <c r="AK25" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AL25" t="n">
         <v>34</v>
       </c>
       <c r="AM25" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AN25" t="n">
-        <v>11.5</v>
+        <v>8</v>
       </c>
       <c r="AO25" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AP25" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AQ25" t="n">
+        <v>19</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>38</v>
+      </c>
+      <c r="AS25" t="n">
         <v>16</v>
       </c>
-      <c r="AR25" t="n">
-        <v>32</v>
-      </c>
-      <c r="AS25" t="n">
+      <c r="AT25" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW25" t="n">
         <v>65</v>
       </c>
-      <c r="AT25" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>50</v>
-      </c>
       <c r="AX25" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY25" t="n">
         <v>9.800000000000001</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>9.6</v>
       </c>
       <c r="AZ25" t="n">
         <v>19</v>
       </c>
       <c r="BA25" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="BB25" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="BC25" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BD25" t="n">
         <v>30</v>
       </c>
       <c r="BE25" t="n">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="BF25" t="n">
-        <v>10.5</v>
+        <v>7.2</v>
       </c>
       <c r="BG25" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-06 18:35:36</t>
+          <t>2026-05-06 19:03:29</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5404,186 +5404,186 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="G26" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="H26" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T26" t="n">
         <v>1.83</v>
       </c>
-      <c r="H26" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="I26" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="J26" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="K26" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N26" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1.97</v>
-      </c>
       <c r="U26" t="n">
-        <v>1.97</v>
+        <v>2.14</v>
       </c>
       <c r="V26" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="W26" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="X26" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="Z26" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="AA26" t="n">
-        <v>130</v>
+        <v>85</v>
       </c>
       <c r="AB26" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AC26" t="n">
         <v>8.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AF26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG26" t="n">
         <v>10.5</v>
       </c>
-      <c r="AG26" t="n">
-        <v>10</v>
-      </c>
       <c r="AH26" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK26" t="n">
         <v>21</v>
       </c>
-      <c r="AI26" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>19</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>20</v>
-      </c>
       <c r="AL26" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AM26" t="n">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="AN26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP26" t="n">
         <v>13</v>
       </c>
-      <c r="AO26" t="n">
-        <v>90</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AQ26" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AS26" t="n">
-        <v>40</v>
+        <v>16.5</v>
       </c>
       <c r="AT26" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU26" t="n">
         <v>8</v>
       </c>
       <c r="AV26" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AW26" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="AX26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY26" t="n">
         <v>9.6</v>
       </c>
-      <c r="AY26" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AZ26" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>50</v>
+      </c>
+      <c r="BB26" t="n">
         <v>19.5</v>
       </c>
-      <c r="BA26" t="n">
-        <v>55</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>18</v>
-      </c>
       <c r="BC26" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BD26" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BE26" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BF26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BG26" t="n">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-06 18:35:36</t>
+          <t>2026-05-06 19:03:29</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Moroccan Botola Pro 1</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,191 +5593,191 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Nottm Forest</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.37</v>
+        <v>1.81</v>
       </c>
       <c r="G27" t="n">
-        <v>1.46</v>
+        <v>1.82</v>
       </c>
       <c r="H27" t="n">
-        <v>10</v>
+        <v>4.9</v>
       </c>
       <c r="I27" t="n">
-        <v>15.5</v>
+        <v>5</v>
       </c>
       <c r="J27" t="n">
+        <v>4</v>
+      </c>
+      <c r="K27" t="n">
         <v>4.1</v>
       </c>
-      <c r="K27" t="n">
-        <v>5.8</v>
-      </c>
       <c r="L27" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="M27" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N27" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="O27" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R27" t="n">
         <v>1.39</v>
       </c>
-      <c r="P27" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.27</v>
-      </c>
       <c r="S27" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="T27" t="n">
-        <v>2.42</v>
+        <v>1.86</v>
       </c>
       <c r="U27" t="n">
-        <v>1.56</v>
+        <v>2.08</v>
       </c>
       <c r="V27" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="W27" t="n">
-        <v>3.15</v>
+        <v>2.2</v>
       </c>
       <c r="X27" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="Y27" t="n">
-        <v>70</v>
+        <v>17.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA27" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB27" t="n">
-        <v>970</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC27" t="n">
-        <v>21</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD27" t="n">
-        <v>180</v>
+        <v>19</v>
       </c>
       <c r="AE27" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF27" t="n">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="AG27" t="n">
-        <v>970</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH27" t="n">
-        <v>190</v>
+        <v>19.5</v>
       </c>
       <c r="AI27" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ27" t="n">
-        <v>180</v>
+        <v>18.5</v>
       </c>
       <c r="AK27" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AL27" t="n">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="AM27" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN27" t="n">
-        <v>42</v>
+        <v>11.5</v>
       </c>
       <c r="AO27" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP27" t="n">
-        <v>5.8</v>
+        <v>14.5</v>
       </c>
       <c r="AQ27" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>32</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>65</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>50</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>50</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>90</v>
+      </c>
+      <c r="BF27" t="n">
         <v>10.5</v>
       </c>
-      <c r="AR27" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>3</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>3.8</v>
-      </c>
       <c r="BG27" t="n">
-        <v>8.6</v>
+        <v>65</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-06 18:35:36</t>
+          <t>2026-05-06 19:03:29</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5787,191 +5787,191 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>CA Platense</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Penarol</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.16</v>
+        <v>1.78</v>
       </c>
       <c r="G28" t="n">
-        <v>2.34</v>
+        <v>1.79</v>
       </c>
       <c r="H28" t="n">
-        <v>3.9</v>
+        <v>5.2</v>
       </c>
       <c r="I28" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="J28" t="n">
-        <v>3</v>
+        <v>3.95</v>
       </c>
       <c r="K28" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="L28" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="M28" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="N28" t="n">
-        <v>2.58</v>
+        <v>3.7</v>
       </c>
       <c r="O28" t="n">
-        <v>1.54</v>
+        <v>1.35</v>
       </c>
       <c r="P28" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.8</v>
+        <v>2.08</v>
       </c>
       <c r="R28" t="n">
-        <v>1.19</v>
+        <v>1.35</v>
       </c>
       <c r="S28" t="n">
-        <v>5.3</v>
+        <v>3.75</v>
       </c>
       <c r="T28" t="n">
-        <v>2.12</v>
+        <v>1.97</v>
       </c>
       <c r="U28" t="n">
-        <v>1.74</v>
+        <v>1.97</v>
       </c>
       <c r="V28" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="W28" t="n">
-        <v>1.74</v>
+        <v>2.26</v>
       </c>
       <c r="X28" t="n">
-        <v>9</v>
+        <v>13.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>11</v>
+        <v>16.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AA28" t="n">
-        <v>900</v>
+        <v>140</v>
       </c>
       <c r="AB28" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC28" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD28" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ28" t="n">
         <v>18.5</v>
       </c>
-      <c r="AE28" t="n">
-        <v>160</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>260</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>900</v>
-      </c>
       <c r="AK28" t="n">
+        <v>19</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>90</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>32</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>60</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>55</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>70</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BG28" t="n">
         <v>75</v>
       </c>
-      <c r="AL28" t="n">
-        <v>150</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>240</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>34</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>140</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BG28" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-06 18:35:36</t>
+          <t>2026-05-06 19:03:29</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,184 +5981,184 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>LDU</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.6</v>
+        <v>1.37</v>
       </c>
       <c r="G29" t="n">
-        <v>1.63</v>
+        <v>1.46</v>
       </c>
       <c r="H29" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I29" t="n">
-        <v>7.8</v>
+        <v>15.5</v>
       </c>
       <c r="J29" t="n">
         <v>4.1</v>
       </c>
       <c r="K29" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="L29" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="M29" t="n">
         <v>1.08</v>
       </c>
       <c r="N29" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="O29" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P29" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R29" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="S29" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W29" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="X29" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>70</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>180</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>190</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>180</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>42</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX29" t="n">
         <v>4</v>
       </c>
-      <c r="T29" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W29" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="X29" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>19</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>290</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>28</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>120</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>200</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>15</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>11</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>190</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>18</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU29" t="n">
+      <c r="AY29" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB29" t="n">
         <v>8.6</v>
       </c>
-      <c r="AV29" t="n">
-        <v>24</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>24</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>14</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BC29" t="n">
-        <v>16.5</v>
+        <v>6</v>
       </c>
       <c r="BD29" t="n">
-        <v>40</v>
+        <v>3.4</v>
       </c>
       <c r="BE29" t="n">
-        <v>14.5</v>
+        <v>3.1</v>
       </c>
       <c r="BF29" t="n">
-        <v>10</v>
+        <v>3.8</v>
       </c>
       <c r="BG29" t="n">
-        <v>12</v>
+        <v>8.6</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-06 18:35:36</t>
+          <t>2026-05-06 19:03:29</t>
         </is>
       </c>
     </row>
@@ -6175,27 +6175,27 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>CA Platense</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Universitario de Deportes</t>
+          <t>Penarol</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>2.16</v>
       </c>
       <c r="G30" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="H30" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="I30" t="n">
         <v>4.4</v>
@@ -6204,100 +6204,100 @@
         <v>3</v>
       </c>
       <c r="K30" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="L30" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="M30" t="n">
         <v>1.12</v>
       </c>
       <c r="N30" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="O30" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="P30" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="R30" t="n">
         <v>1.19</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="T30" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="U30" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="V30" t="n">
         <v>1.29</v>
       </c>
       <c r="W30" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="X30" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Y30" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z30" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="AA30" t="n">
-        <v>110</v>
+        <v>900</v>
       </c>
       <c r="AB30" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AC30" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD30" t="n">
         <v>18.5</v>
       </c>
       <c r="AE30" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AF30" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG30" t="n">
         <v>12</v>
       </c>
       <c r="AH30" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AI30" t="n">
-        <v>100</v>
+        <v>260</v>
       </c>
       <c r="AJ30" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>75</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>150</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>240</v>
+      </c>
+      <c r="AN30" t="n">
         <v>34</v>
       </c>
-      <c r="AK30" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>32</v>
-      </c>
       <c r="AO30" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="AP30" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AQ30" t="n">
         <v>9.4</v>
@@ -6306,53 +6306,53 @@
         <v>18</v>
       </c>
       <c r="AS30" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AT30" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AU30" t="n">
         <v>6.2</v>
       </c>
       <c r="AV30" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX30" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY30" t="n">
         <v>10</v>
       </c>
       <c r="AZ30" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA30" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BB30" t="n">
         <v>8.4</v>
       </c>
       <c r="BC30" t="n">
-        <v>21</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD30" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BE30" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BF30" t="n">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="BG30" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-05-06 18:35:36</t>
+          <t>2026-05-06 19:03:29</t>
         </is>
       </c>
     </row>
@@ -6369,184 +6369,184 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Ind Medellin</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>LDU</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>4.9</v>
+        <v>1.59</v>
       </c>
       <c r="G31" t="n">
-        <v>5.6</v>
+        <v>1.63</v>
       </c>
       <c r="H31" t="n">
-        <v>1.82</v>
+        <v>7</v>
       </c>
       <c r="I31" t="n">
-        <v>1.92</v>
+        <v>7.8</v>
       </c>
       <c r="J31" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="K31" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="L31" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="M31" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N31" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="O31" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="P31" t="n">
-        <v>1.69</v>
+        <v>1.87</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="R31" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S31" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="T31" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="U31" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="V31" t="n">
-        <v>2.08</v>
+        <v>1.16</v>
       </c>
       <c r="W31" t="n">
-        <v>1.21</v>
+        <v>2.58</v>
       </c>
       <c r="X31" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>290</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>200</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>190</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>24</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>24</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>14</v>
+      </c>
+      <c r="BB31" t="n">
         <v>11.5</v>
       </c>
-      <c r="Y31" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>11</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>22</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>15</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>24</v>
-      </c>
-      <c r="AF31" t="n">
+      <c r="BC31" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD31" t="n">
         <v>40</v>
       </c>
-      <c r="AG31" t="n">
-        <v>22</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>160</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>90</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>95</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>140</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>9</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BE31" t="n">
-        <v>10</v>
+        <v>14.5</v>
       </c>
       <c r="BF31" t="n">
         <v>10</v>
       </c>
       <c r="BG31" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-05-06 18:35:36</t>
+          <t>2026-05-06 19:03:29</t>
         </is>
       </c>
     </row>
@@ -6563,184 +6563,572 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>23:00:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Junior FC Barranquilla</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cerro Porteno</t>
+          <t>Universitario de Deportes</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.04</v>
+        <v>2.16</v>
       </c>
       <c r="G32" t="n">
-        <v>1000</v>
+        <v>2.4</v>
       </c>
       <c r="H32" t="n">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="I32" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="J32" t="n">
-        <v>1.06</v>
+        <v>3</v>
       </c>
       <c r="K32" t="n">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="L32" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="M32" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N32" t="n">
-        <v>1.25</v>
+        <v>2.6</v>
       </c>
       <c r="O32" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="P32" t="n">
-        <v>1.24</v>
+        <v>1.53</v>
       </c>
       <c r="Q32" t="n">
         <v>2.5</v>
       </c>
       <c r="R32" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="X32" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>23</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>2026-05-06 19:03:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Ind Medellin</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="G33" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N33" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S33" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V33" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X33" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>40</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>160</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>90</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>95</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>140</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BH33" t="inlineStr">
+        <is>
+          <t>2026-05-06 19:03:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>23:00:00</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Junior FC Barranquilla</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Cerro Porteno</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N34" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R34" t="n">
         <v>1.18</v>
       </c>
-      <c r="S32" t="n">
+      <c r="S34" t="n">
         <v>2.5</v>
       </c>
-      <c r="T32" t="n">
+      <c r="T34" t="n">
         <v>1.11</v>
       </c>
-      <c r="U32" t="n">
+      <c r="U34" t="n">
         <v>1.11</v>
       </c>
-      <c r="V32" t="n">
+      <c r="V34" t="n">
         <v>1.02</v>
       </c>
-      <c r="W32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH32" t="inlineStr">
-        <is>
-          <t>2026-05-06 18:35:36</t>
+      <c r="W34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH34" t="inlineStr">
+        <is>
+          <t>2026-05-06 19:03:29</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-07.xlsx
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="G2" t="n">
         <v>2.68</v>
       </c>
       <c r="H2" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I2" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="J2" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="K2" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="L2" t="n">
         <v>1.69</v>
@@ -805,7 +805,7 @@
         <v>1.34</v>
       </c>
       <c r="V2" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W2" t="n">
         <v>1.59</v>
@@ -814,103 +814,103 @@
         <v>6.6</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG2" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP2" t="n">
         <v>3.25</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="BF2" t="n">
         <v>1.55</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-06 19:03:29</t>
+          <t>2026-05-06 21:20:12</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
         <v>500</v>
       </c>
       <c r="AM3" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN3" t="n">
         <v>500</v>
@@ -1068,7 +1068,7 @@
         <v>5.8</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AT3" t="n">
         <v>5.6</v>
@@ -1080,7 +1080,7 @@
         <v>7</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="AX3" t="n">
         <v>6.2</v>
@@ -1092,19 +1092,19 @@
         <v>6</v>
       </c>
       <c r="BA3" t="n">
-        <v>7.4</v>
+        <v>5.8</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>3.55</v>
+        <v>2.96</v>
       </c>
       <c r="BF3" t="n">
         <v>7</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-06 19:03:29</t>
+          <t>2026-05-06 21:20:12</t>
         </is>
       </c>
     </row>
@@ -1145,170 +1145,170 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.04</v>
+        <v>2.18</v>
       </c>
       <c r="G4" t="n">
-        <v>100</v>
+        <v>2.52</v>
       </c>
       <c r="H4" t="n">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="I4" t="n">
-        <v>100</v>
+        <v>4.3</v>
       </c>
       <c r="J4" t="n">
-        <v>1.04</v>
+        <v>2.84</v>
       </c>
       <c r="K4" t="n">
-        <v>100</v>
+        <v>6.2</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
       </c>
       <c r="M4" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S4" t="n">
         <v>1.01</v>
       </c>
-      <c r="N4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.05</v>
-      </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="V4" t="n">
-        <v>1.02</v>
+        <v>1.32</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>1.65</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.03</v>
+        <v>1.86</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.03</v>
+        <v>2.16</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.03</v>
+        <v>2.36</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.03</v>
+        <v>2.52</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.03</v>
+        <v>1.89</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.02</v>
+        <v>3.2</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.02</v>
+        <v>3.35</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-06 19:03:29</t>
+          <t>2026-05-06 21:20:12</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="G5" t="n">
         <v>1.8</v>
@@ -1390,7 +1390,7 @@
         <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-06 19:03:29</t>
+          <t>2026-05-06 21:20:12</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-06 19:03:29</t>
+          <t>2026-05-06 21:20:12</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
         <v>1.62</v>
       </c>
       <c r="G7" t="n">
-        <v>44</v>
+        <v>6.4</v>
       </c>
       <c r="H7" t="n">
         <v>2.74</v>
@@ -1742,7 +1742,7 @@
         <v>2.84</v>
       </c>
       <c r="K7" t="n">
-        <v>44</v>
+        <v>8.6</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -1769,7 +1769,7 @@
         <v>1.41</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="U7" t="n">
         <v>1.01</v>
@@ -1781,55 +1781,55 @@
         <v>1.65</v>
       </c>
       <c r="X7" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC7" t="n">
         <v>95</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ7" t="n">
         <v>900</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO7" t="n">
         <v>1000</v>
@@ -1838,59 +1838,59 @@
         <v>5.1</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.03</v>
+        <v>1.55</v>
       </c>
       <c r="BG7" t="n">
         <v>1.55</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-06 19:03:29</t>
+          <t>2026-05-06 21:20:12</t>
         </is>
       </c>
     </row>
@@ -1924,13 +1924,13 @@
         <v>19.5</v>
       </c>
       <c r="G8" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H8" t="n">
         <v>1.25</v>
       </c>
       <c r="I8" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="J8" t="n">
         <v>5.4</v>
@@ -1945,7 +1945,7 @@
         <v>1.09</v>
       </c>
       <c r="N8" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="O8" t="n">
         <v>1.42</v>
@@ -1963,28 +1963,28 @@
         <v>4.2</v>
       </c>
       <c r="T8" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U8" t="n">
         <v>1.33</v>
       </c>
       <c r="V8" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="W8" t="n">
         <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="Y8" t="n">
         <v>5.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AA8" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AB8" t="n">
         <v>120</v>
@@ -2026,65 +2026,65 @@
         <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AP8" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ8" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AR8" t="n">
         <v>5.1</v>
       </c>
       <c r="AS8" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT8" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AU8" t="n">
         <v>12.5</v>
       </c>
       <c r="AV8" t="n">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="AW8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BG8" t="n">
         <v>6.6</v>
       </c>
-      <c r="AX8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>8</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>9</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-06 19:03:29</t>
+          <t>2026-05-06 21:20:12</t>
         </is>
       </c>
     </row>
@@ -2121,16 +2121,16 @@
         <v>3.95</v>
       </c>
       <c r="H9" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="I9" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="J9" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="K9" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L9" t="n">
         <v>1.56</v>
@@ -2139,7 +2139,7 @@
         <v>1.12</v>
       </c>
       <c r="N9" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="O9" t="n">
         <v>1.5</v>
@@ -2169,7 +2169,7 @@
         <v>1.33</v>
       </c>
       <c r="X9" t="n">
-        <v>9.4</v>
+        <v>17.5</v>
       </c>
       <c r="Y9" t="n">
         <v>8</v>
@@ -2199,34 +2199,34 @@
         <v>970</v>
       </c>
       <c r="AH9" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AI9" t="n">
-        <v>460</v>
+        <v>500</v>
       </c>
       <c r="AJ9" t="n">
         <v>900</v>
       </c>
       <c r="AK9" t="n">
-        <v>440</v>
+        <v>500</v>
       </c>
       <c r="AL9" t="n">
-        <v>460</v>
+        <v>500</v>
       </c>
       <c r="AM9" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AN9" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AO9" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AP9" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AQ9" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AR9" t="n">
         <v>10</v>
@@ -2256,29 +2256,29 @@
         <v>11.5</v>
       </c>
       <c r="BA9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC9" t="n">
         <v>8</v>
       </c>
-      <c r="BB9" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BD9" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE9" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BG9" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-06 19:03:29</t>
+          <t>2026-05-06 21:20:12</t>
         </is>
       </c>
     </row>
@@ -2312,13 +2312,13 @@
         <v>1.62</v>
       </c>
       <c r="G10" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="H10" t="n">
         <v>5</v>
       </c>
       <c r="I10" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="J10" t="n">
         <v>4.1</v>
@@ -2366,25 +2366,25 @@
         <v>90</v>
       </c>
       <c r="Y10" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="Z10" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AA10" t="n">
-        <v>170</v>
+        <v>700</v>
       </c>
       <c r="AB10" t="n">
-        <v>970</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC10" t="n">
         <v>12.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>21</v>
+        <v>500</v>
       </c>
       <c r="AE10" t="n">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="AF10" t="n">
         <v>19.5</v>
@@ -2393,7 +2393,7 @@
         <v>36</v>
       </c>
       <c r="AH10" t="n">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="AI10" t="n">
         <v>320</v>
@@ -2405,16 +2405,16 @@
         <v>65</v>
       </c>
       <c r="AL10" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AM10" t="n">
-        <v>130</v>
+        <v>580</v>
       </c>
       <c r="AN10" t="n">
         <v>10.5</v>
       </c>
       <c r="AO10" t="n">
-        <v>160</v>
+        <v>700</v>
       </c>
       <c r="AP10" t="n">
         <v>7.6</v>
@@ -2423,10 +2423,10 @@
         <v>9</v>
       </c>
       <c r="AR10" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AS10" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AT10" t="n">
         <v>7.6</v>
@@ -2438,10 +2438,10 @@
         <v>10.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AX10" t="n">
-        <v>6.8</v>
+        <v>5.6</v>
       </c>
       <c r="AY10" t="n">
         <v>5.8</v>
@@ -2450,29 +2450,29 @@
         <v>11.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BB10" t="n">
         <v>9</v>
       </c>
       <c r="BC10" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BD10" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BE10" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BF10" t="n">
         <v>7.8</v>
       </c>
       <c r="BG10" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-06 19:03:29</t>
+          <t>2026-05-06 21:20:12</t>
         </is>
       </c>
     </row>
@@ -2503,13 +2503,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="G11" t="n">
         <v>95</v>
       </c>
       <c r="H11" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="I11" t="n">
         <v>90</v>
@@ -2518,7 +2518,7 @@
         <v>1.04</v>
       </c>
       <c r="K11" t="n">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -2557,58 +2557,58 @@
         <v>1.02</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP11" t="n">
         <v>1.03</v>
@@ -2656,17 +2656,17 @@
         <v>1.03</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.05</v>
+        <v>1.55</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.05</v>
+        <v>1.55</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-06 19:03:29</t>
+          <t>2026-05-06 21:20:12</t>
         </is>
       </c>
     </row>
@@ -2703,7 +2703,7 @@
         <v>1.82</v>
       </c>
       <c r="H12" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="I12" t="n">
         <v>5.5</v>
@@ -2739,7 +2739,7 @@
         <v>3.55</v>
       </c>
       <c r="T12" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="U12" t="n">
         <v>1.94</v>
@@ -2754,7 +2754,7 @@
         <v>15.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>970</v>
+        <v>29</v>
       </c>
       <c r="Z12" t="n">
         <v>100</v>
@@ -2769,13 +2769,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD12" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AE12" t="n">
         <v>400</v>
       </c>
       <c r="AF12" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AG12" t="n">
         <v>10.5</v>
@@ -2784,7 +2784,7 @@
         <v>44</v>
       </c>
       <c r="AI12" t="n">
-        <v>320</v>
+        <v>700</v>
       </c>
       <c r="AJ12" t="n">
         <v>22</v>
@@ -2796,13 +2796,13 @@
         <v>95</v>
       </c>
       <c r="AM12" t="n">
-        <v>390</v>
+        <v>580</v>
       </c>
       <c r="AN12" t="n">
         <v>29</v>
       </c>
       <c r="AO12" t="n">
-        <v>310</v>
+        <v>700</v>
       </c>
       <c r="AP12" t="n">
         <v>7</v>
@@ -2814,7 +2814,7 @@
         <v>7.4</v>
       </c>
       <c r="AS12" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AT12" t="n">
         <v>7</v>
@@ -2823,10 +2823,10 @@
         <v>4.9</v>
       </c>
       <c r="AV12" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AW12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX12" t="n">
         <v>5.6</v>
@@ -2835,32 +2835,32 @@
         <v>5.8</v>
       </c>
       <c r="AZ12" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BA12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB12" t="n">
         <v>9</v>
       </c>
       <c r="BC12" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BD12" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE12" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BF12" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BG12" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-06 19:03:29</t>
+          <t>2026-05-06 21:20:12</t>
         </is>
       </c>
     </row>
@@ -2894,16 +2894,16 @@
         <v>3</v>
       </c>
       <c r="G13" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="H13" t="n">
         <v>2.88</v>
       </c>
       <c r="I13" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J13" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="K13" t="n">
         <v>3.1</v>
@@ -2921,7 +2921,7 @@
         <v>1.59</v>
       </c>
       <c r="P13" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Q13" t="n">
         <v>2.62</v>
@@ -2948,103 +2948,103 @@
         <v>970</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA13" t="n">
         <v>900</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ13" t="n">
         <v>900</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP13" t="n">
         <v>4.2</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.06</v>
+        <v>1.19</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.06</v>
+        <v>1.21</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.06</v>
+        <v>1.21</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.06</v>
+        <v>1.21</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.06</v>
+        <v>1.21</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.06</v>
+        <v>1.21</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.06</v>
+        <v>1.21</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.06</v>
+        <v>1.21</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.06</v>
+        <v>1.21</v>
       </c>
       <c r="BF13" t="n">
         <v>1.55</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-06 19:03:29</t>
+          <t>2026-05-06 21:20:12</t>
         </is>
       </c>
     </row>
@@ -3085,16 +3085,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="G14" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="H14" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="I14" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J14" t="n">
         <v>4.2</v>
@@ -3112,22 +3112,22 @@
         <v>4.8</v>
       </c>
       <c r="O14" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P14" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="Q14" t="n">
         <v>1.63</v>
       </c>
       <c r="R14" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S14" t="n">
         <v>2.58</v>
       </c>
       <c r="T14" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U14" t="n">
         <v>2.2</v>
@@ -3142,13 +3142,13 @@
         <v>40</v>
       </c>
       <c r="Y14" t="n">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="Z14" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AA14" t="n">
-        <v>150</v>
+        <v>700</v>
       </c>
       <c r="AB14" t="n">
         <v>11</v>
@@ -3160,73 +3160,73 @@
         <v>27</v>
       </c>
       <c r="AE14" t="n">
-        <v>320</v>
+        <v>700</v>
       </c>
       <c r="AF14" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG14" t="n">
         <v>10.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AI14" t="n">
-        <v>250</v>
+        <v>700</v>
       </c>
       <c r="AJ14" t="n">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="AK14" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="AL14" t="n">
         <v>75</v>
       </c>
       <c r="AM14" t="n">
-        <v>320</v>
+        <v>580</v>
       </c>
       <c r="AN14" t="n">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AO14" t="n">
-        <v>120</v>
+        <v>700</v>
       </c>
       <c r="AP14" t="n">
-        <v>5</v>
+        <v>7.2</v>
       </c>
       <c r="AQ14" t="n">
         <v>11.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>5.7</v>
+        <v>9</v>
       </c>
       <c r="AS14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AT14" t="n">
         <v>6.2</v>
       </c>
       <c r="AU14" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AV14" t="n">
         <v>17</v>
       </c>
       <c r="AW14" t="n">
-        <v>5.8</v>
+        <v>9.4</v>
       </c>
       <c r="AX14" t="n">
         <v>6.2</v>
       </c>
       <c r="AY14" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ14" t="n">
         <v>13.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>5.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB14" t="n">
         <v>12</v>
@@ -3235,10 +3235,10 @@
         <v>11.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>5.2</v>
+        <v>7.8</v>
       </c>
       <c r="BE14" t="n">
-        <v>6</v>
+        <v>9.4</v>
       </c>
       <c r="BF14" t="n">
         <v>6.6</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-06 19:03:29</t>
+          <t>2026-05-06 21:20:12</t>
         </is>
       </c>
     </row>
@@ -3285,7 +3285,7 @@
         <v>90</v>
       </c>
       <c r="H15" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="I15" t="n">
         <v>2</v>
@@ -3306,22 +3306,22 @@
         <v>1.25</v>
       </c>
       <c r="O15" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="P15" t="n">
         <v>1.24</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="R15" t="n">
         <v>1.15</v>
       </c>
       <c r="S15" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T15" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="U15" t="n">
         <v>1.01</v>
@@ -3435,14 +3435,14 @@
         <v>1.01</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.05</v>
+        <v>1.55</v>
       </c>
       <c r="BG15" t="n">
         <v>1.05</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-06 19:03:29</t>
+          <t>2026-05-06 21:20:12</t>
         </is>
       </c>
     </row>
@@ -3515,7 +3515,7 @@
         <v>1.72</v>
       </c>
       <c r="T16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="U16" t="n">
         <v>1.01</v>
@@ -3527,116 +3527,116 @@
         <v>1.69</v>
       </c>
       <c r="X16" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC16" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD16" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE16" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF16" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG16" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH16" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK16" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM16" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG16" t="n">
         <v>1.55</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-06 19:03:29</t>
+          <t>2026-05-06 21:20:12</t>
         </is>
       </c>
     </row>
@@ -3682,25 +3682,25 @@
         <v>3.4</v>
       </c>
       <c r="K17" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N17" t="n">
         <v>3.7</v>
       </c>
       <c r="O17" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="P17" t="n">
         <v>1.91</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="R17" t="n">
         <v>1.36</v>
@@ -3709,7 +3709,7 @@
         <v>3.3</v>
       </c>
       <c r="T17" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U17" t="n">
         <v>2.14</v>
@@ -3721,7 +3721,7 @@
         <v>1.68</v>
       </c>
       <c r="X17" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="Y17" t="n">
         <v>16</v>
@@ -3784,7 +3784,7 @@
         <v>17.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AT17" t="n">
         <v>7.6</v>
@@ -3796,7 +3796,7 @@
         <v>10.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AX17" t="n">
         <v>11</v>
@@ -3808,29 +3808,29 @@
         <v>12.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BB17" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BC17" t="n">
         <v>18</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BF17" t="n">
         <v>13.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-06 19:03:29</t>
+          <t>2026-05-06 21:20:12</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="G18" t="n">
         <v>1.78</v>
@@ -3888,7 +3888,7 @@
         <v>4.3</v>
       </c>
       <c r="O18" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P18" t="n">
         <v>2.16</v>
@@ -3903,7 +3903,7 @@
         <v>2.88</v>
       </c>
       <c r="T18" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="U18" t="n">
         <v>2.12</v>
@@ -3921,13 +3921,13 @@
         <v>40</v>
       </c>
       <c r="Z18" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AA18" t="n">
         <v>900</v>
       </c>
       <c r="AB18" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC18" t="n">
         <v>9.800000000000001</v>
@@ -3948,7 +3948,7 @@
         <v>32</v>
       </c>
       <c r="AI18" t="n">
-        <v>160</v>
+        <v>700</v>
       </c>
       <c r="AJ18" t="n">
         <v>30</v>
@@ -3957,7 +3957,7 @@
         <v>29</v>
       </c>
       <c r="AL18" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AM18" t="n">
         <v>580</v>
@@ -3966,7 +3966,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AO18" t="n">
-        <v>80</v>
+        <v>700</v>
       </c>
       <c r="AP18" t="n">
         <v>14</v>
@@ -3978,7 +3978,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AS18" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AT18" t="n">
         <v>7.6</v>
@@ -4002,7 +4002,7 @@
         <v>14.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB18" t="n">
         <v>13.5</v>
@@ -4011,10 +4011,10 @@
         <v>13</v>
       </c>
       <c r="BD18" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE18" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF18" t="n">
         <v>7</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-06 19:03:29</t>
+          <t>2026-05-06 21:20:12</t>
         </is>
       </c>
     </row>
@@ -4058,13 +4058,13 @@
         <v>1.88</v>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="H19" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I19" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J19" t="n">
         <v>3.1</v>
@@ -4076,19 +4076,19 @@
         <v>1.01</v>
       </c>
       <c r="M19" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N19" t="n">
         <v>2.72</v>
       </c>
       <c r="O19" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="P19" t="n">
         <v>1.55</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="R19" t="n">
         <v>1.2</v>
@@ -4100,13 +4100,13 @@
         <v>2.1</v>
       </c>
       <c r="U19" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="V19" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W19" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X19" t="n">
         <v>9.6</v>
@@ -4115,13 +4115,13 @@
         <v>16</v>
       </c>
       <c r="Z19" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AA19" t="n">
         <v>900</v>
       </c>
       <c r="AB19" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AC19" t="n">
         <v>7.8</v>
@@ -4142,10 +4142,10 @@
         <v>25</v>
       </c>
       <c r="AI19" t="n">
-        <v>540</v>
+        <v>700</v>
       </c>
       <c r="AJ19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK19" t="n">
         <v>27</v>
@@ -4154,13 +4154,13 @@
         <v>120</v>
       </c>
       <c r="AM19" t="n">
-        <v>210</v>
+        <v>500</v>
       </c>
       <c r="AN19" t="n">
         <v>23</v>
       </c>
       <c r="AO19" t="n">
-        <v>190</v>
+        <v>700</v>
       </c>
       <c r="AP19" t="n">
         <v>8.199999999999999</v>
@@ -4169,13 +4169,13 @@
         <v>13</v>
       </c>
       <c r="AR19" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AS19" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT19" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AU19" t="n">
         <v>6.4</v>
@@ -4184,41 +4184,41 @@
         <v>21</v>
       </c>
       <c r="AW19" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX19" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY19" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ19" t="n">
         <v>20</v>
       </c>
       <c r="BA19" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BB19" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BC19" t="n">
         <v>21</v>
       </c>
       <c r="BD19" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BE19" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BF19" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BG19" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-06 19:03:29</t>
+          <t>2026-05-06 21:20:12</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="G20" t="n">
         <v>2.04</v>
@@ -4297,7 +4297,7 @@
         <v>1.7</v>
       </c>
       <c r="V20" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W20" t="n">
         <v>1.96</v>
@@ -4306,7 +4306,7 @@
         <v>8.4</v>
       </c>
       <c r="Y20" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z20" t="n">
         <v>38</v>
@@ -4348,7 +4348,7 @@
         <v>65</v>
       </c>
       <c r="AM20" t="n">
-        <v>240</v>
+        <v>580</v>
       </c>
       <c r="AN20" t="n">
         <v>26</v>
@@ -4363,13 +4363,13 @@
         <v>10.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>9.199999999999999</v>
+        <v>29</v>
       </c>
       <c r="AS20" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AT20" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AU20" t="n">
         <v>7</v>
@@ -4378,7 +4378,7 @@
         <v>18</v>
       </c>
       <c r="AW20" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AX20" t="n">
         <v>9.4</v>
@@ -4390,29 +4390,29 @@
         <v>25</v>
       </c>
       <c r="BA20" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BB20" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="BC20" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BD20" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BE20" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BF20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BG20" t="n">
         <v>11.5</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-06 19:03:29</t>
+          <t>2026-05-06 21:20:12</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-06 19:03:29</t>
+          <t>2026-05-06 21:20:12</t>
         </is>
       </c>
     </row>
@@ -4703,10 +4703,10 @@
         <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC22" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AD22" t="n">
         <v>1000</v>
@@ -4715,10 +4715,10 @@
         <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG22" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH22" t="n">
         <v>1000</v>
@@ -4727,25 +4727,25 @@
         <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK22" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL22" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM22" t="n">
         <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="AO22" t="n">
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="AQ22" t="n">
         <v>4.2</v>
@@ -4757,10 +4757,10 @@
         <v>4.2</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AV22" t="n">
         <v>4.2</v>
@@ -4769,38 +4769,38 @@
         <v>4.2</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="BA22" t="n">
         <v>4.2</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BG22" t="n">
         <v>4.2</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-06 19:03:29</t>
+          <t>2026-05-06 21:20:12</t>
         </is>
       </c>
     </row>
@@ -4831,16 +4831,16 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="H23" t="n">
         <v>1.34</v>
       </c>
       <c r="I23" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="J23" t="n">
         <v>5.9</v>
@@ -4855,7 +4855,7 @@
         <v>1.02</v>
       </c>
       <c r="N23" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="O23" t="n">
         <v>1.12</v>
@@ -4870,7 +4870,7 @@
         <v>1.89</v>
       </c>
       <c r="S23" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="T23" t="n">
         <v>1.66</v>
@@ -4879,25 +4879,25 @@
         <v>2.26</v>
       </c>
       <c r="V23" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="W23" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X23" t="n">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="Y23" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z23" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AA23" t="n">
         <v>13.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AC23" t="n">
         <v>15.5</v>
@@ -4906,13 +4906,13 @@
         <v>12</v>
       </c>
       <c r="AE23" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AF23" t="n">
-        <v>540</v>
+        <v>130</v>
       </c>
       <c r="AG23" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AH23" t="n">
         <v>38</v>
@@ -4921,25 +4921,25 @@
         <v>48</v>
       </c>
       <c r="AJ23" t="n">
-        <v>260</v>
+        <v>340</v>
       </c>
       <c r="AK23" t="n">
         <v>240</v>
       </c>
       <c r="AL23" t="n">
-        <v>390</v>
+        <v>190</v>
       </c>
       <c r="AM23" t="n">
-        <v>320</v>
+        <v>80</v>
       </c>
       <c r="AN23" t="n">
-        <v>320</v>
+        <v>140</v>
       </c>
       <c r="AO23" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AP23" t="n">
-        <v>9.199999999999999</v>
+        <v>44</v>
       </c>
       <c r="AQ23" t="n">
         <v>12</v>
@@ -4951,19 +4951,19 @@
         <v>10.5</v>
       </c>
       <c r="AT23" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU23" t="n">
         <v>11</v>
       </c>
       <c r="AV23" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AW23" t="n">
         <v>11.5</v>
       </c>
       <c r="AX23" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AY23" t="n">
         <v>16</v>
@@ -4975,26 +4975,26 @@
         <v>19</v>
       </c>
       <c r="BB23" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC23" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BD23" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE23" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF23" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BG23" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-06 19:03:29</t>
+          <t>2026-05-06 21:20:12</t>
         </is>
       </c>
     </row>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="G24" t="n">
         <v>1.5</v>
@@ -5034,19 +5034,19 @@
         <v>6</v>
       </c>
       <c r="I24" t="n">
-        <v>19.5</v>
+        <v>32</v>
       </c>
       <c r="J24" t="n">
         <v>4.3</v>
       </c>
       <c r="K24" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="L24" t="n">
         <v>1.47</v>
       </c>
       <c r="M24" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N24" t="n">
         <v>3.15</v>
@@ -5058,19 +5058,19 @@
         <v>1.68</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="R24" t="n">
         <v>1.25</v>
       </c>
       <c r="S24" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="T24" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="U24" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="V24" t="n">
         <v>1.08</v>
@@ -5118,25 +5118,25 @@
         <v>32</v>
       </c>
       <c r="AK24" t="n">
-        <v>970</v>
+        <v>65</v>
       </c>
       <c r="AL24" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AM24" t="n">
         <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>970</v>
+        <v>29</v>
       </c>
       <c r="AO24" t="n">
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>6.2</v>
+        <v>4.1</v>
       </c>
       <c r="AQ24" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="AR24" t="n">
         <v>4.2</v>
@@ -5145,13 +5145,13 @@
         <v>4.2</v>
       </c>
       <c r="AT24" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="AU24" t="n">
-        <v>5.8</v>
+        <v>4.5</v>
       </c>
       <c r="AV24" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="AW24" t="n">
         <v>4.2</v>
@@ -5163,32 +5163,32 @@
         <v>6.4</v>
       </c>
       <c r="AZ24" t="n">
-        <v>6</v>
+        <v>3.15</v>
       </c>
       <c r="BA24" t="n">
         <v>4.2</v>
       </c>
       <c r="BB24" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="BC24" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.35</v>
+        <v>2.56</v>
       </c>
       <c r="BE24" t="n">
-        <v>3.9</v>
+        <v>2.96</v>
       </c>
       <c r="BF24" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="BG24" t="n">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-06 19:03:29</t>
+          <t>2026-05-06 21:20:12</t>
         </is>
       </c>
     </row>
@@ -5219,19 +5219,19 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="G25" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="H25" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I25" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J25" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K25" t="n">
         <v>4.5</v>
@@ -5243,7 +5243,7 @@
         <v>1.05</v>
       </c>
       <c r="N25" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O25" t="n">
         <v>1.26</v>
@@ -5255,7 +5255,7 @@
         <v>1.79</v>
       </c>
       <c r="R25" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S25" t="n">
         <v>2.94</v>
@@ -5267,28 +5267,28 @@
         <v>2.08</v>
       </c>
       <c r="V25" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W25" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="X25" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Y25" t="n">
         <v>23</v>
       </c>
       <c r="Z25" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AA25" t="n">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="AB25" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC25" t="n">
         <v>9.800000000000001</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>10</v>
       </c>
       <c r="AD25" t="n">
         <v>23</v>
@@ -5297,25 +5297,25 @@
         <v>190</v>
       </c>
       <c r="AF25" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG25" t="n">
         <v>10.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI25" t="n">
         <v>80</v>
       </c>
       <c r="AJ25" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AK25" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AL25" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM25" t="n">
         <v>110</v>
@@ -5327,19 +5327,19 @@
         <v>90</v>
       </c>
       <c r="AP25" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR25" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="AS25" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AT25" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU25" t="n">
         <v>9.199999999999999</v>
@@ -5348,7 +5348,7 @@
         <v>21</v>
       </c>
       <c r="AW25" t="n">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="AX25" t="n">
         <v>9.199999999999999</v>
@@ -5357,32 +5357,32 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ25" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="BB25" t="n">
         <v>14</v>
       </c>
       <c r="BC25" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BE25" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="BF25" t="n">
         <v>7.2</v>
       </c>
       <c r="BG25" t="n">
-        <v>70</v>
+        <v>17</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-06 19:03:29</t>
+          <t>2026-05-06 21:20:12</t>
         </is>
       </c>
     </row>
@@ -5443,16 +5443,16 @@
         <v>1.32</v>
       </c>
       <c r="P26" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q26" t="n">
         <v>1.95</v>
       </c>
       <c r="R26" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S26" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T26" t="n">
         <v>1.83</v>
@@ -5470,7 +5470,7 @@
         <v>15.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Z26" t="n">
         <v>30</v>
@@ -5521,7 +5521,7 @@
         <v>55</v>
       </c>
       <c r="AP26" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ26" t="n">
         <v>13.5</v>
@@ -5557,7 +5557,7 @@
         <v>50</v>
       </c>
       <c r="BB26" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BC26" t="n">
         <v>19.5</v>
@@ -5569,14 +5569,14 @@
         <v>44</v>
       </c>
       <c r="BF26" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BG26" t="n">
         <v>46</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-06 19:03:29</t>
+          <t>2026-05-06 21:20:12</t>
         </is>
       </c>
     </row>
@@ -5607,10 +5607,10 @@
         </is>
       </c>
       <c r="F27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G27" t="n">
         <v>1.81</v>
-      </c>
-      <c r="G27" t="n">
-        <v>1.82</v>
       </c>
       <c r="H27" t="n">
         <v>4.9</v>
@@ -5637,7 +5637,7 @@
         <v>1.31</v>
       </c>
       <c r="P27" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q27" t="n">
         <v>1.94</v>
@@ -5646,10 +5646,10 @@
         <v>1.39</v>
       </c>
       <c r="S27" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="T27" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U27" t="n">
         <v>2.08</v>
@@ -5658,13 +5658,13 @@
         <v>1.25</v>
       </c>
       <c r="W27" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="X27" t="n">
         <v>15</v>
       </c>
       <c r="Y27" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Z27" t="n">
         <v>36</v>
@@ -5676,10 +5676,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AC27" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD27" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE27" t="n">
         <v>60</v>
@@ -5700,7 +5700,7 @@
         <v>18.5</v>
       </c>
       <c r="AK27" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AL27" t="n">
         <v>34</v>
@@ -5724,7 +5724,7 @@
         <v>32</v>
       </c>
       <c r="AS27" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AT27" t="n">
         <v>8.4</v>
@@ -5736,22 +5736,22 @@
         <v>17.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AX27" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AY27" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ27" t="n">
         <v>19</v>
       </c>
       <c r="BA27" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BB27" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BC27" t="n">
         <v>17</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-06 19:03:29</t>
+          <t>2026-05-06 21:20:12</t>
         </is>
       </c>
     </row>
@@ -5801,22 +5801,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="G28" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="H28" t="n">
         <v>5.2</v>
       </c>
       <c r="I28" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="J28" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K28" t="n">
         <v>3.95</v>
-      </c>
-      <c r="K28" t="n">
-        <v>4</v>
       </c>
       <c r="L28" t="n">
         <v>1.43</v>
@@ -5825,10 +5825,10 @@
         <v>1.08</v>
       </c>
       <c r="N28" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O28" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P28" t="n">
         <v>1.91</v>
@@ -5843,19 +5843,19 @@
         <v>3.75</v>
       </c>
       <c r="T28" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="U28" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="V28" t="n">
         <v>1.23</v>
       </c>
       <c r="W28" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="X28" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Y28" t="n">
         <v>16.5</v>
@@ -5885,7 +5885,7 @@
         <v>10</v>
       </c>
       <c r="AH28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI28" t="n">
         <v>80</v>
@@ -5909,13 +5909,13 @@
         <v>90</v>
       </c>
       <c r="AP28" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ28" t="n">
         <v>15</v>
       </c>
       <c r="AR28" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AS28" t="n">
         <v>40</v>
@@ -5924,13 +5924,13 @@
         <v>7.8</v>
       </c>
       <c r="AU28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV28" t="n">
         <v>19</v>
       </c>
       <c r="AW28" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AX28" t="n">
         <v>9.4</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-06 19:03:29</t>
+          <t>2026-05-06 21:20:12</t>
         </is>
       </c>
     </row>
@@ -6028,19 +6028,19 @@
         <v>1.81</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R29" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S29" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="T29" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="U29" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="V29" t="n">
         <v>1.07</v>
@@ -6061,7 +6061,7 @@
         <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>970</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC29" t="n">
         <v>21</v>
@@ -6091,19 +6091,19 @@
         <v>970</v>
       </c>
       <c r="AL29" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AM29" t="n">
         <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="AO29" t="n">
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>5.8</v>
+        <v>9.6</v>
       </c>
       <c r="AQ29" t="n">
         <v>10.5</v>
@@ -6115,7 +6115,7 @@
         <v>4.2</v>
       </c>
       <c r="AT29" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AU29" t="n">
         <v>6.4</v>
@@ -6127,38 +6127,38 @@
         <v>4.2</v>
       </c>
       <c r="AX29" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AY29" t="n">
         <v>6.4</v>
       </c>
       <c r="AZ29" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BA29" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BB29" t="n">
         <v>8.6</v>
       </c>
       <c r="BC29" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BD29" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="BE29" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="BF29" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BG29" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-06 19:03:29</t>
+          <t>2026-05-06 21:20:12</t>
         </is>
       </c>
     </row>
@@ -6189,7 +6189,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G30" t="n">
         <v>2.34</v>
@@ -6201,52 +6201,52 @@
         <v>4.4</v>
       </c>
       <c r="J30" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="K30" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="L30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N30" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="P30" t="n">
         <v>1.48</v>
       </c>
-      <c r="M30" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N30" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="O30" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="P30" t="n">
-        <v>1.53</v>
-      </c>
       <c r="Q30" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="R30" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S30" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="T30" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="U30" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="V30" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W30" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="X30" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y30" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z30" t="n">
         <v>48</v>
@@ -6255,16 +6255,16 @@
         <v>900</v>
       </c>
       <c r="AB30" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AC30" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD30" t="n">
         <v>18.5</v>
       </c>
       <c r="AE30" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AF30" t="n">
         <v>13</v>
@@ -6273,10 +6273,10 @@
         <v>12</v>
       </c>
       <c r="AH30" t="n">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AI30" t="n">
-        <v>260</v>
+        <v>500</v>
       </c>
       <c r="AJ30" t="n">
         <v>900</v>
@@ -6285,74 +6285,74 @@
         <v>75</v>
       </c>
       <c r="AL30" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AM30" t="n">
-        <v>240</v>
+        <v>500</v>
       </c>
       <c r="AN30" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="AO30" t="n">
-        <v>140</v>
+        <v>500</v>
       </c>
       <c r="AP30" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AQ30" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR30" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="AS30" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AT30" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AU30" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AV30" t="n">
         <v>15.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AX30" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY30" t="n">
         <v>10</v>
       </c>
       <c r="AZ30" t="n">
-        <v>20</v>
+        <v>8.6</v>
       </c>
       <c r="BA30" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BB30" t="n">
-        <v>8.4</v>
+        <v>27</v>
       </c>
       <c r="BC30" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BD30" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BE30" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BF30" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG30" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-05-06 19:03:29</t>
+          <t>2026-05-06 21:20:12</t>
         </is>
       </c>
     </row>
@@ -6386,7 +6386,7 @@
         <v>1.59</v>
       </c>
       <c r="G31" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="H31" t="n">
         <v>7</v>
@@ -6398,22 +6398,22 @@
         <v>4.1</v>
       </c>
       <c r="K31" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L31" t="n">
         <v>1.38</v>
       </c>
       <c r="M31" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N31" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O31" t="n">
         <v>1.38</v>
       </c>
       <c r="P31" t="n">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="Q31" t="n">
         <v>2.12</v>
@@ -6431,13 +6431,13 @@
         <v>1.78</v>
       </c>
       <c r="V31" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="W31" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="X31" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y31" t="n">
         <v>19</v>
@@ -6449,7 +6449,7 @@
         <v>290</v>
       </c>
       <c r="AB31" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC31" t="n">
         <v>9.199999999999999</v>
@@ -6458,10 +6458,10 @@
         <v>28</v>
       </c>
       <c r="AE31" t="n">
-        <v>120</v>
+        <v>260</v>
       </c>
       <c r="AF31" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AG31" t="n">
         <v>10.5</v>
@@ -6470,7 +6470,7 @@
         <v>27</v>
       </c>
       <c r="AI31" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AJ31" t="n">
         <v>14.5</v>
@@ -6482,71 +6482,71 @@
         <v>48</v>
       </c>
       <c r="AM31" t="n">
-        <v>190</v>
+        <v>580</v>
       </c>
       <c r="AN31" t="n">
         <v>11</v>
       </c>
       <c r="AO31" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AP31" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AQ31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR31" t="n">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="AS31" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AT31" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AU31" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV31" t="n">
         <v>24</v>
       </c>
       <c r="AW31" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AX31" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AY31" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ31" t="n">
         <v>24</v>
       </c>
       <c r="BA31" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BB31" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BC31" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="BD31" t="n">
         <v>40</v>
       </c>
       <c r="BE31" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BF31" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG31" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-05-06 19:03:29</t>
+          <t>2026-05-06 21:20:12</t>
         </is>
       </c>
     </row>
@@ -6589,7 +6589,7 @@
         <v>4.4</v>
       </c>
       <c r="J32" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="K32" t="n">
         <v>3.35</v>
@@ -6607,10 +6607,10 @@
         <v>1.51</v>
       </c>
       <c r="P32" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="R32" t="n">
         <v>1.19</v>
@@ -6637,7 +6637,7 @@
         <v>11.5</v>
       </c>
       <c r="Z32" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA32" t="n">
         <v>110</v>
@@ -6649,7 +6649,7 @@
         <v>7.6</v>
       </c>
       <c r="AD32" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE32" t="n">
         <v>70</v>
@@ -6694,7 +6694,7 @@
         <v>18</v>
       </c>
       <c r="AS32" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AT32" t="n">
         <v>6.2</v>
@@ -6706,7 +6706,7 @@
         <v>15</v>
       </c>
       <c r="AW32" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AX32" t="n">
         <v>11</v>
@@ -6718,29 +6718,29 @@
         <v>19.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BB32" t="n">
         <v>8.6</v>
       </c>
       <c r="BC32" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="BD32" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE32" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BF32" t="n">
         <v>23</v>
       </c>
       <c r="BG32" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-05-06 19:03:29</t>
+          <t>2026-05-06 21:20:12</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="G33" t="n">
         <v>5.6</v>
@@ -6849,7 +6849,7 @@
         <v>24</v>
       </c>
       <c r="AF33" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AG33" t="n">
         <v>22</v>
@@ -6912,7 +6912,7 @@
         <v>19.5</v>
       </c>
       <c r="BA33" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB33" t="n">
         <v>10</v>
@@ -6921,7 +6921,7 @@
         <v>9.6</v>
       </c>
       <c r="BD33" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BE33" t="n">
         <v>10</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-05-06 19:03:29</t>
+          <t>2026-05-06 21:20:12</t>
         </is>
       </c>
     </row>
@@ -6965,19 +6965,19 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G34" t="n">
         <v>1000</v>
       </c>
       <c r="H34" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I34" t="n">
         <v>1000</v>
       </c>
       <c r="J34" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="K34" t="n">
         <v>1000</v>
@@ -6992,7 +6992,7 @@
         <v>1.25</v>
       </c>
       <c r="O34" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="P34" t="n">
         <v>1.24</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-05-06 19:03:29</t>
+          <t>2026-05-06 21:20:12</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-07.xlsx
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="G2" t="n">
         <v>2.68</v>
@@ -766,13 +766,13 @@
         <v>4.3</v>
       </c>
       <c r="I2" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J2" t="n">
         <v>2.38</v>
       </c>
       <c r="K2" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="L2" t="n">
         <v>1.69</v>
@@ -784,10 +784,10 @@
         <v>1.94</v>
       </c>
       <c r="O2" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="P2" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Q2" t="n">
         <v>3.15</v>
@@ -796,7 +796,7 @@
         <v>1.12</v>
       </c>
       <c r="S2" t="n">
-        <v>3.15</v>
+        <v>1.05</v>
       </c>
       <c r="T2" t="n">
         <v>2.22</v>
@@ -805,7 +805,7 @@
         <v>1.34</v>
       </c>
       <c r="V2" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W2" t="n">
         <v>1.59</v>
@@ -823,7 +823,7 @@
         <v>500</v>
       </c>
       <c r="AB2" t="n">
-        <v>970</v>
+        <v>110</v>
       </c>
       <c r="AC2" t="n">
         <v>500</v>
@@ -835,10 +835,10 @@
         <v>500</v>
       </c>
       <c r="AF2" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AG2" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AH2" t="n">
         <v>500</v>
@@ -859,58 +859,58 @@
         <v>500</v>
       </c>
       <c r="AN2" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO2" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP2" t="n">
         <v>3.25</v>
       </c>
       <c r="AQ2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AY2" t="n">
         <v>1.34</v>
       </c>
-      <c r="AR2" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AZ2" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="BF2" t="n">
         <v>1.55</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="G3" t="n">
         <v>3.35</v>
@@ -960,10 +960,10 @@
         <v>2.4</v>
       </c>
       <c r="I3" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K3" t="n">
         <v>3.75</v>
@@ -975,34 +975,34 @@
         <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P3" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="Q3" t="n">
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S3" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="T3" t="n">
         <v>1.77</v>
       </c>
       <c r="U3" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V3" t="n">
         <v>1.58</v>
       </c>
       <c r="W3" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X3" t="n">
         <v>90</v>
@@ -1014,7 +1014,7 @@
         <v>970</v>
       </c>
       <c r="AA3" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB3" t="n">
         <v>500</v>
@@ -1041,80 +1041,80 @@
         <v>500</v>
       </c>
       <c r="AJ3" t="n">
-        <v>900</v>
+        <v>340</v>
       </c>
       <c r="AK3" t="n">
         <v>500</v>
       </c>
       <c r="AL3" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="AM3" t="n">
         <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO3" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP3" t="n">
         <v>5.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AR3" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.5</v>
+        <v>3.55</v>
       </c>
       <c r="AT3" t="n">
         <v>5.6</v>
       </c>
       <c r="AU3" t="n">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV3" t="n">
         <v>7</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="AX3" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AY3" t="n">
         <v>7.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.4</v>
+        <v>4.4</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.6</v>
+        <v>28</v>
       </c>
       <c r="BE3" t="n">
-        <v>2.96</v>
+        <v>3.75</v>
       </c>
       <c r="BF3" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BG3" t="n">
         <v>6.6</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -1148,16 +1148,16 @@
         <v>2.18</v>
       </c>
       <c r="G4" t="n">
-        <v>2.52</v>
+        <v>2.74</v>
       </c>
       <c r="H4" t="n">
         <v>3.25</v>
       </c>
       <c r="I4" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J4" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="K4" t="n">
         <v>6.2</v>
@@ -1184,7 +1184,7 @@
         <v>1.2</v>
       </c>
       <c r="S4" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="T4" t="n">
         <v>1.97</v>
@@ -1199,10 +1199,10 @@
         <v>1.65</v>
       </c>
       <c r="X4" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="Y4" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="Z4" t="n">
         <v>500</v>
@@ -1211,22 +1211,22 @@
         <v>900</v>
       </c>
       <c r="AB4" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AC4" t="n">
         <v>14</v>
       </c>
       <c r="AD4" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AE4" t="n">
         <v>500</v>
       </c>
       <c r="AF4" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AG4" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AH4" t="n">
         <v>500</v>
@@ -1253,13 +1253,13 @@
         <v>500</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.2</v>
+        <v>2.88</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.5</v>
+        <v>2.56</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.86</v>
+        <v>2.02</v>
       </c>
       <c r="AS4" t="n">
         <v>3.35</v>
@@ -1268,7 +1268,7 @@
         <v>3.25</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AV4" t="n">
         <v>2.16</v>
@@ -1277,13 +1277,13 @@
         <v>3.3</v>
       </c>
       <c r="AX4" t="n">
-        <v>2.36</v>
+        <v>2.6</v>
       </c>
       <c r="AY4" t="n">
         <v>2.52</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.89</v>
+        <v>2.04</v>
       </c>
       <c r="BA4" t="n">
         <v>3.35</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
         <v>2.04</v>
       </c>
       <c r="I5" t="n">
-        <v>180</v>
+        <v>990</v>
       </c>
       <c r="J5" t="n">
         <v>2.32</v>
@@ -1363,13 +1363,13 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="O5" t="n">
         <v>1.01</v>
       </c>
       <c r="P5" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Q5" t="n">
         <v>1.01</v>
@@ -1381,10 +1381,10 @@
         <v>1.39</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V5" t="n">
         <v>1.01</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -1557,13 +1557,13 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="O6" t="n">
         <v>1.01</v>
       </c>
       <c r="P6" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Q6" t="n">
         <v>1.01</v>
@@ -1572,13 +1572,13 @@
         <v>1.07</v>
       </c>
       <c r="S6" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V6" t="n">
         <v>1.02</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -1751,7 +1751,7 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="O7" t="n">
         <v>1.01</v>
@@ -1766,13 +1766,13 @@
         <v>1.07</v>
       </c>
       <c r="S7" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T7" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V7" t="n">
         <v>1.19</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -2053,38 +2053,38 @@
         <v>6.8</v>
       </c>
       <c r="AX8" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="AY8" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ8" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BA8" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB8" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BC8" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BE8" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF8" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG8" t="n">
         <v>6.6</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -2312,16 +2312,16 @@
         <v>1.62</v>
       </c>
       <c r="G10" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="H10" t="n">
         <v>5</v>
       </c>
       <c r="I10" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J10" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K10" t="n">
         <v>4.9</v>
@@ -2339,7 +2339,7 @@
         <v>1.27</v>
       </c>
       <c r="P10" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q10" t="n">
         <v>1.76</v>
@@ -2354,19 +2354,19 @@
         <v>1.81</v>
       </c>
       <c r="U10" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V10" t="n">
         <v>1.2</v>
       </c>
       <c r="W10" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="X10" t="n">
         <v>90</v>
       </c>
       <c r="Y10" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="Z10" t="n">
         <v>500</v>
@@ -2375,7 +2375,7 @@
         <v>700</v>
       </c>
       <c r="AB10" t="n">
-        <v>9.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="AC10" t="n">
         <v>12.5</v>
@@ -2417,13 +2417,13 @@
         <v>700</v>
       </c>
       <c r="AP10" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ10" t="n">
         <v>9</v>
       </c>
       <c r="AR10" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="AS10" t="n">
         <v>4.4</v>
@@ -2432,13 +2432,13 @@
         <v>7.6</v>
       </c>
       <c r="AU10" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AV10" t="n">
-        <v>10.5</v>
+        <v>6.8</v>
       </c>
       <c r="AW10" t="n">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="AX10" t="n">
         <v>5.6</v>
@@ -2450,29 +2450,29 @@
         <v>11.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BB10" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC10" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>6.6</v>
+        <v>18</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BF10" t="n">
         <v>7.8</v>
       </c>
       <c r="BG10" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -2515,7 +2515,7 @@
         <v>90</v>
       </c>
       <c r="J11" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="K11" t="n">
         <v>32</v>
@@ -2527,28 +2527,28 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="O11" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="P11" t="n">
         <v>1.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="R11" t="n">
         <v>1.24</v>
       </c>
       <c r="S11" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="T11" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U11" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V11" t="n">
         <v>1.02</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -2772,7 +2772,7 @@
         <v>500</v>
       </c>
       <c r="AE12" t="n">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="AF12" t="n">
         <v>20</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="G13" t="n">
         <v>3.4</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -3085,10 +3085,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="G14" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="H14" t="n">
         <v>5.7</v>
@@ -3145,7 +3145,7 @@
         <v>500</v>
       </c>
       <c r="Z14" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="AA14" t="n">
         <v>700</v>
@@ -3157,7 +3157,7 @@
         <v>12.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE14" t="n">
         <v>700</v>
@@ -3193,10 +3193,10 @@
         <v>700</v>
       </c>
       <c r="AP14" t="n">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>11.5</v>
+        <v>7.6</v>
       </c>
       <c r="AR14" t="n">
         <v>9</v>
@@ -3205,7 +3205,7 @@
         <v>10</v>
       </c>
       <c r="AT14" t="n">
-        <v>6.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU14" t="n">
         <v>5.3</v>
@@ -3238,7 +3238,7 @@
         <v>7.8</v>
       </c>
       <c r="BE14" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BF14" t="n">
         <v>6.6</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.12</v>
+        <v>1.83</v>
       </c>
       <c r="G15" t="n">
         <v>90</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -3491,13 +3491,13 @@
         <v>8</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M16" t="n">
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>1.77</v>
+        <v>2.86</v>
       </c>
       <c r="O16" t="n">
         <v>1.28</v>
@@ -3509,16 +3509,16 @@
         <v>1.72</v>
       </c>
       <c r="R16" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="S16" t="n">
-        <v>1.72</v>
+        <v>2.5</v>
       </c>
       <c r="T16" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="U16" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V16" t="n">
         <v>1.26</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -4055,19 +4055,19 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="G19" t="n">
         <v>1.97</v>
       </c>
       <c r="H19" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="I19" t="n">
         <v>6.4</v>
       </c>
       <c r="J19" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K19" t="n">
         <v>3.4</v>
@@ -4085,7 +4085,7 @@
         <v>1.49</v>
       </c>
       <c r="P19" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q19" t="n">
         <v>2.48</v>
@@ -4094,7 +4094,7 @@
         <v>1.2</v>
       </c>
       <c r="S19" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="T19" t="n">
         <v>2.1</v>
@@ -4103,7 +4103,7 @@
         <v>1.75</v>
       </c>
       <c r="V19" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W19" t="n">
         <v>2.02</v>
@@ -4172,7 +4172,7 @@
         <v>9</v>
       </c>
       <c r="AS19" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AT19" t="n">
         <v>5.6</v>
@@ -4181,7 +4181,7 @@
         <v>6.4</v>
       </c>
       <c r="AV19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW19" t="n">
         <v>8.800000000000001</v>
@@ -4205,10 +4205,10 @@
         <v>21</v>
       </c>
       <c r="BD19" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE19" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF19" t="n">
         <v>18.5</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
         <v>4.7</v>
       </c>
       <c r="I20" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J20" t="n">
         <v>3.3</v>
@@ -4324,7 +4324,7 @@
         <v>22</v>
       </c>
       <c r="AE20" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AF20" t="n">
         <v>13</v>
@@ -4345,7 +4345,7 @@
         <v>29</v>
       </c>
       <c r="AL20" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AM20" t="n">
         <v>580</v>
@@ -4396,7 +4396,7 @@
         <v>22</v>
       </c>
       <c r="BC20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BD20" t="n">
         <v>10.5</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -4449,13 +4449,13 @@
         <v>1.52</v>
       </c>
       <c r="H21" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="I21" t="n">
         <v>9.6</v>
       </c>
       <c r="J21" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K21" t="n">
         <v>5.2</v>
@@ -4497,7 +4497,7 @@
         <v>2.92</v>
       </c>
       <c r="X21" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Y21" t="n">
         <v>32</v>
@@ -4518,7 +4518,7 @@
         <v>36</v>
       </c>
       <c r="AE21" t="n">
-        <v>320</v>
+        <v>170</v>
       </c>
       <c r="AF21" t="n">
         <v>8.6</v>
@@ -4536,7 +4536,7 @@
         <v>13.5</v>
       </c>
       <c r="AK21" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AL21" t="n">
         <v>44</v>
@@ -4548,7 +4548,7 @@
         <v>8</v>
       </c>
       <c r="AO21" t="n">
-        <v>650</v>
+        <v>220</v>
       </c>
       <c r="AP21" t="n">
         <v>14.5</v>
@@ -4557,10 +4557,10 @@
         <v>21</v>
       </c>
       <c r="AR21" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT21" t="n">
         <v>7</v>
@@ -4584,7 +4584,7 @@
         <v>22</v>
       </c>
       <c r="BA21" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BB21" t="n">
         <v>11</v>
@@ -4602,11 +4602,11 @@
         <v>6.6</v>
       </c>
       <c r="BG21" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -4646,22 +4646,22 @@
         <v>3.3</v>
       </c>
       <c r="I22" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="J22" t="n">
         <v>3.75</v>
       </c>
       <c r="K22" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="L22" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M22" t="n">
         <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>1.64</v>
+        <v>2.74</v>
       </c>
       <c r="O22" t="n">
         <v>1.37</v>
@@ -4673,19 +4673,19 @@
         <v>2</v>
       </c>
       <c r="R22" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S22" t="n">
-        <v>2</v>
+        <v>2.56</v>
       </c>
       <c r="T22" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U22" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V22" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W22" t="n">
         <v>2.96</v>
@@ -4745,7 +4745,7 @@
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AQ22" t="n">
         <v>4.2</v>
@@ -4757,10 +4757,10 @@
         <v>4.2</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AV22" t="n">
         <v>4.2</v>
@@ -4769,38 +4769,38 @@
         <v>4.2</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AY22" t="n">
         <v>1.15</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="BA22" t="n">
         <v>4.2</v>
       </c>
       <c r="BB22" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BF22" t="n">
         <v>1.14</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>1.11</v>
       </c>
       <c r="BG22" t="n">
         <v>4.2</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="G23" t="n">
         <v>10.5</v>
@@ -4843,7 +4843,7 @@
         <v>1.37</v>
       </c>
       <c r="J23" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="K23" t="n">
         <v>6.8</v>
@@ -4912,7 +4912,7 @@
         <v>130</v>
       </c>
       <c r="AG23" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AH23" t="n">
         <v>38</v>
@@ -4939,7 +4939,7 @@
         <v>3.9</v>
       </c>
       <c r="AP23" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AQ23" t="n">
         <v>12</v>
@@ -4951,7 +4951,7 @@
         <v>10.5</v>
       </c>
       <c r="AT23" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU23" t="n">
         <v>11</v>
@@ -4984,7 +4984,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BE23" t="n">
-        <v>8.199999999999999</v>
+        <v>28</v>
       </c>
       <c r="BF23" t="n">
         <v>8.4</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="G24" t="n">
         <v>1.5</v>
@@ -5055,13 +5055,13 @@
         <v>1.43</v>
       </c>
       <c r="P24" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="Q24" t="n">
         <v>2.24</v>
       </c>
       <c r="R24" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S24" t="n">
         <v>3.95</v>
@@ -5148,7 +5148,7 @@
         <v>4.2</v>
       </c>
       <c r="AU24" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AV24" t="n">
         <v>4.2</v>
@@ -5172,10 +5172,10 @@
         <v>5.2</v>
       </c>
       <c r="BC24" t="n">
-        <v>4.1</v>
+        <v>3.05</v>
       </c>
       <c r="BD24" t="n">
-        <v>2.56</v>
+        <v>3.15</v>
       </c>
       <c r="BE24" t="n">
         <v>2.96</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="G25" t="n">
         <v>1.64</v>
@@ -5249,19 +5249,19 @@
         <v>1.26</v>
       </c>
       <c r="P25" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="R25" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S25" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="T25" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="U25" t="n">
         <v>2.08</v>
@@ -5276,7 +5276,7 @@
         <v>18</v>
       </c>
       <c r="Y25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z25" t="n">
         <v>50</v>
@@ -5285,7 +5285,7 @@
         <v>170</v>
       </c>
       <c r="AB25" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC25" t="n">
         <v>9.800000000000001</v>
@@ -5303,7 +5303,7 @@
         <v>10.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI25" t="n">
         <v>80</v>
@@ -5321,7 +5321,7 @@
         <v>110</v>
       </c>
       <c r="AN25" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO25" t="n">
         <v>90</v>
@@ -5330,16 +5330,16 @@
         <v>15.5</v>
       </c>
       <c r="AQ25" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>38</v>
+      </c>
+      <c r="AS25" t="n">
         <v>20</v>
       </c>
-      <c r="AR25" t="n">
-        <v>30</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>18.5</v>
-      </c>
       <c r="AT25" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AU25" t="n">
         <v>9.199999999999999</v>
@@ -5348,7 +5348,7 @@
         <v>21</v>
       </c>
       <c r="AW25" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AX25" t="n">
         <v>9.199999999999999</v>
@@ -5357,10 +5357,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ25" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA25" t="n">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="BB25" t="n">
         <v>14</v>
@@ -5375,14 +5375,14 @@
         <v>50</v>
       </c>
       <c r="BF25" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -5416,13 +5416,13 @@
         <v>2</v>
       </c>
       <c r="G26" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="H26" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I26" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J26" t="n">
         <v>3.8</v>
@@ -5431,43 +5431,43 @@
         <v>3.85</v>
       </c>
       <c r="L26" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="M26" t="n">
         <v>1.07</v>
       </c>
       <c r="N26" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="O26" t="n">
         <v>1.32</v>
       </c>
       <c r="P26" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="R26" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S26" t="n">
         <v>3.65</v>
       </c>
       <c r="T26" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U26" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V26" t="n">
         <v>1.31</v>
       </c>
       <c r="W26" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="X26" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y26" t="n">
         <v>15.5</v>
@@ -5479,7 +5479,7 @@
         <v>85</v>
       </c>
       <c r="AB26" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC26" t="n">
         <v>8.4</v>
@@ -5497,7 +5497,7 @@
         <v>10.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI26" t="n">
         <v>60</v>
@@ -5506,22 +5506,22 @@
         <v>24</v>
       </c>
       <c r="AK26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL26" t="n">
         <v>36</v>
       </c>
       <c r="AM26" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AN26" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AO26" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AP26" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AQ26" t="n">
         <v>13.5</v>
@@ -5530,19 +5530,19 @@
         <v>27</v>
       </c>
       <c r="AS26" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AT26" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AU26" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV26" t="n">
         <v>15</v>
       </c>
       <c r="AW26" t="n">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="AX26" t="n">
         <v>11</v>
@@ -5569,14 +5569,14 @@
         <v>44</v>
       </c>
       <c r="BF26" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BG26" t="n">
         <v>46</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -5607,16 +5607,16 @@
         </is>
       </c>
       <c r="F27" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="G27" t="n">
         <v>1.8</v>
       </c>
-      <c r="G27" t="n">
-        <v>1.81</v>
-      </c>
       <c r="H27" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I27" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J27" t="n">
         <v>4</v>
@@ -5631,22 +5631,22 @@
         <v>1.07</v>
       </c>
       <c r="N27" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O27" t="n">
         <v>1.31</v>
       </c>
       <c r="P27" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="R27" t="n">
         <v>1.39</v>
       </c>
       <c r="S27" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="T27" t="n">
         <v>1.87</v>
@@ -5655,10 +5655,10 @@
         <v>2.08</v>
       </c>
       <c r="V27" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W27" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="X27" t="n">
         <v>15</v>
@@ -5667,7 +5667,7 @@
         <v>18</v>
       </c>
       <c r="Z27" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AA27" t="n">
         <v>120</v>
@@ -5679,7 +5679,7 @@
         <v>9</v>
       </c>
       <c r="AD27" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AE27" t="n">
         <v>60</v>
@@ -5721,13 +5721,13 @@
         <v>16.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AS27" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AT27" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU27" t="n">
         <v>8.6</v>
@@ -5736,7 +5736,7 @@
         <v>17.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AX27" t="n">
         <v>9.800000000000001</v>
@@ -5745,7 +5745,7 @@
         <v>9.4</v>
       </c>
       <c r="AZ27" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BA27" t="n">
         <v>55</v>
@@ -5760,7 +5760,7 @@
         <v>30</v>
       </c>
       <c r="BE27" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BF27" t="n">
         <v>10.5</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -5801,13 +5801,13 @@
         </is>
       </c>
       <c r="F28" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="G28" t="n">
         <v>1.8</v>
       </c>
-      <c r="G28" t="n">
-        <v>1.81</v>
-      </c>
       <c r="H28" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I28" t="n">
         <v>5.4</v>
@@ -5822,19 +5822,19 @@
         <v>1.43</v>
       </c>
       <c r="M28" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N28" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O28" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P28" t="n">
         <v>1.91</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="R28" t="n">
         <v>1.35</v>
@@ -5843,22 +5843,22 @@
         <v>3.75</v>
       </c>
       <c r="T28" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="U28" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="V28" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W28" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="X28" t="n">
         <v>14</v>
       </c>
       <c r="Y28" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Z28" t="n">
         <v>40</v>
@@ -5867,7 +5867,7 @@
         <v>140</v>
       </c>
       <c r="AB28" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC28" t="n">
         <v>8.6</v>
@@ -5879,13 +5879,13 @@
         <v>75</v>
       </c>
       <c r="AF28" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AG28" t="n">
         <v>10</v>
       </c>
       <c r="AH28" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI28" t="n">
         <v>80</v>
@@ -5912,19 +5912,19 @@
         <v>13</v>
       </c>
       <c r="AQ28" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AR28" t="n">
         <v>36</v>
       </c>
       <c r="AS28" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AT28" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AU28" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV28" t="n">
         <v>19</v>
@@ -5933,7 +5933,7 @@
         <v>65</v>
       </c>
       <c r="AX28" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY28" t="n">
         <v>9.6</v>
@@ -5942,7 +5942,7 @@
         <v>19.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BB28" t="n">
         <v>17.5</v>
@@ -5957,14 +5957,14 @@
         <v>70</v>
       </c>
       <c r="BF28" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BG28" t="n">
         <v>75</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -6103,7 +6103,7 @@
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>9.6</v>
+        <v>5.8</v>
       </c>
       <c r="AQ29" t="n">
         <v>10.5</v>
@@ -6139,13 +6139,13 @@
         <v>4.3</v>
       </c>
       <c r="BB29" t="n">
-        <v>8.6</v>
+        <v>5.6</v>
       </c>
       <c r="BC29" t="n">
         <v>6.4</v>
       </c>
       <c r="BD29" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BE29" t="n">
         <v>3.9</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -6207,7 +6207,7 @@
         <v>3.3</v>
       </c>
       <c r="L30" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="M30" t="n">
         <v>1.13</v>
@@ -6237,7 +6237,7 @@
         <v>1.7</v>
       </c>
       <c r="V30" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W30" t="n">
         <v>1.75</v>
@@ -6258,7 +6258,7 @@
         <v>6.8</v>
       </c>
       <c r="AC30" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD30" t="n">
         <v>18.5</v>
@@ -6267,7 +6267,7 @@
         <v>500</v>
       </c>
       <c r="AF30" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG30" t="n">
         <v>12</v>
@@ -6306,7 +6306,7 @@
         <v>24</v>
       </c>
       <c r="AS30" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AT30" t="n">
         <v>5.9</v>
@@ -6318,7 +6318,7 @@
         <v>15.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AX30" t="n">
         <v>11</v>
@@ -6327,32 +6327,32 @@
         <v>10</v>
       </c>
       <c r="AZ30" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BA30" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BB30" t="n">
         <v>27</v>
       </c>
       <c r="BC30" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BD30" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>13</v>
+      </c>
+      <c r="BF30" t="n">
         <v>10.5</v>
       </c>
-      <c r="BE30" t="n">
-        <v>12</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BG30" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -6416,7 +6416,7 @@
         <v>1.79</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R31" t="n">
         <v>1.29</v>
@@ -6437,7 +6437,7 @@
         <v>2.6</v>
       </c>
       <c r="X31" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y31" t="n">
         <v>19</v>
@@ -6455,10 +6455,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD31" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AE31" t="n">
-        <v>260</v>
+        <v>140</v>
       </c>
       <c r="AF31" t="n">
         <v>8.6</v>
@@ -6467,7 +6467,7 @@
         <v>10.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI31" t="n">
         <v>180</v>
@@ -6482,13 +6482,13 @@
         <v>48</v>
       </c>
       <c r="AM31" t="n">
-        <v>580</v>
+        <v>700</v>
       </c>
       <c r="AN31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO31" t="n">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="AP31" t="n">
         <v>10.5</v>
@@ -6497,10 +6497,10 @@
         <v>17</v>
       </c>
       <c r="AR31" t="n">
-        <v>50</v>
+        <v>13.5</v>
       </c>
       <c r="AS31" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AT31" t="n">
         <v>6.2</v>
@@ -6512,7 +6512,7 @@
         <v>24</v>
       </c>
       <c r="AW31" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AX31" t="n">
         <v>7.8</v>
@@ -6524,29 +6524,29 @@
         <v>24</v>
       </c>
       <c r="BA31" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="BB31" t="n">
         <v>13</v>
       </c>
       <c r="BC31" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BD31" t="n">
         <v>40</v>
       </c>
       <c r="BE31" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="BF31" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BG31" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -6577,10 +6577,10 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G32" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H32" t="n">
         <v>3.75</v>
@@ -6592,7 +6592,7 @@
         <v>2.98</v>
       </c>
       <c r="K32" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L32" t="n">
         <v>1.49</v>
@@ -6625,7 +6625,7 @@
         <v>1.76</v>
       </c>
       <c r="V32" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W32" t="n">
         <v>1.72</v>
@@ -6733,14 +6733,14 @@
         <v>10</v>
       </c>
       <c r="BF32" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="BG32" t="n">
         <v>9.6</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -6774,19 +6774,19 @@
         <v>5</v>
       </c>
       <c r="G33" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="H33" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="I33" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="J33" t="n">
         <v>3.5</v>
       </c>
       <c r="K33" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L33" t="n">
         <v>1.42</v>
@@ -6801,7 +6801,7 @@
         <v>1.42</v>
       </c>
       <c r="P33" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="Q33" t="n">
         <v>2.24</v>
@@ -6813,16 +6813,16 @@
         <v>4.3</v>
       </c>
       <c r="T33" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U33" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="V33" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="W33" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X33" t="n">
         <v>11.5</v>
@@ -6849,7 +6849,7 @@
         <v>24</v>
       </c>
       <c r="AF33" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AG33" t="n">
         <v>22</v>
@@ -6867,7 +6867,7 @@
         <v>90</v>
       </c>
       <c r="AL33" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AM33" t="n">
         <v>200</v>
@@ -6879,7 +6879,7 @@
         <v>17.5</v>
       </c>
       <c r="AP33" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ33" t="n">
         <v>6.4</v>
@@ -6891,7 +6891,7 @@
         <v>17.5</v>
       </c>
       <c r="AT33" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AU33" t="n">
         <v>7</v>
@@ -6903,7 +6903,7 @@
         <v>19.5</v>
       </c>
       <c r="AX33" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AY33" t="n">
         <v>17.5</v>
@@ -6912,13 +6912,13 @@
         <v>19.5</v>
       </c>
       <c r="BA33" t="n">
-        <v>8.800000000000001</v>
+        <v>40</v>
       </c>
       <c r="BB33" t="n">
         <v>10</v>
       </c>
       <c r="BC33" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BD33" t="n">
         <v>9.6</v>
@@ -6927,14 +6927,14 @@
         <v>10</v>
       </c>
       <c r="BF33" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG33" t="n">
         <v>14.5</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-07.xlsx
@@ -760,61 +760,61 @@
         <v>2.5</v>
       </c>
       <c r="G2" t="n">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="H2" t="n">
         <v>4.3</v>
       </c>
       <c r="I2" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="J2" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="K2" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="L2" t="n">
-        <v>1.69</v>
+        <v>1.78</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="N2" t="n">
-        <v>1.94</v>
+        <v>2.16</v>
       </c>
       <c r="O2" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="P2" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.15</v>
+        <v>3.7</v>
       </c>
       <c r="R2" t="n">
         <v>1.12</v>
       </c>
       <c r="S2" t="n">
-        <v>1.05</v>
+        <v>8.4</v>
       </c>
       <c r="T2" t="n">
-        <v>2.22</v>
+        <v>1.78</v>
       </c>
       <c r="U2" t="n">
         <v>1.34</v>
       </c>
       <c r="V2" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="W2" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="X2" t="n">
-        <v>6.6</v>
+        <v>970</v>
       </c>
       <c r="Y2" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Z2" t="n">
         <v>500</v>
@@ -826,10 +826,10 @@
         <v>110</v>
       </c>
       <c r="AC2" t="n">
-        <v>500</v>
+        <v>95</v>
       </c>
       <c r="AD2" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AE2" t="n">
         <v>500</v>
@@ -838,10 +838,10 @@
         <v>160</v>
       </c>
       <c r="AG2" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AH2" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AI2" t="n">
         <v>500</v>
@@ -868,49 +868,49 @@
         <v>3.25</v>
       </c>
       <c r="AQ2" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AU2" t="n">
         <v>1.38</v>
       </c>
-      <c r="AR2" t="n">
+      <c r="AV2" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AX2" t="n">
         <v>1.39</v>
       </c>
-      <c r="AS2" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AY2" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="BF2" t="n">
         <v>1.55</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-06 23:36:18</t>
+          <t>2026-05-07 01:55:26</t>
         </is>
       </c>
     </row>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="G3" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H3" t="n">
         <v>2.4</v>
@@ -963,10 +963,10 @@
         <v>2.7</v>
       </c>
       <c r="J3" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K3" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="L3" t="n">
         <v>1.42</v>
@@ -975,49 +975,49 @@
         <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="O3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="R3" t="n">
         <v>1.34</v>
       </c>
-      <c r="P3" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.31</v>
-      </c>
       <c r="S3" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="T3" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="U3" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="V3" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W3" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="X3" t="n">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="Y3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z3" t="n">
         <v>500</v>
       </c>
-      <c r="Z3" t="n">
-        <v>970</v>
-      </c>
       <c r="AA3" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB3" t="n">
-        <v>500</v>
+        <v>21</v>
       </c>
       <c r="AC3" t="n">
         <v>14</v>
@@ -1032,7 +1032,7 @@
         <v>500</v>
       </c>
       <c r="AG3" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AH3" t="n">
         <v>60</v>
@@ -1059,16 +1059,16 @@
         <v>600</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AQ3" t="n">
         <v>5.1</v>
       </c>
       <c r="AR3" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="AS3" t="n">
-        <v>3.55</v>
+        <v>7.4</v>
       </c>
       <c r="AT3" t="n">
         <v>5.6</v>
@@ -1080,31 +1080,31 @@
         <v>7</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.4</v>
+        <v>7</v>
       </c>
       <c r="AX3" t="n">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="AY3" t="n">
         <v>7.6</v>
       </c>
       <c r="AZ3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE3" t="n">
         <v>6.4</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>28</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>3.75</v>
       </c>
       <c r="BF3" t="n">
         <v>7.4</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-06 23:36:18</t>
+          <t>2026-05-07 01:55:26</t>
         </is>
       </c>
     </row>
@@ -1145,61 +1145,61 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G4" t="n">
-        <v>2.74</v>
+        <v>2.44</v>
       </c>
       <c r="H4" t="n">
         <v>3.25</v>
       </c>
       <c r="I4" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="J4" t="n">
-        <v>2.78</v>
+        <v>3.25</v>
       </c>
       <c r="K4" t="n">
-        <v>6.2</v>
+        <v>3.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="M4" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>2.36</v>
+        <v>2.88</v>
       </c>
       <c r="O4" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="P4" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.98</v>
+        <v>2.26</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="S4" t="n">
-        <v>1.05</v>
+        <v>4.1</v>
       </c>
       <c r="T4" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="U4" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="V4" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W4" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="X4" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="Y4" t="n">
         <v>970</v>
@@ -1211,7 +1211,7 @@
         <v>900</v>
       </c>
       <c r="AB4" t="n">
-        <v>970</v>
+        <v>44</v>
       </c>
       <c r="AC4" t="n">
         <v>14</v>
@@ -1229,7 +1229,7 @@
         <v>970</v>
       </c>
       <c r="AH4" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AI4" t="n">
         <v>500</v>
@@ -1244,71 +1244,71 @@
         <v>500</v>
       </c>
       <c r="AM4" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN4" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO4" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="AQ4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AX4" t="n">
         <v>2.56</v>
       </c>
-      <c r="AR4" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AS4" t="n">
+      <c r="AY4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BB4" t="n">
         <v>3.35</v>
       </c>
-      <c r="AT4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BA4" t="n">
+      <c r="BC4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD4" t="n">
         <v>3.35</v>
       </c>
-      <c r="BB4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>3.3</v>
-      </c>
       <c r="BE4" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-06 23:36:18</t>
+          <t>2026-05-07 01:55:26</t>
         </is>
       </c>
     </row>
@@ -1342,19 +1342,19 @@
         <v>1.2</v>
       </c>
       <c r="G5" t="n">
-        <v>1.8</v>
+        <v>1.59</v>
       </c>
       <c r="H5" t="n">
-        <v>2.04</v>
+        <v>4.8</v>
       </c>
       <c r="I5" t="n">
         <v>990</v>
       </c>
       <c r="J5" t="n">
-        <v>2.32</v>
+        <v>3.7</v>
       </c>
       <c r="K5" t="n">
-        <v>950</v>
+        <v>32</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1369,7 +1369,7 @@
         <v>1.01</v>
       </c>
       <c r="P5" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="Q5" t="n">
         <v>1.01</v>
@@ -1390,7 +1390,7 @@
         <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.72</v>
+        <v>2.6</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1405,10 +1405,10 @@
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD5" t="n">
         <v>1000</v>
@@ -1417,10 +1417,10 @@
         <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH5" t="n">
         <v>1000</v>
@@ -1432,77 +1432,77 @@
         <v>900</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM5" t="n">
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="BG5" t="n">
         <v>1.55</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-06 23:36:18</t>
+          <t>2026-05-07 01:55:26</t>
         </is>
       </c>
     </row>
@@ -1533,170 +1533,170 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.04</v>
+        <v>1.94</v>
       </c>
       <c r="G6" t="n">
-        <v>200</v>
+        <v>2.16</v>
       </c>
       <c r="H6" t="n">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="I6" t="n">
-        <v>250</v>
+        <v>4.6</v>
       </c>
       <c r="J6" t="n">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="K6" t="n">
-        <v>100</v>
+        <v>3.9</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>1.1</v>
+        <v>3.35</v>
       </c>
       <c r="O6" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="P6" t="n">
-        <v>1.09</v>
+        <v>1.83</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="R6" t="n">
-        <v>1.07</v>
+        <v>1.3</v>
       </c>
       <c r="S6" t="n">
-        <v>1.43</v>
+        <v>3.6</v>
       </c>
       <c r="T6" t="n">
-        <v>1.11</v>
+        <v>1.84</v>
       </c>
       <c r="U6" t="n">
-        <v>1.11</v>
+        <v>2.04</v>
       </c>
       <c r="V6" t="n">
-        <v>1.02</v>
+        <v>1.28</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1.86</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-06 23:36:18</t>
+          <t>2026-05-07 01:55:26</t>
         </is>
       </c>
     </row>
@@ -1727,170 +1727,170 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.62</v>
+        <v>1.97</v>
       </c>
       <c r="G7" t="n">
-        <v>6.4</v>
+        <v>2.14</v>
       </c>
       <c r="H7" t="n">
-        <v>2.74</v>
+        <v>3.55</v>
       </c>
       <c r="I7" t="n">
-        <v>44</v>
+        <v>4.3</v>
       </c>
       <c r="J7" t="n">
-        <v>2.84</v>
+        <v>3.55</v>
       </c>
       <c r="K7" t="n">
-        <v>8.6</v>
+        <v>3.95</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="O7" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="P7" t="n">
-        <v>1.07</v>
+        <v>1.92</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="R7" t="n">
-        <v>1.07</v>
+        <v>1.36</v>
       </c>
       <c r="S7" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="T7" t="n">
-        <v>1.11</v>
+        <v>1.76</v>
       </c>
       <c r="U7" t="n">
-        <v>1.11</v>
+        <v>2.12</v>
       </c>
       <c r="V7" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="W7" t="n">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="X7" t="n">
-        <v>500</v>
+        <v>16</v>
       </c>
       <c r="Y7" t="n">
-        <v>500</v>
+        <v>15.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="AA7" t="n">
         <v>900</v>
       </c>
       <c r="AB7" t="n">
-        <v>500</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC7" t="n">
-        <v>95</v>
+        <v>8.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>500</v>
+        <v>17</v>
       </c>
       <c r="AE7" t="n">
         <v>500</v>
       </c>
       <c r="AF7" t="n">
-        <v>500</v>
+        <v>13.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>500</v>
+        <v>11</v>
       </c>
       <c r="AH7" t="n">
-        <v>500</v>
+        <v>18</v>
       </c>
       <c r="AI7" t="n">
         <v>500</v>
       </c>
       <c r="AJ7" t="n">
-        <v>900</v>
+        <v>25</v>
       </c>
       <c r="AK7" t="n">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="AL7" t="n">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AM7" t="n">
         <v>500</v>
       </c>
       <c r="AN7" t="n">
-        <v>500</v>
+        <v>14.5</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU7" t="n">
         <v>5.1</v>
       </c>
-      <c r="AQ7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AV7" t="n">
-        <v>1.1</v>
+        <v>7.2</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.1</v>
+        <v>10</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.1</v>
+        <v>6.4</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.1</v>
+        <v>5.8</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.1</v>
+        <v>7.4</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.1</v>
+        <v>10</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.1</v>
+        <v>8.4</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.1</v>
+        <v>8</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.1</v>
+        <v>11</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.55</v>
+        <v>6.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.55</v>
+        <v>10</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-06 23:36:18</t>
+          <t>2026-05-07 01:55:26</t>
         </is>
       </c>
     </row>
@@ -1921,170 +1921,170 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>19.5</v>
+        <v>9.6</v>
       </c>
       <c r="G8" t="n">
+        <v>15</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V8" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AB8" t="n">
         <v>29</v>
       </c>
-      <c r="H8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J8" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="K8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X8" t="n">
-        <v>16</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>120</v>
-      </c>
       <c r="AC8" t="n">
-        <v>29</v>
+        <v>11.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>14.5</v>
+        <v>32</v>
       </c>
       <c r="AE8" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AG8" t="n">
-        <v>460</v>
+        <v>160</v>
       </c>
       <c r="AH8" t="n">
-        <v>380</v>
+        <v>50</v>
       </c>
       <c r="AI8" t="n">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="AJ8" t="n">
         <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>430</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>350</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>440</v>
       </c>
       <c r="AN8" t="n">
         <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="AP8" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ8" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AR8" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AS8" t="n">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="AT8" t="n">
-        <v>7.8</v>
+        <v>5.7</v>
       </c>
       <c r="AU8" t="n">
-        <v>12.5</v>
+        <v>4.5</v>
       </c>
       <c r="AV8" t="n">
         <v>8.4</v>
       </c>
       <c r="AW8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AX8" t="n">
         <v>6.8</v>
       </c>
-      <c r="AX8" t="n">
-        <v>5.8</v>
-      </c>
       <c r="AY8" t="n">
-        <v>9</v>
+        <v>6.2</v>
       </c>
       <c r="AZ8" t="n">
-        <v>8.800000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="BA8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BG8" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BB8" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-06 23:36:18</t>
+          <t>2026-05-07 01:55:26</t>
         </is>
       </c>
     </row>
@@ -2115,19 +2115,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="G9" t="n">
         <v>3.95</v>
       </c>
       <c r="H9" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="I9" t="n">
-        <v>2.58</v>
+        <v>2.44</v>
       </c>
       <c r="J9" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="K9" t="n">
         <v>3.35</v>
@@ -2139,19 +2139,19 @@
         <v>1.12</v>
       </c>
       <c r="N9" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="O9" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="P9" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S9" t="n">
         <v>5.1</v>
@@ -2160,19 +2160,19 @@
         <v>2.04</v>
       </c>
       <c r="U9" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="V9" t="n">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="W9" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="X9" t="n">
         <v>17.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Z9" t="n">
         <v>38</v>
@@ -2181,10 +2181,10 @@
         <v>900</v>
       </c>
       <c r="AB9" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="AC9" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD9" t="n">
         <v>21</v>
@@ -2193,13 +2193,13 @@
         <v>110</v>
       </c>
       <c r="AF9" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AG9" t="n">
         <v>970</v>
       </c>
       <c r="AH9" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AI9" t="n">
         <v>500</v>
@@ -2208,77 +2208,77 @@
         <v>900</v>
       </c>
       <c r="AK9" t="n">
-        <v>500</v>
+        <v>440</v>
       </c>
       <c r="AL9" t="n">
         <v>500</v>
       </c>
       <c r="AM9" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN9" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO9" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP9" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="AQ9" t="n">
         <v>6.6</v>
       </c>
       <c r="AR9" t="n">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="AS9" t="n">
         <v>26</v>
       </c>
       <c r="AT9" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AU9" t="n">
         <v>6.2</v>
       </c>
       <c r="AV9" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AW9" t="n">
         <v>24</v>
       </c>
       <c r="AX9" t="n">
-        <v>10.5</v>
+        <v>19.5</v>
       </c>
       <c r="AY9" t="n">
         <v>13</v>
       </c>
       <c r="AZ9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB9" t="n">
         <v>11.5</v>
       </c>
-      <c r="BA9" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BC9" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BD9" t="n">
-        <v>8.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>8.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="BF9" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BG9" t="n">
-        <v>7.4</v>
+        <v>27</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-06 23:36:18</t>
+          <t>2026-05-07 01:55:26</t>
         </is>
       </c>
     </row>
@@ -2309,61 +2309,61 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="G10" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="H10" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="I10" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="J10" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K10" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="L10" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="M10" t="n">
         <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="O10" t="n">
         <v>1.27</v>
       </c>
       <c r="P10" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="U10" t="n">
         <v>2.08</v>
       </c>
-      <c r="Q10" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.02</v>
-      </c>
       <c r="V10" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W10" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="X10" t="n">
-        <v>90</v>
+        <v>970</v>
       </c>
       <c r="Y10" t="n">
         <v>970</v>
@@ -2372,16 +2372,16 @@
         <v>500</v>
       </c>
       <c r="AA10" t="n">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="AB10" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AC10" t="n">
         <v>12.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AE10" t="n">
         <v>700</v>
@@ -2393,10 +2393,10 @@
         <v>36</v>
       </c>
       <c r="AH10" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AI10" t="n">
-        <v>320</v>
+        <v>700</v>
       </c>
       <c r="AJ10" t="n">
         <v>48</v>
@@ -2411,46 +2411,46 @@
         <v>580</v>
       </c>
       <c r="AN10" t="n">
-        <v>10.5</v>
+        <v>29</v>
       </c>
       <c r="AO10" t="n">
         <v>700</v>
       </c>
       <c r="AP10" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AQ10" t="n">
         <v>9</v>
       </c>
       <c r="AR10" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AT10" t="n">
-        <v>7.6</v>
+        <v>5.1</v>
       </c>
       <c r="AU10" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="AV10" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AW10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AX10" t="n">
         <v>6</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>5.6</v>
       </c>
       <c r="AY10" t="n">
         <v>5.8</v>
       </c>
       <c r="AZ10" t="n">
-        <v>11.5</v>
+        <v>7.2</v>
       </c>
       <c r="BA10" t="n">
-        <v>7.8</v>
+        <v>4.9</v>
       </c>
       <c r="BB10" t="n">
         <v>9.199999999999999</v>
@@ -2459,20 +2459,20 @@
         <v>10.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>18</v>
+        <v>7.6</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BF10" t="n">
-        <v>7.8</v>
+        <v>5.4</v>
       </c>
       <c r="BG10" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-06 23:36:18</t>
+          <t>2026-05-07 01:55:26</t>
         </is>
       </c>
     </row>
@@ -2503,46 +2503,46 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.09</v>
+        <v>1.97</v>
       </c>
       <c r="G11" t="n">
-        <v>95</v>
+        <v>2.12</v>
       </c>
       <c r="H11" t="n">
-        <v>1.09</v>
+        <v>3.2</v>
       </c>
       <c r="I11" t="n">
-        <v>90</v>
+        <v>3.9</v>
       </c>
       <c r="J11" t="n">
-        <v>1.09</v>
+        <v>3.9</v>
       </c>
       <c r="K11" t="n">
-        <v>32</v>
+        <v>5.4</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="M11" t="n">
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="O11" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="P11" t="n">
-        <v>1.25</v>
+        <v>3.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.07</v>
+        <v>1.32</v>
       </c>
       <c r="R11" t="n">
-        <v>1.24</v>
+        <v>2.08</v>
       </c>
       <c r="S11" t="n">
-        <v>1.07</v>
+        <v>1.8</v>
       </c>
       <c r="T11" t="n">
         <v>1.11</v>
@@ -2551,16 +2551,16 @@
         <v>1.11</v>
       </c>
       <c r="V11" t="n">
-        <v>1.02</v>
+        <v>1.37</v>
       </c>
       <c r="W11" t="n">
-        <v>1.02</v>
+        <v>1.89</v>
       </c>
       <c r="X11" t="n">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="Y11" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Z11" t="n">
         <v>500</v>
@@ -2569,13 +2569,13 @@
         <v>500</v>
       </c>
       <c r="AB11" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AC11" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AD11" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AE11" t="n">
         <v>500</v>
@@ -2584,10 +2584,10 @@
         <v>500</v>
       </c>
       <c r="AG11" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AH11" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AI11" t="n">
         <v>500</v>
@@ -2602,61 +2602,61 @@
         <v>500</v>
       </c>
       <c r="AM11" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN11" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO11" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.03</v>
+        <v>2</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.03</v>
+        <v>1.21</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.03</v>
+        <v>1.21</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.03</v>
+        <v>1.21</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.03</v>
+        <v>1.21</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="BF11" t="n">
         <v>1.55</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-06 23:36:18</t>
+          <t>2026-05-07 01:55:26</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
         <v>1.78</v>
       </c>
       <c r="G12" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="H12" t="n">
         <v>5.1</v>
@@ -2709,7 +2709,7 @@
         <v>5.5</v>
       </c>
       <c r="J12" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K12" t="n">
         <v>4.1</v>
@@ -2718,43 +2718,43 @@
         <v>1.42</v>
       </c>
       <c r="M12" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N12" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="O12" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="P12" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="Q12" t="n">
         <v>2.02</v>
       </c>
       <c r="R12" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="S12" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T12" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="U12" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="V12" t="n">
         <v>1.22</v>
       </c>
       <c r="W12" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="X12" t="n">
-        <v>15.5</v>
+        <v>28</v>
       </c>
       <c r="Y12" t="n">
-        <v>29</v>
+        <v>17.5</v>
       </c>
       <c r="Z12" t="n">
         <v>100</v>
@@ -2763,13 +2763,13 @@
         <v>900</v>
       </c>
       <c r="AB12" t="n">
-        <v>9</v>
+        <v>13.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AD12" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AE12" t="n">
         <v>700</v>
@@ -2781,16 +2781,16 @@
         <v>10.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="AI12" t="n">
         <v>700</v>
       </c>
       <c r="AJ12" t="n">
-        <v>22</v>
+        <v>900</v>
       </c>
       <c r="AK12" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="AL12" t="n">
         <v>95</v>
@@ -2799,7 +2799,7 @@
         <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="AO12" t="n">
         <v>700</v>
@@ -2811,56 +2811,56 @@
         <v>8.4</v>
       </c>
       <c r="AR12" t="n">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="AS12" t="n">
-        <v>8.4</v>
+        <v>4.8</v>
       </c>
       <c r="AT12" t="n">
         <v>7</v>
       </c>
       <c r="AU12" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>8</v>
+        <v>4.7</v>
       </c>
       <c r="AX12" t="n">
-        <v>5.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY12" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AZ12" t="n">
-        <v>6.4</v>
+        <v>11.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BB12" t="n">
         <v>9</v>
       </c>
       <c r="BC12" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="BD12" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BE12" t="n">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="BF12" t="n">
-        <v>5.3</v>
+        <v>11</v>
       </c>
       <c r="BG12" t="n">
-        <v>8.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-06 23:36:18</t>
+          <t>2026-05-07 01:55:26</t>
         </is>
       </c>
     </row>
@@ -2894,97 +2894,97 @@
         <v>3.05</v>
       </c>
       <c r="G13" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="H13" t="n">
         <v>2.88</v>
       </c>
       <c r="I13" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="J13" t="n">
-        <v>2.54</v>
+        <v>2.84</v>
       </c>
       <c r="K13" t="n">
         <v>3.1</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="M13" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="N13" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="O13" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="P13" t="n">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="R13" t="n">
         <v>1.18</v>
       </c>
       <c r="S13" t="n">
-        <v>2.62</v>
+        <v>6</v>
       </c>
       <c r="T13" t="n">
-        <v>1.78</v>
+        <v>2.16</v>
       </c>
       <c r="U13" t="n">
-        <v>1.35</v>
+        <v>1.72</v>
       </c>
       <c r="V13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W13" t="n">
         <v>1.45</v>
       </c>
-      <c r="W13" t="n">
-        <v>1.41</v>
-      </c>
       <c r="X13" t="n">
-        <v>970</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y13" t="n">
-        <v>500</v>
+        <v>8.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>500</v>
+        <v>18.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>900</v>
+        <v>250</v>
       </c>
       <c r="AB13" t="n">
-        <v>500</v>
+        <v>8.6</v>
       </c>
       <c r="AC13" t="n">
-        <v>500</v>
+        <v>7.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>500</v>
+        <v>15</v>
       </c>
       <c r="AE13" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="AF13" t="n">
-        <v>500</v>
+        <v>19</v>
       </c>
       <c r="AG13" t="n">
-        <v>500</v>
+        <v>15</v>
       </c>
       <c r="AH13" t="n">
-        <v>500</v>
+        <v>25</v>
       </c>
       <c r="AI13" t="n">
         <v>500</v>
       </c>
       <c r="AJ13" t="n">
-        <v>900</v>
+        <v>290</v>
       </c>
       <c r="AK13" t="n">
-        <v>500</v>
+        <v>290</v>
       </c>
       <c r="AL13" t="n">
         <v>500</v>
@@ -2993,68 +2993,68 @@
         <v>500</v>
       </c>
       <c r="AN13" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO13" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP13" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.19</v>
+        <v>6.8</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.2</v>
+        <v>14.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.21</v>
+        <v>9</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.2</v>
+        <v>7.2</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.18</v>
+        <v>6</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.2</v>
+        <v>11.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.21</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.2</v>
+        <v>16</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.2</v>
+        <v>12.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.21</v>
+        <v>20</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.21</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.21</v>
+        <v>9</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.21</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.21</v>
+        <v>9.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.21</v>
+        <v>10</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.55</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.55</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-06 23:36:18</t>
+          <t>2026-05-07 01:55:26</t>
         </is>
       </c>
     </row>
@@ -3085,55 +3085,55 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="G14" t="n">
         <v>1.68</v>
       </c>
       <c r="H14" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="I14" t="n">
         <v>6.8</v>
       </c>
       <c r="J14" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K14" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M14" t="n">
         <v>1.04</v>
       </c>
       <c r="N14" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O14" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P14" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="R14" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S14" t="n">
-        <v>2.58</v>
+        <v>2.72</v>
       </c>
       <c r="T14" t="n">
         <v>1.7</v>
       </c>
       <c r="U14" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V14" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W14" t="n">
         <v>2.46</v>
@@ -3142,10 +3142,10 @@
         <v>40</v>
       </c>
       <c r="Y14" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Z14" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AA14" t="n">
         <v>700</v>
@@ -3157,7 +3157,7 @@
         <v>12.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>25</v>
+        <v>950</v>
       </c>
       <c r="AE14" t="n">
         <v>700</v>
@@ -3166,7 +3166,7 @@
         <v>11.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH14" t="n">
         <v>25</v>
@@ -3196,25 +3196,25 @@
         <v>10.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR14" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT14" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AU14" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AV14" t="n">
         <v>17</v>
       </c>
       <c r="AW14" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AX14" t="n">
         <v>6.2</v>
@@ -3223,22 +3223,22 @@
         <v>8.6</v>
       </c>
       <c r="AZ14" t="n">
-        <v>13.5</v>
+        <v>9</v>
       </c>
       <c r="BA14" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BB14" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BC14" t="n">
         <v>11.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BE14" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BF14" t="n">
         <v>6.6</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-06 23:36:18</t>
+          <t>2026-05-07 01:55:26</t>
         </is>
       </c>
     </row>
@@ -3279,170 +3279,170 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.83</v>
+        <v>4.5</v>
       </c>
       <c r="G15" t="n">
-        <v>90</v>
+        <v>5.8</v>
       </c>
       <c r="H15" t="n">
-        <v>1.11</v>
+        <v>1.76</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="J15" t="n">
-        <v>2.52</v>
+        <v>3.7</v>
       </c>
       <c r="K15" t="n">
-        <v>70</v>
+        <v>4.3</v>
       </c>
       <c r="L15" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M15" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>1.25</v>
+        <v>3.8</v>
       </c>
       <c r="O15" t="n">
         <v>1.3</v>
       </c>
       <c r="P15" t="n">
-        <v>1.24</v>
+        <v>1.95</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.3</v>
+        <v>1.92</v>
       </c>
       <c r="R15" t="n">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3</v>
+        <v>3.35</v>
       </c>
       <c r="T15" t="n">
-        <v>1.05</v>
+        <v>1.84</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="V15" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>1.22</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG15" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH15" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK15" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AL15" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AM15" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN15" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.55</v>
+        <v>4</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.05</v>
+        <v>4.9</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-06 23:36:18</t>
+          <t>2026-05-07 01:55:26</t>
         </is>
       </c>
     </row>
@@ -3473,46 +3473,46 @@
         </is>
       </c>
       <c r="F16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="H16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q16" t="n">
         <v>1.78</v>
       </c>
-      <c r="G16" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="H16" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="I16" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K16" t="n">
-        <v>8</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N16" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.72</v>
-      </c>
       <c r="R16" t="n">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="S16" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="T16" t="n">
         <v>1.11</v>
@@ -3521,122 +3521,122 @@
         <v>1.11</v>
       </c>
       <c r="V16" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="W16" t="n">
-        <v>1.69</v>
+        <v>2.02</v>
       </c>
       <c r="X16" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Y16" t="n">
-        <v>500</v>
+        <v>19</v>
       </c>
       <c r="Z16" t="n">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AA16" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB16" t="n">
-        <v>500</v>
+        <v>11</v>
       </c>
       <c r="AC16" t="n">
-        <v>500</v>
+        <v>9.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>500</v>
+        <v>18.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AF16" t="n">
-        <v>500</v>
+        <v>13.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>500</v>
+        <v>11</v>
       </c>
       <c r="AH16" t="n">
-        <v>500</v>
+        <v>18.5</v>
       </c>
       <c r="AI16" t="n">
         <v>500</v>
       </c>
       <c r="AJ16" t="n">
-        <v>900</v>
+        <v>22</v>
       </c>
       <c r="AK16" t="n">
-        <v>500</v>
+        <v>20</v>
       </c>
       <c r="AL16" t="n">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="AM16" t="n">
         <v>500</v>
       </c>
       <c r="AN16" t="n">
-        <v>500</v>
+        <v>11.5</v>
       </c>
       <c r="AO16" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.06</v>
+        <v>15</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.07</v>
+        <v>15</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.07</v>
+        <v>5.2</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.07</v>
+        <v>5.7</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.07</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.07</v>
+        <v>15</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.07</v>
+        <v>5.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.07</v>
+        <v>10.5</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.07</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.07</v>
+        <v>15</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.07</v>
+        <v>5.7</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.07</v>
+        <v>4.8</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.07</v>
+        <v>16</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.07</v>
+        <v>5.2</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.07</v>
+        <v>5.7</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.55</v>
+        <v>9.4</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.55</v>
+        <v>5.6</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-06 23:36:18</t>
+          <t>2026-05-07 01:55:26</t>
         </is>
       </c>
     </row>
@@ -3667,37 +3667,37 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G17" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="H17" t="n">
         <v>3.3</v>
       </c>
       <c r="I17" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="J17" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K17" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L17" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N17" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="O17" t="n">
         <v>1.33</v>
       </c>
       <c r="P17" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="Q17" t="n">
         <v>2</v>
@@ -3706,7 +3706,7 @@
         <v>1.36</v>
       </c>
       <c r="S17" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="T17" t="n">
         <v>1.74</v>
@@ -3715,22 +3715,22 @@
         <v>2.14</v>
       </c>
       <c r="V17" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W17" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="X17" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y17" t="n">
         <v>16</v>
       </c>
       <c r="Z17" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AA17" t="n">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="AB17" t="n">
         <v>11</v>
@@ -3739,10 +3739,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD17" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AE17" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF17" t="n">
         <v>18.5</v>
@@ -3754,25 +3754,25 @@
         <v>21</v>
       </c>
       <c r="AI17" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AJ17" t="n">
         <v>34</v>
       </c>
       <c r="AK17" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AL17" t="n">
         <v>40</v>
       </c>
       <c r="AM17" t="n">
-        <v>110</v>
+        <v>580</v>
       </c>
       <c r="AN17" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AO17" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AP17" t="n">
         <v>10.5</v>
@@ -3784,7 +3784,7 @@
         <v>17.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="AT17" t="n">
         <v>7.6</v>
@@ -3796,7 +3796,7 @@
         <v>10.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="AX17" t="n">
         <v>11</v>
@@ -3808,29 +3808,29 @@
         <v>12.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="BB17" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="BC17" t="n">
         <v>18</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="BF17" t="n">
         <v>13.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-06 23:36:18</t>
+          <t>2026-05-07 01:55:26</t>
         </is>
       </c>
     </row>
@@ -3864,49 +3864,49 @@
         <v>1.68</v>
       </c>
       <c r="G18" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="H18" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="I18" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="J18" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K18" t="n">
         <v>4.6</v>
       </c>
       <c r="L18" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="M18" t="n">
         <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="O18" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P18" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="R18" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S18" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="T18" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="U18" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V18" t="n">
         <v>1.21</v>
@@ -3918,7 +3918,7 @@
         <v>22</v>
       </c>
       <c r="Y18" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="Z18" t="n">
         <v>500</v>
@@ -3933,19 +3933,19 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD18" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="AE18" t="n">
-        <v>170</v>
+        <v>700</v>
       </c>
       <c r="AF18" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AG18" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH18" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="AI18" t="n">
         <v>700</v>
@@ -3963,68 +3963,68 @@
         <v>580</v>
       </c>
       <c r="AN18" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AO18" t="n">
         <v>700</v>
       </c>
       <c r="AP18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV18" t="n">
         <v>14</v>
       </c>
-      <c r="AQ18" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AW18" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AX18" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AY18" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ18" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BB18" t="n">
         <v>14.5</v>
       </c>
-      <c r="BA18" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>13.5</v>
-      </c>
       <c r="BC18" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="BE18" t="n">
-        <v>9.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="BF18" t="n">
         <v>7</v>
       </c>
       <c r="BG18" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-06 23:36:18</t>
+          <t>2026-05-07 01:55:26</t>
         </is>
       </c>
     </row>
@@ -4055,55 +4055,55 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="G19" t="n">
         <v>1.97</v>
       </c>
       <c r="H19" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="I19" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="J19" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K19" t="n">
         <v>3.4</v>
       </c>
       <c r="L19" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="M19" t="n">
         <v>1.12</v>
       </c>
       <c r="N19" t="n">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="O19" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="P19" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="R19" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T19" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U19" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="V19" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="W19" t="n">
         <v>2.02</v>
@@ -4124,7 +4124,7 @@
         <v>6.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD19" t="n">
         <v>26</v>
@@ -4133,7 +4133,7 @@
         <v>260</v>
       </c>
       <c r="AF19" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG19" t="n">
         <v>11.5</v>
@@ -4148,7 +4148,7 @@
         <v>24</v>
       </c>
       <c r="AK19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL19" t="n">
         <v>120</v>
@@ -4157,7 +4157,7 @@
         <v>500</v>
       </c>
       <c r="AN19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO19" t="n">
         <v>700</v>
@@ -4169,56 +4169,56 @@
         <v>13</v>
       </c>
       <c r="AR19" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AS19" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AT19" t="n">
         <v>5.6</v>
       </c>
       <c r="AU19" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW19" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX19" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AY19" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA19" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BB19" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BC19" t="n">
         <v>21</v>
       </c>
       <c r="BD19" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BE19" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF19" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BG19" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-06 23:36:18</t>
+          <t>2026-05-07 01:55:26</t>
         </is>
       </c>
     </row>
@@ -4249,61 +4249,61 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="G20" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H20" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I20" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J20" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K20" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L20" t="n">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="M20" t="n">
         <v>1.13</v>
       </c>
       <c r="N20" t="n">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="O20" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="P20" t="n">
         <v>1.53</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="R20" t="n">
         <v>1.18</v>
       </c>
       <c r="S20" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="T20" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="U20" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="V20" t="n">
         <v>1.24</v>
       </c>
       <c r="W20" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="X20" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="Y20" t="n">
         <v>12.5</v>
@@ -4327,7 +4327,7 @@
         <v>100</v>
       </c>
       <c r="AF20" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AG20" t="n">
         <v>11.5</v>
@@ -4336,7 +4336,7 @@
         <v>28</v>
       </c>
       <c r="AI20" t="n">
-        <v>220</v>
+        <v>130</v>
       </c>
       <c r="AJ20" t="n">
         <v>25</v>
@@ -4345,10 +4345,10 @@
         <v>29</v>
       </c>
       <c r="AL20" t="n">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="AM20" t="n">
-        <v>580</v>
+        <v>240</v>
       </c>
       <c r="AN20" t="n">
         <v>26</v>
@@ -4357,40 +4357,40 @@
         <v>170</v>
       </c>
       <c r="AP20" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AQ20" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR20" t="n">
-        <v>29</v>
+        <v>11.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AT20" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AU20" t="n">
         <v>7</v>
       </c>
       <c r="AV20" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AX20" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY20" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA20" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BB20" t="n">
         <v>22</v>
@@ -4399,20 +4399,20 @@
         <v>25</v>
       </c>
       <c r="BD20" t="n">
-        <v>10.5</v>
+        <v>34</v>
       </c>
       <c r="BE20" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BF20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BG20" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-06 23:36:18</t>
+          <t>2026-05-07 01:55:26</t>
         </is>
       </c>
     </row>
@@ -4443,55 +4443,55 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="G21" t="n">
         <v>1.52</v>
       </c>
       <c r="H21" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="I21" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="J21" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K21" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L21" t="n">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="M21" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N21" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="O21" t="n">
         <v>1.28</v>
       </c>
       <c r="P21" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T21" t="n">
         <v>2</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="U21" t="n">
         <v>1.83</v>
       </c>
-      <c r="R21" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.8</v>
-      </c>
       <c r="V21" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W21" t="n">
         <v>2.92</v>
@@ -4500,55 +4500,55 @@
         <v>16.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="Z21" t="n">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="AA21" t="n">
-        <v>630</v>
+        <v>390</v>
       </c>
       <c r="AB21" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AC21" t="n">
         <v>11</v>
       </c>
       <c r="AD21" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AE21" t="n">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="AF21" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG21" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="AI21" t="n">
-        <v>330</v>
+        <v>160</v>
       </c>
       <c r="AJ21" t="n">
         <v>13.5</v>
       </c>
       <c r="AK21" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL21" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AM21" t="n">
-        <v>450</v>
+        <v>210</v>
       </c>
       <c r="AN21" t="n">
         <v>8</v>
       </c>
       <c r="AO21" t="n">
-        <v>220</v>
+        <v>190</v>
       </c>
       <c r="AP21" t="n">
         <v>14.5</v>
@@ -4557,13 +4557,13 @@
         <v>21</v>
       </c>
       <c r="AR21" t="n">
-        <v>10.5</v>
+        <v>25</v>
       </c>
       <c r="AS21" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AT21" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AU21" t="n">
         <v>9</v>
@@ -4575,7 +4575,7 @@
         <v>11</v>
       </c>
       <c r="AX21" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY21" t="n">
         <v>9</v>
@@ -4584,7 +4584,7 @@
         <v>22</v>
       </c>
       <c r="BA21" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="BB21" t="n">
         <v>11</v>
@@ -4593,20 +4593,20 @@
         <v>14</v>
       </c>
       <c r="BD21" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BE21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BF21" t="n">
         <v>6.6</v>
       </c>
       <c r="BG21" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-06 23:36:18</t>
+          <t>2026-05-07 01:55:26</t>
         </is>
       </c>
     </row>
@@ -4637,46 +4637,46 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="G22" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="H22" t="n">
-        <v>3.3</v>
+        <v>7.6</v>
       </c>
       <c r="I22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J22" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K22" t="n">
-        <v>6.8</v>
+        <v>5.1</v>
       </c>
       <c r="L22" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="M22" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N22" t="n">
-        <v>2.74</v>
+        <v>3.35</v>
       </c>
       <c r="O22" t="n">
         <v>1.37</v>
       </c>
       <c r="P22" t="n">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="R22" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="S22" t="n">
-        <v>2.56</v>
+        <v>3.85</v>
       </c>
       <c r="T22" t="n">
         <v>1.11</v>
@@ -4685,13 +4685,13 @@
         <v>1.11</v>
       </c>
       <c r="V22" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="W22" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="X22" t="n">
-        <v>90</v>
+        <v>950</v>
       </c>
       <c r="Y22" t="n">
         <v>1000</v>
@@ -4703,10 +4703,10 @@
         <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AC22" t="n">
-        <v>95</v>
+        <v>950</v>
       </c>
       <c r="AD22" t="n">
         <v>1000</v>
@@ -4718,7 +4718,7 @@
         <v>500</v>
       </c>
       <c r="AG22" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AH22" t="n">
         <v>1000</v>
@@ -4727,7 +4727,7 @@
         <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK22" t="n">
         <v>500</v>
@@ -4745,7 +4745,7 @@
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AQ22" t="n">
         <v>4.2</v>
@@ -4757,10 +4757,10 @@
         <v>4.2</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="AV22" t="n">
         <v>4.2</v>
@@ -4769,38 +4769,38 @@
         <v>4.2</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="BA22" t="n">
         <v>4.2</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="BE22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BF22" t="n">
         <v>1.19</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>1.14</v>
       </c>
       <c r="BG22" t="n">
         <v>4.2</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-06 23:36:18</t>
+          <t>2026-05-07 01:55:26</t>
         </is>
       </c>
     </row>
@@ -4834,94 +4834,94 @@
         <v>9.4</v>
       </c>
       <c r="G23" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="H23" t="n">
         <v>1.34</v>
       </c>
       <c r="I23" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="J23" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="K23" t="n">
         <v>6.8</v>
       </c>
       <c r="L23" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="M23" t="n">
         <v>1.02</v>
       </c>
       <c r="N23" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="O23" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P23" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="R23" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="S23" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="T23" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="U23" t="n">
         <v>2.26</v>
       </c>
       <c r="V23" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="W23" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X23" t="n">
-        <v>120</v>
+        <v>950</v>
       </c>
       <c r="Y23" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z23" t="n">
         <v>12</v>
       </c>
       <c r="AA23" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AB23" t="n">
-        <v>120</v>
+        <v>950</v>
       </c>
       <c r="AC23" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AD23" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE23" t="n">
         <v>14</v>
       </c>
       <c r="AF23" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AG23" t="n">
-        <v>95</v>
+        <v>38</v>
       </c>
       <c r="AH23" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="AI23" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="AJ23" t="n">
-        <v>340</v>
+        <v>290</v>
       </c>
       <c r="AK23" t="n">
         <v>240</v>
@@ -4930,10 +4930,10 @@
         <v>190</v>
       </c>
       <c r="AM23" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AN23" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AO23" t="n">
         <v>3.9</v>
@@ -4951,7 +4951,7 @@
         <v>10.5</v>
       </c>
       <c r="AT23" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU23" t="n">
         <v>11</v>
@@ -4963,7 +4963,7 @@
         <v>11.5</v>
       </c>
       <c r="AX23" t="n">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="AY23" t="n">
         <v>16</v>
@@ -4975,26 +4975,26 @@
         <v>19</v>
       </c>
       <c r="BB23" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BC23" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BD23" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BE23" t="n">
         <v>28</v>
       </c>
       <c r="BF23" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG23" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-06 23:36:18</t>
+          <t>2026-05-07 01:55:26</t>
         </is>
       </c>
     </row>
@@ -5025,52 +5025,52 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="G24" t="n">
         <v>1.5</v>
       </c>
       <c r="H24" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="I24" t="n">
-        <v>32</v>
+        <v>19.5</v>
       </c>
       <c r="J24" t="n">
         <v>4.3</v>
       </c>
       <c r="K24" t="n">
-        <v>5.9</v>
+        <v>5</v>
       </c>
       <c r="L24" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="M24" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N24" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="O24" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="P24" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.24</v>
+        <v>2.36</v>
       </c>
       <c r="R24" t="n">
         <v>1.24</v>
       </c>
       <c r="S24" t="n">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="T24" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="U24" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="V24" t="n">
         <v>1.08</v>
@@ -5082,7 +5082,7 @@
         <v>970</v>
       </c>
       <c r="Y24" t="n">
-        <v>80</v>
+        <v>950</v>
       </c>
       <c r="Z24" t="n">
         <v>1000</v>
@@ -5097,28 +5097,28 @@
         <v>42</v>
       </c>
       <c r="AD24" t="n">
-        <v>180</v>
+        <v>950</v>
       </c>
       <c r="AE24" t="n">
         <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AG24" t="n">
         <v>970</v>
       </c>
       <c r="AH24" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AI24" t="n">
         <v>1000</v>
       </c>
       <c r="AJ24" t="n">
-        <v>32</v>
+        <v>180</v>
       </c>
       <c r="AK24" t="n">
-        <v>65</v>
+        <v>970</v>
       </c>
       <c r="AL24" t="n">
         <v>500</v>
@@ -5133,7 +5133,7 @@
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="AQ24" t="n">
         <v>4.2</v>
@@ -5148,7 +5148,7 @@
         <v>4.2</v>
       </c>
       <c r="AU24" t="n">
-        <v>4.9</v>
+        <v>3.85</v>
       </c>
       <c r="AV24" t="n">
         <v>4.2</v>
@@ -5163,32 +5163,32 @@
         <v>6.4</v>
       </c>
       <c r="AZ24" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="BA24" t="n">
         <v>4.2</v>
       </c>
       <c r="BB24" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BC24" t="n">
-        <v>3.05</v>
+        <v>3.85</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BE24" t="n">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="BF24" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BG24" t="n">
-        <v>8.800000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-06 23:36:18</t>
+          <t>2026-05-07 01:55:26</t>
         </is>
       </c>
     </row>
@@ -5219,16 +5219,16 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="G25" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="H25" t="n">
         <v>6</v>
       </c>
       <c r="I25" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J25" t="n">
         <v>4.3</v>
@@ -5237,43 +5237,43 @@
         <v>4.5</v>
       </c>
       <c r="L25" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O25" t="n">
         <v>1.29</v>
       </c>
-      <c r="M25" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N25" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1.26</v>
-      </c>
       <c r="P25" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="R25" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="S25" t="n">
-        <v>2.98</v>
+        <v>3.25</v>
       </c>
       <c r="T25" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="U25" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="V25" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W25" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="X25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y25" t="n">
         <v>22</v>
@@ -5285,19 +5285,19 @@
         <v>170</v>
       </c>
       <c r="AB25" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC25" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD25" t="n">
         <v>23</v>
       </c>
       <c r="AE25" t="n">
-        <v>190</v>
+        <v>85</v>
       </c>
       <c r="AF25" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AG25" t="n">
         <v>10.5</v>
@@ -5306,58 +5306,58 @@
         <v>22</v>
       </c>
       <c r="AI25" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AJ25" t="n">
         <v>15.5</v>
       </c>
       <c r="AK25" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AL25" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AM25" t="n">
-        <v>110</v>
+        <v>580</v>
       </c>
       <c r="AN25" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>19</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>44</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>18</v>
+      </c>
+      <c r="AT25" t="n">
         <v>8.199999999999999</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>90</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>38</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>20</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>8.6</v>
       </c>
       <c r="AU25" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AV25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW25" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AX25" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AY25" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ25" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA25" t="n">
         <v>65</v>
@@ -5375,14 +5375,14 @@
         <v>50</v>
       </c>
       <c r="BF25" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG25" t="n">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-06 23:36:18</t>
+          <t>2026-05-07 01:55:26</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G26" t="n">
         <v>2.04</v>
@@ -5437,25 +5437,25 @@
         <v>1.07</v>
       </c>
       <c r="N26" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="O26" t="n">
         <v>1.32</v>
       </c>
       <c r="P26" t="n">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="Q26" t="n">
         <v>1.96</v>
       </c>
       <c r="R26" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="S26" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="T26" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="U26" t="n">
         <v>2.12</v>
@@ -5467,7 +5467,7 @@
         <v>1.96</v>
       </c>
       <c r="X26" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Y26" t="n">
         <v>15.5</v>
@@ -5479,10 +5479,10 @@
         <v>85</v>
       </c>
       <c r="AB26" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AC26" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD26" t="n">
         <v>16.5</v>
@@ -5494,7 +5494,7 @@
         <v>12.5</v>
       </c>
       <c r="AG26" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH26" t="n">
         <v>18.5</v>
@@ -5509,28 +5509,28 @@
         <v>22</v>
       </c>
       <c r="AL26" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM26" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AN26" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO26" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP26" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ26" t="n">
         <v>13.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AS26" t="n">
-        <v>15.5</v>
+        <v>28</v>
       </c>
       <c r="AT26" t="n">
         <v>8.6</v>
@@ -5542,7 +5542,7 @@
         <v>15</v>
       </c>
       <c r="AW26" t="n">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="AX26" t="n">
         <v>11</v>
@@ -5554,7 +5554,7 @@
         <v>17</v>
       </c>
       <c r="BA26" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BB26" t="n">
         <v>20</v>
@@ -5566,17 +5566,17 @@
         <v>32</v>
       </c>
       <c r="BE26" t="n">
+        <v>80</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BG26" t="n">
         <v>44</v>
       </c>
-      <c r="BF26" t="n">
-        <v>13</v>
-      </c>
-      <c r="BG26" t="n">
-        <v>46</v>
-      </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-06 23:36:18</t>
+          <t>2026-05-07 01:55:26</t>
         </is>
       </c>
     </row>
@@ -5613,10 +5613,10 @@
         <v>1.8</v>
       </c>
       <c r="H27" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I27" t="n">
         <v>5</v>
-      </c>
-      <c r="I27" t="n">
-        <v>5.1</v>
       </c>
       <c r="J27" t="n">
         <v>4</v>
@@ -5637,25 +5637,25 @@
         <v>1.31</v>
       </c>
       <c r="P27" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="R27" t="n">
         <v>1.39</v>
       </c>
       <c r="S27" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T27" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="U27" t="n">
         <v>2.08</v>
       </c>
       <c r="V27" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W27" t="n">
         <v>2.24</v>
@@ -5664,10 +5664,10 @@
         <v>15</v>
       </c>
       <c r="Y27" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA27" t="n">
         <v>120</v>
@@ -5688,7 +5688,7 @@
         <v>10.5</v>
       </c>
       <c r="AG27" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AH27" t="n">
         <v>19.5</v>
@@ -5697,7 +5697,7 @@
         <v>65</v>
       </c>
       <c r="AJ27" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AK27" t="n">
         <v>17.5</v>
@@ -5712,7 +5712,7 @@
         <v>11.5</v>
       </c>
       <c r="AO27" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AP27" t="n">
         <v>14.5</v>
@@ -5724,10 +5724,10 @@
         <v>34</v>
       </c>
       <c r="AS27" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AT27" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU27" t="n">
         <v>8.6</v>
@@ -5736,16 +5736,16 @@
         <v>17.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AX27" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY27" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ27" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA27" t="n">
         <v>55</v>
@@ -5757,10 +5757,10 @@
         <v>17</v>
       </c>
       <c r="BD27" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE27" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BF27" t="n">
         <v>10.5</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-06 23:36:18</t>
+          <t>2026-05-07 01:55:26</t>
         </is>
       </c>
     </row>
@@ -5807,46 +5807,46 @@
         <v>1.8</v>
       </c>
       <c r="H28" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I28" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="J28" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K28" t="n">
         <v>3.9</v>
       </c>
-      <c r="K28" t="n">
-        <v>3.95</v>
-      </c>
       <c r="L28" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M28" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N28" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="O28" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P28" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="R28" t="n">
         <v>1.35</v>
       </c>
       <c r="S28" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="T28" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="U28" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="V28" t="n">
         <v>1.22</v>
@@ -5855,10 +5855,10 @@
         <v>2.24</v>
       </c>
       <c r="X28" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z28" t="n">
         <v>40</v>
@@ -5870,7 +5870,7 @@
         <v>8</v>
       </c>
       <c r="AC28" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD28" t="n">
         <v>21</v>
@@ -5879,7 +5879,7 @@
         <v>75</v>
       </c>
       <c r="AF28" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AG28" t="n">
         <v>10</v>
@@ -5888,7 +5888,7 @@
         <v>22</v>
       </c>
       <c r="AI28" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AJ28" t="n">
         <v>18.5</v>
@@ -5906,7 +5906,7 @@
         <v>12.5</v>
       </c>
       <c r="AO28" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AP28" t="n">
         <v>13</v>
@@ -5933,16 +5933,16 @@
         <v>65</v>
       </c>
       <c r="AX28" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY28" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ28" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA28" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="BB28" t="n">
         <v>17.5</v>
@@ -5957,14 +5957,14 @@
         <v>70</v>
       </c>
       <c r="BF28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BG28" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-06 23:36:18</t>
+          <t>2026-05-07 01:55:26</t>
         </is>
       </c>
     </row>
@@ -5995,91 +5995,91 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="G29" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="H29" t="n">
         <v>10</v>
       </c>
       <c r="I29" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="J29" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="K29" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="L29" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="M29" t="n">
         <v>1.08</v>
       </c>
       <c r="N29" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="O29" t="n">
         <v>1.39</v>
       </c>
       <c r="P29" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="R29" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S29" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="T29" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="U29" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="V29" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W29" t="n">
         <v>3.15</v>
       </c>
       <c r="X29" t="n">
-        <v>970</v>
+        <v>90</v>
       </c>
       <c r="Y29" t="n">
-        <v>70</v>
+        <v>950</v>
       </c>
       <c r="Z29" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AA29" t="n">
         <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>9.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="AC29" t="n">
         <v>21</v>
       </c>
       <c r="AD29" t="n">
-        <v>180</v>
+        <v>950</v>
       </c>
       <c r="AE29" t="n">
         <v>1000</v>
       </c>
       <c r="AF29" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AG29" t="n">
         <v>970</v>
       </c>
       <c r="AH29" t="n">
-        <v>190</v>
+        <v>950</v>
       </c>
       <c r="AI29" t="n">
         <v>1000</v>
@@ -6109,56 +6109,56 @@
         <v>10.5</v>
       </c>
       <c r="AR29" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AS29" t="n">
         <v>4.2</v>
       </c>
       <c r="AT29" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AU29" t="n">
         <v>6.4</v>
       </c>
       <c r="AV29" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="AW29" t="n">
         <v>4.2</v>
       </c>
       <c r="AX29" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AY29" t="n">
         <v>6.4</v>
       </c>
       <c r="AZ29" t="n">
-        <v>4.1</v>
+        <v>6.2</v>
       </c>
       <c r="BA29" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BB29" t="n">
-        <v>5.6</v>
+        <v>8.6</v>
       </c>
       <c r="BC29" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BD29" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="BE29" t="n">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="BF29" t="n">
-        <v>3.9</v>
+        <v>7.4</v>
       </c>
       <c r="BG29" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-06 23:36:18</t>
+          <t>2026-05-07 01:55:26</t>
         </is>
       </c>
     </row>
@@ -6189,58 +6189,58 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="G30" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="H30" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I30" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J30" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="K30" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L30" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="M30" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N30" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="O30" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="P30" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.76</v>
+        <v>2.96</v>
       </c>
       <c r="R30" t="n">
         <v>1.18</v>
       </c>
       <c r="S30" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="T30" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="U30" t="n">
         <v>1.7</v>
       </c>
       <c r="V30" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W30" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X30" t="n">
         <v>8.199999999999999</v>
@@ -6255,13 +6255,13 @@
         <v>900</v>
       </c>
       <c r="AB30" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AC30" t="n">
         <v>7.4</v>
       </c>
       <c r="AD30" t="n">
-        <v>18.5</v>
+        <v>90</v>
       </c>
       <c r="AE30" t="n">
         <v>500</v>
@@ -6273,7 +6273,7 @@
         <v>12</v>
       </c>
       <c r="AH30" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AI30" t="n">
         <v>500</v>
@@ -6318,16 +6318,16 @@
         <v>15.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AX30" t="n">
         <v>11</v>
       </c>
       <c r="AY30" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ30" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="BA30" t="n">
         <v>12.5</v>
@@ -6342,17 +6342,17 @@
         <v>11.5</v>
       </c>
       <c r="BE30" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BF30" t="n">
         <v>10.5</v>
       </c>
       <c r="BG30" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-05-06 23:36:18</t>
+          <t>2026-05-07 01:55:26</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="G31" t="n">
         <v>1.62</v>
@@ -6392,7 +6392,7 @@
         <v>7</v>
       </c>
       <c r="I31" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J31" t="n">
         <v>4.1</v>
@@ -6401,28 +6401,28 @@
         <v>4.2</v>
       </c>
       <c r="L31" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="M31" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N31" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="O31" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P31" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R31" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T31" t="n">
         <v>2.16</v>
@@ -6431,13 +6431,13 @@
         <v>1.78</v>
       </c>
       <c r="V31" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W31" t="n">
         <v>2.6</v>
       </c>
       <c r="X31" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y31" t="n">
         <v>19</v>
@@ -6449,13 +6449,13 @@
         <v>290</v>
       </c>
       <c r="AB31" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC31" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AD31" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AE31" t="n">
         <v>140</v>
@@ -6473,37 +6473,37 @@
         <v>180</v>
       </c>
       <c r="AJ31" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AK31" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AL31" t="n">
         <v>48</v>
       </c>
       <c r="AM31" t="n">
-        <v>700</v>
+        <v>580</v>
       </c>
       <c r="AN31" t="n">
         <v>12</v>
       </c>
       <c r="AO31" t="n">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="AP31" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ31" t="n">
         <v>17</v>
       </c>
       <c r="AR31" t="n">
-        <v>13.5</v>
+        <v>50</v>
       </c>
       <c r="AS31" t="n">
         <v>13</v>
       </c>
       <c r="AT31" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU31" t="n">
         <v>8.199999999999999</v>
@@ -6524,13 +6524,13 @@
         <v>24</v>
       </c>
       <c r="BA31" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BB31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BC31" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BD31" t="n">
         <v>40</v>
@@ -6539,14 +6539,14 @@
         <v>14.5</v>
       </c>
       <c r="BF31" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BG31" t="n">
         <v>13</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-05-06 23:36:18</t>
+          <t>2026-05-07 01:55:26</t>
         </is>
       </c>
     </row>
@@ -6577,82 +6577,82 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="G32" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="H32" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="I32" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="J32" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="K32" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L32" t="n">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="M32" t="n">
         <v>1.12</v>
       </c>
       <c r="N32" t="n">
-        <v>2.6</v>
+        <v>2.76</v>
       </c>
       <c r="O32" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="P32" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.52</v>
+        <v>2.66</v>
       </c>
       <c r="R32" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="T32" t="n">
         <v>2.06</v>
       </c>
       <c r="U32" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="V32" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W32" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="X32" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Y32" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z32" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA32" t="n">
         <v>110</v>
       </c>
       <c r="AB32" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC32" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD32" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE32" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF32" t="n">
         <v>13.5</v>
@@ -6664,7 +6664,7 @@
         <v>24</v>
       </c>
       <c r="AI32" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AJ32" t="n">
         <v>34</v>
@@ -6694,7 +6694,7 @@
         <v>18</v>
       </c>
       <c r="AS32" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AT32" t="n">
         <v>6.2</v>
@@ -6706,7 +6706,7 @@
         <v>15</v>
       </c>
       <c r="AW32" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AX32" t="n">
         <v>11</v>
@@ -6718,29 +6718,29 @@
         <v>19.5</v>
       </c>
       <c r="BA32" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB32" t="n">
         <v>9.4</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>8.6</v>
       </c>
       <c r="BC32" t="n">
         <v>26</v>
       </c>
       <c r="BD32" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BE32" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BF32" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="BG32" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-05-06 23:36:18</t>
+          <t>2026-05-07 01:55:26</t>
         </is>
       </c>
     </row>
@@ -6771,58 +6771,58 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="G33" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="H33" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="I33" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="J33" t="n">
         <v>3.5</v>
       </c>
       <c r="K33" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L33" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="M33" t="n">
         <v>1.09</v>
       </c>
       <c r="N33" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O33" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P33" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="R33" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S33" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="T33" t="n">
         <v>2.04</v>
       </c>
       <c r="U33" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V33" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="W33" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X33" t="n">
         <v>11.5</v>
@@ -6837,7 +6837,7 @@
         <v>22</v>
       </c>
       <c r="AB33" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC33" t="n">
         <v>8.199999999999999</v>
@@ -6852,13 +6852,13 @@
         <v>42</v>
       </c>
       <c r="AG33" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH33" t="n">
         <v>24</v>
       </c>
       <c r="AI33" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AJ33" t="n">
         <v>160</v>
@@ -6867,7 +6867,7 @@
         <v>90</v>
       </c>
       <c r="AL33" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AM33" t="n">
         <v>200</v>
@@ -6876,7 +6876,7 @@
         <v>140</v>
       </c>
       <c r="AO33" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AP33" t="n">
         <v>9.800000000000001</v>
@@ -6903,7 +6903,7 @@
         <v>19.5</v>
       </c>
       <c r="AX33" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AY33" t="n">
         <v>17.5</v>
@@ -6912,29 +6912,29 @@
         <v>19.5</v>
       </c>
       <c r="BA33" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="BB33" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC33" t="n">
         <v>10</v>
       </c>
-      <c r="BC33" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BD33" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BE33" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF33" t="n">
         <v>10</v>
-      </c>
-      <c r="BF33" t="n">
-        <v>9.800000000000001</v>
       </c>
       <c r="BG33" t="n">
         <v>14.5</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-05-06 23:36:18</t>
+          <t>2026-05-07 01:55:26</t>
         </is>
       </c>
     </row>
@@ -6965,46 +6965,46 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.09</v>
+        <v>2.08</v>
       </c>
       <c r="G34" t="n">
-        <v>1000</v>
+        <v>2.16</v>
       </c>
       <c r="H34" t="n">
-        <v>1.09</v>
+        <v>4.1</v>
       </c>
       <c r="I34" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="J34" t="n">
-        <v>1.09</v>
+        <v>3.25</v>
       </c>
       <c r="K34" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="L34" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="M34" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N34" t="n">
-        <v>1.25</v>
+        <v>2.88</v>
       </c>
       <c r="O34" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="P34" t="n">
-        <v>1.24</v>
+        <v>1.61</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="R34" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S34" t="n">
-        <v>2.5</v>
+        <v>5.1</v>
       </c>
       <c r="T34" t="n">
         <v>1.11</v>
@@ -7013,10 +7013,10 @@
         <v>1.11</v>
       </c>
       <c r="V34" t="n">
-        <v>1.02</v>
+        <v>1.29</v>
       </c>
       <c r="W34" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="X34" t="n">
         <v>1000</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-05-06 23:36:18</t>
+          <t>2026-05-07 01:55:26</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-07.xlsx
@@ -760,7 +760,7 @@
         <v>2.5</v>
       </c>
       <c r="G2" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="H2" t="n">
         <v>4.3</v>
@@ -769,34 +769,34 @@
         <v>4.5</v>
       </c>
       <c r="J2" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="K2" t="n">
         <v>2.7</v>
       </c>
       <c r="L2" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="M2" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="N2" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="O2" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="P2" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="R2" t="n">
         <v>1.12</v>
       </c>
       <c r="S2" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="T2" t="n">
         <v>1.78</v>
@@ -808,7 +808,7 @@
         <v>1.28</v>
       </c>
       <c r="W2" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="X2" t="n">
         <v>970</v>
@@ -838,7 +838,7 @@
         <v>160</v>
       </c>
       <c r="AG2" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="AH2" t="n">
         <v>950</v>
@@ -868,49 +868,49 @@
         <v>3.25</v>
       </c>
       <c r="AQ2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR2" t="n">
         <v>1.41</v>
       </c>
-      <c r="AR2" t="n">
+      <c r="AS2" t="n">
         <v>1.42</v>
       </c>
-      <c r="AS2" t="n">
-        <v>1.43</v>
-      </c>
       <c r="AT2" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AU2" t="n">
         <v>1.38</v>
       </c>
       <c r="AV2" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AW2" t="n">
         <v>1.42</v>
       </c>
-      <c r="AW2" t="n">
+      <c r="AX2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BC2" t="n">
         <v>1.43</v>
       </c>
-      <c r="AX2" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="BC2" t="n">
+      <c r="BD2" t="n">
         <v>1.42</v>
       </c>
-      <c r="BD2" t="n">
-        <v>1.43</v>
-      </c>
       <c r="BE2" t="n">
-        <v>1.43</v>
+        <v>100</v>
       </c>
       <c r="BF2" t="n">
         <v>1.55</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-07 01:55:26</t>
+          <t>2026-05-07 04:14:56</t>
         </is>
       </c>
     </row>
@@ -951,61 +951,61 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="G3" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H3" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="I3" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K3" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="L3" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M3" t="n">
         <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="O3" t="n">
         <v>1.32</v>
       </c>
       <c r="P3" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S3" t="n">
         <v>3.5</v>
       </c>
       <c r="T3" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U3" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="V3" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W3" t="n">
         <v>1.45</v>
       </c>
       <c r="X3" t="n">
-        <v>19</v>
+        <v>500</v>
       </c>
       <c r="Y3" t="n">
         <v>17.5</v>
@@ -1023,7 +1023,7 @@
         <v>14</v>
       </c>
       <c r="AD3" t="n">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="AE3" t="n">
         <v>500</v>
@@ -1032,7 +1032,7 @@
         <v>500</v>
       </c>
       <c r="AG3" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AH3" t="n">
         <v>60</v>
@@ -1047,7 +1047,7 @@
         <v>500</v>
       </c>
       <c r="AL3" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="AM3" t="n">
         <v>580</v>
@@ -1062,25 +1062,25 @@
         <v>6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AR3" t="n">
         <v>7.6</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AT3" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="AV3" t="n">
         <v>7</v>
       </c>
       <c r="AW3" t="n">
-        <v>7</v>
+        <v>9.4</v>
       </c>
       <c r="AX3" t="n">
         <v>9</v>
@@ -1092,19 +1092,19 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BA3" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB3" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BC3" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BD3" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="BF3" t="n">
         <v>7.4</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-07 01:55:26</t>
+          <t>2026-05-07 04:14:56</t>
         </is>
       </c>
     </row>
@@ -1145,46 +1145,46 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="G4" t="n">
         <v>2.44</v>
       </c>
       <c r="H4" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="I4" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J4" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="K4" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M4" t="n">
         <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="O4" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P4" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R4" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S4" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="T4" t="n">
         <v>1.96</v>
@@ -1193,13 +1193,13 @@
         <v>1.89</v>
       </c>
       <c r="V4" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W4" t="n">
         <v>1.69</v>
       </c>
       <c r="X4" t="n">
-        <v>950</v>
+        <v>17.5</v>
       </c>
       <c r="Y4" t="n">
         <v>970</v>
@@ -1211,7 +1211,7 @@
         <v>900</v>
       </c>
       <c r="AB4" t="n">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="AC4" t="n">
         <v>14</v>
@@ -1226,10 +1226,10 @@
         <v>970</v>
       </c>
       <c r="AG4" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AH4" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AI4" t="n">
         <v>500</v>
@@ -1241,7 +1241,7 @@
         <v>500</v>
       </c>
       <c r="AL4" t="n">
-        <v>500</v>
+        <v>220</v>
       </c>
       <c r="AM4" t="n">
         <v>580</v>
@@ -1253,62 +1253,62 @@
         <v>600</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.78</v>
+        <v>5.5</v>
       </c>
       <c r="AQ4" t="n">
         <v>5.6</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.34</v>
+        <v>2.8</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.1</v>
+        <v>2.86</v>
       </c>
       <c r="AT4" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AU4" t="n">
         <v>4.5</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.44</v>
+        <v>4.4</v>
       </c>
       <c r="AW4" t="n">
-        <v>3.15</v>
+        <v>2.86</v>
       </c>
       <c r="AX4" t="n">
-        <v>2.56</v>
+        <v>3.95</v>
       </c>
       <c r="AY4" t="n">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="BA4" t="n">
-        <v>3.1</v>
+        <v>2.86</v>
       </c>
       <c r="BB4" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.4</v>
+        <v>2.7</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.35</v>
+        <v>2.72</v>
       </c>
       <c r="BG4" t="n">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-07 01:55:26</t>
+          <t>2026-05-07 04:14:56</t>
         </is>
       </c>
     </row>
@@ -1342,10 +1342,10 @@
         <v>1.2</v>
       </c>
       <c r="G5" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="H5" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I5" t="n">
         <v>990</v>
@@ -1360,25 +1360,25 @@
         <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N5" t="n">
         <v>1.1</v>
       </c>
       <c r="O5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="P5" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="R5" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="S5" t="n">
-        <v>1.39</v>
+        <v>1.75</v>
       </c>
       <c r="T5" t="n">
         <v>1.11</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-07 01:55:26</t>
+          <t>2026-05-07 04:14:56</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="G6" t="n">
         <v>2.16</v>
@@ -1542,73 +1542,73 @@
         <v>3.75</v>
       </c>
       <c r="I6" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J6" t="n">
         <v>3.35</v>
       </c>
       <c r="K6" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="L6" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M6" t="n">
         <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O6" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P6" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S6" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="T6" t="n">
-        <v>1.84</v>
+        <v>1.53</v>
       </c>
       <c r="U6" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V6" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W6" t="n">
         <v>1.86</v>
       </c>
       <c r="X6" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z6" t="n">
         <v>32</v>
       </c>
       <c r="AA6" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB6" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD6" t="n">
         <v>17.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>190</v>
+        <v>55</v>
       </c>
       <c r="AF6" t="n">
         <v>13.5</v>
@@ -1617,7 +1617,7 @@
         <v>11</v>
       </c>
       <c r="AH6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI6" t="n">
         <v>240</v>
@@ -1629,74 +1629,74 @@
         <v>23</v>
       </c>
       <c r="AL6" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AM6" t="n">
         <v>580</v>
       </c>
       <c r="AN6" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AO6" t="n">
-        <v>70</v>
+        <v>600</v>
       </c>
       <c r="AP6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AV6" t="n">
         <v>5.8</v>
       </c>
-      <c r="AQ6" t="n">
+      <c r="AW6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>5.9</v>
       </c>
-      <c r="AR6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AV6" t="n">
+      <c r="BA6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC6" t="n">
         <v>6.2</v>
       </c>
-      <c r="AW6" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BB6" t="n">
+      <c r="BD6" t="n">
         <v>7</v>
       </c>
-      <c r="BC6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BD6" t="n">
+      <c r="BE6" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BG6" t="n">
         <v>7.8</v>
       </c>
-      <c r="BE6" t="n">
-        <v>9</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-07 01:55:26</t>
+          <t>2026-05-07 04:14:56</t>
         </is>
       </c>
     </row>
@@ -1727,61 +1727,61 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="G7" t="n">
         <v>2.14</v>
       </c>
       <c r="H7" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N7" t="n">
         <v>3.55</v>
       </c>
-      <c r="I7" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N7" t="n">
-        <v>3.6</v>
-      </c>
       <c r="O7" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V7" t="n">
         <v>1.29</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.3</v>
       </c>
       <c r="W7" t="n">
         <v>1.87</v>
       </c>
       <c r="X7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Y7" t="n">
         <v>15.5</v>
@@ -1790,31 +1790,31 @@
         <v>32</v>
       </c>
       <c r="AA7" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AF7" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG7" t="n">
         <v>11</v>
       </c>
       <c r="AH7" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>500</v>
+        <v>230</v>
       </c>
       <c r="AJ7" t="n">
         <v>25</v>
@@ -1823,43 +1823,43 @@
         <v>22</v>
       </c>
       <c r="AL7" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM7" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN7" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AO7" t="n">
         <v>600</v>
       </c>
       <c r="AP7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AQ7" t="n">
         <v>7</v>
       </c>
-      <c r="AQ7" t="n">
-        <v>6.8</v>
-      </c>
       <c r="AR7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AS7" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="AU7" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AV7" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AW7" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX7" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AY7" t="n">
         <v>5.8</v>
@@ -1871,26 +1871,26 @@
         <v>10</v>
       </c>
       <c r="BB7" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BC7" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BD7" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BE7" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BF7" t="n">
         <v>6.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-07 01:55:26</t>
+          <t>2026-05-07 04:14:56</t>
         </is>
       </c>
     </row>
@@ -1921,91 +1921,91 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="G8" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H8" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="I8" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="J8" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="K8" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="L8" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="M8" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="O8" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="P8" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="R8" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S8" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="T8" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="U8" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="V8" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
         <v>13.5</v>
       </c>
       <c r="Y8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Z8" t="n">
         <v>6.2</v>
       </c>
-      <c r="Z8" t="n">
-        <v>6.8</v>
-      </c>
       <c r="AA8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>36</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD8" t="n">
         <v>12.5</v>
       </c>
-      <c r="AB8" t="n">
-        <v>29</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>32</v>
-      </c>
       <c r="AE8" t="n">
-        <v>500</v>
+        <v>20</v>
       </c>
       <c r="AF8" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AG8" t="n">
-        <v>160</v>
+        <v>70</v>
       </c>
       <c r="AH8" t="n">
-        <v>50</v>
+        <v>950</v>
       </c>
       <c r="AI8" t="n">
         <v>500</v>
@@ -2014,77 +2014,77 @@
         <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>430</v>
+        <v>510</v>
       </c>
       <c r="AL8" t="n">
-        <v>350</v>
+        <v>550</v>
       </c>
       <c r="AM8" t="n">
-        <v>440</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
         <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="AP8" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AQ8" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AR8" t="n">
         <v>5.4</v>
       </c>
       <c r="AS8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE8" t="n">
         <v>10</v>
       </c>
-      <c r="AT8" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BA8" t="n">
+      <c r="BF8" t="n">
+        <v>15</v>
+      </c>
+      <c r="BG8" t="n">
         <v>6.6</v>
       </c>
-      <c r="BB8" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-07 01:55:26</t>
+          <t>2026-05-07 04:14:56</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="G9" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="I9" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="J9" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K9" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L9" t="n">
         <v>1.56</v>
@@ -2154,22 +2154,22 @@
         <v>1.21</v>
       </c>
       <c r="S9" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="T9" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U9" t="n">
         <v>1.83</v>
       </c>
       <c r="V9" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="W9" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="X9" t="n">
-        <v>17.5</v>
+        <v>9.6</v>
       </c>
       <c r="Y9" t="n">
         <v>7.8</v>
@@ -2181,7 +2181,7 @@
         <v>900</v>
       </c>
       <c r="AB9" t="n">
-        <v>26</v>
+        <v>12.5</v>
       </c>
       <c r="AC9" t="n">
         <v>7.4</v>
@@ -2196,10 +2196,10 @@
         <v>500</v>
       </c>
       <c r="AG9" t="n">
-        <v>970</v>
+        <v>80</v>
       </c>
       <c r="AH9" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AI9" t="n">
         <v>500</v>
@@ -2223,19 +2223,19 @@
         <v>600</v>
       </c>
       <c r="AP9" t="n">
-        <v>5.4</v>
+        <v>8</v>
       </c>
       <c r="AQ9" t="n">
         <v>6.6</v>
       </c>
       <c r="AR9" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS9" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="AT9" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AU9" t="n">
         <v>6.2</v>
@@ -2244,7 +2244,7 @@
         <v>10</v>
       </c>
       <c r="AW9" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="AX9" t="n">
         <v>19.5</v>
@@ -2253,32 +2253,32 @@
         <v>13</v>
       </c>
       <c r="AZ9" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB9" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BA9" t="n">
-        <v>11</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BC9" t="n">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD9" t="n">
-        <v>11.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE9" t="n">
-        <v>12.5</v>
+        <v>9.6</v>
       </c>
       <c r="BF9" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG9" t="n">
         <v>7.8</v>
       </c>
-      <c r="BG9" t="n">
-        <v>27</v>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-07 01:55:26</t>
+          <t>2026-05-07 04:14:56</t>
         </is>
       </c>
     </row>
@@ -2309,28 +2309,28 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="G10" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="H10" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="I10" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="J10" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K10" t="n">
         <v>4.1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>4.7</v>
       </c>
       <c r="L10" t="n">
         <v>1.39</v>
       </c>
       <c r="M10" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N10" t="n">
         <v>4.3</v>
@@ -2339,31 +2339,31 @@
         <v>1.27</v>
       </c>
       <c r="P10" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="Q10" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T10" t="n">
         <v>1.81</v>
       </c>
-      <c r="R10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.78</v>
-      </c>
       <c r="U10" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V10" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W10" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="X10" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="Y10" t="n">
         <v>970</v>
@@ -2375,37 +2375,37 @@
         <v>900</v>
       </c>
       <c r="AB10" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AC10" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD10" t="n">
         <v>970</v>
       </c>
       <c r="AE10" t="n">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="AF10" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="AH10" t="n">
-        <v>950</v>
+        <v>60</v>
       </c>
       <c r="AI10" t="n">
         <v>700</v>
       </c>
       <c r="AJ10" t="n">
-        <v>48</v>
+        <v>900</v>
       </c>
       <c r="AK10" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AL10" t="n">
-        <v>500</v>
+        <v>95</v>
       </c>
       <c r="AM10" t="n">
         <v>580</v>
@@ -2417,28 +2417,28 @@
         <v>700</v>
       </c>
       <c r="AP10" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ10" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR10" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AT10" t="n">
-        <v>5.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU10" t="n">
         <v>5.8</v>
       </c>
       <c r="AV10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AW10" t="n">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="AX10" t="n">
         <v>6</v>
@@ -2447,10 +2447,10 @@
         <v>5.8</v>
       </c>
       <c r="AZ10" t="n">
-        <v>7.2</v>
+        <v>11.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.9</v>
+        <v>10</v>
       </c>
       <c r="BB10" t="n">
         <v>9.199999999999999</v>
@@ -2459,20 +2459,20 @@
         <v>10.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>7.6</v>
+        <v>15</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.3</v>
+        <v>10.5</v>
       </c>
       <c r="BF10" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BG10" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-07 01:55:26</t>
+          <t>2026-05-07 04:14:56</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="G11" t="n">
         <v>2.12</v>
@@ -2518,31 +2518,31 @@
         <v>3.9</v>
       </c>
       <c r="K11" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="L11" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="M11" t="n">
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>3.7</v>
+        <v>8</v>
       </c>
       <c r="O11" t="n">
         <v>1.09</v>
       </c>
       <c r="P11" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="R11" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="S11" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="T11" t="n">
         <v>1.11</v>
@@ -2551,7 +2551,7 @@
         <v>1.11</v>
       </c>
       <c r="V11" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W11" t="n">
         <v>1.89</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-07 01:55:26</t>
+          <t>2026-05-07 04:14:56</t>
         </is>
       </c>
     </row>
@@ -2697,16 +2697,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="G12" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="H12" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="I12" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="J12" t="n">
         <v>3.8</v>
@@ -2730,7 +2730,7 @@
         <v>1.93</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R12" t="n">
         <v>1.35</v>
@@ -2742,19 +2742,19 @@
         <v>1.89</v>
       </c>
       <c r="U12" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="V12" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W12" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="X12" t="n">
         <v>28</v>
       </c>
       <c r="Y12" t="n">
-        <v>17.5</v>
+        <v>26</v>
       </c>
       <c r="Z12" t="n">
         <v>100</v>
@@ -2766,7 +2766,7 @@
         <v>13.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>12</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD12" t="n">
         <v>950</v>
@@ -2775,22 +2775,22 @@
         <v>700</v>
       </c>
       <c r="AF12" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AG12" t="n">
         <v>10.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="AI12" t="n">
         <v>700</v>
       </c>
       <c r="AJ12" t="n">
-        <v>900</v>
+        <v>48</v>
       </c>
       <c r="AK12" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="AL12" t="n">
         <v>95</v>
@@ -2799,7 +2799,7 @@
         <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="AO12" t="n">
         <v>700</v>
@@ -2811,56 +2811,56 @@
         <v>8.4</v>
       </c>
       <c r="AR12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS12" t="n">
         <v>10</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>4.8</v>
       </c>
       <c r="AT12" t="n">
         <v>7</v>
       </c>
       <c r="AU12" t="n">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV12" t="n">
         <v>10.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.7</v>
+        <v>9.6</v>
       </c>
       <c r="AX12" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AY12" t="n">
-        <v>5.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ12" t="n">
         <v>11.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BB12" t="n">
         <v>9</v>
       </c>
       <c r="BC12" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BD12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BE12" t="n">
         <v>10</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>11.5</v>
       </c>
       <c r="BF12" t="n">
         <v>11</v>
       </c>
       <c r="BG12" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-07 01:55:26</t>
+          <t>2026-05-07 04:14:56</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="G13" t="n">
         <v>3.25</v>
@@ -2900,31 +2900,31 @@
         <v>2.88</v>
       </c>
       <c r="I13" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="J13" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="K13" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="L13" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="M13" t="n">
         <v>1.15</v>
       </c>
       <c r="N13" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="O13" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="P13" t="n">
         <v>1.47</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="R13" t="n">
         <v>1.18</v>
@@ -2939,13 +2939,13 @@
         <v>1.72</v>
       </c>
       <c r="V13" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="W13" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="X13" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Y13" t="n">
         <v>8.4</v>
@@ -2957,7 +2957,7 @@
         <v>250</v>
       </c>
       <c r="AB13" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC13" t="n">
         <v>7.2</v>
@@ -2966,13 +2966,13 @@
         <v>15</v>
       </c>
       <c r="AE13" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="AF13" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AH13" t="n">
         <v>25</v>
@@ -2984,7 +2984,7 @@
         <v>290</v>
       </c>
       <c r="AK13" t="n">
-        <v>290</v>
+        <v>60</v>
       </c>
       <c r="AL13" t="n">
         <v>500</v>
@@ -2999,16 +2999,16 @@
         <v>600</v>
       </c>
       <c r="AP13" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AQ13" t="n">
         <v>6.8</v>
       </c>
       <c r="AR13" t="n">
-        <v>14.5</v>
+        <v>8</v>
       </c>
       <c r="AS13" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT13" t="n">
         <v>7.2</v>
@@ -3020,41 +3020,41 @@
         <v>11.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>9.199999999999999</v>
+        <v>20</v>
       </c>
       <c r="AX13" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AZ13" t="n">
         <v>20</v>
       </c>
       <c r="BA13" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>25</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>38</v>
+      </c>
+      <c r="BD13" t="n">
         <v>9.800000000000001</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>9</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>9.4</v>
       </c>
       <c r="BE13" t="n">
         <v>10</v>
       </c>
       <c r="BF13" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-07 01:55:26</t>
+          <t>2026-05-07 04:14:56</t>
         </is>
       </c>
     </row>
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="G14" t="n">
         <v>1.68</v>
       </c>
       <c r="H14" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="I14" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="J14" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="K14" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L14" t="n">
         <v>1.32</v>
@@ -3109,34 +3109,34 @@
         <v>1.04</v>
       </c>
       <c r="N14" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O14" t="n">
         <v>1.22</v>
       </c>
       <c r="P14" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q14" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="T14" t="n">
         <v>1.67</v>
       </c>
-      <c r="R14" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.7</v>
-      </c>
       <c r="U14" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W14" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="X14" t="n">
         <v>40</v>
@@ -3163,22 +3163,22 @@
         <v>700</v>
       </c>
       <c r="AF14" t="n">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="AG14" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI14" t="n">
         <v>700</v>
       </c>
       <c r="AJ14" t="n">
-        <v>48</v>
+        <v>180</v>
       </c>
       <c r="AK14" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AL14" t="n">
         <v>75</v>
@@ -3193,13 +3193,13 @@
         <v>700</v>
       </c>
       <c r="AP14" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ14" t="n">
-        <v>8.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>9.800000000000001</v>
+        <v>18</v>
       </c>
       <c r="AS14" t="n">
         <v>11</v>
@@ -3208,47 +3208,47 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AU14" t="n">
-        <v>5.6</v>
+        <v>8.6</v>
       </c>
       <c r="AV14" t="n">
-        <v>17</v>
+        <v>10.5</v>
       </c>
       <c r="AW14" t="n">
+        <v>23</v>
+      </c>
+      <c r="AX14" t="n">
         <v>10</v>
       </c>
-      <c r="AX14" t="n">
-        <v>6.2</v>
-      </c>
       <c r="AY14" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ14" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BA14" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="BB14" t="n">
         <v>14</v>
       </c>
       <c r="BC14" t="n">
-        <v>11.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD14" t="n">
-        <v>8.4</v>
+        <v>14.5</v>
       </c>
       <c r="BE14" t="n">
-        <v>10.5</v>
+        <v>29</v>
       </c>
       <c r="BF14" t="n">
         <v>6.6</v>
       </c>
       <c r="BG14" t="n">
-        <v>42</v>
+        <v>10.5</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-07 01:55:26</t>
+          <t>2026-05-07 04:14:56</t>
         </is>
       </c>
     </row>
@@ -3279,16 +3279,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="G15" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="H15" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="I15" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="J15" t="n">
         <v>3.7</v>
@@ -3306,13 +3306,13 @@
         <v>3.8</v>
       </c>
       <c r="O15" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P15" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="R15" t="n">
         <v>1.36</v>
@@ -3321,22 +3321,22 @@
         <v>3.35</v>
       </c>
       <c r="T15" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U15" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="V15" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="W15" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="X15" t="n">
-        <v>29</v>
+        <v>500</v>
       </c>
       <c r="Y15" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="Z15" t="n">
         <v>40</v>
@@ -3354,7 +3354,7 @@
         <v>970</v>
       </c>
       <c r="AE15" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AF15" t="n">
         <v>500</v>
@@ -3387,62 +3387,62 @@
         <v>29</v>
       </c>
       <c r="AP15" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="AQ15" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AR15" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AU15" t="n">
         <v>4.8</v>
       </c>
-      <c r="AS15" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AV15" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.4</v>
+        <v>2.46</v>
       </c>
       <c r="AX15" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BG15" t="n">
         <v>5.5</v>
       </c>
-      <c r="AY15" t="n">
-        <v>4</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>4</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-07 01:55:26</t>
+          <t>2026-05-07 04:14:56</t>
         </is>
       </c>
     </row>
@@ -3473,25 +3473,25 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="G16" t="n">
         <v>1.97</v>
       </c>
       <c r="H16" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I16" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="J16" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="K16" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L16" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M16" t="n">
         <v>1.05</v>
@@ -3500,43 +3500,43 @@
         <v>4.2</v>
       </c>
       <c r="O16" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P16" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="R16" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="T16" t="n">
-        <v>1.11</v>
+        <v>1.69</v>
       </c>
       <c r="U16" t="n">
-        <v>1.11</v>
+        <v>2.2</v>
       </c>
       <c r="V16" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="W16" t="n">
         <v>2.02</v>
       </c>
       <c r="X16" t="n">
-        <v>950</v>
+        <v>19</v>
       </c>
       <c r="Y16" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Z16" t="n">
         <v>36</v>
       </c>
       <c r="AA16" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB16" t="n">
         <v>11</v>
@@ -3545,13 +3545,13 @@
         <v>9.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AE16" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AF16" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG16" t="n">
         <v>11</v>
@@ -3560,13 +3560,13 @@
         <v>18.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AJ16" t="n">
         <v>22</v>
       </c>
       <c r="AK16" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL16" t="n">
         <v>34</v>
@@ -3575,68 +3575,68 @@
         <v>500</v>
       </c>
       <c r="AN16" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AO16" t="n">
-        <v>600</v>
+        <v>55</v>
       </c>
       <c r="AP16" t="n">
-        <v>15</v>
+        <v>6.4</v>
       </c>
       <c r="AQ16" t="n">
-        <v>15</v>
+        <v>6.4</v>
       </c>
       <c r="AR16" t="n">
-        <v>5.2</v>
+        <v>22</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT16" t="n">
-        <v>8.800000000000001</v>
+        <v>5.1</v>
       </c>
       <c r="AU16" t="n">
-        <v>7.8</v>
+        <v>4.8</v>
       </c>
       <c r="AV16" t="n">
-        <v>15</v>
+        <v>6.4</v>
       </c>
       <c r="AW16" t="n">
-        <v>5.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX16" t="n">
         <v>10.5</v>
       </c>
       <c r="AY16" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE16" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AZ16" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BF16" t="n">
-        <v>9.4</v>
+        <v>5.1</v>
       </c>
       <c r="BG16" t="n">
-        <v>5.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-07 01:55:26</t>
+          <t>2026-05-07 04:14:56</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G17" t="n">
         <v>2.4</v>
@@ -3676,10 +3676,10 @@
         <v>3.3</v>
       </c>
       <c r="I17" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="J17" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K17" t="n">
         <v>3.75</v>
@@ -3691,13 +3691,13 @@
         <v>1.07</v>
       </c>
       <c r="N17" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="O17" t="n">
         <v>1.33</v>
       </c>
       <c r="P17" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="Q17" t="n">
         <v>2</v>
@@ -3706,10 +3706,10 @@
         <v>1.36</v>
       </c>
       <c r="S17" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="T17" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="U17" t="n">
         <v>2.14</v>
@@ -3724,19 +3724,19 @@
         <v>15</v>
       </c>
       <c r="Y17" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Z17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA17" t="n">
         <v>160</v>
       </c>
       <c r="AB17" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD17" t="n">
         <v>15</v>
@@ -3745,19 +3745,19 @@
         <v>40</v>
       </c>
       <c r="AF17" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AG17" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AI17" t="n">
         <v>130</v>
       </c>
       <c r="AJ17" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK17" t="n">
         <v>26</v>
@@ -3772,65 +3772,65 @@
         <v>20</v>
       </c>
       <c r="AO17" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AP17" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AQ17" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AR17" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AS17" t="n">
-        <v>5.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT17" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU17" t="n">
         <v>6.8</v>
       </c>
       <c r="AV17" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AW17" t="n">
-        <v>5.6</v>
+        <v>8.4</v>
       </c>
       <c r="AX17" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AY17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BA17" t="n">
         <v>8.4</v>
       </c>
-      <c r="AZ17" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BB17" t="n">
-        <v>5.8</v>
+        <v>14</v>
       </c>
       <c r="BC17" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BD17" t="n">
-        <v>5.6</v>
+        <v>8.4</v>
       </c>
       <c r="BE17" t="n">
-        <v>5.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF17" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="BG17" t="n">
-        <v>5.8</v>
+        <v>8</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-07 01:55:26</t>
+          <t>2026-05-07 04:14:56</t>
         </is>
       </c>
     </row>
@@ -3864,16 +3864,16 @@
         <v>1.68</v>
       </c>
       <c r="G18" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="H18" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="I18" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="J18" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K18" t="n">
         <v>4.6</v>
@@ -3885,40 +3885,40 @@
         <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O18" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P18" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="R18" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S18" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="T18" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U18" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="V18" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W18" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="X18" t="n">
         <v>22</v>
       </c>
       <c r="Y18" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="Z18" t="n">
         <v>500</v>
@@ -3942,10 +3942,10 @@
         <v>11</v>
       </c>
       <c r="AG18" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AH18" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="AI18" t="n">
         <v>700</v>
@@ -3969,62 +3969,62 @@
         <v>700</v>
       </c>
       <c r="AP18" t="n">
-        <v>14.5</v>
+        <v>9.6</v>
       </c>
       <c r="AQ18" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR18" t="n">
-        <v>11</v>
+        <v>19.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AT18" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AU18" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV18" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AW18" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AX18" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AY18" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ18" t="n">
-        <v>8.199999999999999</v>
+        <v>16.5</v>
       </c>
       <c r="BA18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD18" t="n">
         <v>11.5</v>
       </c>
-      <c r="BB18" t="n">
+      <c r="BE18" t="n">
         <v>14.5</v>
       </c>
-      <c r="BC18" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>10</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BF18" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BG18" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-07 01:55:26</t>
+          <t>2026-05-07 04:14:56</t>
         </is>
       </c>
     </row>
@@ -4055,22 +4055,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="G19" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="H19" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="I19" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="J19" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="K19" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="L19" t="n">
         <v>1.55</v>
@@ -4082,13 +4082,13 @@
         <v>2.88</v>
       </c>
       <c r="O19" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="P19" t="n">
         <v>1.59</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="R19" t="n">
         <v>1.21</v>
@@ -4097,16 +4097,16 @@
         <v>5.1</v>
       </c>
       <c r="T19" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U19" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="V19" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="W19" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="X19" t="n">
         <v>9.6</v>
@@ -4121,16 +4121,16 @@
         <v>900</v>
       </c>
       <c r="AB19" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AC19" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD19" t="n">
         <v>26</v>
       </c>
       <c r="AE19" t="n">
-        <v>260</v>
+        <v>700</v>
       </c>
       <c r="AF19" t="n">
         <v>10.5</v>
@@ -4151,31 +4151,31 @@
         <v>26</v>
       </c>
       <c r="AL19" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="AM19" t="n">
         <v>500</v>
       </c>
       <c r="AN19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO19" t="n">
         <v>700</v>
       </c>
       <c r="AP19" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AQ19" t="n">
         <v>13</v>
       </c>
       <c r="AR19" t="n">
-        <v>9.6</v>
+        <v>13</v>
       </c>
       <c r="AS19" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AT19" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AU19" t="n">
         <v>6.6</v>
@@ -4184,13 +4184,13 @@
         <v>21</v>
       </c>
       <c r="AW19" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AX19" t="n">
         <v>8.6</v>
       </c>
       <c r="AY19" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ19" t="n">
         <v>21</v>
@@ -4205,20 +4205,20 @@
         <v>21</v>
       </c>
       <c r="BD19" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="BE19" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BF19" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BG19" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-07 01:55:26</t>
+          <t>2026-05-07 04:14:56</t>
         </is>
       </c>
     </row>
@@ -4249,16 +4249,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="G20" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="H20" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="I20" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="J20" t="n">
         <v>3.25</v>
@@ -4267,79 +4267,79 @@
         <v>3.4</v>
       </c>
       <c r="L20" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="M20" t="n">
         <v>1.13</v>
       </c>
       <c r="N20" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="O20" t="n">
         <v>1.56</v>
       </c>
       <c r="P20" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="R20" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S20" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="T20" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="U20" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="V20" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W20" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="X20" t="n">
         <v>8.6</v>
       </c>
       <c r="Y20" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z20" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AA20" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AB20" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AC20" t="n">
         <v>7.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE20" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AF20" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG20" t="n">
         <v>11.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI20" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AJ20" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AK20" t="n">
         <v>29</v>
@@ -4348,25 +4348,25 @@
         <v>65</v>
       </c>
       <c r="AM20" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AN20" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO20" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AP20" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AQ20" t="n">
         <v>10</v>
       </c>
       <c r="AR20" t="n">
-        <v>11.5</v>
+        <v>28</v>
       </c>
       <c r="AS20" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AT20" t="n">
         <v>6</v>
@@ -4375,13 +4375,13 @@
         <v>7</v>
       </c>
       <c r="AV20" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AW20" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AX20" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AY20" t="n">
         <v>10</v>
@@ -4390,29 +4390,29 @@
         <v>24</v>
       </c>
       <c r="BA20" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BB20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC20" t="n">
         <v>25</v>
       </c>
       <c r="BD20" t="n">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="BE20" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BF20" t="n">
         <v>23</v>
       </c>
       <c r="BG20" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-07 01:55:26</t>
+          <t>2026-05-07 04:14:56</t>
         </is>
       </c>
     </row>
@@ -4446,19 +4446,19 @@
         <v>1.46</v>
       </c>
       <c r="G21" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="H21" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="I21" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="J21" t="n">
         <v>4.5</v>
       </c>
       <c r="K21" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L21" t="n">
         <v>1.37</v>
@@ -4467,7 +4467,7 @@
         <v>1.06</v>
       </c>
       <c r="N21" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O21" t="n">
         <v>1.28</v>
@@ -4476,25 +4476,25 @@
         <v>2.04</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S21" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T21" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="U21" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="V21" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="W21" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="X21" t="n">
         <v>16.5</v>
@@ -4503,37 +4503,37 @@
         <v>27</v>
       </c>
       <c r="Z21" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AA21" t="n">
-        <v>390</v>
+        <v>340</v>
       </c>
       <c r="AB21" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AC21" t="n">
         <v>11</v>
       </c>
       <c r="AD21" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AE21" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AF21" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AG21" t="n">
         <v>10.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI21" t="n">
-        <v>160</v>
+        <v>260</v>
       </c>
       <c r="AJ21" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AK21" t="n">
         <v>16.5</v>
@@ -4542,16 +4542,16 @@
         <v>40</v>
       </c>
       <c r="AM21" t="n">
-        <v>210</v>
+        <v>390</v>
       </c>
       <c r="AN21" t="n">
         <v>8</v>
       </c>
       <c r="AO21" t="n">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="AP21" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AQ21" t="n">
         <v>21</v>
@@ -4560,22 +4560,22 @@
         <v>25</v>
       </c>
       <c r="AS21" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AT21" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU21" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AV21" t="n">
         <v>26</v>
       </c>
       <c r="AW21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX21" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AY21" t="n">
         <v>9</v>
@@ -4596,17 +4596,17 @@
         <v>32</v>
       </c>
       <c r="BE21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BF21" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BG21" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-07 01:55:26</t>
+          <t>2026-05-07 04:14:56</t>
         </is>
       </c>
     </row>
@@ -4640,19 +4640,19 @@
         <v>1.45</v>
       </c>
       <c r="G22" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="H22" t="n">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="I22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J22" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="K22" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="L22" t="n">
         <v>1.44</v>
@@ -4661,76 +4661,76 @@
         <v>1.08</v>
       </c>
       <c r="N22" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="O22" t="n">
         <v>1.37</v>
       </c>
       <c r="P22" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R22" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S22" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T22" t="n">
-        <v>1.11</v>
+        <v>2.3</v>
       </c>
       <c r="U22" t="n">
-        <v>1.11</v>
+        <v>1.64</v>
       </c>
       <c r="V22" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="W22" t="n">
-        <v>2.94</v>
+        <v>3.15</v>
       </c>
       <c r="X22" t="n">
+        <v>90</v>
+      </c>
+      <c r="Y22" t="n">
         <v>950</v>
       </c>
-      <c r="Y22" t="n">
-        <v>1000</v>
-      </c>
       <c r="Z22" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AA22" t="n">
         <v>1000</v>
       </c>
       <c r="AB22" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD22" t="n">
         <v>950</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>950</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1000</v>
       </c>
       <c r="AE22" t="n">
         <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>500</v>
+        <v>7.8</v>
       </c>
       <c r="AG22" t="n">
+        <v>36</v>
+      </c>
+      <c r="AH22" t="n">
         <v>950</v>
       </c>
-      <c r="AH22" t="n">
-        <v>1000</v>
-      </c>
       <c r="AI22" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AJ22" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AK22" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="AL22" t="n">
         <v>500</v>
@@ -4745,62 +4745,62 @@
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.23</v>
+        <v>10</v>
       </c>
       <c r="AQ22" t="n">
-        <v>4.2</v>
+        <v>6.6</v>
       </c>
       <c r="AR22" t="n">
-        <v>4.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS22" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.19</v>
+        <v>3.8</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.21</v>
+        <v>9</v>
       </c>
       <c r="AV22" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="AW22" t="n">
-        <v>4.2</v>
+        <v>8.4</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.21</v>
+        <v>5.8</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.2</v>
+        <v>5</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.25</v>
+        <v>7</v>
       </c>
       <c r="BA22" t="n">
-        <v>4.2</v>
+        <v>8.4</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.23</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.22</v>
+        <v>6</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.23</v>
+        <v>7.6</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.25</v>
+        <v>8.6</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.19</v>
+        <v>4.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>4.2</v>
+        <v>8.6</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-07 01:55:26</t>
+          <t>2026-05-07 04:14:56</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G23" t="n">
         <v>11</v>
@@ -4843,10 +4843,10 @@
         <v>1.36</v>
       </c>
       <c r="J23" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="K23" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="L23" t="n">
         <v>1.22</v>
@@ -4861,70 +4861,70 @@
         <v>1.13</v>
       </c>
       <c r="P23" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="R23" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="S23" t="n">
         <v>2.02</v>
       </c>
       <c r="T23" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="U23" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="V23" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="W23" t="n">
         <v>1.11</v>
       </c>
       <c r="X23" t="n">
-        <v>950</v>
+        <v>48</v>
       </c>
       <c r="Y23" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Z23" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AA23" t="n">
         <v>13</v>
       </c>
       <c r="AB23" t="n">
-        <v>950</v>
+        <v>55</v>
       </c>
       <c r="AC23" t="n">
         <v>15</v>
       </c>
       <c r="AD23" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE23" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF23" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AG23" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AH23" t="n">
         <v>22</v>
       </c>
       <c r="AI23" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AJ23" t="n">
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="AK23" t="n">
-        <v>240</v>
+        <v>110</v>
       </c>
       <c r="AL23" t="n">
         <v>190</v>
@@ -4933,7 +4933,7 @@
         <v>90</v>
       </c>
       <c r="AN23" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="AO23" t="n">
         <v>3.9</v>
@@ -4942,59 +4942,59 @@
         <v>46</v>
       </c>
       <c r="AQ23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR23" t="n">
         <v>10</v>
       </c>
       <c r="AS23" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AT23" t="n">
-        <v>9.199999999999999</v>
+        <v>27</v>
       </c>
       <c r="AU23" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AV23" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW23" t="n">
         <v>11.5</v>
       </c>
       <c r="AX23" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AY23" t="n">
+        <v>30</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>22</v>
+      </c>
+      <c r="BB23" t="n">
         <v>16</v>
       </c>
-      <c r="AZ23" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>19</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>10</v>
-      </c>
       <c r="BC23" t="n">
-        <v>10</v>
+        <v>15.5</v>
       </c>
       <c r="BD23" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="BE23" t="n">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="BF23" t="n">
-        <v>9.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="BG23" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-07 01:55:26</t>
+          <t>2026-05-07 04:14:56</t>
         </is>
       </c>
     </row>
@@ -5025,22 +5025,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="G24" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="H24" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="I24" t="n">
-        <v>19.5</v>
+        <v>32</v>
       </c>
       <c r="J24" t="n">
         <v>4.3</v>
       </c>
       <c r="K24" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L24" t="n">
         <v>1.51</v>
@@ -5049,28 +5049,28 @@
         <v>1.09</v>
       </c>
       <c r="N24" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O24" t="n">
         <v>1.45</v>
       </c>
       <c r="P24" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="Q24" t="n">
         <v>2.36</v>
       </c>
       <c r="R24" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S24" t="n">
         <v>4.6</v>
       </c>
       <c r="T24" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="U24" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="V24" t="n">
         <v>1.08</v>
@@ -5091,7 +5091,7 @@
         <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AC24" t="n">
         <v>42</v>
@@ -5106,10 +5106,10 @@
         <v>6.8</v>
       </c>
       <c r="AG24" t="n">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="AH24" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI24" t="n">
         <v>1000</v>
@@ -5133,7 +5133,7 @@
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>3.65</v>
+        <v>3.15</v>
       </c>
       <c r="AQ24" t="n">
         <v>4.2</v>
@@ -5148,7 +5148,7 @@
         <v>4.2</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="AV24" t="n">
         <v>4.2</v>
@@ -5157,38 +5157,38 @@
         <v>4.2</v>
       </c>
       <c r="AX24" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="AY24" t="n">
         <v>6.4</v>
       </c>
       <c r="AZ24" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BA24" t="n">
         <v>4.2</v>
       </c>
       <c r="BB24" t="n">
-        <v>4.9</v>
+        <v>8.6</v>
       </c>
       <c r="BC24" t="n">
-        <v>3.85</v>
+        <v>3.25</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="BE24" t="n">
-        <v>3.25</v>
+        <v>2.94</v>
       </c>
       <c r="BF24" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BG24" t="n">
-        <v>5.8</v>
+        <v>8.4</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-07 01:55:26</t>
+          <t>2026-05-07 04:14:56</t>
         </is>
       </c>
     </row>
@@ -5219,25 +5219,25 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="G25" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="H25" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="I25" t="n">
         <v>6</v>
-      </c>
-      <c r="I25" t="n">
-        <v>6.2</v>
       </c>
       <c r="J25" t="n">
         <v>4.3</v>
       </c>
       <c r="K25" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L25" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M25" t="n">
         <v>1.06</v>
@@ -5252,10 +5252,10 @@
         <v>2.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="R25" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S25" t="n">
         <v>3.25</v>
@@ -5264,25 +5264,25 @@
         <v>1.93</v>
       </c>
       <c r="U25" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V25" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W25" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="X25" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Z25" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AA25" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AB25" t="n">
         <v>8.800000000000001</v>
@@ -5291,70 +5291,70 @@
         <v>9.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE25" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AF25" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG25" t="n">
         <v>10.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI25" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ25" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AK25" t="n">
         <v>16.5</v>
       </c>
       <c r="AL25" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AM25" t="n">
-        <v>580</v>
+        <v>120</v>
       </c>
       <c r="AN25" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO25" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP25" t="n">
         <v>15</v>
       </c>
       <c r="AQ25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR25" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AS25" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AT25" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AU25" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AV25" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="AX25" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AY25" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ25" t="n">
         <v>19.5</v>
@@ -5363,26 +5363,26 @@
         <v>65</v>
       </c>
       <c r="BB25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BC25" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BD25" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BE25" t="n">
         <v>50</v>
       </c>
       <c r="BF25" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BG25" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-07 01:55:26</t>
+          <t>2026-05-07 04:14:56</t>
         </is>
       </c>
     </row>
@@ -5413,10 +5413,10 @@
         </is>
       </c>
       <c r="F26" t="n">
+        <v>2</v>
+      </c>
+      <c r="G26" t="n">
         <v>2.02</v>
-      </c>
-      <c r="G26" t="n">
-        <v>2.04</v>
       </c>
       <c r="H26" t="n">
         <v>4</v>
@@ -5431,43 +5431,43 @@
         <v>3.85</v>
       </c>
       <c r="L26" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M26" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N26" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="O26" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P26" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="R26" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S26" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="T26" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="U26" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="V26" t="n">
         <v>1.31</v>
       </c>
       <c r="W26" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="X26" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Y26" t="n">
         <v>15.5</v>
@@ -5500,7 +5500,7 @@
         <v>18.5</v>
       </c>
       <c r="AI26" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ26" t="n">
         <v>24</v>
@@ -5521,19 +5521,19 @@
         <v>55</v>
       </c>
       <c r="AP26" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ26" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AR26" t="n">
         <v>26</v>
       </c>
       <c r="AS26" t="n">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="AT26" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AU26" t="n">
         <v>7.8</v>
@@ -5560,7 +5560,7 @@
         <v>20</v>
       </c>
       <c r="BC26" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BD26" t="n">
         <v>32</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-07 01:55:26</t>
+          <t>2026-05-07 04:14:56</t>
         </is>
       </c>
     </row>
@@ -5613,10 +5613,10 @@
         <v>1.8</v>
       </c>
       <c r="H27" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="I27" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="J27" t="n">
         <v>4</v>
@@ -5625,7 +5625,7 @@
         <v>4.1</v>
       </c>
       <c r="L27" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M27" t="n">
         <v>1.07</v>
@@ -5637,25 +5637,25 @@
         <v>1.31</v>
       </c>
       <c r="P27" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="R27" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S27" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="T27" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="U27" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V27" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="W27" t="n">
         <v>2.24</v>
@@ -5664,19 +5664,19 @@
         <v>15</v>
       </c>
       <c r="Y27" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Z27" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AA27" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AB27" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AC27" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD27" t="n">
         <v>19</v>
@@ -5691,13 +5691,13 @@
         <v>9.6</v>
       </c>
       <c r="AH27" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI27" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ27" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AK27" t="n">
         <v>17.5</v>
@@ -5712,7 +5712,7 @@
         <v>11.5</v>
       </c>
       <c r="AO27" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AP27" t="n">
         <v>14.5</v>
@@ -5724,7 +5724,7 @@
         <v>34</v>
       </c>
       <c r="AS27" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AT27" t="n">
         <v>8.4</v>
@@ -5739,19 +5739,19 @@
         <v>55</v>
       </c>
       <c r="AX27" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY27" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ27" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BA27" t="n">
         <v>55</v>
       </c>
       <c r="BB27" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BC27" t="n">
         <v>17</v>
@@ -5760,7 +5760,7 @@
         <v>32</v>
       </c>
       <c r="BE27" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BF27" t="n">
         <v>10.5</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-07 01:55:26</t>
+          <t>2026-05-07 04:14:56</t>
         </is>
       </c>
     </row>
@@ -5822,31 +5822,31 @@
         <v>1.44</v>
       </c>
       <c r="M28" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N28" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="O28" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P28" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="R28" t="n">
         <v>1.35</v>
       </c>
       <c r="S28" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="T28" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="U28" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="V28" t="n">
         <v>1.22</v>
@@ -5855,10 +5855,10 @@
         <v>2.24</v>
       </c>
       <c r="X28" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Y28" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Z28" t="n">
         <v>40</v>
@@ -5870,7 +5870,7 @@
         <v>8</v>
       </c>
       <c r="AC28" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD28" t="n">
         <v>21</v>
@@ -5879,25 +5879,25 @@
         <v>75</v>
       </c>
       <c r="AF28" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AG28" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI28" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ28" t="n">
         <v>18.5</v>
       </c>
       <c r="AK28" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL28" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM28" t="n">
         <v>130</v>
@@ -5906,7 +5906,7 @@
         <v>12.5</v>
       </c>
       <c r="AO28" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AP28" t="n">
         <v>13</v>
@@ -5924,7 +5924,7 @@
         <v>7.6</v>
       </c>
       <c r="AU28" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AV28" t="n">
         <v>19</v>
@@ -5933,7 +5933,7 @@
         <v>65</v>
       </c>
       <c r="AX28" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AY28" t="n">
         <v>9.6</v>
@@ -5942,7 +5942,7 @@
         <v>20</v>
       </c>
       <c r="BA28" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BB28" t="n">
         <v>17.5</v>
@@ -5954,17 +5954,17 @@
         <v>36</v>
       </c>
       <c r="BE28" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="BF28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BG28" t="n">
         <v>85</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-07 01:55:26</t>
+          <t>2026-05-07 04:14:56</t>
         </is>
       </c>
     </row>
@@ -5995,25 +5995,25 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="G29" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="H29" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="I29" t="n">
         <v>13.5</v>
       </c>
       <c r="J29" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K29" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="L29" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="M29" t="n">
         <v>1.08</v>
@@ -6022,25 +6022,25 @@
         <v>3.3</v>
       </c>
       <c r="O29" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P29" t="n">
         <v>1.77</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="R29" t="n">
         <v>1.28</v>
       </c>
       <c r="S29" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T29" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="U29" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="V29" t="n">
         <v>1.08</v>
@@ -6097,7 +6097,7 @@
         <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AO29" t="n">
         <v>1000</v>
@@ -6109,7 +6109,7 @@
         <v>10.5</v>
       </c>
       <c r="AR29" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AS29" t="n">
         <v>4.2</v>
@@ -6121,19 +6121,19 @@
         <v>6.4</v>
       </c>
       <c r="AV29" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="AW29" t="n">
         <v>4.2</v>
       </c>
       <c r="AX29" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AY29" t="n">
         <v>6.4</v>
       </c>
       <c r="AZ29" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BA29" t="n">
         <v>4.2</v>
@@ -6145,10 +6145,10 @@
         <v>6.8</v>
       </c>
       <c r="BD29" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="BE29" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BF29" t="n">
         <v>7.4</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-07 01:55:26</t>
+          <t>2026-05-07 04:14:56</t>
         </is>
       </c>
     </row>
@@ -6201,31 +6201,31 @@
         <v>4.3</v>
       </c>
       <c r="J30" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K30" t="n">
         <v>3.25</v>
       </c>
       <c r="L30" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="M30" t="n">
         <v>1.14</v>
       </c>
       <c r="N30" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="O30" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="P30" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="R30" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S30" t="n">
         <v>6.2</v>
@@ -6303,7 +6303,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AR30" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="AS30" t="n">
         <v>12.5</v>
@@ -6342,7 +6342,7 @@
         <v>11.5</v>
       </c>
       <c r="BE30" t="n">
-        <v>13.5</v>
+        <v>25</v>
       </c>
       <c r="BF30" t="n">
         <v>10.5</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-05-07 01:55:26</t>
+          <t>2026-05-07 04:14:56</t>
         </is>
       </c>
     </row>
@@ -6383,19 +6383,19 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="G31" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="H31" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="I31" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="J31" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K31" t="n">
         <v>4.2</v>
@@ -6413,31 +6413,31 @@
         <v>1.39</v>
       </c>
       <c r="P31" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R31" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S31" t="n">
         <v>4.1</v>
       </c>
       <c r="T31" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="U31" t="n">
         <v>1.78</v>
       </c>
       <c r="V31" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W31" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="X31" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y31" t="n">
         <v>19</v>
@@ -6470,10 +6470,10 @@
         <v>28</v>
       </c>
       <c r="AI31" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AJ31" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AK31" t="n">
         <v>19</v>
@@ -6488,28 +6488,28 @@
         <v>12</v>
       </c>
       <c r="AO31" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="AP31" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AQ31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR31" t="n">
-        <v>50</v>
+        <v>13.5</v>
       </c>
       <c r="AS31" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AT31" t="n">
         <v>6.4</v>
       </c>
       <c r="AU31" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW31" t="n">
         <v>14</v>
@@ -6524,29 +6524,29 @@
         <v>24</v>
       </c>
       <c r="BA31" t="n">
-        <v>13</v>
+        <v>110</v>
       </c>
       <c r="BB31" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BC31" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BD31" t="n">
         <v>40</v>
       </c>
       <c r="BE31" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BF31" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BG31" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-05-07 01:55:26</t>
+          <t>2026-05-07 04:14:56</t>
         </is>
       </c>
     </row>
@@ -6601,22 +6601,22 @@
         <v>1.12</v>
       </c>
       <c r="N32" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="O32" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="P32" t="n">
         <v>1.56</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="R32" t="n">
         <v>1.2</v>
       </c>
       <c r="S32" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="T32" t="n">
         <v>2.06</v>
@@ -6634,10 +6634,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Y32" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Z32" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AA32" t="n">
         <v>110</v>
@@ -6652,7 +6652,7 @@
         <v>17.5</v>
       </c>
       <c r="AE32" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AF32" t="n">
         <v>13.5</v>
@@ -6667,7 +6667,7 @@
         <v>90</v>
       </c>
       <c r="AJ32" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK32" t="n">
         <v>32</v>
@@ -6694,7 +6694,7 @@
         <v>18</v>
       </c>
       <c r="AS32" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AT32" t="n">
         <v>6.2</v>
@@ -6706,7 +6706,7 @@
         <v>15</v>
       </c>
       <c r="AW32" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AX32" t="n">
         <v>11</v>
@@ -6718,10 +6718,10 @@
         <v>19.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BB32" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC32" t="n">
         <v>26</v>
@@ -6730,17 +6730,17 @@
         <v>10.5</v>
       </c>
       <c r="BE32" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BF32" t="n">
         <v>23</v>
       </c>
       <c r="BG32" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-05-07 01:55:26</t>
+          <t>2026-05-07 04:14:56</t>
         </is>
       </c>
     </row>
@@ -6795,7 +6795,7 @@
         <v>1.09</v>
       </c>
       <c r="N33" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O33" t="n">
         <v>1.43</v>
@@ -6804,22 +6804,22 @@
         <v>1.74</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="R33" t="n">
         <v>1.26</v>
       </c>
       <c r="S33" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="T33" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U33" t="n">
         <v>1.81</v>
       </c>
       <c r="V33" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="W33" t="n">
         <v>1.23</v>
@@ -6849,7 +6849,7 @@
         <v>24</v>
       </c>
       <c r="AF33" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AG33" t="n">
         <v>21</v>
@@ -6876,10 +6876,10 @@
         <v>140</v>
       </c>
       <c r="AO33" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AP33" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ33" t="n">
         <v>6.4</v>
@@ -6903,7 +6903,7 @@
         <v>19.5</v>
       </c>
       <c r="AX33" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AY33" t="n">
         <v>17.5</v>
@@ -6915,13 +6915,13 @@
         <v>32</v>
       </c>
       <c r="BB33" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BC33" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD33" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE33" t="n">
         <v>10.5</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-05-07 01:55:26</t>
+          <t>2026-05-07 04:14:56</t>
         </is>
       </c>
     </row>
@@ -6998,10 +6998,10 @@
         <v>1.61</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="R34" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S34" t="n">
         <v>5.1</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-05-07 01:55:26</t>
+          <t>2026-05-07 04:14:56</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-07.xlsx
@@ -757,40 +757,40 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="G2" t="n">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="H2" t="n">
         <v>4.3</v>
       </c>
       <c r="I2" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="J2" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="K2" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="L2" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="M2" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="N2" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="O2" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="P2" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="R2" t="n">
         <v>1.12</v>
@@ -799,128 +799,128 @@
         <v>8.6</v>
       </c>
       <c r="T2" t="n">
-        <v>1.78</v>
+        <v>2.46</v>
       </c>
       <c r="U2" t="n">
         <v>1.34</v>
       </c>
       <c r="V2" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W2" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="X2" t="n">
-        <v>970</v>
+        <v>5.7</v>
       </c>
       <c r="Y2" t="n">
-        <v>950</v>
+        <v>9.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>500</v>
+        <v>27</v>
       </c>
       <c r="AA2" t="n">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="AB2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE2" t="n">
         <v>110</v>
       </c>
-      <c r="AC2" t="n">
-        <v>95</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>500</v>
-      </c>
       <c r="AF2" t="n">
-        <v>160</v>
+        <v>13</v>
       </c>
       <c r="AG2" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="AH2" t="n">
-        <v>950</v>
+        <v>40</v>
       </c>
       <c r="AI2" t="n">
-        <v>500</v>
+        <v>180</v>
       </c>
       <c r="AJ2" t="n">
-        <v>500</v>
+        <v>42</v>
       </c>
       <c r="AK2" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="AL2" t="n">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AM2" t="n">
         <v>500</v>
       </c>
       <c r="AN2" t="n">
-        <v>600</v>
+        <v>65</v>
       </c>
       <c r="AO2" t="n">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.25</v>
+        <v>5.3</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.4</v>
+        <v>5.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.41</v>
+        <v>11.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.42</v>
+        <v>5.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.38</v>
+        <v>5.4</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.38</v>
+        <v>6</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.55</v>
+        <v>14</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.42</v>
+        <v>5.4</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.38</v>
+        <v>10.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.28</v>
+        <v>12.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.42</v>
+        <v>17</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.42</v>
+        <v>5.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.42</v>
+        <v>17.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.43</v>
+        <v>20</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.42</v>
+        <v>5.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.55</v>
+        <v>10.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.55</v>
+        <v>5.5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -951,19 +951,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.92</v>
+        <v>2.62</v>
       </c>
       <c r="G3" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="H3" t="n">
-        <v>2.42</v>
+        <v>2.66</v>
       </c>
       <c r="I3" t="n">
-        <v>2.68</v>
+        <v>2.94</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K3" t="n">
         <v>3.7</v>
@@ -975,13 +975,13 @@
         <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O3" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P3" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="Q3" t="n">
         <v>2</v>
@@ -990,28 +990,28 @@
         <v>1.35</v>
       </c>
       <c r="S3" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="T3" t="n">
         <v>1.74</v>
       </c>
       <c r="U3" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="V3" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="W3" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="X3" t="n">
-        <v>500</v>
+        <v>25</v>
       </c>
       <c r="Y3" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="Z3" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AA3" t="n">
         <v>900</v>
@@ -1023,25 +1023,25 @@
         <v>14</v>
       </c>
       <c r="AD3" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AE3" t="n">
         <v>500</v>
       </c>
       <c r="AF3" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AG3" t="n">
         <v>500</v>
       </c>
       <c r="AH3" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AI3" t="n">
         <v>500</v>
       </c>
       <c r="AJ3" t="n">
-        <v>340</v>
+        <v>500</v>
       </c>
       <c r="AK3" t="n">
         <v>500</v>
@@ -1062,28 +1062,28 @@
         <v>6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR3" t="n">
         <v>7.6</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT3" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="AU3" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AV3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AW3" t="n">
-        <v>9.4</v>
+        <v>13</v>
       </c>
       <c r="AX3" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AY3" t="n">
         <v>7.6</v>
@@ -1092,19 +1092,19 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BA3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB3" t="n">
         <v>8.6</v>
       </c>
-      <c r="BB3" t="n">
-        <v>9</v>
-      </c>
       <c r="BC3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD3" t="n">
         <v>8.4</v>
       </c>
-      <c r="BD3" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BE3" t="n">
-        <v>5.5</v>
+        <v>10.5</v>
       </c>
       <c r="BF3" t="n">
         <v>7.4</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -1145,73 +1145,73 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.16</v>
+        <v>2.34</v>
       </c>
       <c r="G4" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="H4" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="I4" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="J4" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S4" t="n">
         <v>4.5</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N4" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S4" t="n">
-        <v>4.3</v>
       </c>
       <c r="T4" t="n">
         <v>1.96</v>
       </c>
       <c r="U4" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V4" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="W4" t="n">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="X4" t="n">
-        <v>17.5</v>
+        <v>500</v>
       </c>
       <c r="Y4" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="Z4" t="n">
         <v>500</v>
       </c>
       <c r="AA4" t="n">
-        <v>900</v>
+        <v>270</v>
       </c>
       <c r="AB4" t="n">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC4" t="n">
         <v>14</v>
@@ -1226,10 +1226,10 @@
         <v>970</v>
       </c>
       <c r="AG4" t="n">
-        <v>500</v>
+        <v>14</v>
       </c>
       <c r="AH4" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AI4" t="n">
         <v>500</v>
@@ -1241,7 +1241,7 @@
         <v>500</v>
       </c>
       <c r="AL4" t="n">
-        <v>220</v>
+        <v>500</v>
       </c>
       <c r="AM4" t="n">
         <v>580</v>
@@ -1253,62 +1253,62 @@
         <v>600</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.86</v>
+        <v>7.6</v>
       </c>
       <c r="AT4" t="n">
         <v>4.6</v>
       </c>
       <c r="AU4" t="n">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.4</v>
+        <v>6.8</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.86</v>
+        <v>7.4</v>
       </c>
       <c r="AX4" t="n">
-        <v>3.95</v>
+        <v>7</v>
       </c>
       <c r="AY4" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2.62</v>
+        <v>6.2</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.86</v>
+        <v>7.6</v>
       </c>
       <c r="BB4" t="n">
-        <v>3.05</v>
+        <v>5.2</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.7</v>
+        <v>6.8</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.2</v>
+        <v>7.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>2.96</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.72</v>
+        <v>5.2</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.84</v>
+        <v>3.85</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -1339,64 +1339,64 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="G5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="I5" t="n">
+        <v>28</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="U5" t="n">
         <v>1.5</v>
       </c>
-      <c r="H5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="I5" t="n">
-        <v>990</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K5" t="n">
-        <v>32</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.11</v>
-      </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W5" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z5" t="n">
         <v>1000</v>
@@ -1405,34 +1405,34 @@
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD5" t="n">
         <v>950</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>950</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1000</v>
       </c>
       <c r="AE5" t="n">
         <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AG5" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH5" t="n">
         <v>950</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1000</v>
       </c>
       <c r="AI5" t="n">
         <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK5" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AL5" t="n">
         <v>500</v>
@@ -1441,68 +1441,68 @@
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>600</v>
+        <v>29</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.12</v>
+        <v>2.18</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.12</v>
+        <v>6.6</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.12</v>
+        <v>4.2</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.12</v>
+        <v>4.2</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.07</v>
+        <v>3.75</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.09</v>
+        <v>2.34</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.12</v>
+        <v>4.2</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.12</v>
+        <v>4.2</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.11</v>
+        <v>3.7</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.11</v>
+        <v>2.06</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.12</v>
+        <v>6.8</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.12</v>
+        <v>4.2</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.11</v>
+        <v>2.62</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.1</v>
+        <v>2.38</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.11</v>
+        <v>7</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.12</v>
+        <v>1.91</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.09</v>
+        <v>3.7</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.55</v>
+        <v>7.8</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -1533,13 +1533,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="G6" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="H6" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
         <v>4.7</v>
@@ -1548,155 +1548,155 @@
         <v>3.35</v>
       </c>
       <c r="K6" t="n">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="L6" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="M6" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O6" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="P6" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.98</v>
+        <v>2.16</v>
       </c>
       <c r="R6" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S6" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="T6" t="n">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="U6" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V6" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W6" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="X6" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y6" t="n">
         <v>15.5</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>16</v>
       </c>
       <c r="Z6" t="n">
         <v>32</v>
       </c>
       <c r="AA6" t="n">
-        <v>500</v>
+        <v>290</v>
       </c>
       <c r="AB6" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AE6" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF6" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG6" t="n">
         <v>11</v>
       </c>
       <c r="AH6" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AI6" t="n">
         <v>240</v>
       </c>
       <c r="AJ6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK6" t="n">
         <v>23</v>
       </c>
       <c r="AL6" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM6" t="n">
         <v>580</v>
       </c>
       <c r="AN6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>270</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>25</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>16</v>
       </c>
-      <c r="AO6" t="n">
-        <v>600</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BA6" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.4</v>
+        <v>19.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>6.2</v>
+        <v>18</v>
       </c>
       <c r="BD6" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE6" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>5.6</v>
+        <v>13.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -1727,170 +1727,170 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.02</v>
+        <v>2.24</v>
       </c>
       <c r="G7" t="n">
-        <v>2.14</v>
+        <v>2.46</v>
       </c>
       <c r="H7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I7" t="n">
         <v>3.65</v>
       </c>
-      <c r="I7" t="n">
-        <v>4.6</v>
-      </c>
       <c r="J7" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K7" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L7" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M7" t="n">
         <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="O7" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="P7" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.92</v>
+        <v>1.99</v>
       </c>
       <c r="R7" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S7" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="T7" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="U7" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="V7" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="W7" t="n">
-        <v>1.87</v>
+        <v>1.69</v>
       </c>
       <c r="X7" t="n">
         <v>15</v>
       </c>
       <c r="Y7" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AA7" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AC7" t="n">
         <v>8.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AE7" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AF7" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AG7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH7" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AI7" t="n">
         <v>230</v>
       </c>
       <c r="AJ7" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AK7" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AL7" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM7" t="n">
-        <v>580</v>
+        <v>100</v>
       </c>
       <c r="AN7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>48</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>26</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>20</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>15</v>
+      </c>
+      <c r="BF7" t="n">
         <v>15.5</v>
       </c>
-      <c r="AO7" t="n">
-        <v>600</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>9</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BG7" t="n">
-        <v>9.800000000000001</v>
+        <v>27</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -1921,170 +1921,170 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="G8" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="H8" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="I8" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="J8" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="K8" t="n">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="L8" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M8" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="W8" t="n">
         <v>1.08</v>
       </c>
-      <c r="N8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.05</v>
-      </c>
       <c r="X8" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AA8" t="n">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="AB8" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="AC8" t="n">
-        <v>42</v>
+        <v>11.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AF8" t="n">
+        <v>170</v>
+      </c>
+      <c r="AG8" t="n">
         <v>160</v>
       </c>
-      <c r="AG8" t="n">
-        <v>70</v>
-      </c>
       <c r="AH8" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AI8" t="n">
         <v>500</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AK8" t="n">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="AL8" t="n">
-        <v>550</v>
+        <v>400</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>660</v>
       </c>
       <c r="AO8" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AP8" t="n">
         <v>10</v>
       </c>
       <c r="AQ8" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="AR8" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AT8" t="n">
-        <v>18.5</v>
+        <v>24</v>
       </c>
       <c r="AU8" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV8" t="n">
         <v>10.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>6.8</v>
+        <v>16.5</v>
       </c>
       <c r="AX8" t="n">
-        <v>9.800000000000001</v>
+        <v>36</v>
       </c>
       <c r="AY8" t="n">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="AZ8" t="n">
-        <v>18.5</v>
+        <v>36</v>
       </c>
       <c r="BA8" t="n">
-        <v>9.199999999999999</v>
+        <v>55</v>
       </c>
       <c r="BB8" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BC8" t="n">
-        <v>6.4</v>
+        <v>11</v>
       </c>
       <c r="BD8" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BE8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BF8" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="H9" t="n">
         <v>2.26</v>
@@ -2127,158 +2127,158 @@
         <v>2.42</v>
       </c>
       <c r="J9" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="K9" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="L9" t="n">
-        <v>1.56</v>
+        <v>1.41</v>
       </c>
       <c r="M9" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="N9" t="n">
-        <v>2.78</v>
+        <v>5</v>
       </c>
       <c r="O9" t="n">
-        <v>1.51</v>
+        <v>1.22</v>
       </c>
       <c r="P9" t="n">
-        <v>1.58</v>
+        <v>2.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.56</v>
+        <v>1.67</v>
       </c>
       <c r="R9" t="n">
-        <v>1.21</v>
+        <v>1.55</v>
       </c>
       <c r="S9" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X9" t="n">
+        <v>140</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>32</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>90</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>190</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AS9" t="n">
         <v>5</v>
       </c>
-      <c r="T9" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="X9" t="n">
+      <c r="AT9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV9" t="n">
         <v>9.6</v>
       </c>
-      <c r="Y9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>38</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>500</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>80</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>60</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>440</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>600</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>600</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>8</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AS9" t="n">
+      <c r="AW9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ9" t="n">
         <v>14</v>
       </c>
-      <c r="AT9" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AX9" t="n">
+      <c r="BA9" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD9" t="n">
         <v>19.5</v>
       </c>
-      <c r="AY9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BE9" t="n">
-        <v>9.6</v>
+        <v>5.4</v>
       </c>
       <c r="BF9" t="n">
-        <v>4</v>
+        <v>18.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>7.8</v>
+        <v>11.5</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -2309,67 +2309,67 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="G10" t="n">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="H10" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="I10" t="n">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="J10" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="K10" t="n">
         <v>4.1</v>
       </c>
       <c r="L10" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M10" t="n">
         <v>1.06</v>
       </c>
       <c r="N10" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="O10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V10" t="n">
         <v>1.27</v>
       </c>
-      <c r="P10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.21</v>
-      </c>
       <c r="W10" t="n">
-        <v>2.26</v>
+        <v>2.08</v>
       </c>
       <c r="X10" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="Y10" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="Z10" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AA10" t="n">
         <v>900</v>
@@ -2378,101 +2378,101 @@
         <v>10</v>
       </c>
       <c r="AC10" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AD10" t="n">
-        <v>970</v>
+        <v>120</v>
       </c>
       <c r="AE10" t="n">
         <v>400</v>
       </c>
       <c r="AF10" t="n">
-        <v>17.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AH10" t="n">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="AI10" t="n">
-        <v>700</v>
+        <v>320</v>
       </c>
       <c r="AJ10" t="n">
-        <v>900</v>
+        <v>22</v>
       </c>
       <c r="AK10" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="AL10" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AM10" t="n">
         <v>580</v>
       </c>
       <c r="AN10" t="n">
-        <v>29</v>
+        <v>12.5</v>
       </c>
       <c r="AO10" t="n">
-        <v>700</v>
+        <v>310</v>
       </c>
       <c r="AP10" t="n">
-        <v>9.199999999999999</v>
+        <v>14</v>
       </c>
       <c r="AQ10" t="n">
-        <v>9.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>16</v>
+        <v>19.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>3.9</v>
+        <v>9.4</v>
       </c>
       <c r="AT10" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AU10" t="n">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>46</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY10" t="n">
         <v>9</v>
       </c>
-      <c r="AW10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>5.8</v>
-      </c>
       <c r="AZ10" t="n">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA10" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BF10" t="n">
         <v>10</v>
       </c>
-      <c r="BB10" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>15</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BG10" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="G11" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="H11" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="I11" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="J11" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="K11" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="L11" t="n">
         <v>1.18</v>
@@ -2527,22 +2527,22 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="O11" t="n">
         <v>1.09</v>
       </c>
       <c r="P11" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="R11" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="S11" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="T11" t="n">
         <v>1.11</v>
@@ -2551,10 +2551,10 @@
         <v>1.11</v>
       </c>
       <c r="V11" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W11" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="X11" t="n">
         <v>80</v>
@@ -2614,49 +2614,49 @@
         <v>2</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AR11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AT11" t="n">
         <v>1.21</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>1.2</v>
       </c>
       <c r="AU11" t="n">
         <v>1.22</v>
       </c>
       <c r="AV11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AY11" t="n">
         <v>1.2</v>
       </c>
-      <c r="AW11" t="n">
+      <c r="AZ11" t="n">
         <v>1.22</v>
       </c>
-      <c r="AX11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>1.21</v>
-      </c>
       <c r="BA11" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="BF11" t="n">
         <v>1.55</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -2697,64 +2697,64 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="G12" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="H12" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="I12" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="J12" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="K12" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="L12" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M12" t="n">
         <v>1.07</v>
       </c>
       <c r="N12" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="O12" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="P12" t="n">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="Q12" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="R12" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="S12" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="T12" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="U12" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="V12" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W12" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="X12" t="n">
         <v>28</v>
       </c>
       <c r="Y12" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="Z12" t="n">
         <v>100</v>
@@ -2763,13 +2763,13 @@
         <v>900</v>
       </c>
       <c r="AB12" t="n">
-        <v>13.5</v>
+        <v>8.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD12" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AE12" t="n">
         <v>700</v>
@@ -2778,16 +2778,16 @@
         <v>12</v>
       </c>
       <c r="AG12" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH12" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AI12" t="n">
         <v>700</v>
       </c>
       <c r="AJ12" t="n">
-        <v>48</v>
+        <v>900</v>
       </c>
       <c r="AK12" t="n">
         <v>50</v>
@@ -2799,37 +2799,37 @@
         <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>29</v>
+        <v>11.5</v>
       </c>
       <c r="AO12" t="n">
         <v>700</v>
       </c>
       <c r="AP12" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AQ12" t="n">
         <v>8.4</v>
       </c>
       <c r="AR12" t="n">
-        <v>8.800000000000001</v>
+        <v>18.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="AT12" t="n">
         <v>7</v>
       </c>
       <c r="AU12" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV12" t="n">
         <v>10.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>9.6</v>
+        <v>12.5</v>
       </c>
       <c r="AX12" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AY12" t="n">
         <v>8.800000000000001</v>
@@ -2838,29 +2838,29 @@
         <v>11.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>9.6</v>
+        <v>12.5</v>
       </c>
       <c r="BB12" t="n">
-        <v>9</v>
+        <v>15.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="BE12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BF12" t="n">
         <v>10</v>
       </c>
-      <c r="BF12" t="n">
-        <v>11</v>
-      </c>
       <c r="BG12" t="n">
-        <v>9.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -2891,22 +2891,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="G13" t="n">
         <v>3.25</v>
       </c>
       <c r="H13" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="I13" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J13" t="n">
         <v>2.78</v>
       </c>
       <c r="K13" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="L13" t="n">
         <v>1.64</v>
@@ -2921,7 +2921,7 @@
         <v>1.61</v>
       </c>
       <c r="P13" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="Q13" t="n">
         <v>2.94</v>
@@ -2930,13 +2930,13 @@
         <v>1.18</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="T13" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="U13" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="V13" t="n">
         <v>1.46</v>
@@ -2945,7 +2945,7 @@
         <v>1.44</v>
       </c>
       <c r="X13" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Y13" t="n">
         <v>8.4</v>
@@ -2954,7 +2954,7 @@
         <v>18.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>250</v>
+        <v>120</v>
       </c>
       <c r="AB13" t="n">
         <v>8.4</v>
@@ -2966,7 +2966,7 @@
         <v>15</v>
       </c>
       <c r="AE13" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="AF13" t="n">
         <v>19.5</v>
@@ -2978,16 +2978,16 @@
         <v>25</v>
       </c>
       <c r="AI13" t="n">
-        <v>500</v>
+        <v>170</v>
       </c>
       <c r="AJ13" t="n">
         <v>290</v>
       </c>
       <c r="AK13" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AL13" t="n">
-        <v>500</v>
+        <v>190</v>
       </c>
       <c r="AM13" t="n">
         <v>500</v>
@@ -3002,13 +3002,13 @@
         <v>6.6</v>
       </c>
       <c r="AQ13" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AR13" t="n">
-        <v>8</v>
+        <v>15.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>9.800000000000001</v>
+        <v>44</v>
       </c>
       <c r="AT13" t="n">
         <v>7.2</v>
@@ -3017,10 +3017,10 @@
         <v>6</v>
       </c>
       <c r="AV13" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW13" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="AX13" t="n">
         <v>16.5</v>
@@ -3029,32 +3029,32 @@
         <v>12</v>
       </c>
       <c r="AZ13" t="n">
-        <v>20</v>
+        <v>15.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BB13" t="n">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="BC13" t="n">
         <v>38</v>
       </c>
       <c r="BD13" t="n">
-        <v>9.800000000000001</v>
+        <v>48</v>
       </c>
       <c r="BE13" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF13" t="n">
-        <v>9.6</v>
+        <v>25</v>
       </c>
       <c r="BG13" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -3085,10 +3085,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="G14" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="H14" t="n">
         <v>5.5</v>
@@ -3112,13 +3112,13 @@
         <v>5.1</v>
       </c>
       <c r="O14" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P14" t="n">
         <v>2.42</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="R14" t="n">
         <v>1.55</v>
@@ -3127,28 +3127,28 @@
         <v>2.68</v>
       </c>
       <c r="T14" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="U14" t="n">
         <v>2.26</v>
       </c>
       <c r="V14" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W14" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="X14" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Y14" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="Z14" t="n">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="AA14" t="n">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="AB14" t="n">
         <v>11</v>
@@ -3157,28 +3157,28 @@
         <v>12.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>950</v>
+        <v>26</v>
       </c>
       <c r="AE14" t="n">
-        <v>700</v>
+        <v>320</v>
       </c>
       <c r="AF14" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AG14" t="n">
         <v>10.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI14" t="n">
         <v>700</v>
       </c>
       <c r="AJ14" t="n">
-        <v>180</v>
+        <v>48</v>
       </c>
       <c r="AK14" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL14" t="n">
         <v>75</v>
@@ -3187,7 +3187,7 @@
         <v>580</v>
       </c>
       <c r="AN14" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AO14" t="n">
         <v>700</v>
@@ -3196,25 +3196,25 @@
         <v>11</v>
       </c>
       <c r="AQ14" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR14" t="n">
         <v>18</v>
       </c>
       <c r="AS14" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AT14" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU14" t="n">
         <v>8.6</v>
       </c>
       <c r="AV14" t="n">
-        <v>10.5</v>
+        <v>18.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="AX14" t="n">
         <v>10</v>
@@ -3223,32 +3223,32 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ14" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BB14" t="n">
         <v>14</v>
       </c>
       <c r="BC14" t="n">
-        <v>9.199999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BE14" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BF14" t="n">
         <v>6.6</v>
       </c>
       <c r="BG14" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -3279,61 +3279,61 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="G15" t="n">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="I15" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="J15" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="K15" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L15" t="n">
         <v>1.4</v>
       </c>
       <c r="M15" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N15" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="O15" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="P15" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="Q15" t="n">
         <v>1.9</v>
       </c>
       <c r="R15" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S15" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="T15" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="U15" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V15" t="n">
-        <v>2.22</v>
+        <v>2.36</v>
       </c>
       <c r="W15" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="X15" t="n">
-        <v>500</v>
+        <v>28</v>
       </c>
       <c r="Y15" t="n">
         <v>500</v>
@@ -3363,7 +3363,7 @@
         <v>950</v>
       </c>
       <c r="AH15" t="n">
-        <v>950</v>
+        <v>60</v>
       </c>
       <c r="AI15" t="n">
         <v>500</v>
@@ -3387,19 +3387,19 @@
         <v>29</v>
       </c>
       <c r="AP15" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AQ15" t="n">
         <v>4.6</v>
       </c>
       <c r="AR15" t="n">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.46</v>
+        <v>6.6</v>
       </c>
       <c r="AT15" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AU15" t="n">
         <v>4.8</v>
@@ -3408,41 +3408,41 @@
         <v>5</v>
       </c>
       <c r="AW15" t="n">
-        <v>2.46</v>
+        <v>6.6</v>
       </c>
       <c r="AX15" t="n">
-        <v>2.54</v>
+        <v>9</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.78</v>
+        <v>7.8</v>
       </c>
       <c r="AZ15" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.6</v>
+        <v>8</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.91</v>
+        <v>9</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.82</v>
+        <v>9</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.85</v>
+        <v>9</v>
       </c>
       <c r="BE15" t="n">
-        <v>2.4</v>
+        <v>2.82</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.83</v>
+        <v>9</v>
       </c>
       <c r="BG15" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -3473,58 +3473,58 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="G16" t="n">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="H16" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I16" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="J16" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K16" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="L16" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M16" t="n">
         <v>1.05</v>
       </c>
       <c r="N16" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O16" t="n">
         <v>1.25</v>
       </c>
       <c r="P16" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="R16" t="n">
         <v>1.44</v>
       </c>
       <c r="S16" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="T16" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="U16" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="V16" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W16" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="X16" t="n">
         <v>19</v>
@@ -3536,7 +3536,7 @@
         <v>36</v>
       </c>
       <c r="AA16" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB16" t="n">
         <v>11</v>
@@ -3563,16 +3563,16 @@
         <v>55</v>
       </c>
       <c r="AJ16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK16" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL16" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM16" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN16" t="n">
         <v>11</v>
@@ -3581,62 +3581,62 @@
         <v>55</v>
       </c>
       <c r="AP16" t="n">
-        <v>6.4</v>
+        <v>16</v>
       </c>
       <c r="AQ16" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AR16" t="n">
         <v>22</v>
       </c>
       <c r="AS16" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT16" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AU16" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AV16" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AW16" t="n">
-        <v>8.199999999999999</v>
+        <v>17.5</v>
       </c>
       <c r="AX16" t="n">
         <v>10.5</v>
       </c>
       <c r="AY16" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AZ16" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BA16" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BB16" t="n">
         <v>17.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BD16" t="n">
-        <v>7.6</v>
+        <v>20</v>
       </c>
       <c r="BE16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF16" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BF16" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BG16" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -3667,37 +3667,37 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="G17" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="H17" t="n">
         <v>3.3</v>
       </c>
       <c r="I17" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="J17" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K17" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="L17" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M17" t="n">
         <v>1.07</v>
       </c>
       <c r="N17" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="O17" t="n">
         <v>1.33</v>
       </c>
       <c r="P17" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="Q17" t="n">
         <v>2</v>
@@ -3706,28 +3706,28 @@
         <v>1.36</v>
       </c>
       <c r="S17" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T17" t="n">
         <v>1.79</v>
       </c>
       <c r="U17" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V17" t="n">
         <v>1.4</v>
       </c>
       <c r="W17" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="X17" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA17" t="n">
         <v>160</v>
@@ -3736,7 +3736,7 @@
         <v>10.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD17" t="n">
         <v>15</v>
@@ -3745,34 +3745,34 @@
         <v>40</v>
       </c>
       <c r="AF17" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH17" t="n">
         <v>18</v>
       </c>
       <c r="AI17" t="n">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="AJ17" t="n">
         <v>32</v>
       </c>
       <c r="AK17" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL17" t="n">
         <v>40</v>
       </c>
       <c r="AM17" t="n">
-        <v>580</v>
+        <v>150</v>
       </c>
       <c r="AN17" t="n">
         <v>20</v>
       </c>
       <c r="AO17" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AP17" t="n">
         <v>12</v>
@@ -3784,53 +3784,53 @@
         <v>20</v>
       </c>
       <c r="AS17" t="n">
-        <v>8.800000000000001</v>
+        <v>27</v>
       </c>
       <c r="AT17" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AU17" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV17" t="n">
         <v>12</v>
       </c>
       <c r="AW17" t="n">
-        <v>8.4</v>
+        <v>24</v>
       </c>
       <c r="AX17" t="n">
         <v>13</v>
       </c>
       <c r="AY17" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ17" t="n">
-        <v>6.6</v>
+        <v>14.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>8.4</v>
+        <v>22</v>
       </c>
       <c r="BB17" t="n">
-        <v>14</v>
+        <v>19.5</v>
       </c>
       <c r="BC17" t="n">
         <v>21</v>
       </c>
       <c r="BD17" t="n">
-        <v>8.4</v>
+        <v>17.5</v>
       </c>
       <c r="BE17" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BF17" t="n">
         <v>16</v>
       </c>
       <c r="BG17" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -3867,7 +3867,7 @@
         <v>1.74</v>
       </c>
       <c r="H18" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="I18" t="n">
         <v>5.8</v>
@@ -3876,7 +3876,7 @@
         <v>4.1</v>
       </c>
       <c r="K18" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L18" t="n">
         <v>1.35</v>
@@ -3885,28 +3885,28 @@
         <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O18" t="n">
         <v>1.26</v>
       </c>
       <c r="P18" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="R18" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S18" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="T18" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="U18" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="V18" t="n">
         <v>1.2</v>
@@ -3927,31 +3927,31 @@
         <v>900</v>
       </c>
       <c r="AB18" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AC18" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>21</v>
+        <v>950</v>
       </c>
       <c r="AE18" t="n">
         <v>700</v>
       </c>
       <c r="AF18" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG18" t="n">
         <v>9.6</v>
       </c>
       <c r="AH18" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AI18" t="n">
         <v>700</v>
       </c>
       <c r="AJ18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK18" t="n">
         <v>29</v>
@@ -3963,37 +3963,37 @@
         <v>580</v>
       </c>
       <c r="AN18" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AO18" t="n">
         <v>700</v>
       </c>
       <c r="AP18" t="n">
-        <v>9.6</v>
+        <v>16.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>9.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="AR18" t="n">
-        <v>19.5</v>
+        <v>27</v>
       </c>
       <c r="AS18" t="n">
         <v>15</v>
       </c>
       <c r="AT18" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AU18" t="n">
         <v>8.6</v>
       </c>
       <c r="AV18" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AW18" t="n">
-        <v>13.5</v>
+        <v>42</v>
       </c>
       <c r="AX18" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY18" t="n">
         <v>9</v>
@@ -4002,29 +4002,29 @@
         <v>16.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>13.5</v>
+        <v>30</v>
       </c>
       <c r="BB18" t="n">
-        <v>8.6</v>
+        <v>14.5</v>
       </c>
       <c r="BC18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE18" t="n">
         <v>15</v>
       </c>
-      <c r="BD18" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BF18" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BG18" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -4055,49 +4055,49 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="G19" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="H19" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="I19" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J19" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="K19" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="L19" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="M19" t="n">
         <v>1.12</v>
       </c>
       <c r="N19" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="O19" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="P19" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S19" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="T19" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U19" t="n">
         <v>1.74</v>
@@ -4106,49 +4106,49 @@
         <v>1.18</v>
       </c>
       <c r="W19" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="X19" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y19" t="n">
         <v>16</v>
       </c>
       <c r="Z19" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AA19" t="n">
-        <v>900</v>
+        <v>200</v>
       </c>
       <c r="AB19" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD19" t="n">
         <v>26</v>
       </c>
       <c r="AE19" t="n">
-        <v>700</v>
+        <v>110</v>
       </c>
       <c r="AF19" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AG19" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH19" t="n">
         <v>25</v>
       </c>
       <c r="AI19" t="n">
-        <v>700</v>
+        <v>140</v>
       </c>
       <c r="AJ19" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK19" t="n">
         <v>24</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>26</v>
       </c>
       <c r="AL19" t="n">
         <v>60</v>
@@ -4157,68 +4157,68 @@
         <v>500</v>
       </c>
       <c r="AN19" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AO19" t="n">
-        <v>700</v>
+        <v>180</v>
       </c>
       <c r="AP19" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR19" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="AS19" t="n">
-        <v>9.4</v>
+        <v>15.5</v>
       </c>
       <c r="AT19" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AU19" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV19" t="n">
         <v>21</v>
       </c>
       <c r="AW19" t="n">
-        <v>9.4</v>
+        <v>15.5</v>
       </c>
       <c r="AX19" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AY19" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA19" t="n">
-        <v>9.4</v>
+        <v>16</v>
       </c>
       <c r="BB19" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="BC19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD19" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE19" t="n">
         <v>28</v>
       </c>
-      <c r="BE19" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BF19" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="BG19" t="n">
-        <v>9.4</v>
+        <v>16.5</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -4249,13 +4249,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G20" t="n">
         <v>2.1</v>
       </c>
       <c r="H20" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I20" t="n">
         <v>4.9</v>
@@ -4264,7 +4264,7 @@
         <v>3.25</v>
       </c>
       <c r="K20" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L20" t="n">
         <v>1.62</v>
@@ -4279,28 +4279,28 @@
         <v>1.56</v>
       </c>
       <c r="P20" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="R20" t="n">
         <v>1.19</v>
       </c>
       <c r="S20" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="T20" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="U20" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="V20" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W20" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="X20" t="n">
         <v>8.6</v>
@@ -4315,7 +4315,7 @@
         <v>140</v>
       </c>
       <c r="AB20" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AC20" t="n">
         <v>7.6</v>
@@ -4360,16 +4360,16 @@
         <v>8</v>
       </c>
       <c r="AQ20" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR20" t="n">
         <v>28</v>
       </c>
       <c r="AS20" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AT20" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU20" t="n">
         <v>7</v>
@@ -4378,7 +4378,7 @@
         <v>17</v>
       </c>
       <c r="AW20" t="n">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="AX20" t="n">
         <v>10</v>
@@ -4390,7 +4390,7 @@
         <v>24</v>
       </c>
       <c r="BA20" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="BB20" t="n">
         <v>23</v>
@@ -4399,20 +4399,20 @@
         <v>25</v>
       </c>
       <c r="BD20" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="BE20" t="n">
+        <v>46</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>24</v>
+      </c>
+      <c r="BG20" t="n">
         <v>13.5</v>
       </c>
-      <c r="BF20" t="n">
-        <v>23</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>13</v>
-      </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -4443,22 +4443,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="G21" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="H21" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="J21" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K21" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L21" t="n">
         <v>1.37</v>
@@ -4467,16 +4467,16 @@
         <v>1.06</v>
       </c>
       <c r="N21" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O21" t="n">
         <v>1.28</v>
       </c>
       <c r="P21" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="R21" t="n">
         <v>1.41</v>
@@ -4485,7 +4485,7 @@
         <v>3.25</v>
       </c>
       <c r="T21" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U21" t="n">
         <v>1.8</v>
@@ -4494,10 +4494,10 @@
         <v>1.11</v>
       </c>
       <c r="W21" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="X21" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Y21" t="n">
         <v>27</v>
@@ -4506,7 +4506,7 @@
         <v>80</v>
       </c>
       <c r="AA21" t="n">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="AB21" t="n">
         <v>8</v>
@@ -4518,16 +4518,16 @@
         <v>34</v>
       </c>
       <c r="AE21" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AF21" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG21" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH21" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="AI21" t="n">
         <v>260</v>
@@ -4539,52 +4539,52 @@
         <v>16.5</v>
       </c>
       <c r="AL21" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AM21" t="n">
-        <v>390</v>
+        <v>180</v>
       </c>
       <c r="AN21" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AO21" t="n">
         <v>210</v>
       </c>
       <c r="AP21" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AQ21" t="n">
         <v>21</v>
       </c>
       <c r="AR21" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="AS21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT21" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU21" t="n">
         <v>9.4</v>
       </c>
       <c r="AV21" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AW21" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AX21" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AY21" t="n">
         <v>9</v>
       </c>
       <c r="AZ21" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BA21" t="n">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="BB21" t="n">
         <v>11</v>
@@ -4593,20 +4593,20 @@
         <v>14</v>
       </c>
       <c r="BD21" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE21" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BF21" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BG21" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="G22" t="n">
         <v>1.46</v>
@@ -4649,43 +4649,43 @@
         <v>12</v>
       </c>
       <c r="J22" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K22" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="L22" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M22" t="n">
         <v>1.08</v>
       </c>
       <c r="N22" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="O22" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P22" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S22" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="T22" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="U22" t="n">
         <v>1.64</v>
       </c>
       <c r="V22" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="W22" t="n">
         <v>3.15</v>
@@ -4697,28 +4697,28 @@
         <v>950</v>
       </c>
       <c r="Z22" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AA22" t="n">
         <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>42</v>
+        <v>11.5</v>
       </c>
       <c r="AD22" t="n">
         <v>950</v>
       </c>
       <c r="AE22" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AF22" t="n">
         <v>7.8</v>
       </c>
       <c r="AG22" t="n">
-        <v>36</v>
+        <v>11.5</v>
       </c>
       <c r="AH22" t="n">
         <v>950</v>
@@ -4739,52 +4739,52 @@
         <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>29</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO22" t="n">
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AQ22" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AR22" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AS22" t="n">
-        <v>4.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT22" t="n">
-        <v>3.8</v>
+        <v>5.4</v>
       </c>
       <c r="AU22" t="n">
         <v>9</v>
       </c>
       <c r="AV22" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AW22" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC22" t="n">
         <v>8.4</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>5</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>7</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>6</v>
       </c>
       <c r="BD22" t="n">
         <v>7.6</v>
@@ -4793,14 +4793,14 @@
         <v>8.6</v>
       </c>
       <c r="BF22" t="n">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="BG22" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -4831,16 +4831,16 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="G23" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="H23" t="n">
         <v>1.34</v>
       </c>
       <c r="I23" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="J23" t="n">
         <v>5.9</v>
@@ -4855,40 +4855,40 @@
         <v>1.02</v>
       </c>
       <c r="N23" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="O23" t="n">
         <v>1.13</v>
       </c>
       <c r="P23" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="Q23" t="n">
         <v>1.4</v>
       </c>
       <c r="R23" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="S23" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="T23" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="U23" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="V23" t="n">
         <v>3.7</v>
       </c>
       <c r="W23" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X23" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="Y23" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z23" t="n">
         <v>11.5</v>
@@ -4909,7 +4909,7 @@
         <v>13</v>
       </c>
       <c r="AF23" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AG23" t="n">
         <v>36</v>
@@ -4918,7 +4918,7 @@
         <v>22</v>
       </c>
       <c r="AI23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ23" t="n">
         <v>310</v>
@@ -4927,16 +4927,16 @@
         <v>110</v>
       </c>
       <c r="AL23" t="n">
-        <v>190</v>
+        <v>85</v>
       </c>
       <c r="AM23" t="n">
         <v>90</v>
       </c>
       <c r="AN23" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AO23" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AP23" t="n">
         <v>46</v>
@@ -4945,56 +4945,56 @@
         <v>13</v>
       </c>
       <c r="AR23" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AS23" t="n">
         <v>11.5</v>
       </c>
       <c r="AT23" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="AU23" t="n">
         <v>13.5</v>
       </c>
       <c r="AV23" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW23" t="n">
         <v>11.5</v>
       </c>
       <c r="AX23" t="n">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="AY23" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AZ23" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA23" t="n">
         <v>22</v>
       </c>
       <c r="BB23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC23" t="n">
-        <v>15.5</v>
+        <v>48</v>
       </c>
       <c r="BD23" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="BE23" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="BF23" t="n">
-        <v>14</v>
+        <v>80</v>
       </c>
       <c r="BG23" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="G24" t="n">
         <v>1.49</v>
@@ -5034,7 +5034,7 @@
         <v>7</v>
       </c>
       <c r="I24" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="J24" t="n">
         <v>4.3</v>
@@ -5052,37 +5052,37 @@
         <v>3</v>
       </c>
       <c r="O24" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="P24" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="R24" t="n">
         <v>1.23</v>
       </c>
       <c r="S24" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="T24" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="U24" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="V24" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W24" t="n">
-        <v>2.94</v>
+        <v>2.76</v>
       </c>
       <c r="X24" t="n">
         <v>970</v>
       </c>
       <c r="Y24" t="n">
-        <v>950</v>
+        <v>80</v>
       </c>
       <c r="Z24" t="n">
         <v>1000</v>
@@ -5091,7 +5091,7 @@
         <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AC24" t="n">
         <v>42</v>
@@ -5103,10 +5103,10 @@
         <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>6.8</v>
+        <v>40</v>
       </c>
       <c r="AG24" t="n">
-        <v>36</v>
+        <v>970</v>
       </c>
       <c r="AH24" t="n">
         <v>950</v>
@@ -5115,7 +5115,7 @@
         <v>1000</v>
       </c>
       <c r="AJ24" t="n">
-        <v>180</v>
+        <v>900</v>
       </c>
       <c r="AK24" t="n">
         <v>970</v>
@@ -5133,7 +5133,7 @@
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>3.15</v>
+        <v>5.7</v>
       </c>
       <c r="AQ24" t="n">
         <v>4.2</v>
@@ -5148,7 +5148,7 @@
         <v>4.2</v>
       </c>
       <c r="AU24" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="AV24" t="n">
         <v>4.2</v>
@@ -5163,32 +5163,32 @@
         <v>6.4</v>
       </c>
       <c r="AZ24" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="BA24" t="n">
         <v>4.2</v>
       </c>
       <c r="BB24" t="n">
-        <v>8.6</v>
+        <v>5.7</v>
       </c>
       <c r="BC24" t="n">
-        <v>3.25</v>
+        <v>6.6</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="BE24" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="BF24" t="n">
-        <v>5.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG24" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -5219,16 +5219,16 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="G25" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="H25" t="n">
         <v>5.9</v>
       </c>
       <c r="I25" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="J25" t="n">
         <v>4.3</v>
@@ -5237,82 +5237,82 @@
         <v>4.4</v>
       </c>
       <c r="L25" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M25" t="n">
         <v>1.06</v>
       </c>
       <c r="N25" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O25" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P25" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="R25" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="S25" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T25" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="U25" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="V25" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W25" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="X25" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y25" t="n">
         <v>20</v>
       </c>
       <c r="Z25" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AA25" t="n">
         <v>180</v>
       </c>
       <c r="AB25" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC25" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF25" t="n">
         <v>9.6</v>
       </c>
-      <c r="AD25" t="n">
+      <c r="AG25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH25" t="n">
         <v>22</v>
       </c>
-      <c r="AE25" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>21</v>
-      </c>
       <c r="AI25" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AJ25" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AK25" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AL25" t="n">
         <v>36</v>
@@ -5321,7 +5321,7 @@
         <v>120</v>
       </c>
       <c r="AN25" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AO25" t="n">
         <v>110</v>
@@ -5330,25 +5330,25 @@
         <v>15</v>
       </c>
       <c r="AQ25" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AS25" t="n">
-        <v>19.5</v>
+        <v>36</v>
       </c>
       <c r="AT25" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU25" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AV25" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AW25" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AX25" t="n">
         <v>9.199999999999999</v>
@@ -5357,7 +5357,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ25" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA25" t="n">
         <v>65</v>
@@ -5366,23 +5366,23 @@
         <v>15</v>
       </c>
       <c r="BC25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD25" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE25" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="BF25" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG25" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -5422,16 +5422,16 @@
         <v>4</v>
       </c>
       <c r="I26" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J26" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K26" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="L26" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M26" t="n">
         <v>1.06</v>
@@ -5440,37 +5440,37 @@
         <v>4.1</v>
       </c>
       <c r="O26" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P26" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="R26" t="n">
         <v>1.4</v>
       </c>
       <c r="S26" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="T26" t="n">
         <v>1.8</v>
       </c>
       <c r="U26" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="V26" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W26" t="n">
         <v>1.98</v>
       </c>
       <c r="X26" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y26" t="n">
         <v>16</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>15.5</v>
       </c>
       <c r="Z26" t="n">
         <v>30</v>
@@ -5479,7 +5479,7 @@
         <v>85</v>
       </c>
       <c r="AB26" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC26" t="n">
         <v>8.6</v>
@@ -5488,16 +5488,16 @@
         <v>16.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AF26" t="n">
         <v>12.5</v>
       </c>
       <c r="AG26" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AI26" t="n">
         <v>55</v>
@@ -5506,28 +5506,28 @@
         <v>24</v>
       </c>
       <c r="AK26" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AL26" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AM26" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN26" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>50</v>
+      </c>
+      <c r="AP26" t="n">
         <v>14.5</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>14</v>
       </c>
       <c r="AQ26" t="n">
         <v>14</v>
       </c>
       <c r="AR26" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AS26" t="n">
         <v>70</v>
@@ -5536,7 +5536,7 @@
         <v>9</v>
       </c>
       <c r="AU26" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV26" t="n">
         <v>15</v>
@@ -5548,35 +5548,35 @@
         <v>11</v>
       </c>
       <c r="AY26" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ26" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA26" t="n">
         <v>48</v>
       </c>
       <c r="BB26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC26" t="n">
         <v>19</v>
       </c>
       <c r="BD26" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BE26" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BF26" t="n">
         <v>12.5</v>
       </c>
       <c r="BG26" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -5634,13 +5634,13 @@
         <v>4.1</v>
       </c>
       <c r="O27" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P27" t="n">
         <v>2.04</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="R27" t="n">
         <v>1.4</v>
@@ -5670,13 +5670,13 @@
         <v>38</v>
       </c>
       <c r="AA27" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AB27" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC27" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD27" t="n">
         <v>19</v>
@@ -5694,7 +5694,7 @@
         <v>19</v>
       </c>
       <c r="AI27" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ27" t="n">
         <v>18.5</v>
@@ -5706,37 +5706,37 @@
         <v>34</v>
       </c>
       <c r="AM27" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN27" t="n">
         <v>11.5</v>
       </c>
       <c r="AO27" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AP27" t="n">
         <v>14.5</v>
       </c>
       <c r="AQ27" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AR27" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AS27" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AT27" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU27" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV27" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AX27" t="n">
         <v>9.800000000000001</v>
@@ -5745,32 +5745,32 @@
         <v>9.4</v>
       </c>
       <c r="AZ27" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BA27" t="n">
         <v>55</v>
       </c>
       <c r="BB27" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BC27" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BD27" t="n">
         <v>32</v>
       </c>
       <c r="BE27" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BF27" t="n">
         <v>10.5</v>
       </c>
       <c r="BG27" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -5801,10 +5801,10 @@
         </is>
       </c>
       <c r="F28" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="G28" t="n">
         <v>1.79</v>
-      </c>
-      <c r="G28" t="n">
-        <v>1.8</v>
       </c>
       <c r="H28" t="n">
         <v>5.4</v>
@@ -5813,10 +5813,10 @@
         <v>5.5</v>
       </c>
       <c r="J28" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K28" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L28" t="n">
         <v>1.44</v>
@@ -5834,7 +5834,7 @@
         <v>1.92</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R28" t="n">
         <v>1.35</v>
@@ -5843,16 +5843,16 @@
         <v>3.7</v>
       </c>
       <c r="T28" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="U28" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V28" t="n">
         <v>1.22</v>
       </c>
       <c r="W28" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="X28" t="n">
         <v>14</v>
@@ -5867,10 +5867,10 @@
         <v>140</v>
       </c>
       <c r="AB28" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD28" t="n">
         <v>21</v>
@@ -5897,13 +5897,13 @@
         <v>18.5</v>
       </c>
       <c r="AL28" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM28" t="n">
         <v>130</v>
       </c>
       <c r="AN28" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AO28" t="n">
         <v>100</v>
@@ -5912,22 +5912,22 @@
         <v>13</v>
       </c>
       <c r="AQ28" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AR28" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AS28" t="n">
-        <v>42</v>
+        <v>120</v>
       </c>
       <c r="AT28" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU28" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV28" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW28" t="n">
         <v>65</v>
@@ -5948,7 +5948,7 @@
         <v>17.5</v>
       </c>
       <c r="BC28" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BD28" t="n">
         <v>36</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -5995,22 +5995,22 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="G29" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="H29" t="n">
         <v>10.5</v>
       </c>
       <c r="I29" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="J29" t="n">
         <v>4.3</v>
       </c>
       <c r="K29" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="L29" t="n">
         <v>1.46</v>
@@ -6025,7 +6025,7 @@
         <v>1.38</v>
       </c>
       <c r="P29" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q29" t="n">
         <v>2.14</v>
@@ -6037,16 +6037,16 @@
         <v>4</v>
       </c>
       <c r="T29" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="U29" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="V29" t="n">
         <v>1.08</v>
       </c>
       <c r="W29" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="X29" t="n">
         <v>90</v>
@@ -6073,7 +6073,7 @@
         <v>1000</v>
       </c>
       <c r="AF29" t="n">
-        <v>12</v>
+        <v>7.6</v>
       </c>
       <c r="AG29" t="n">
         <v>970</v>
@@ -6085,7 +6085,7 @@
         <v>1000</v>
       </c>
       <c r="AJ29" t="n">
-        <v>180</v>
+        <v>20</v>
       </c>
       <c r="AK29" t="n">
         <v>970</v>
@@ -6097,7 +6097,7 @@
         <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="AO29" t="n">
         <v>1000</v>
@@ -6109,56 +6109,56 @@
         <v>10.5</v>
       </c>
       <c r="AR29" t="n">
-        <v>4.2</v>
+        <v>8.4</v>
       </c>
       <c r="AS29" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AT29" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AU29" t="n">
-        <v>6.4</v>
+        <v>9</v>
       </c>
       <c r="AV29" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AW29" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="AX29" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="AY29" t="n">
         <v>6.4</v>
       </c>
       <c r="AZ29" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BA29" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="BB29" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC29" t="n">
-        <v>6.8</v>
+        <v>10</v>
       </c>
       <c r="BD29" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BE29" t="n">
-        <v>3.4</v>
+        <v>5.4</v>
       </c>
       <c r="BF29" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BG29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -6189,46 +6189,46 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.22</v>
+        <v>2.34</v>
       </c>
       <c r="G30" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="H30" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I30" t="n">
         <v>4</v>
       </c>
-      <c r="I30" t="n">
-        <v>4.3</v>
-      </c>
       <c r="J30" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K30" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L30" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="M30" t="n">
         <v>1.14</v>
       </c>
       <c r="N30" t="n">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="O30" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="P30" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="R30" t="n">
         <v>1.17</v>
       </c>
       <c r="S30" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="T30" t="n">
         <v>2.24</v>
@@ -6237,16 +6237,16 @@
         <v>1.7</v>
       </c>
       <c r="V30" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W30" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="X30" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="Y30" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z30" t="n">
         <v>48</v>
@@ -6255,7 +6255,7 @@
         <v>900</v>
       </c>
       <c r="AB30" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AC30" t="n">
         <v>7.4</v>
@@ -6267,13 +6267,13 @@
         <v>500</v>
       </c>
       <c r="AF30" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH30" t="n">
-        <v>950</v>
+        <v>34</v>
       </c>
       <c r="AI30" t="n">
         <v>500</v>
@@ -6291,68 +6291,68 @@
         <v>500</v>
       </c>
       <c r="AN30" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AO30" t="n">
         <v>500</v>
       </c>
       <c r="AP30" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AQ30" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AR30" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AS30" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AT30" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AU30" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV30" t="n">
         <v>15.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX30" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY30" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ30" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BA30" t="n">
-        <v>12.5</v>
+        <v>32</v>
       </c>
       <c r="BB30" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BC30" t="n">
+        <v>30</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BF30" t="n">
         <v>10</v>
       </c>
-      <c r="BD30" t="n">
+      <c r="BG30" t="n">
         <v>11.5</v>
       </c>
-      <c r="BE30" t="n">
-        <v>25</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BG30" t="n">
-        <v>13</v>
-      </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -6383,22 +6383,22 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="G31" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="H31" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="I31" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="J31" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K31" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L31" t="n">
         <v>1.46</v>
@@ -6407,40 +6407,40 @@
         <v>1.08</v>
       </c>
       <c r="N31" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O31" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P31" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="R31" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S31" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T31" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="U31" t="n">
         <v>1.78</v>
       </c>
       <c r="V31" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="W31" t="n">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="X31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Z31" t="n">
         <v>60</v>
@@ -6449,104 +6449,104 @@
         <v>290</v>
       </c>
       <c r="AB31" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AC31" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AD31" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AE31" t="n">
         <v>140</v>
       </c>
       <c r="AF31" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG31" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH31" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI31" t="n">
-        <v>170</v>
+        <v>700</v>
       </c>
       <c r="AJ31" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AK31" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL31" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM31" t="n">
         <v>580</v>
       </c>
       <c r="AN31" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AO31" t="n">
         <v>200</v>
       </c>
       <c r="AP31" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AQ31" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AR31" t="n">
-        <v>13.5</v>
+        <v>48</v>
       </c>
       <c r="AS31" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AT31" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AU31" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV31" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AW31" t="n">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="AX31" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AY31" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA31" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="BB31" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BC31" t="n">
         <v>16.5</v>
       </c>
       <c r="BD31" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BE31" t="n">
-        <v>15.5</v>
+        <v>20</v>
       </c>
       <c r="BF31" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BG31" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -6577,19 +6577,19 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G32" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="H32" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="I32" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="J32" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K32" t="n">
         <v>3.3</v>
@@ -6607,70 +6607,70 @@
         <v>1.52</v>
       </c>
       <c r="P32" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="R32" t="n">
         <v>1.2</v>
       </c>
       <c r="S32" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="T32" t="n">
         <v>2.06</v>
       </c>
       <c r="U32" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V32" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W32" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="X32" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z32" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AA32" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AB32" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC32" t="n">
         <v>7.4</v>
       </c>
       <c r="AD32" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE32" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AF32" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG32" t="n">
         <v>12</v>
       </c>
       <c r="AH32" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI32" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AJ32" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AK32" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AL32" t="n">
         <v>60</v>
@@ -6679,22 +6679,22 @@
         <v>200</v>
       </c>
       <c r="AN32" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AO32" t="n">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="AP32" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AQ32" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR32" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AS32" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="AT32" t="n">
         <v>6.2</v>
@@ -6703,13 +6703,13 @@
         <v>6.2</v>
       </c>
       <c r="AV32" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW32" t="n">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="AX32" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY32" t="n">
         <v>10</v>
@@ -6718,29 +6718,29 @@
         <v>19.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="BB32" t="n">
-        <v>9.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BC32" t="n">
         <v>26</v>
       </c>
       <c r="BD32" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BE32" t="n">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="BF32" t="n">
-        <v>23</v>
+        <v>6.8</v>
       </c>
       <c r="BG32" t="n">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -6771,25 +6771,25 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="G33" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="H33" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="I33" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="J33" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K33" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="L33" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="M33" t="n">
         <v>1.09</v>
@@ -6798,7 +6798,7 @@
         <v>3.2</v>
       </c>
       <c r="O33" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P33" t="n">
         <v>1.74</v>
@@ -6819,25 +6819,25 @@
         <v>1.81</v>
       </c>
       <c r="V33" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="W33" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="X33" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y33" t="n">
         <v>7.4</v>
       </c>
       <c r="Z33" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AA33" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB33" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AC33" t="n">
         <v>8.199999999999999</v>
@@ -6846,13 +6846,13 @@
         <v>11</v>
       </c>
       <c r="AE33" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF33" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AG33" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AH33" t="n">
         <v>24</v>
@@ -6861,10 +6861,10 @@
         <v>48</v>
       </c>
       <c r="AJ33" t="n">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="AK33" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AL33" t="n">
         <v>95</v>
@@ -6876,7 +6876,7 @@
         <v>140</v>
       </c>
       <c r="AO33" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AP33" t="n">
         <v>10</v>
@@ -6885,56 +6885,56 @@
         <v>6.4</v>
       </c>
       <c r="AR33" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS33" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AT33" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AU33" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV33" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AW33" t="n">
-        <v>19.5</v>
+        <v>7</v>
       </c>
       <c r="AX33" t="n">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="AY33" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AZ33" t="n">
         <v>19.5</v>
       </c>
       <c r="BA33" t="n">
-        <v>32</v>
+        <v>8.4</v>
       </c>
       <c r="BB33" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BC33" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD33" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BE33" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BF33" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG33" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -6998,13 +6998,13 @@
         <v>1.61</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="R34" t="n">
         <v>1.21</v>
       </c>
       <c r="S34" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="T34" t="n">
         <v>1.11</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH34"/>
+  <dimension ref="A1:BH36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,49 +757,49 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="G2" t="n">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="H2" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J2" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="K2" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="L2" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O2" t="n">
         <v>1.78</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="N2" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.81</v>
       </c>
       <c r="P2" t="n">
         <v>1.35</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="R2" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S2" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="T2" t="n">
-        <v>2.46</v>
+        <v>1.78</v>
       </c>
       <c r="U2" t="n">
         <v>1.34</v>
@@ -808,119 +808,119 @@
         <v>1.27</v>
       </c>
       <c r="W2" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="X2" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AA2" t="n">
-        <v>130</v>
+        <v>200</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="AC2" t="n">
-        <v>7.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AE2" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AF2" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>55</v>
+        <v>13.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AI2" t="n">
         <v>180</v>
       </c>
       <c r="AJ2" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AK2" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AL2" t="n">
         <v>110</v>
       </c>
       <c r="AM2" t="n">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="AN2" t="n">
-        <v>65</v>
+        <v>600</v>
       </c>
       <c r="AO2" t="n">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="AR2" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.5</v>
+        <v>8.6</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="AU2" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.4</v>
+        <v>17</v>
       </c>
       <c r="AX2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY2" t="n">
-        <v>12.5</v>
+        <v>7.6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BB2" t="n">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="BC2" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.4</v>
+        <v>10</v>
       </c>
       <c r="BE2" t="n">
         <v>110</v>
       </c>
       <c r="BF2" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-07 06:34:22</t>
+          <t>2026-05-07 08:55:50</t>
         </is>
       </c>
     </row>
@@ -951,55 +951,55 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="G3" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="H3" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="I3" t="n">
-        <v>2.94</v>
+        <v>2.78</v>
       </c>
       <c r="J3" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="K3" t="n">
         <v>3.7</v>
       </c>
       <c r="L3" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="M3" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="O3" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="P3" t="n">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="Q3" t="n">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="R3" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="S3" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="T3" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="U3" t="n">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="V3" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="W3" t="n">
         <v>1.53</v>
@@ -1017,7 +1017,7 @@
         <v>900</v>
       </c>
       <c r="AB3" t="n">
-        <v>21</v>
+        <v>500</v>
       </c>
       <c r="AC3" t="n">
         <v>14</v>
@@ -1035,13 +1035,13 @@
         <v>500</v>
       </c>
       <c r="AH3" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AI3" t="n">
         <v>500</v>
       </c>
       <c r="AJ3" t="n">
-        <v>500</v>
+        <v>340</v>
       </c>
       <c r="AK3" t="n">
         <v>500</v>
@@ -1059,22 +1059,22 @@
         <v>600</v>
       </c>
       <c r="AP3" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AQ3" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AR3" t="n">
-        <v>7.6</v>
+        <v>14</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AT3" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AU3" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AV3" t="n">
         <v>10</v>
@@ -1089,39 +1089,39 @@
         <v>7.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BA3" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC3" t="n">
         <v>8.6</v>
       </c>
-      <c r="BC3" t="n">
-        <v>16.5</v>
-      </c>
       <c r="BD3" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>10.5</v>
+        <v>4.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>7.4</v>
+        <v>16</v>
       </c>
       <c r="BG3" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-07 06:34:22</t>
+          <t>2026-05-07 08:55:50</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Serbian First League</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1136,186 +1136,186 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Tekstilac Odzaci</t>
+          <t>Paradou</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Fk Smederevo</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.34</v>
+        <v>3.25</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6</v>
+        <v>3.45</v>
       </c>
       <c r="H4" t="n">
-        <v>3.2</v>
+        <v>2.48</v>
       </c>
       <c r="I4" t="n">
-        <v>3.6</v>
+        <v>2.58</v>
       </c>
       <c r="J4" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K4" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="M4" t="n">
         <v>1.1</v>
       </c>
       <c r="N4" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="O4" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="P4" t="n">
         <v>1.65</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="R4" t="n">
         <v>1.23</v>
       </c>
       <c r="S4" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="T4" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="V4" t="n">
-        <v>1.38</v>
+        <v>1.63</v>
       </c>
       <c r="W4" t="n">
-        <v>1.63</v>
+        <v>1.4</v>
       </c>
       <c r="X4" t="n">
-        <v>500</v>
+        <v>12</v>
       </c>
       <c r="Y4" t="n">
-        <v>500</v>
+        <v>8.4</v>
       </c>
       <c r="Z4" t="n">
-        <v>500</v>
+        <v>15</v>
       </c>
       <c r="AA4" t="n">
-        <v>270</v>
+        <v>55</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>14</v>
+        <v>7.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AF4" t="n">
-        <v>970</v>
+        <v>34</v>
       </c>
       <c r="AG4" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>950</v>
+        <v>23</v>
       </c>
       <c r="AI4" t="n">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AJ4" t="n">
         <v>900</v>
       </c>
       <c r="AK4" t="n">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="AL4" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AM4" t="n">
-        <v>580</v>
+        <v>170</v>
       </c>
       <c r="AN4" t="n">
         <v>600</v>
       </c>
       <c r="AO4" t="n">
-        <v>600</v>
+        <v>60</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.1</v>
+        <v>9</v>
       </c>
       <c r="AQ4" t="n">
-        <v>9.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.6</v>
+        <v>18.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>4.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>6.8</v>
+        <v>10.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="AX4" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="AY4" t="n">
-        <v>5.5</v>
+        <v>13</v>
       </c>
       <c r="AZ4" t="n">
-        <v>6.2</v>
+        <v>18.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>7.6</v>
+        <v>30</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.2</v>
+        <v>11</v>
       </c>
       <c r="BC4" t="n">
-        <v>6.8</v>
+        <v>19</v>
       </c>
       <c r="BD4" t="n">
-        <v>7.6</v>
+        <v>32</v>
       </c>
       <c r="BE4" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.2</v>
+        <v>14</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.85</v>
+        <v>11</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-07 06:34:22</t>
+          <t>2026-05-07 08:55:50</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Serbian First League</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1330,186 +1330,186 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SU Dinamo Jug</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FK Usce Novi Beograd</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.28</v>
+        <v>13</v>
       </c>
       <c r="G5" t="n">
-        <v>1.36</v>
+        <v>16</v>
       </c>
       <c r="H5" t="n">
-        <v>8.6</v>
+        <v>1.33</v>
       </c>
       <c r="I5" t="n">
-        <v>28</v>
+        <v>1.35</v>
       </c>
       <c r="J5" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="K5" t="n">
-        <v>6.8</v>
+        <v>5.6</v>
       </c>
       <c r="L5" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="M5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V5" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="W5" t="n">
         <v>1.06</v>
       </c>
-      <c r="N5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W5" t="n">
-        <v>3.8</v>
-      </c>
       <c r="X5" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="Y5" t="n">
-        <v>950</v>
+        <v>6.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AB5" t="n">
+        <v>36</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>170</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>60</v>
+      </c>
+      <c r="AH5" t="n">
         <v>970</v>
       </c>
-      <c r="AC5" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>950</v>
-      </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AJ5" t="n">
-        <v>500</v>
+        <v>980</v>
       </c>
       <c r="AK5" t="n">
-        <v>970</v>
+        <v>490</v>
       </c>
       <c r="AL5" t="n">
-        <v>500</v>
+        <v>390</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>790</v>
       </c>
       <c r="AN5" t="n">
+        <v>930</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT5" t="n">
         <v>29</v>
       </c>
-      <c r="AO5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>3.75</v>
-      </c>
       <c r="AU5" t="n">
-        <v>2.34</v>
+        <v>11</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.2</v>
+        <v>10.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.2</v>
+        <v>16.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>3.7</v>
+        <v>50</v>
       </c>
       <c r="AY5" t="n">
-        <v>2.06</v>
+        <v>50</v>
       </c>
       <c r="AZ5" t="n">
-        <v>6.8</v>
+        <v>44</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.2</v>
+        <v>60</v>
       </c>
       <c r="BB5" t="n">
-        <v>2.62</v>
+        <v>12</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.38</v>
+        <v>11.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>7</v>
+        <v>11.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.91</v>
+        <v>12</v>
       </c>
       <c r="BF5" t="n">
-        <v>3.7</v>
+        <v>14.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-07 06:34:22</t>
+          <t>2026-05-07 08:55:50</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Serbian First League</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1524,55 +1524,55 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FK Borac Cacak</t>
+          <t>FK Tukums 2000</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FK Graficar</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.97</v>
+        <v>1.66</v>
       </c>
       <c r="G6" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P6" t="n">
         <v>2.12</v>
       </c>
-      <c r="H6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.79</v>
-      </c>
       <c r="Q6" t="n">
-        <v>2.16</v>
+        <v>1.82</v>
       </c>
       <c r="R6" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="S6" t="n">
-        <v>3.9</v>
+        <v>3.05</v>
       </c>
       <c r="T6" t="n">
         <v>1.83</v>
@@ -1581,122 +1581,122 @@
         <v>2.04</v>
       </c>
       <c r="V6" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="W6" t="n">
-        <v>1.89</v>
+        <v>2.4</v>
       </c>
       <c r="X6" t="n">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>15.5</v>
+        <v>22</v>
       </c>
       <c r="Z6" t="n">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="AA6" t="n">
-        <v>290</v>
+        <v>160</v>
       </c>
       <c r="AB6" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>27</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AT6" t="n">
         <v>8.4</v>
       </c>
-      <c r="AD6" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>240</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL6" t="n">
+      <c r="AU6" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AW6" t="n">
         <v>40</v>
       </c>
-      <c r="AM6" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>17</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>270</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>25</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV6" t="n">
+      <c r="AX6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB6" t="n">
         <v>14.5</v>
       </c>
-      <c r="AW6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>9</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>19.5</v>
-      </c>
       <c r="BC6" t="n">
-        <v>18</v>
+        <v>14.5</v>
       </c>
       <c r="BD6" t="n">
+        <v>29</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BF6" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BE6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BF6" t="n">
+      <c r="BG6" t="n">
         <v>13.5</v>
       </c>
-      <c r="BG6" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-07 06:34:22</t>
+          <t>2026-05-07 08:55:50</t>
         </is>
       </c>
     </row>
@@ -1718,31 +1718,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FK Dubocica</t>
+          <t>FK Borac Cacak</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FK FAP</t>
+          <t>FK Graficar</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.24</v>
+        <v>1.87</v>
       </c>
       <c r="G7" t="n">
-        <v>2.46</v>
+        <v>1.98</v>
       </c>
       <c r="H7" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="I7" t="n">
-        <v>3.65</v>
+        <v>5.1</v>
       </c>
       <c r="J7" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="K7" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L7" t="n">
         <v>1.43</v>
@@ -1751,153 +1751,153 @@
         <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="O7" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="P7" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="R7" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="S7" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="T7" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="U7" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="V7" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="W7" t="n">
-        <v>1.69</v>
+        <v>2.02</v>
       </c>
       <c r="X7" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>13.5</v>
+        <v>17</v>
       </c>
       <c r="Z7" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="AA7" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AB7" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AE7" t="n">
-        <v>42</v>
+        <v>190</v>
       </c>
       <c r="AF7" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH7" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AI7" t="n">
-        <v>230</v>
+        <v>160</v>
       </c>
       <c r="AJ7" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="AK7" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AL7" t="n">
         <v>40</v>
       </c>
       <c r="AM7" t="n">
-        <v>100</v>
+        <v>580</v>
       </c>
       <c r="AN7" t="n">
-        <v>19</v>
+        <v>14.5</v>
       </c>
       <c r="AO7" t="n">
-        <v>48</v>
+        <v>270</v>
       </c>
       <c r="AP7" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AQ7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AR7" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="AS7" t="n">
-        <v>26</v>
+        <v>7.6</v>
       </c>
       <c r="AT7" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AU7" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV7" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AW7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC7" t="n">
         <v>16.5</v>
       </c>
-      <c r="AX7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>20</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>18.5</v>
-      </c>
       <c r="BD7" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BE7" t="n">
         <v>15</v>
       </c>
       <c r="BF7" t="n">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>27</v>
+        <v>7.6</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-07 06:34:22</t>
+          <t>2026-05-07 08:55:50</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>Serbian First League</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1912,186 +1912,186 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>SU Dinamo Jug</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>FK Usce Novi Beograd</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>10.5</v>
+        <v>1.21</v>
       </c>
       <c r="G8" t="n">
-        <v>13</v>
+        <v>1.26</v>
       </c>
       <c r="H8" t="n">
-        <v>1.42</v>
+        <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>1.46</v>
+        <v>28</v>
       </c>
       <c r="J8" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="K8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W8" t="n">
         <v>4.8</v>
       </c>
-      <c r="L8" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="P8" t="n">
+      <c r="X8" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>500</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>29</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BE8" t="n">
         <v>1.72</v>
       </c>
-      <c r="Q8" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V8" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>12</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>28</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>170</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>160</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>700</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>500</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>400</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>660</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>6</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>24</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>36</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>40</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>36</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>55</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>11</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>11</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>11</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>11</v>
-      </c>
       <c r="BF8" t="n">
-        <v>14.5</v>
+        <v>1.93</v>
       </c>
       <c r="BG8" t="n">
-        <v>7.8</v>
+        <v>4.2</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-07 06:34:22</t>
+          <t>2026-05-07 08:55:50</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>Serbian First League</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2106,186 +2106,186 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Paradou</t>
+          <t>Tekstilac Odzaci</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Fk Smederevo</t>
         </is>
       </c>
       <c r="F9" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N9" t="n">
         <v>3</v>
       </c>
-      <c r="G9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N9" t="n">
-        <v>5</v>
-      </c>
       <c r="O9" t="n">
-        <v>1.22</v>
+        <v>1.43</v>
       </c>
       <c r="P9" t="n">
-        <v>2.4</v>
+        <v>1.68</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.67</v>
+        <v>2.28</v>
       </c>
       <c r="R9" t="n">
-        <v>1.55</v>
+        <v>1.24</v>
       </c>
       <c r="S9" t="n">
-        <v>2.62</v>
+        <v>4.5</v>
       </c>
       <c r="T9" t="n">
-        <v>1.11</v>
+        <v>1.98</v>
       </c>
       <c r="U9" t="n">
-        <v>1.47</v>
+        <v>1.86</v>
       </c>
       <c r="V9" t="n">
-        <v>1.72</v>
+        <v>1.3</v>
       </c>
       <c r="W9" t="n">
-        <v>1.43</v>
+        <v>1.83</v>
       </c>
       <c r="X9" t="n">
-        <v>140</v>
+        <v>17.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="Z9" t="n">
-        <v>18.5</v>
+        <v>500</v>
       </c>
       <c r="AA9" t="n">
-        <v>32</v>
+        <v>900</v>
       </c>
       <c r="AB9" t="n">
-        <v>17</v>
+        <v>7.6</v>
       </c>
       <c r="AC9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>500</v>
+      </c>
+      <c r="AG9" t="n">
         <v>11</v>
       </c>
-      <c r="AD9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>23</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>90</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AH9" t="n">
-        <v>16.5</v>
+        <v>950</v>
       </c>
       <c r="AI9" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AJ9" t="n">
-        <v>48</v>
+        <v>900</v>
       </c>
       <c r="AK9" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AL9" t="n">
-        <v>190</v>
+        <v>500</v>
       </c>
       <c r="AM9" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN9" t="n">
-        <v>25</v>
+        <v>600</v>
       </c>
       <c r="AO9" t="n">
-        <v>16</v>
+        <v>600</v>
       </c>
       <c r="AP9" t="n">
-        <v>17.5</v>
+        <v>6.4</v>
       </c>
       <c r="AQ9" t="n">
-        <v>12</v>
+        <v>6.6</v>
       </c>
       <c r="AR9" t="n">
-        <v>15.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AT9" t="n">
-        <v>14</v>
+        <v>6.2</v>
       </c>
       <c r="AU9" t="n">
-        <v>8.4</v>
+        <v>7</v>
       </c>
       <c r="AV9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AW9" t="n">
         <v>9.6</v>
       </c>
-      <c r="AW9" t="n">
-        <v>4.7</v>
-      </c>
       <c r="AX9" t="n">
-        <v>14.5</v>
+        <v>7</v>
       </c>
       <c r="AY9" t="n">
-        <v>11</v>
+        <v>6.6</v>
       </c>
       <c r="AZ9" t="n">
-        <v>14</v>
+        <v>7.6</v>
       </c>
       <c r="BA9" t="n">
-        <v>23</v>
+        <v>7.2</v>
       </c>
       <c r="BB9" t="n">
-        <v>5.3</v>
+        <v>8</v>
       </c>
       <c r="BC9" t="n">
-        <v>5</v>
+        <v>7.8</v>
       </c>
       <c r="BD9" t="n">
-        <v>19.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="BF9" t="n">
-        <v>18.5</v>
+        <v>7.8</v>
       </c>
       <c r="BG9" t="n">
-        <v>11.5</v>
+        <v>7.2</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-07 06:34:22</t>
+          <t>2026-05-07 08:55:50</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Serbian First League</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2300,148 +2300,148 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>FK Tukums 2000</t>
+          <t>FK Dubocica</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>FK FAP</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="G10" t="n">
-        <v>1.92</v>
+        <v>2.04</v>
       </c>
       <c r="H10" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="I10" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J10" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="K10" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="L10" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="M10" t="n">
         <v>1.06</v>
       </c>
       <c r="N10" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="O10" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V10" t="n">
         <v>1.29</v>
       </c>
-      <c r="P10" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.27</v>
-      </c>
       <c r="W10" t="n">
-        <v>2.08</v>
+        <v>1.96</v>
       </c>
       <c r="X10" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="AA10" t="n">
         <v>900</v>
       </c>
       <c r="AB10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>270</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS10" t="n">
         <v>10</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>120</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>400</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>320</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>22</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>310</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>9.4</v>
       </c>
       <c r="AT10" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AU10" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV10" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AX10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY10" t="n">
         <v>9</v>
@@ -2450,36 +2450,36 @@
         <v>15.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="BB10" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>22</v>
+      </c>
+      <c r="BE10" t="n">
         <v>15</v>
       </c>
-      <c r="BC10" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>28</v>
-      </c>
-      <c r="BE10" t="n">
+      <c r="BF10" t="n">
+        <v>12</v>
+      </c>
+      <c r="BG10" t="n">
         <v>9.4</v>
       </c>
-      <c r="BF10" t="n">
-        <v>10</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>13.5</v>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-07 06:34:22</t>
+          <t>2026-05-07 08:55:50</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Finnish Kakkonen</t>
+          <t>Slovenian 2 SNL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,191 +2489,191 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SJK Akatemia 2</t>
+          <t>Slovan Ljublana</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Huima</t>
+          <t>Jesenice</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.97</v>
+        <v>1.63</v>
       </c>
       <c r="G11" t="n">
-        <v>2.14</v>
+        <v>1.72</v>
       </c>
       <c r="H11" t="n">
-        <v>3.1</v>
+        <v>5.2</v>
       </c>
       <c r="I11" t="n">
-        <v>3.55</v>
+        <v>6.4</v>
       </c>
       <c r="J11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="X11" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>26</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>140</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>19</v>
+      </c>
+      <c r="AR11" t="n">
         <v>4.4</v>
       </c>
-      <c r="K11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N11" t="n">
+      <c r="AS11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY11" t="n">
         <v>8.6</v>
       </c>
-      <c r="O11" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="P11" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="X11" t="n">
-        <v>80</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>950</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>500</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>500</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>950</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>950</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>500</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>950</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>500</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>500</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>600</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>600</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AZ11" t="n">
-        <v>1.22</v>
+        <v>15.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.23</v>
+        <v>4.5</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.23</v>
+        <v>14</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.23</v>
+        <v>13.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.23</v>
+        <v>4.2</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.23</v>
+        <v>4.5</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.55</v>
+        <v>3.15</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.55</v>
+        <v>4.5</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-07 06:34:22</t>
+          <t>2026-05-07 08:55:50</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Finnish Ykkosliiga</t>
+          <t>Finnish Kakkonen</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2688,186 +2688,186 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>PK-35 RY</t>
+          <t>SJK Akatemia 2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Huima</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.72</v>
+        <v>2.18</v>
       </c>
       <c r="G12" t="n">
-        <v>1.77</v>
+        <v>2.26</v>
       </c>
       <c r="H12" t="n">
-        <v>5.3</v>
+        <v>2.8</v>
       </c>
       <c r="I12" t="n">
-        <v>5.5</v>
+        <v>2.94</v>
       </c>
       <c r="J12" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="K12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N12" t="n">
+        <v>10</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="P12" t="n">
         <v>4.4</v>
       </c>
-      <c r="L12" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N12" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.99</v>
-      </c>
       <c r="Q12" t="n">
-        <v>1.96</v>
+        <v>1.26</v>
       </c>
       <c r="R12" t="n">
-        <v>1.37</v>
+        <v>2.4</v>
       </c>
       <c r="S12" t="n">
-        <v>3.5</v>
+        <v>1.64</v>
       </c>
       <c r="T12" t="n">
-        <v>1.91</v>
+        <v>1.11</v>
       </c>
       <c r="U12" t="n">
-        <v>1.98</v>
+        <v>1.2</v>
       </c>
       <c r="V12" t="n">
-        <v>1.22</v>
+        <v>1.52</v>
       </c>
       <c r="W12" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="X12" t="n">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="Y12" t="n">
-        <v>29</v>
+        <v>950</v>
       </c>
       <c r="Z12" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AA12" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB12" t="n">
-        <v>8.4</v>
+        <v>950</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.199999999999999</v>
+        <v>950</v>
       </c>
       <c r="AD12" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE12" t="n">
         <v>500</v>
       </c>
-      <c r="AE12" t="n">
-        <v>700</v>
-      </c>
       <c r="AF12" t="n">
-        <v>12</v>
+        <v>500</v>
       </c>
       <c r="AG12" t="n">
-        <v>10</v>
+        <v>950</v>
       </c>
       <c r="AH12" t="n">
-        <v>44</v>
+        <v>950</v>
       </c>
       <c r="AI12" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="AJ12" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK12" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AL12" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AM12" t="n">
         <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>11.5</v>
+        <v>600</v>
       </c>
       <c r="AO12" t="n">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="AP12" t="n">
-        <v>7.6</v>
+        <v>2</v>
       </c>
       <c r="AQ12" t="n">
-        <v>8.4</v>
+        <v>1.21</v>
       </c>
       <c r="AR12" t="n">
-        <v>18.5</v>
+        <v>1.22</v>
       </c>
       <c r="AS12" t="n">
-        <v>13.5</v>
+        <v>1.23</v>
       </c>
       <c r="AT12" t="n">
-        <v>7</v>
+        <v>1.21</v>
       </c>
       <c r="AU12" t="n">
-        <v>8.199999999999999</v>
+        <v>1.22</v>
       </c>
       <c r="AV12" t="n">
-        <v>10.5</v>
+        <v>1.22</v>
       </c>
       <c r="AW12" t="n">
-        <v>12.5</v>
+        <v>1.23</v>
       </c>
       <c r="AX12" t="n">
-        <v>9</v>
+        <v>1.21</v>
       </c>
       <c r="AY12" t="n">
-        <v>8.800000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="AZ12" t="n">
-        <v>11.5</v>
+        <v>1.22</v>
       </c>
       <c r="BA12" t="n">
-        <v>12.5</v>
+        <v>1.23</v>
       </c>
       <c r="BB12" t="n">
-        <v>15.5</v>
+        <v>1.23</v>
       </c>
       <c r="BC12" t="n">
-        <v>10.5</v>
+        <v>1.23</v>
       </c>
       <c r="BD12" t="n">
-        <v>11</v>
+        <v>1.23</v>
       </c>
       <c r="BE12" t="n">
-        <v>13.5</v>
+        <v>1.23</v>
       </c>
       <c r="BF12" t="n">
-        <v>10</v>
+        <v>1.55</v>
       </c>
       <c r="BG12" t="n">
-        <v>13</v>
+        <v>1.55</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-07 06:34:22</t>
+          <t>2026-05-07 08:55:50</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Moroccan Botola Pro 1</t>
+          <t>Finnish Ykkosliiga</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2882,186 +2882,186 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>DHJ El Jadida</t>
+          <t>PK-35 RY</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>HUSA Agadir</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.05</v>
+        <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>3.25</v>
+        <v>2.06</v>
       </c>
       <c r="H13" t="n">
-        <v>2.92</v>
+        <v>3.95</v>
       </c>
       <c r="I13" t="n">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="J13" t="n">
-        <v>2.78</v>
+        <v>3.7</v>
       </c>
       <c r="K13" t="n">
-        <v>2.98</v>
+        <v>3.9</v>
       </c>
       <c r="L13" t="n">
-        <v>1.64</v>
+        <v>1.41</v>
       </c>
       <c r="M13" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="N13" t="n">
-        <v>2.46</v>
+        <v>3.9</v>
       </c>
       <c r="O13" t="n">
-        <v>1.61</v>
+        <v>1.32</v>
       </c>
       <c r="P13" t="n">
-        <v>1.46</v>
+        <v>1.97</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.94</v>
+        <v>1.98</v>
       </c>
       <c r="R13" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="S13" t="n">
-        <v>6.2</v>
+        <v>3.55</v>
       </c>
       <c r="T13" t="n">
-        <v>2.14</v>
+        <v>1.8</v>
       </c>
       <c r="U13" t="n">
-        <v>1.71</v>
+        <v>2.08</v>
       </c>
       <c r="V13" t="n">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="W13" t="n">
-        <v>1.44</v>
+        <v>1.94</v>
       </c>
       <c r="X13" t="n">
-        <v>7.8</v>
+        <v>20</v>
       </c>
       <c r="Y13" t="n">
-        <v>8.4</v>
+        <v>15</v>
       </c>
       <c r="Z13" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>400</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>700</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>700</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR13" t="n">
         <v>18.5</v>
       </c>
-      <c r="AA13" t="n">
-        <v>120</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>250</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>170</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>290</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>190</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>600</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>600</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AS13" t="n">
-        <v>44</v>
+        <v>10.5</v>
       </c>
       <c r="AT13" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AU13" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="AV13" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AW13" t="n">
-        <v>38</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX13" t="n">
-        <v>16.5</v>
+        <v>10</v>
       </c>
       <c r="AY13" t="n">
-        <v>12</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ13" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="BA13" t="n">
         <v>34</v>
       </c>
       <c r="BB13" t="n">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="BC13" t="n">
-        <v>38</v>
+        <v>13.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>48</v>
+        <v>18.5</v>
       </c>
       <c r="BE13" t="n">
         <v>10.5</v>
       </c>
       <c r="BF13" t="n">
-        <v>25</v>
+        <v>13.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-07 06:34:22</t>
+          <t>2026-05-07 08:55:50</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Polish I Liga</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3076,186 +3076,186 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LKS Lodz</t>
+          <t>DHJ El Jadida</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pogon Grodzisk Mazowiecki</t>
+          <t>HUSA Agadir</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.65</v>
+        <v>3.05</v>
       </c>
       <c r="G14" t="n">
-        <v>1.66</v>
+        <v>3.2</v>
       </c>
       <c r="H14" t="n">
-        <v>5.5</v>
+        <v>2.98</v>
       </c>
       <c r="I14" t="n">
-        <v>6.4</v>
+        <v>3.15</v>
       </c>
       <c r="J14" t="n">
-        <v>4.3</v>
+        <v>2.82</v>
       </c>
       <c r="K14" t="n">
-        <v>4.6</v>
+        <v>2.9</v>
       </c>
       <c r="L14" t="n">
-        <v>1.32</v>
+        <v>1.64</v>
       </c>
       <c r="M14" t="n">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="N14" t="n">
-        <v>5.1</v>
+        <v>2.52</v>
       </c>
       <c r="O14" t="n">
-        <v>1.21</v>
+        <v>1.6</v>
       </c>
       <c r="P14" t="n">
-        <v>2.42</v>
+        <v>1.47</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.65</v>
+        <v>2.92</v>
       </c>
       <c r="R14" t="n">
-        <v>1.55</v>
+        <v>1.18</v>
       </c>
       <c r="S14" t="n">
-        <v>2.68</v>
+        <v>6</v>
       </c>
       <c r="T14" t="n">
-        <v>1.69</v>
+        <v>2.2</v>
       </c>
       <c r="U14" t="n">
-        <v>2.26</v>
+        <v>1.74</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2</v>
+        <v>1.46</v>
       </c>
       <c r="W14" t="n">
-        <v>2.48</v>
+        <v>1.46</v>
       </c>
       <c r="X14" t="n">
-        <v>38</v>
+        <v>7.8</v>
       </c>
       <c r="Y14" t="n">
-        <v>500</v>
+        <v>8.4</v>
       </c>
       <c r="Z14" t="n">
-        <v>85</v>
+        <v>18.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>900</v>
+        <v>120</v>
       </c>
       <c r="AB14" t="n">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>12.5</v>
+        <v>7.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="AE14" t="n">
-        <v>320</v>
+        <v>250</v>
       </c>
       <c r="AF14" t="n">
         <v>19.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH14" t="n">
         <v>25</v>
       </c>
       <c r="AI14" t="n">
-        <v>700</v>
+        <v>170</v>
       </c>
       <c r="AJ14" t="n">
+        <v>290</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>190</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>600</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>600</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>44</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>38</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>46</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>38</v>
+      </c>
+      <c r="BD14" t="n">
         <v>48</v>
       </c>
-      <c r="AK14" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>700</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS14" t="n">
+      <c r="BE14" t="n">
         <v>10.5</v>
       </c>
-      <c r="AT14" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>40</v>
-      </c>
-      <c r="AX14" t="n">
+      <c r="BF14" t="n">
+        <v>25</v>
+      </c>
+      <c r="BG14" t="n">
         <v>10</v>
       </c>
-      <c r="AY14" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>26</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>14</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>15</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>30</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-07 06:34:22</t>
+          <t>2026-05-07 08:55:50</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Romanian Liga II</t>
+          <t>Polish I Liga</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3270,186 +3270,186 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CSA Steaua Bucuresti</t>
+          <t>LKS Lodz</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ACS Sepsi OSK</t>
+          <t>Pogon Grodzisk Mazowiecki</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>5.8</v>
+        <v>1.61</v>
       </c>
       <c r="G15" t="n">
-        <v>8.800000000000001</v>
+        <v>1.65</v>
       </c>
       <c r="H15" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="I15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N15" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="Q15" t="n">
         <v>1.65</v>
       </c>
-      <c r="I15" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N15" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.9</v>
-      </c>
       <c r="R15" t="n">
-        <v>1.37</v>
+        <v>1.56</v>
       </c>
       <c r="S15" t="n">
-        <v>3.3</v>
+        <v>2.68</v>
       </c>
       <c r="T15" t="n">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="U15" t="n">
-        <v>1.98</v>
+        <v>2.28</v>
       </c>
       <c r="V15" t="n">
-        <v>2.36</v>
+        <v>1.19</v>
       </c>
       <c r="W15" t="n">
-        <v>1.13</v>
+        <v>2.52</v>
       </c>
       <c r="X15" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="Y15" t="n">
         <v>500</v>
       </c>
       <c r="Z15" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AA15" t="n">
         <v>900</v>
       </c>
       <c r="AB15" t="n">
-        <v>950</v>
+        <v>11.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>42</v>
+        <v>10.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>970</v>
+        <v>27</v>
       </c>
       <c r="AE15" t="n">
-        <v>500</v>
+        <v>320</v>
       </c>
       <c r="AF15" t="n">
-        <v>500</v>
+        <v>19</v>
       </c>
       <c r="AG15" t="n">
-        <v>950</v>
+        <v>10</v>
       </c>
       <c r="AH15" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="AI15" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="AJ15" t="n">
-        <v>900</v>
+        <v>28</v>
       </c>
       <c r="AK15" t="n">
-        <v>700</v>
+        <v>26</v>
       </c>
       <c r="AL15" t="n">
-        <v>700</v>
+        <v>75</v>
       </c>
       <c r="AM15" t="n">
         <v>580</v>
       </c>
       <c r="AN15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AO15" t="n">
         <v>700</v>
       </c>
-      <c r="AO15" t="n">
-        <v>29</v>
-      </c>
       <c r="AP15" t="n">
-        <v>6.2</v>
+        <v>20</v>
       </c>
       <c r="AQ15" t="n">
-        <v>4.6</v>
+        <v>11.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>7.2</v>
+        <v>18</v>
       </c>
       <c r="AS15" t="n">
-        <v>6.6</v>
+        <v>10.5</v>
       </c>
       <c r="AT15" t="n">
-        <v>2.4</v>
+        <v>9.4</v>
       </c>
       <c r="AU15" t="n">
-        <v>4.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV15" t="n">
-        <v>5</v>
+        <v>18.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>6.6</v>
+        <v>23</v>
       </c>
       <c r="AX15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY15" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AZ15" t="n">
-        <v>7</v>
+        <v>11.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="BB15" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="BC15" t="n">
-        <v>9</v>
+        <v>13.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="BE15" t="n">
-        <v>2.82</v>
+        <v>30</v>
       </c>
       <c r="BF15" t="n">
-        <v>9</v>
+        <v>6.4</v>
       </c>
       <c r="BG15" t="n">
-        <v>5.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-07 06:34:22</t>
+          <t>2026-05-07 08:55:50</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Jordanian Premier League</t>
+          <t>Romanian Liga II</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,191 +3459,191 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>13:45:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>CSA Steaua Bucuresti</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Buqaa</t>
+          <t>ACS Sepsi OSK</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.85</v>
+        <v>5.1</v>
       </c>
       <c r="G16" t="n">
-        <v>1.91</v>
+        <v>5.9</v>
       </c>
       <c r="H16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K16" t="n">
         <v>4.1</v>
       </c>
-      <c r="I16" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J16" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K16" t="n">
-        <v>4.5</v>
-      </c>
       <c r="L16" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="M16" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N16" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="O16" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="P16" t="n">
-        <v>2.16</v>
+        <v>1.87</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.76</v>
+        <v>2.02</v>
       </c>
       <c r="R16" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="S16" t="n">
-        <v>2.92</v>
+        <v>3.65</v>
       </c>
       <c r="T16" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="U16" t="n">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="V16" t="n">
-        <v>1.28</v>
+        <v>2.2</v>
       </c>
       <c r="W16" t="n">
-        <v>2.08</v>
+        <v>1.2</v>
       </c>
       <c r="X16" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="Y16" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="Z16" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AA16" t="n">
         <v>900</v>
       </c>
       <c r="AB16" t="n">
-        <v>11</v>
+        <v>950</v>
       </c>
       <c r="AC16" t="n">
-        <v>9.6</v>
+        <v>14</v>
       </c>
       <c r="AD16" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AE16" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AF16" t="n">
-        <v>13</v>
+        <v>500</v>
       </c>
       <c r="AG16" t="n">
-        <v>11</v>
+        <v>950</v>
       </c>
       <c r="AH16" t="n">
-        <v>18.5</v>
+        <v>950</v>
       </c>
       <c r="AI16" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AJ16" t="n">
-        <v>21</v>
+        <v>900</v>
       </c>
       <c r="AK16" t="n">
-        <v>19</v>
+        <v>700</v>
       </c>
       <c r="AL16" t="n">
-        <v>32</v>
+        <v>700</v>
       </c>
       <c r="AM16" t="n">
         <v>580</v>
       </c>
       <c r="AN16" t="n">
-        <v>11</v>
+        <v>700</v>
       </c>
       <c r="AO16" t="n">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="AP16" t="n">
-        <v>16</v>
+        <v>6.8</v>
       </c>
       <c r="AQ16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AS16" t="n">
         <v>6.6</v>
       </c>
-      <c r="AR16" t="n">
-        <v>22</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AT16" t="n">
-        <v>5.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU16" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="AV16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW16" t="n">
         <v>6.6</v>
       </c>
-      <c r="AW16" t="n">
-        <v>17.5</v>
-      </c>
       <c r="AX16" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY16" t="n">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="AZ16" t="n">
         <v>6.6</v>
       </c>
       <c r="BA16" t="n">
-        <v>8.6</v>
+        <v>4.8</v>
       </c>
       <c r="BB16" t="n">
-        <v>17.5</v>
+        <v>9</v>
       </c>
       <c r="BC16" t="n">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD16" t="n">
-        <v>20</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE16" t="n">
-        <v>9.199999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="BF16" t="n">
-        <v>8.800000000000001</v>
+        <v>2.84</v>
       </c>
       <c r="BG16" t="n">
-        <v>8.6</v>
+        <v>5.4</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-07 06:34:22</t>
+          <t>2026-05-07 08:55:50</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Turkish 1 Lig</t>
+          <t>Slovenian 2 SNL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,191 +3653,191 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Bodrum Belediyesi Bodrumspor</t>
+          <t>Rudar</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Krsko</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.38</v>
+        <v>1.49</v>
       </c>
       <c r="G17" t="n">
-        <v>2.42</v>
+        <v>1.59</v>
       </c>
       <c r="H17" t="n">
-        <v>3.3</v>
+        <v>6.2</v>
       </c>
       <c r="I17" t="n">
-        <v>3.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="K17" t="n">
-        <v>3.6</v>
+        <v>5.8</v>
       </c>
       <c r="L17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R17" t="n">
         <v>1.42</v>
       </c>
-      <c r="M17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N17" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.36</v>
-      </c>
       <c r="S17" t="n">
-        <v>3.55</v>
+        <v>2.84</v>
       </c>
       <c r="T17" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="U17" t="n">
-        <v>2.12</v>
+        <v>1.87</v>
       </c>
       <c r="V17" t="n">
-        <v>1.4</v>
+        <v>1.12</v>
       </c>
       <c r="W17" t="n">
-        <v>1.71</v>
+        <v>2.6</v>
       </c>
       <c r="X17" t="n">
-        <v>14.5</v>
+        <v>950</v>
       </c>
       <c r="Y17" t="n">
-        <v>13.5</v>
+        <v>950</v>
       </c>
       <c r="Z17" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>10.5</v>
+        <v>950</v>
       </c>
       <c r="AC17" t="n">
-        <v>8.199999999999999</v>
+        <v>950</v>
       </c>
       <c r="AD17" t="n">
-        <v>15</v>
+        <v>950</v>
       </c>
       <c r="AE17" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>15.5</v>
+        <v>11</v>
       </c>
       <c r="AG17" t="n">
-        <v>12</v>
+        <v>950</v>
       </c>
       <c r="AH17" t="n">
-        <v>18</v>
+        <v>950</v>
       </c>
       <c r="AI17" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="AK17" t="n">
-        <v>27</v>
+        <v>18.5</v>
       </c>
       <c r="AL17" t="n">
         <v>40</v>
       </c>
       <c r="AM17" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>20</v>
+        <v>8.6</v>
       </c>
       <c r="AO17" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>12</v>
+        <v>4.1</v>
       </c>
       <c r="AQ17" t="n">
-        <v>11</v>
+        <v>4.3</v>
       </c>
       <c r="AR17" t="n">
-        <v>20</v>
+        <v>3.3</v>
       </c>
       <c r="AS17" t="n">
-        <v>27</v>
+        <v>2.5</v>
       </c>
       <c r="AT17" t="n">
-        <v>8.800000000000001</v>
+        <v>3.45</v>
       </c>
       <c r="AU17" t="n">
-        <v>7.2</v>
+        <v>3.65</v>
       </c>
       <c r="AV17" t="n">
-        <v>12</v>
+        <v>4.4</v>
       </c>
       <c r="AW17" t="n">
-        <v>24</v>
+        <v>3.35</v>
       </c>
       <c r="AX17" t="n">
-        <v>13</v>
+        <v>3.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>10</v>
+        <v>3.55</v>
       </c>
       <c r="AZ17" t="n">
-        <v>14.5</v>
+        <v>4.3</v>
       </c>
       <c r="BA17" t="n">
-        <v>22</v>
+        <v>3.45</v>
       </c>
       <c r="BB17" t="n">
-        <v>19.5</v>
+        <v>3.85</v>
       </c>
       <c r="BC17" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="BD17" t="n">
-        <v>17.5</v>
+        <v>4.5</v>
       </c>
       <c r="BE17" t="n">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="BF17" t="n">
-        <v>16</v>
+        <v>3.2</v>
       </c>
       <c r="BG17" t="n">
-        <v>8.6</v>
+        <v>3.8</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-07 06:34:22</t>
+          <t>2026-05-07 08:55:50</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Turkish 1 Lig</t>
+          <t>Jordanian Premier League</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,191 +3847,191 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:45:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Corum Belediyespor</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Keciorengucu</t>
+          <t>Al Buqaa</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="G18" t="n">
-        <v>1.74</v>
+        <v>1.91</v>
       </c>
       <c r="H18" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="I18" t="n">
-        <v>5.8</v>
+        <v>4.6</v>
       </c>
       <c r="J18" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K18" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L18" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M18" t="n">
         <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="O18" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="P18" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="R18" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="S18" t="n">
-        <v>3.05</v>
+        <v>2.82</v>
       </c>
       <c r="T18" t="n">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="U18" t="n">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="V18" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="W18" t="n">
-        <v>2.34</v>
+        <v>2.1</v>
       </c>
       <c r="X18" t="n">
         <v>22</v>
       </c>
       <c r="Y18" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="Z18" t="n">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AA18" t="n">
         <v>900</v>
       </c>
       <c r="AB18" t="n">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AD18" t="n">
-        <v>950</v>
+        <v>19</v>
       </c>
       <c r="AE18" t="n">
-        <v>700</v>
+        <v>55</v>
       </c>
       <c r="AF18" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AG18" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AH18" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AI18" t="n">
-        <v>700</v>
+        <v>55</v>
       </c>
       <c r="AJ18" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="AK18" t="n">
-        <v>29</v>
+        <v>18.5</v>
       </c>
       <c r="AL18" t="n">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="AM18" t="n">
         <v>580</v>
       </c>
       <c r="AN18" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO18" t="n">
-        <v>700</v>
+        <v>48</v>
       </c>
       <c r="AP18" t="n">
         <v>16.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AR18" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="AS18" t="n">
-        <v>15</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT18" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU18" t="n">
         <v>8.4</v>
       </c>
-      <c r="AU18" t="n">
-        <v>8.6</v>
-      </c>
       <c r="AV18" t="n">
-        <v>18</v>
+        <v>6.6</v>
       </c>
       <c r="AW18" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AX18" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AY18" t="n">
         <v>9</v>
       </c>
       <c r="AZ18" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>30</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB18" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BC18" t="n">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="BD18" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="BE18" t="n">
-        <v>15</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF18" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG18" t="n">
-        <v>14</v>
+        <v>8.6</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-07 06:34:22</t>
+          <t>2026-05-07 08:55:50</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Turkish 1 Lig</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4046,186 +4046,186 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>National Bank</t>
+          <t>Bodrum Belediyesi Bodrumspor</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ismaily</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="G19" t="n">
-        <v>1.89</v>
+        <v>2.4</v>
       </c>
       <c r="H19" t="n">
-        <v>5.8</v>
+        <v>3.3</v>
       </c>
       <c r="I19" t="n">
-        <v>6.4</v>
+        <v>3.55</v>
       </c>
       <c r="J19" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="K19" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="L19" t="n">
-        <v>1.54</v>
+        <v>1.42</v>
       </c>
       <c r="M19" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="N19" t="n">
-        <v>2.92</v>
+        <v>3.75</v>
       </c>
       <c r="O19" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="P19" t="n">
-        <v>1.61</v>
+        <v>1.92</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.5</v>
+        <v>2.02</v>
       </c>
       <c r="R19" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>3.55</v>
       </c>
       <c r="T19" t="n">
-        <v>2.16</v>
+        <v>1.79</v>
       </c>
       <c r="U19" t="n">
-        <v>1.74</v>
+        <v>2.12</v>
       </c>
       <c r="V19" t="n">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="W19" t="n">
-        <v>2.12</v>
+        <v>1.71</v>
       </c>
       <c r="X19" t="n">
-        <v>9.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="AA19" t="n">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="AB19" t="n">
-        <v>6.6</v>
+        <v>10.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD19" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="AE19" t="n">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="AF19" t="n">
-        <v>9.6</v>
+        <v>15.5</v>
       </c>
       <c r="AG19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>40</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ19" t="n">
         <v>11</v>
       </c>
-      <c r="AH19" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>140</v>
-      </c>
-      <c r="AJ19" t="n">
+      <c r="AR19" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>32</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>40</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BC19" t="n">
         <v>21</v>
       </c>
-      <c r="AK19" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>180</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>30</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>22</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>16</v>
-      </c>
-      <c r="BB19" t="n">
+      <c r="BD19" t="n">
         <v>17.5</v>
       </c>
-      <c r="BC19" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>32</v>
-      </c>
       <c r="BE19" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="BF19" t="n">
         <v>16</v>
       </c>
       <c r="BG19" t="n">
-        <v>16.5</v>
+        <v>12</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-07 06:34:22</t>
+          <t>2026-05-07 08:55:50</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Turkish 1 Lig</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4240,186 +4240,186 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Corum Belediyespor</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ZED FC</t>
+          <t>Keciorengucu</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.04</v>
+        <v>1.7</v>
       </c>
       <c r="G20" t="n">
-        <v>2.1</v>
+        <v>1.77</v>
       </c>
       <c r="H20" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="I20" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="J20" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="K20" t="n">
-        <v>3.35</v>
+        <v>4.3</v>
       </c>
       <c r="L20" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="M20" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="N20" t="n">
-        <v>2.66</v>
+        <v>4.4</v>
       </c>
       <c r="O20" t="n">
-        <v>1.56</v>
+        <v>1.26</v>
       </c>
       <c r="P20" t="n">
-        <v>1.53</v>
+        <v>2.16</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.74</v>
+        <v>1.8</v>
       </c>
       <c r="R20" t="n">
-        <v>1.19</v>
+        <v>1.45</v>
       </c>
       <c r="S20" t="n">
-        <v>5.8</v>
+        <v>3</v>
       </c>
       <c r="T20" t="n">
-        <v>2.24</v>
+        <v>1.79</v>
       </c>
       <c r="U20" t="n">
-        <v>1.72</v>
+        <v>2.12</v>
       </c>
       <c r="V20" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="W20" t="n">
-        <v>1.9</v>
+        <v>2.28</v>
       </c>
       <c r="X20" t="n">
-        <v>8.6</v>
+        <v>19</v>
       </c>
       <c r="Y20" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="Z20" t="n">
-        <v>32</v>
+        <v>120</v>
       </c>
       <c r="AA20" t="n">
-        <v>140</v>
+        <v>900</v>
       </c>
       <c r="AB20" t="n">
-        <v>6.6</v>
+        <v>9.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="AE20" t="n">
-        <v>90</v>
+        <v>700</v>
       </c>
       <c r="AF20" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG20" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AH20" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AI20" t="n">
-        <v>120</v>
+        <v>700</v>
       </c>
       <c r="AJ20" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AK20" t="n">
         <v>29</v>
       </c>
       <c r="AL20" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM20" t="n">
-        <v>230</v>
+        <v>580</v>
       </c>
       <c r="AN20" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>310</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AR20" t="n">
         <v>27</v>
       </c>
-      <c r="AO20" t="n">
-        <v>150</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>28</v>
-      </c>
       <c r="AS20" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>14</v>
+      </c>
+      <c r="BB20" t="n">
         <v>14.5</v>
       </c>
-      <c r="AT20" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>55</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>24</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>16</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>23</v>
-      </c>
       <c r="BC20" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="BD20" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="BE20" t="n">
-        <v>46</v>
+        <v>15.5</v>
       </c>
       <c r="BF20" t="n">
-        <v>24</v>
+        <v>8.4</v>
       </c>
       <c r="BG20" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-07 06:34:22</t>
+          <t>2026-05-07 08:55:50</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4434,186 +4434,186 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>FK Auda</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SC Grobina</t>
+          <t>ZED FC</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.45</v>
+        <v>2.06</v>
       </c>
       <c r="G21" t="n">
-        <v>1.47</v>
+        <v>2.08</v>
       </c>
       <c r="H21" t="n">
-        <v>8.800000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="I21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="X21" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>95</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>230</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>27</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>130</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ21" t="n">
         <v>10.5</v>
       </c>
-      <c r="J21" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="K21" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N21" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W21" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="X21" t="n">
+      <c r="AR21" t="n">
+        <v>28</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV21" t="n">
         <v>17</v>
       </c>
-      <c r="Y21" t="n">
-        <v>27</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>80</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>350</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>34</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>160</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>46</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>260</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>13</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>210</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>21</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>60</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>13</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>29</v>
-      </c>
       <c r="AW21" t="n">
-        <v>13.5</v>
+        <v>65</v>
       </c>
       <c r="AX21" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AY21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ21" t="n">
         <v>24</v>
       </c>
       <c r="BA21" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>23</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE21" t="n">
         <v>46</v>
       </c>
-      <c r="BB21" t="n">
-        <v>11</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>14</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>34</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>15.5</v>
-      </c>
       <c r="BF21" t="n">
-        <v>6.6</v>
+        <v>22</v>
       </c>
       <c r="BG21" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-07 06:34:22</t>
+          <t>2026-05-07 08:55:50</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Moroccan Botola Pro 1</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4623,191 +4623,191 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>National Bank</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Union de Touarga</t>
+          <t>Ismaily</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.44</v>
+        <v>1.9</v>
       </c>
       <c r="G22" t="n">
-        <v>1.46</v>
+        <v>1.94</v>
       </c>
       <c r="H22" t="n">
-        <v>9.6</v>
+        <v>5.4</v>
       </c>
       <c r="I22" t="n">
-        <v>12</v>
+        <v>5.8</v>
       </c>
       <c r="J22" t="n">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="K22" t="n">
-        <v>5.1</v>
+        <v>3.4</v>
       </c>
       <c r="L22" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="M22" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="N22" t="n">
-        <v>3.3</v>
+        <v>2.92</v>
       </c>
       <c r="O22" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="P22" t="n">
-        <v>1.79</v>
+        <v>1.61</v>
       </c>
       <c r="Q22" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="n">
         <v>2.14</v>
       </c>
-      <c r="R22" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.32</v>
-      </c>
       <c r="U22" t="n">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="V22" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="W22" t="n">
-        <v>3.15</v>
+        <v>2.06</v>
       </c>
       <c r="X22" t="n">
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="Y22" t="n">
-        <v>950</v>
+        <v>14.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>110</v>
+        <v>42</v>
       </c>
       <c r="AA22" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AB22" t="n">
         <v>6.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>11.5</v>
+        <v>7.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>950</v>
+        <v>24</v>
       </c>
       <c r="AE22" t="n">
-        <v>270</v>
+        <v>110</v>
       </c>
       <c r="AF22" t="n">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="AG22" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH22" t="n">
-        <v>950</v>
+        <v>25</v>
       </c>
       <c r="AI22" t="n">
-        <v>230</v>
+        <v>260</v>
       </c>
       <c r="AJ22" t="n">
-        <v>160</v>
+        <v>21</v>
       </c>
       <c r="AK22" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="AL22" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM22" t="n">
         <v>500</v>
       </c>
-      <c r="AM22" t="n">
-        <v>1000</v>
-      </c>
       <c r="AN22" t="n">
-        <v>9.800000000000001</v>
+        <v>22</v>
       </c>
       <c r="AO22" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AP22" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>34</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AT22" t="n">
         <v>6</v>
       </c>
-      <c r="AQ22" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>5.4</v>
-      </c>
       <c r="AU22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX22" t="n">
         <v>9</v>
       </c>
-      <c r="AV22" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>6.2</v>
-      </c>
       <c r="AY22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ22" t="n">
-        <v>8.199999999999999</v>
+        <v>21</v>
       </c>
       <c r="BA22" t="n">
-        <v>4.5</v>
+        <v>15</v>
       </c>
       <c r="BB22" t="n">
-        <v>5.7</v>
+        <v>18.5</v>
       </c>
       <c r="BC22" t="n">
-        <v>8.4</v>
+        <v>22</v>
       </c>
       <c r="BD22" t="n">
-        <v>7.6</v>
+        <v>32</v>
       </c>
       <c r="BE22" t="n">
-        <v>8.6</v>
+        <v>28</v>
       </c>
       <c r="BF22" t="n">
-        <v>8</v>
+        <v>17.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-07 06:34:22</t>
+          <t>2026-05-07 08:55:50</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,191 +4817,191 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Al-Shabab (KSA)</t>
+          <t>FK Auda</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>SC Grobina</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>9.4</v>
+        <v>1.48</v>
       </c>
       <c r="G23" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="H23" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="I23" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K23" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N23" t="n">
+        <v>4</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W23" t="n">
+        <v>3</v>
+      </c>
+      <c r="X23" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>27</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>80</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>350</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC23" t="n">
         <v>10.5</v>
       </c>
-      <c r="H23" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="J23" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="K23" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N23" t="n">
+      <c r="AD23" t="n">
+        <v>36</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>150</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>260</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN23" t="n">
         <v>8</v>
       </c>
-      <c r="O23" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="P23" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="U23" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="V23" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X23" t="n">
-        <v>65</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AA23" t="n">
+      <c r="AO23" t="n">
+        <v>200</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>23</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>44</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>28</v>
+      </c>
+      <c r="AW23" t="n">
         <v>13</v>
       </c>
-      <c r="AB23" t="n">
-        <v>55</v>
-      </c>
-      <c r="AC23" t="n">
+      <c r="AX23" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>24</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>29</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>26</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>16</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BG23" t="n">
         <v>15</v>
       </c>
-      <c r="AD23" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>13</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>110</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>36</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>25</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>310</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>110</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>85</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>100</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>46</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>42</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>44</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>32</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>22</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>15</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>48</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>50</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>48</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>80</v>
-      </c>
-      <c r="BG23" t="n">
-        <v>3.45</v>
-      </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-07 06:34:22</t>
+          <t>2026-05-07 08:55:50</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,114 +5011,114 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Union de Touarga</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="G24" t="n">
         <v>1.49</v>
       </c>
       <c r="H24" t="n">
-        <v>7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>17</v>
+        <v>11.5</v>
       </c>
       <c r="J24" t="n">
         <v>4.3</v>
       </c>
       <c r="K24" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="L24" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="M24" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S24" t="n">
+        <v>4</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W24" t="n">
         <v>3</v>
       </c>
-      <c r="O24" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S24" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W24" t="n">
-        <v>2.76</v>
-      </c>
       <c r="X24" t="n">
-        <v>970</v>
+        <v>90</v>
       </c>
       <c r="Y24" t="n">
-        <v>80</v>
+        <v>950</v>
       </c>
       <c r="Z24" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AA24" t="n">
         <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>970</v>
+        <v>6.4</v>
       </c>
       <c r="AC24" t="n">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="AD24" t="n">
         <v>950</v>
       </c>
       <c r="AE24" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AF24" t="n">
-        <v>40</v>
+        <v>7.4</v>
       </c>
       <c r="AG24" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AH24" t="n">
         <v>950</v>
       </c>
       <c r="AI24" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AJ24" t="n">
-        <v>900</v>
+        <v>160</v>
       </c>
       <c r="AK24" t="n">
-        <v>970</v>
+        <v>150</v>
       </c>
       <c r="AL24" t="n">
         <v>500</v>
@@ -5133,69 +5133,69 @@
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AQ24" t="n">
-        <v>4.2</v>
+        <v>8.4</v>
       </c>
       <c r="AR24" t="n">
-        <v>4.2</v>
+        <v>9.6</v>
       </c>
       <c r="AS24" t="n">
-        <v>4.2</v>
+        <v>10.5</v>
       </c>
       <c r="AT24" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="AU24" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AW24" t="n">
         <v>5.3</v>
       </c>
-      <c r="AV24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AX24" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="AY24" t="n">
         <v>6.4</v>
       </c>
       <c r="AZ24" t="n">
-        <v>3.05</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA24" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="BB24" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BC24" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.15</v>
+        <v>9</v>
       </c>
       <c r="BE24" t="n">
-        <v>2.88</v>
+        <v>10</v>
       </c>
       <c r="BF24" t="n">
-        <v>8.199999999999999</v>
+        <v>5.2</v>
       </c>
       <c r="BG24" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-07 06:34:22</t>
+          <t>2026-05-07 08:55:50</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,191 +5205,191 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Al-Shabab (KSA)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Shakhtar</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.64</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>1.66</v>
+        <v>10.5</v>
       </c>
       <c r="H25" t="n">
-        <v>5.9</v>
+        <v>1.34</v>
       </c>
       <c r="I25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="J25" t="n">
         <v>6.2</v>
       </c>
-      <c r="J25" t="n">
-        <v>4.3</v>
-      </c>
       <c r="K25" t="n">
-        <v>4.4</v>
+        <v>6.8</v>
       </c>
       <c r="L25" t="n">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="M25" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="N25" t="n">
-        <v>4.1</v>
+        <v>8.4</v>
       </c>
       <c r="O25" t="n">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="P25" t="n">
-        <v>2.04</v>
+        <v>3.45</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.92</v>
+        <v>1.38</v>
       </c>
       <c r="R25" t="n">
-        <v>1.41</v>
+        <v>1.99</v>
       </c>
       <c r="S25" t="n">
-        <v>3.3</v>
+        <v>1.96</v>
       </c>
       <c r="T25" t="n">
-        <v>1.97</v>
+        <v>1.67</v>
       </c>
       <c r="U25" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="V25" t="n">
-        <v>1.19</v>
+        <v>3.75</v>
       </c>
       <c r="W25" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="X25" t="n">
+        <v>55</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>13</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>55</v>
+      </c>
+      <c r="AC25" t="n">
         <v>16</v>
       </c>
-      <c r="Y25" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>48</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>180</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AD25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>110</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>36</v>
+      </c>
+      <c r="AH25" t="n">
         <v>23</v>
       </c>
-      <c r="AE25" t="n">
+      <c r="AI25" t="n">
+        <v>26</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>360</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>110</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM25" t="n">
         <v>90</v>
       </c>
-      <c r="AF25" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AG25" t="n">
+      <c r="AN25" t="n">
+        <v>110</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>46</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AV25" t="n">
         <v>10</v>
       </c>
-      <c r="AH25" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>16</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>42</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>36</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>20</v>
-      </c>
       <c r="AW25" t="n">
-        <v>60</v>
+        <v>11.5</v>
       </c>
       <c r="AX25" t="n">
-        <v>9.199999999999999</v>
+        <v>30</v>
       </c>
       <c r="AY25" t="n">
-        <v>9.800000000000001</v>
+        <v>29</v>
       </c>
       <c r="AZ25" t="n">
         <v>20</v>
       </c>
       <c r="BA25" t="n">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="BB25" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BC25" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="BD25" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="BE25" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="BF25" t="n">
-        <v>8.800000000000001</v>
+        <v>36</v>
       </c>
       <c r="BG25" t="n">
-        <v>85</v>
+        <v>3.4</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-07 06:34:22</t>
+          <t>2026-05-07 08:55:50</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5404,186 +5404,186 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2</v>
+        <v>1.47</v>
       </c>
       <c r="G26" t="n">
-        <v>2.02</v>
+        <v>1.5</v>
       </c>
       <c r="H26" t="n">
-        <v>4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>4.1</v>
+        <v>11.5</v>
       </c>
       <c r="J26" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="K26" t="n">
-        <v>3.95</v>
+        <v>4.8</v>
       </c>
       <c r="L26" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="M26" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="N26" t="n">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="O26" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="P26" t="n">
-        <v>2.08</v>
+        <v>1.67</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.91</v>
+        <v>2.38</v>
       </c>
       <c r="R26" t="n">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="S26" t="n">
-        <v>3.35</v>
+        <v>4.8</v>
       </c>
       <c r="T26" t="n">
-        <v>1.8</v>
+        <v>2.58</v>
       </c>
       <c r="U26" t="n">
-        <v>2.2</v>
+        <v>1.54</v>
       </c>
       <c r="V26" t="n">
-        <v>1.32</v>
+        <v>1.09</v>
       </c>
       <c r="W26" t="n">
-        <v>1.98</v>
+        <v>2.88</v>
       </c>
       <c r="X26" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="Y26" t="n">
-        <v>16</v>
+        <v>950</v>
       </c>
       <c r="Z26" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AA26" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>9.800000000000001</v>
+        <v>27</v>
       </c>
       <c r="AC26" t="n">
-        <v>8.6</v>
+        <v>42</v>
       </c>
       <c r="AD26" t="n">
-        <v>16.5</v>
+        <v>950</v>
       </c>
       <c r="AE26" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AF26" t="n">
-        <v>12.5</v>
+        <v>40</v>
       </c>
       <c r="AG26" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AH26" t="n">
-        <v>17.5</v>
+        <v>950</v>
       </c>
       <c r="AI26" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ26" t="n">
-        <v>24</v>
+        <v>900</v>
       </c>
       <c r="AK26" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AL26" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AM26" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="AO26" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>14.5</v>
+        <v>5.7</v>
       </c>
       <c r="AQ26" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AR26" t="n">
-        <v>27</v>
+        <v>4.2</v>
       </c>
       <c r="AS26" t="n">
-        <v>70</v>
+        <v>4.2</v>
       </c>
       <c r="AT26" t="n">
-        <v>9</v>
+        <v>4.2</v>
       </c>
       <c r="AU26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BG26" t="n">
         <v>8</v>
       </c>
-      <c r="AV26" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>44</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>48</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>30</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>75</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BG26" t="n">
-        <v>42</v>
-      </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-07 06:34:22</t>
+          <t>2026-05-07 08:55:50</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5598,37 +5598,37 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Nottm Forest</t>
+          <t>Shakhtar</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="G27" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="H27" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="I27" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="J27" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="K27" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="L27" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M27" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N27" t="n">
         <v>4.1</v>
@@ -5640,144 +5640,144 @@
         <v>2.04</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="R27" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S27" t="n">
         <v>3.35</v>
       </c>
       <c r="T27" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="U27" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="V27" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="W27" t="n">
-        <v>2.24</v>
+        <v>2.44</v>
       </c>
       <c r="X27" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>180</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP27" t="n">
         <v>15</v>
       </c>
-      <c r="Y27" t="n">
-        <v>18</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>38</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB27" t="n">
+      <c r="AQ27" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>40</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>95</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU27" t="n">
         <v>9</v>
       </c>
-      <c r="AC27" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG27" t="n">
+      <c r="AV27" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>70</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY27" t="n">
         <v>9.6</v>
       </c>
-      <c r="AH27" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI27" t="n">
+      <c r="AZ27" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA27" t="n">
         <v>65</v>
       </c>
-      <c r="AJ27" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>95</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>75</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>17</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>36</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>100</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>50</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>55</v>
-      </c>
       <c r="BB27" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="BC27" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BD27" t="n">
         <v>32</v>
       </c>
       <c r="BE27" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="BF27" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="BG27" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-07 06:34:22</t>
+          <t>2026-05-07 08:55:50</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5792,186 +5792,186 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.78</v>
+        <v>2.02</v>
       </c>
       <c r="G28" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="I28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T28" t="n">
         <v>1.79</v>
       </c>
-      <c r="H28" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="I28" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J28" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K28" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="L28" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M28" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N28" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="O28" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="P28" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S28" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T28" t="n">
+      <c r="U28" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W28" t="n">
         <v>1.96</v>
       </c>
-      <c r="U28" t="n">
-        <v>2</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W28" t="n">
-        <v>2.26</v>
-      </c>
       <c r="X28" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN28" t="n">
         <v>14</v>
       </c>
-      <c r="Y28" t="n">
-        <v>17</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>140</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE28" t="n">
+      <c r="AO28" t="n">
+        <v>50</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>26</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>65</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>42</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE28" t="n">
         <v>75</v>
       </c>
-      <c r="AF28" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>12</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>100</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>16</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>38</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>120</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>65</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>75</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>100</v>
-      </c>
       <c r="BF28" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BG28" t="n">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-07 06:34:22</t>
+          <t>2026-05-07 08:55:50</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Moroccan Botola Pro 1</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,191 +5981,191 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Nottm Forest</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.42</v>
+        <v>1.79</v>
       </c>
       <c r="G29" t="n">
-        <v>1.47</v>
+        <v>1.8</v>
       </c>
       <c r="H29" t="n">
+        <v>5</v>
+      </c>
+      <c r="I29" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J29" t="n">
+        <v>4</v>
+      </c>
+      <c r="K29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W29" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="X29" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF29" t="n">
         <v>10.5</v>
       </c>
-      <c r="I29" t="n">
-        <v>13</v>
-      </c>
-      <c r="J29" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="K29" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="L29" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="M29" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N29" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O29" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="P29" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S29" t="n">
-        <v>4</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W29" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="X29" t="n">
+      <c r="AG29" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>36</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>95</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>50</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>55</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE29" t="n">
         <v>90</v>
       </c>
-      <c r="Y29" t="n">
-        <v>950</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>130</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>21</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>20</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>970</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>15</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AQ29" t="n">
+      <c r="BF29" t="n">
         <v>10.5</v>
       </c>
-      <c r="AR29" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>10</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>8</v>
-      </c>
       <c r="BG29" t="n">
-        <v>9</v>
+        <v>70</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-07 06:34:22</t>
+          <t>2026-05-07 08:55:50</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6175,191 +6175,191 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>CA Platense</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Penarol</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.34</v>
+        <v>1.78</v>
       </c>
       <c r="G30" t="n">
-        <v>2.42</v>
+        <v>1.79</v>
       </c>
       <c r="H30" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="I30" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K30" t="n">
+        <v>4</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N30" t="n">
         <v>3.8</v>
       </c>
-      <c r="I30" t="n">
-        <v>4</v>
-      </c>
-      <c r="J30" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="K30" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L30" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="M30" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="N30" t="n">
-        <v>2.48</v>
-      </c>
       <c r="O30" t="n">
-        <v>1.63</v>
+        <v>1.34</v>
       </c>
       <c r="P30" t="n">
-        <v>1.47</v>
+        <v>1.93</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.96</v>
+        <v>2.04</v>
       </c>
       <c r="R30" t="n">
-        <v>1.17</v>
+        <v>1.35</v>
       </c>
       <c r="S30" t="n">
-        <v>6.6</v>
+        <v>3.75</v>
       </c>
       <c r="T30" t="n">
-        <v>2.24</v>
+        <v>1.96</v>
       </c>
       <c r="U30" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="V30" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="W30" t="n">
-        <v>1.71</v>
+        <v>2.26</v>
       </c>
       <c r="X30" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>140</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>38</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>120</v>
+      </c>
+      <c r="AT30" t="n">
         <v>7.8</v>
       </c>
-      <c r="Y30" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>48</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD30" t="n">
+      <c r="AU30" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>70</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>80</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>100</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>11</v>
+      </c>
+      <c r="BG30" t="n">
         <v>90</v>
       </c>
-      <c r="AE30" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>75</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>48</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>500</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>7</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>11</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>22</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>32</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>30</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>30</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>34</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>10</v>
-      </c>
-      <c r="BG30" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-05-07 06:34:22</t>
+          <t>2026-05-07 08:55:50</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6369,36 +6369,36 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>LDU</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="G31" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="H31" t="n">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="I31" t="n">
-        <v>7.8</v>
+        <v>12</v>
       </c>
       <c r="J31" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="K31" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="L31" t="n">
         <v>1.46</v>
@@ -6407,146 +6407,146 @@
         <v>1.08</v>
       </c>
       <c r="N31" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="O31" t="n">
         <v>1.38</v>
       </c>
       <c r="P31" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R31" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T31" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="U31" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="V31" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="W31" t="n">
-        <v>2.66</v>
+        <v>3.1</v>
       </c>
       <c r="X31" t="n">
-        <v>13</v>
+        <v>90</v>
       </c>
       <c r="Y31" t="n">
-        <v>20</v>
+        <v>950</v>
       </c>
       <c r="Z31" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="AA31" t="n">
-        <v>290</v>
+        <v>1000</v>
       </c>
       <c r="AB31" t="n">
         <v>6.8</v>
       </c>
       <c r="AC31" t="n">
+        <v>19</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR31" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AD31" t="n">
-        <v>29</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>140</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AG31" t="n">
+      <c r="AS31" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AH31" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>700</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>15</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>200</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>48</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>16.5</v>
-      </c>
       <c r="AT31" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AX31" t="n">
         <v>6.2</v>
       </c>
-      <c r="AU31" t="n">
+      <c r="AY31" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ31" t="n">
         <v>8.6</v>
       </c>
-      <c r="AV31" t="n">
-        <v>26</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>25</v>
-      </c>
       <c r="BA31" t="n">
-        <v>120</v>
+        <v>6.6</v>
       </c>
       <c r="BB31" t="n">
-        <v>13.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC31" t="n">
-        <v>16.5</v>
+        <v>10</v>
       </c>
       <c r="BD31" t="n">
-        <v>38</v>
+        <v>8.4</v>
       </c>
       <c r="BE31" t="n">
-        <v>20</v>
+        <v>9.6</v>
       </c>
       <c r="BF31" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="BG31" t="n">
-        <v>16</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-05-07 06:34:22</t>
+          <t>2026-05-07 08:55:50</t>
         </is>
       </c>
     </row>
@@ -6563,184 +6563,184 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>CA Platense</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Universitario de Deportes</t>
+          <t>Penarol</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="G32" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="H32" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="I32" t="n">
         <v>3.95</v>
       </c>
       <c r="J32" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K32" t="n">
         <v>3.15</v>
       </c>
-      <c r="K32" t="n">
-        <v>3.3</v>
-      </c>
       <c r="L32" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="M32" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="N32" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="O32" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="P32" t="n">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.62</v>
+        <v>2.84</v>
       </c>
       <c r="R32" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="S32" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="T32" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="U32" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="V32" t="n">
         <v>1.33</v>
       </c>
       <c r="W32" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="X32" t="n">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="Y32" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z32" t="n">
-        <v>26</v>
+        <v>120</v>
       </c>
       <c r="AA32" t="n">
-        <v>95</v>
+        <v>900</v>
       </c>
       <c r="AB32" t="n">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="AC32" t="n">
         <v>7.4</v>
       </c>
       <c r="AD32" t="n">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="AE32" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AF32" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG32" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>190</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>48</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>600</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS32" t="n">
         <v>12</v>
       </c>
-      <c r="AH32" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>34</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>85</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>8</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>8</v>
-      </c>
       <c r="AT32" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AU32" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV32" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW32" t="n">
-        <v>7.6</v>
+        <v>44</v>
       </c>
       <c r="AX32" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AY32" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>30</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>30</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>28</v>
+      </c>
+      <c r="BF32" t="n">
         <v>10</v>
       </c>
-      <c r="AZ32" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>26</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>12</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF32" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BG32" t="n">
-        <v>7.8</v>
+        <v>11.5</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-05-07 06:34:22</t>
+          <t>2026-05-07 08:55:50</t>
         </is>
       </c>
     </row>
@@ -6757,184 +6757,184 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Ind Medellin</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>LDU</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>5.3</v>
+        <v>1.55</v>
       </c>
       <c r="G33" t="n">
-        <v>5.8</v>
+        <v>1.56</v>
       </c>
       <c r="H33" t="n">
-        <v>1.8</v>
+        <v>7.4</v>
       </c>
       <c r="I33" t="n">
-        <v>1.85</v>
+        <v>7.8</v>
       </c>
       <c r="J33" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="K33" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="L33" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="M33" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N33" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="O33" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="P33" t="n">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="R33" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="S33" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="T33" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="U33" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="V33" t="n">
-        <v>2.16</v>
+        <v>1.14</v>
       </c>
       <c r="W33" t="n">
-        <v>1.21</v>
+        <v>2.74</v>
       </c>
       <c r="X33" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y33" t="n">
-        <v>7.4</v>
+        <v>20</v>
       </c>
       <c r="Z33" t="n">
-        <v>10.5</v>
+        <v>65</v>
       </c>
       <c r="AA33" t="n">
+        <v>330</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>150</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>700</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>240</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>55</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>27</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>25</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>120</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE33" t="n">
         <v>20</v>
       </c>
-      <c r="AB33" t="n">
-        <v>16</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD33" t="n">
+      <c r="BF33" t="n">
         <v>11</v>
       </c>
-      <c r="AE33" t="n">
-        <v>23</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>46</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>23</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>190</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>110</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>95</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>140</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>16</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>17</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>34</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>9</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BF33" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BG33" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-05-07 06:34:22</t>
+          <t>2026-05-07 08:55:50</t>
         </is>
       </c>
     </row>
@@ -6951,184 +6951,572 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Coquimbo Unido</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Universitario de Deportes</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="H34" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I34" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="J34" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N34" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="X34" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>80</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>28</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>26</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>26</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BH34" t="inlineStr">
+        <is>
+          <t>2026-05-07 08:55:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Ind Medellin</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="G35" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="J35" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N35" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S35" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="V35" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X35" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>42</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>160</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>95</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>130</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>17</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>36</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>15</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>15</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BH35" t="inlineStr">
+        <is>
+          <t>2026-05-07 08:55:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
           <t>23:00:00</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>Junior FC Barranquilla</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>Cerro Porteno</t>
         </is>
       </c>
-      <c r="F34" t="n">
+      <c r="F36" t="n">
         <v>2.08</v>
       </c>
-      <c r="G34" t="n">
+      <c r="G36" t="n">
         <v>2.16</v>
       </c>
-      <c r="H34" t="n">
+      <c r="H36" t="n">
         <v>4.1</v>
       </c>
-      <c r="I34" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J34" t="n">
+      <c r="I36" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J36" t="n">
         <v>3.25</v>
       </c>
-      <c r="K34" t="n">
+      <c r="K36" t="n">
         <v>3.5</v>
       </c>
-      <c r="L34" t="n">
+      <c r="L36" t="n">
         <v>1.54</v>
       </c>
-      <c r="M34" t="n">
+      <c r="M36" t="n">
         <v>1.11</v>
       </c>
-      <c r="N34" t="n">
+      <c r="N36" t="n">
         <v>2.88</v>
       </c>
-      <c r="O34" t="n">
+      <c r="O36" t="n">
         <v>1.49</v>
       </c>
-      <c r="P34" t="n">
+      <c r="P36" t="n">
         <v>1.61</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="Q36" t="n">
         <v>2.54</v>
       </c>
-      <c r="R34" t="n">
+      <c r="R36" t="n">
         <v>1.21</v>
       </c>
-      <c r="S34" t="n">
+      <c r="S36" t="n">
         <v>5.2</v>
       </c>
-      <c r="T34" t="n">
+      <c r="T36" t="n">
         <v>1.11</v>
       </c>
-      <c r="U34" t="n">
+      <c r="U36" t="n">
         <v>1.11</v>
       </c>
-      <c r="V34" t="n">
+      <c r="V36" t="n">
         <v>1.29</v>
       </c>
-      <c r="W34" t="n">
+      <c r="W36" t="n">
         <v>1.86</v>
       </c>
-      <c r="X34" t="n">
+      <c r="X36" t="n">
         <v>1000</v>
       </c>
-      <c r="Y34" t="n">
+      <c r="Y36" t="n">
         <v>1000</v>
       </c>
-      <c r="Z34" t="n">
+      <c r="Z36" t="n">
         <v>1000</v>
       </c>
-      <c r="AA34" t="n">
+      <c r="AA36" t="n">
         <v>1000</v>
       </c>
-      <c r="AB34" t="n">
+      <c r="AB36" t="n">
         <v>1000</v>
       </c>
-      <c r="AC34" t="n">
+      <c r="AC36" t="n">
         <v>1000</v>
       </c>
-      <c r="AD34" t="n">
+      <c r="AD36" t="n">
         <v>1000</v>
       </c>
-      <c r="AE34" t="n">
+      <c r="AE36" t="n">
         <v>1000</v>
       </c>
-      <c r="AF34" t="n">
+      <c r="AF36" t="n">
         <v>1000</v>
       </c>
-      <c r="AG34" t="n">
+      <c r="AG36" t="n">
         <v>1000</v>
       </c>
-      <c r="AH34" t="n">
+      <c r="AH36" t="n">
         <v>1000</v>
       </c>
-      <c r="AI34" t="n">
+      <c r="AI36" t="n">
         <v>1000</v>
       </c>
-      <c r="AJ34" t="n">
+      <c r="AJ36" t="n">
         <v>1000</v>
       </c>
-      <c r="AK34" t="n">
+      <c r="AK36" t="n">
         <v>1000</v>
       </c>
-      <c r="AL34" t="n">
+      <c r="AL36" t="n">
         <v>1000</v>
       </c>
-      <c r="AM34" t="n">
+      <c r="AM36" t="n">
         <v>1000</v>
       </c>
-      <c r="AN34" t="n">
+      <c r="AN36" t="n">
         <v>1000</v>
       </c>
-      <c r="AO34" t="n">
+      <c r="AO36" t="n">
         <v>1000</v>
       </c>
-      <c r="AP34" t="n">
+      <c r="AP36" t="n">
         <v>1.01</v>
       </c>
-      <c r="AQ34" t="n">
+      <c r="AQ36" t="n">
         <v>1.01</v>
       </c>
-      <c r="AR34" t="n">
+      <c r="AR36" t="n">
         <v>1.01</v>
       </c>
-      <c r="AS34" t="n">
+      <c r="AS36" t="n">
         <v>1.01</v>
       </c>
-      <c r="AT34" t="n">
+      <c r="AT36" t="n">
         <v>1.01</v>
       </c>
-      <c r="AU34" t="n">
+      <c r="AU36" t="n">
         <v>1.01</v>
       </c>
-      <c r="AV34" t="n">
+      <c r="AV36" t="n">
         <v>1.01</v>
       </c>
-      <c r="AW34" t="n">
+      <c r="AW36" t="n">
         <v>1.01</v>
       </c>
-      <c r="AX34" t="n">
+      <c r="AX36" t="n">
         <v>1.01</v>
       </c>
-      <c r="AY34" t="n">
+      <c r="AY36" t="n">
         <v>1.01</v>
       </c>
-      <c r="AZ34" t="n">
+      <c r="AZ36" t="n">
         <v>1.01</v>
       </c>
-      <c r="BA34" t="n">
+      <c r="BA36" t="n">
         <v>1.01</v>
       </c>
-      <c r="BB34" t="n">
+      <c r="BB36" t="n">
         <v>1.01</v>
       </c>
-      <c r="BC34" t="n">
+      <c r="BC36" t="n">
         <v>1.01</v>
       </c>
-      <c r="BD34" t="n">
+      <c r="BD36" t="n">
         <v>1.01</v>
       </c>
-      <c r="BE34" t="n">
+      <c r="BE36" t="n">
         <v>1.01</v>
       </c>
-      <c r="BF34" t="n">
+      <c r="BF36" t="n">
         <v>1.01</v>
       </c>
-      <c r="BG34" t="n">
+      <c r="BG36" t="n">
         <v>1.01</v>
       </c>
-      <c r="BH34" t="inlineStr">
-        <is>
-          <t>2026-05-07 06:34:22</t>
+      <c r="BH36" t="inlineStr">
+        <is>
+          <t>2026-05-07 08:55:50</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-07.xlsx
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="G2" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="H2" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="I2" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="J2" t="n">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="K2" t="n">
-        <v>2.78</v>
+        <v>2.58</v>
       </c>
       <c r="L2" t="n">
-        <v>1.76</v>
+        <v>1.97</v>
       </c>
       <c r="M2" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="N2" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="O2" t="n">
-        <v>1.78</v>
+        <v>2.04</v>
       </c>
       <c r="P2" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.55</v>
+        <v>4.6</v>
       </c>
       <c r="R2" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="T2" t="n">
-        <v>1.78</v>
+        <v>2.84</v>
       </c>
       <c r="U2" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="V2" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W2" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="X2" t="n">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="Z2" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
         <v>6</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>24</v>
+        <v>990</v>
       </c>
       <c r="AE2" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG2" t="n">
-        <v>13.5</v>
+        <v>990</v>
       </c>
       <c r="AH2" t="n">
-        <v>38</v>
+        <v>990</v>
       </c>
       <c r="AI2" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>450</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.4</v>
+        <v>4.3</v>
       </c>
       <c r="AQ2" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AR2" t="n">
-        <v>12.5</v>
+        <v>3.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.6</v>
+        <v>3.5</v>
       </c>
       <c r="AT2" t="n">
         <v>4.8</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.4</v>
+        <v>5.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>13</v>
+        <v>3.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>17</v>
+        <v>3.5</v>
       </c>
       <c r="AX2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY2" t="n">
         <v>10</v>
       </c>
-      <c r="AY2" t="n">
-        <v>7.6</v>
-      </c>
       <c r="AZ2" t="n">
-        <v>16.5</v>
+        <v>3.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.2</v>
+        <v>40</v>
       </c>
       <c r="BB2" t="n">
-        <v>23</v>
+        <v>3.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>9</v>
+        <v>3.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="BE2" t="n">
-        <v>110</v>
+        <v>46</v>
       </c>
       <c r="BF2" t="n">
-        <v>9</v>
+        <v>3.95</v>
       </c>
       <c r="BG2" t="n">
-        <v>9.800000000000001</v>
+        <v>3.95</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-07 08:55:50</t>
+          <t>2026-05-07 11:21:53</t>
         </is>
       </c>
     </row>
@@ -951,170 +951,170 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.7</v>
+        <v>4.1</v>
       </c>
       <c r="G3" t="n">
-        <v>2.9</v>
+        <v>4.4</v>
       </c>
       <c r="H3" t="n">
-        <v>2.64</v>
+        <v>1.97</v>
       </c>
       <c r="I3" t="n">
-        <v>2.78</v>
+        <v>2.06</v>
       </c>
       <c r="J3" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K3" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="L3" t="n">
-        <v>1.37</v>
+        <v>1.54</v>
       </c>
       <c r="M3" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="O3" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="P3" t="n">
-        <v>2.08</v>
+        <v>1.91</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.81</v>
+        <v>2.04</v>
       </c>
       <c r="R3" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="S3" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="T3" t="n">
-        <v>1.65</v>
+        <v>1.89</v>
       </c>
       <c r="U3" t="n">
-        <v>2.24</v>
+        <v>1.96</v>
       </c>
       <c r="V3" t="n">
-        <v>1.56</v>
+        <v>2.1</v>
       </c>
       <c r="W3" t="n">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="X3" t="n">
-        <v>25</v>
+        <v>15.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>970</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z3" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AA3" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>14</v>
+        <v>990</v>
       </c>
       <c r="AD3" t="n">
-        <v>970</v>
+        <v>990</v>
       </c>
       <c r="AE3" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>500</v>
+        <v>990</v>
       </c>
       <c r="AH3" t="n">
-        <v>60</v>
+        <v>990</v>
       </c>
       <c r="AI3" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>340</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>6.6</v>
+        <v>10.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>14</v>
+        <v>1.62</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.4</v>
+        <v>1.92</v>
       </c>
       <c r="AT3" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AU3" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="AV3" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AW3" t="n">
-        <v>13</v>
+        <v>1.92</v>
       </c>
       <c r="AX3" t="n">
-        <v>9.6</v>
+        <v>1.92</v>
       </c>
       <c r="AY3" t="n">
-        <v>7.6</v>
+        <v>1.92</v>
       </c>
       <c r="AZ3" t="n">
-        <v>11</v>
+        <v>1.92</v>
       </c>
       <c r="BA3" t="n">
-        <v>8.6</v>
+        <v>1.92</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.800000000000001</v>
+        <v>1.92</v>
       </c>
       <c r="BC3" t="n">
-        <v>8.6</v>
+        <v>1.92</v>
       </c>
       <c r="BD3" t="n">
-        <v>8.6</v>
+        <v>1.92</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.5</v>
+        <v>1.92</v>
       </c>
       <c r="BF3" t="n">
-        <v>16</v>
+        <v>1.92</v>
       </c>
       <c r="BG3" t="n">
-        <v>7.2</v>
+        <v>1.92</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-07 08:55:50</t>
+          <t>2026-05-07 11:21:53</t>
         </is>
       </c>
     </row>
@@ -1145,142 +1145,142 @@
         </is>
       </c>
       <c r="F4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K4" t="n">
         <v>3.25</v>
       </c>
-      <c r="G4" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3.5</v>
-      </c>
       <c r="L4" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="M4" t="n">
         <v>1.1</v>
       </c>
       <c r="N4" t="n">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="O4" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="P4" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="R4" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="S4" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="T4" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U4" t="n">
         <v>2</v>
       </c>
-      <c r="U4" t="n">
-        <v>1.85</v>
-      </c>
       <c r="V4" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="W4" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="X4" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="Z4" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AB4" t="n">
         <v>10.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD4" t="n">
         <v>12.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="AF4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>50</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS4" t="n">
         <v>34</v>
       </c>
-      <c r="AG4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>80</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>120</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>170</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>600</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>18.5</v>
-      </c>
       <c r="AT4" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW4" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="AX4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY4" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AZ4" t="n">
         <v>18.5</v>
@@ -1289,26 +1289,26 @@
         <v>30</v>
       </c>
       <c r="BB4" t="n">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="BD4" t="n">
         <v>32</v>
       </c>
       <c r="BE4" t="n">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="BF4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BG4" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-07 08:55:50</t>
+          <t>2026-05-07 11:21:53</t>
         </is>
       </c>
     </row>
@@ -1339,170 +1339,170 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>13</v>
+        <v>17.5</v>
       </c>
       <c r="G5" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H5" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="I5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="K5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="O5" t="n">
         <v>1.35</v>
       </c>
-      <c r="J5" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.4</v>
-      </c>
       <c r="P5" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="R5" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="S5" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="T5" t="n">
-        <v>2.64</v>
+        <v>2.76</v>
       </c>
       <c r="U5" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="V5" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="W5" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X5" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AB5" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AC5" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AD5" t="n">
         <v>12.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AF5" t="n">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="AG5" t="n">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="AH5" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
         <v>240</v>
       </c>
       <c r="AJ5" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>490</v>
+        <v>590</v>
       </c>
       <c r="AL5" t="n">
-        <v>390</v>
+        <v>710</v>
       </c>
       <c r="AM5" t="n">
-        <v>790</v>
+        <v>680</v>
       </c>
       <c r="AN5" t="n">
-        <v>930</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="AP5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>36</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AV5" t="n">
         <v>11</v>
       </c>
-      <c r="AQ5" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AR5" t="n">
+      <c r="AW5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>65</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>50</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>65</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>16</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BG5" t="n">
         <v>5.7</v>
       </c>
-      <c r="AS5" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>29</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>50</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>50</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>44</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>60</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>12</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>12</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-07 08:55:50</t>
+          <t>2026-05-07 11:21:53</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="G6" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="H6" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I6" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="J6" t="n">
         <v>4.1</v>
       </c>
       <c r="K6" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L6" t="n">
         <v>1.37</v>
@@ -1557,49 +1557,49 @@
         <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O6" t="n">
         <v>1.27</v>
       </c>
       <c r="P6" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q6" t="n">
         <v>1.82</v>
       </c>
       <c r="R6" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="S6" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T6" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="U6" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="V6" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W6" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="X6" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="Y6" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="Z6" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="AA6" t="n">
         <v>160</v>
       </c>
       <c r="AB6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC6" t="n">
         <v>9.800000000000001</v>
@@ -1617,16 +1617,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AH6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI6" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ6" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AK6" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL6" t="n">
         <v>34</v>
@@ -1635,16 +1635,16 @@
         <v>110</v>
       </c>
       <c r="AN6" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO6" t="n">
         <v>85</v>
       </c>
       <c r="AP6" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AQ6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AR6" t="n">
         <v>27</v>
@@ -1653,50 +1653,50 @@
         <v>12.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU6" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV6" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AW6" t="n">
         <v>40</v>
       </c>
       <c r="AX6" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY6" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ6" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA6" t="n">
         <v>38</v>
       </c>
       <c r="BB6" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BC6" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BD6" t="n">
         <v>29</v>
       </c>
       <c r="BE6" t="n">
-        <v>13.5</v>
+        <v>75</v>
       </c>
       <c r="BF6" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BG6" t="n">
         <v>13.5</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-07 08:55:50</t>
+          <t>2026-05-07 11:21:53</t>
         </is>
       </c>
     </row>
@@ -1727,170 +1727,170 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="G7" t="n">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="H7" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="I7" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="J7" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="K7" t="n">
         <v>3.85</v>
       </c>
       <c r="L7" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M7" t="n">
         <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="O7" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="R7" t="n">
         <v>1.35</v>
       </c>
-      <c r="P7" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.32</v>
-      </c>
       <c r="S7" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="T7" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U7" t="n">
         <v>2.04</v>
       </c>
       <c r="V7" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W7" t="n">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="X7" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Y7" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AA7" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AC7" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AD7" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AE7" t="n">
-        <v>190</v>
+        <v>90</v>
       </c>
       <c r="AF7" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AG7" t="n">
         <v>11</v>
       </c>
       <c r="AH7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI7" t="n">
         <v>160</v>
       </c>
       <c r="AJ7" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AK7" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AL7" t="n">
         <v>40</v>
       </c>
       <c r="AM7" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN7" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AO7" t="n">
-        <v>270</v>
+        <v>310</v>
       </c>
       <c r="AP7" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="AS7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU7" t="n">
         <v>7.6</v>
       </c>
-      <c r="AT7" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>7.2</v>
-      </c>
       <c r="AV7" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BB7" t="n">
         <v>15</v>
       </c>
-      <c r="AW7" t="n">
+      <c r="BC7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>85</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG7" t="n">
         <v>7.8</v>
       </c>
-      <c r="AX7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>18</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>29</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>15</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-07 08:55:50</t>
+          <t>2026-05-07 11:21:53</t>
         </is>
       </c>
     </row>
@@ -1921,58 +1921,58 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="G8" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="I8" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J8" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="K8" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="L8" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M8" t="n">
         <v>1.07</v>
       </c>
       <c r="N8" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="O8" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="P8" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.94</v>
+        <v>2.12</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S8" t="n">
         <v>3.3</v>
       </c>
       <c r="T8" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="U8" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="V8" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W8" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="X8" t="n">
         <v>19</v>
@@ -1987,13 +1987,13 @@
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>970</v>
+        <v>5.3</v>
       </c>
       <c r="AC8" t="n">
         <v>970</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE8" t="n">
         <v>1000</v>
@@ -2029,10 +2029,10 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.58</v>
+        <v>3.05</v>
       </c>
       <c r="AQ8" t="n">
-        <v>8</v>
+        <v>4.2</v>
       </c>
       <c r="AR8" t="n">
         <v>4.2</v>
@@ -2041,10 +2041,10 @@
         <v>4.2</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.65</v>
+        <v>3</v>
       </c>
       <c r="AV8" t="n">
         <v>4.2</v>
@@ -2056,35 +2056,35 @@
         <v>3.7</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.71</v>
+        <v>5.3</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.65</v>
+        <v>2.72</v>
       </c>
       <c r="BA8" t="n">
         <v>4.2</v>
       </c>
       <c r="BB8" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.7</v>
+        <v>6.6</v>
       </c>
       <c r="BD8" t="n">
-        <v>2.86</v>
+        <v>5.2</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.72</v>
+        <v>150</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.93</v>
+        <v>4.3</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.2</v>
+        <v>8.6</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-07 08:55:50</t>
+          <t>2026-05-07 11:21:53</t>
         </is>
       </c>
     </row>
@@ -2115,64 +2115,64 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.06</v>
+        <v>1.8</v>
       </c>
       <c r="G9" t="n">
-        <v>2.22</v>
+        <v>1.87</v>
       </c>
       <c r="H9" t="n">
-        <v>3.8</v>
+        <v>4.9</v>
       </c>
       <c r="I9" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="J9" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="K9" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="L9" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="M9" t="n">
         <v>1.09</v>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="O9" t="n">
         <v>1.43</v>
       </c>
       <c r="P9" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="R9" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S9" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="T9" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="U9" t="n">
-        <v>1.86</v>
+        <v>1.76</v>
       </c>
       <c r="V9" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="W9" t="n">
-        <v>1.83</v>
+        <v>2.14</v>
       </c>
       <c r="X9" t="n">
         <v>17.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="Z9" t="n">
         <v>500</v>
@@ -2181,25 +2181,25 @@
         <v>900</v>
       </c>
       <c r="AB9" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AC9" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AE9" t="n">
         <v>500</v>
       </c>
       <c r="AF9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH9" t="n">
         <v>500</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>950</v>
       </c>
       <c r="AI9" t="n">
         <v>500</v>
@@ -2208,7 +2208,7 @@
         <v>900</v>
       </c>
       <c r="AK9" t="n">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AL9" t="n">
         <v>500</v>
@@ -2217,68 +2217,68 @@
         <v>580</v>
       </c>
       <c r="AN9" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AO9" t="n">
         <v>600</v>
       </c>
       <c r="AP9" t="n">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>6.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR9" t="n">
-        <v>9.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>10</v>
+        <v>4.9</v>
       </c>
       <c r="AT9" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX9" t="n">
         <v>6.2</v>
       </c>
-      <c r="AU9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>7</v>
-      </c>
       <c r="AY9" t="n">
-        <v>6.6</v>
+        <v>5.3</v>
       </c>
       <c r="AZ9" t="n">
-        <v>7.6</v>
+        <v>14.5</v>
       </c>
       <c r="BA9" t="n">
         <v>7.2</v>
       </c>
       <c r="BB9" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="BC9" t="n">
-        <v>7.8</v>
+        <v>15.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>9.199999999999999</v>
+        <v>25</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.5</v>
+        <v>110</v>
       </c>
       <c r="BF9" t="n">
-        <v>7.8</v>
+        <v>11.5</v>
       </c>
       <c r="BG9" t="n">
         <v>7.2</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-07 08:55:50</t>
+          <t>2026-05-07 11:21:53</t>
         </is>
       </c>
     </row>
@@ -2309,170 +2309,170 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.96</v>
+        <v>2.14</v>
       </c>
       <c r="G10" t="n">
-        <v>2.04</v>
+        <v>2.28</v>
       </c>
       <c r="H10" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="I10" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="J10" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="K10" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L10" t="n">
         <v>1.42</v>
       </c>
       <c r="M10" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N10" t="n">
         <v>3.8</v>
       </c>
       <c r="O10" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P10" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="R10" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V10" t="n">
         <v>1.37</v>
       </c>
-      <c r="S10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.29</v>
-      </c>
       <c r="W10" t="n">
-        <v>1.96</v>
+        <v>1.79</v>
       </c>
       <c r="X10" t="n">
         <v>15.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="AA10" t="n">
-        <v>900</v>
+        <v>130</v>
       </c>
       <c r="AB10" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD10" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AE10" t="n">
-        <v>55</v>
+        <v>210</v>
       </c>
       <c r="AF10" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH10" t="n">
         <v>21</v>
       </c>
       <c r="AI10" t="n">
-        <v>130</v>
+        <v>55</v>
       </c>
       <c r="AJ10" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK10" t="n">
         <v>25</v>
       </c>
-      <c r="AK10" t="n">
-        <v>22</v>
-      </c>
       <c r="AL10" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM10" t="n">
-        <v>110</v>
+        <v>200</v>
       </c>
       <c r="AN10" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AO10" t="n">
-        <v>270</v>
+        <v>46</v>
       </c>
       <c r="AP10" t="n">
         <v>13</v>
       </c>
       <c r="AQ10" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AS10" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV10" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AX10" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AY10" t="n">
         <v>9</v>
       </c>
       <c r="AZ10" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>20</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB10" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BD10" t="n">
         <v>22</v>
       </c>
       <c r="BE10" t="n">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="BF10" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>9.4</v>
+        <v>17</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-07 08:55:50</t>
+          <t>2026-05-07 11:21:53</t>
         </is>
       </c>
     </row>
@@ -2503,170 +2503,170 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="G11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I11" t="n">
+        <v>5</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q11" t="n">
         <v>1.72</v>
       </c>
-      <c r="H11" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="I11" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="J11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="T11" t="n">
         <v>1.67</v>
       </c>
-      <c r="R11" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.7</v>
-      </c>
       <c r="U11" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="V11" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="W11" t="n">
-        <v>2.36</v>
+        <v>2.1</v>
       </c>
       <c r="X11" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="Y11" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="Z11" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="AA11" t="n">
-        <v>140</v>
+        <v>900</v>
       </c>
       <c r="AB11" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AC11" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AD11" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="AE11" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AF11" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG11" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI11" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AJ11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK11" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AL11" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM11" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AN11" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AO11" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="AP11" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AR11" t="n">
-        <v>4.4</v>
+        <v>24</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT11" t="n">
         <v>9</v>
       </c>
       <c r="AU11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>25</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY11" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AV11" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>8.6</v>
-      </c>
       <c r="AZ11" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.5</v>
+        <v>25</v>
       </c>
       <c r="BB11" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="BC11" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.2</v>
+        <v>19.5</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.5</v>
+        <v>28</v>
       </c>
       <c r="BF11" t="n">
-        <v>3.15</v>
+        <v>8.4</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.5</v>
+        <v>21</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-07 08:55:50</t>
+          <t>2026-05-07 11:21:53</t>
         </is>
       </c>
     </row>
@@ -2697,46 +2697,46 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="G12" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="H12" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="I12" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="J12" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K12" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="L12" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="M12" t="n">
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="O12" t="n">
         <v>1.07</v>
       </c>
       <c r="P12" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="R12" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S12" t="n">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="T12" t="n">
         <v>1.11</v>
@@ -2745,10 +2745,10 @@
         <v>1.2</v>
       </c>
       <c r="V12" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="X12" t="n">
         <v>80</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-07 08:55:50</t>
+          <t>2026-05-07 11:21:53</t>
         </is>
       </c>
     </row>
@@ -2891,16 +2891,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="G13" t="n">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="H13" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="I13" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="J13" t="n">
         <v>3.7</v>
@@ -2915,146 +2915,146 @@
         <v>1.07</v>
       </c>
       <c r="N13" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O13" t="n">
         <v>1.32</v>
       </c>
       <c r="P13" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q13" t="n">
         <v>1.97</v>
       </c>
-      <c r="Q13" t="n">
-        <v>1.98</v>
-      </c>
       <c r="R13" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S13" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T13" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="U13" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="V13" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="W13" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="X13" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="Y13" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>100</v>
+        <v>34</v>
       </c>
       <c r="AA13" t="n">
-        <v>900</v>
+        <v>110</v>
       </c>
       <c r="AB13" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC13" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD13" t="n">
         <v>18</v>
       </c>
       <c r="AE13" t="n">
-        <v>400</v>
+        <v>60</v>
       </c>
       <c r="AF13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG13" t="n">
         <v>10.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>34</v>
+        <v>19.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>700</v>
+        <v>65</v>
       </c>
       <c r="AJ13" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="AK13" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="AL13" t="n">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="AM13" t="n">
-        <v>580</v>
+        <v>110</v>
       </c>
       <c r="AN13" t="n">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="AO13" t="n">
-        <v>700</v>
+        <v>65</v>
       </c>
       <c r="AP13" t="n">
-        <v>8.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="AQ13" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AR13" t="n">
-        <v>18.5</v>
+        <v>27</v>
       </c>
       <c r="AS13" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="AT13" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AU13" t="n">
         <v>7.6</v>
       </c>
       <c r="AV13" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>34</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>40</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>19</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE13" t="n">
         <v>14</v>
       </c>
-      <c r="AW13" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>34</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>9</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BF13" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BG13" t="n">
-        <v>9.800000000000001</v>
+        <v>26</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-07 08:55:50</t>
+          <t>2026-05-07 11:21:53</t>
         </is>
       </c>
     </row>
@@ -3085,103 +3085,103 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="G14" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H14" t="n">
-        <v>2.98</v>
+        <v>3.25</v>
       </c>
       <c r="I14" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="J14" t="n">
-        <v>2.82</v>
+        <v>2.64</v>
       </c>
       <c r="K14" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="L14" t="n">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="M14" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="N14" t="n">
-        <v>2.52</v>
+        <v>2.3</v>
       </c>
       <c r="O14" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="P14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W14" t="n">
         <v>1.47</v>
       </c>
-      <c r="Q14" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S14" t="n">
-        <v>6</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.46</v>
-      </c>
       <c r="X14" t="n">
-        <v>7.8</v>
+        <v>970</v>
       </c>
       <c r="Y14" t="n">
-        <v>8.4</v>
+        <v>970</v>
       </c>
       <c r="Z14" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AA14" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AB14" t="n">
-        <v>8.4</v>
+        <v>970</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.2</v>
+        <v>95</v>
       </c>
       <c r="AD14" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AE14" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="AF14" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AG14" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AH14" t="n">
-        <v>25</v>
+        <v>950</v>
       </c>
       <c r="AI14" t="n">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="AJ14" t="n">
-        <v>290</v>
+        <v>500</v>
       </c>
       <c r="AK14" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AL14" t="n">
-        <v>190</v>
+        <v>500</v>
       </c>
       <c r="AM14" t="n">
         <v>500</v>
@@ -3193,62 +3193,62 @@
         <v>600</v>
       </c>
       <c r="AP14" t="n">
-        <v>6.8</v>
+        <v>4.2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>7</v>
+        <v>3.7</v>
       </c>
       <c r="AR14" t="n">
-        <v>15.5</v>
+        <v>1.34</v>
       </c>
       <c r="AS14" t="n">
-        <v>44</v>
+        <v>1.34</v>
       </c>
       <c r="AT14" t="n">
-        <v>7.2</v>
+        <v>3.95</v>
       </c>
       <c r="AU14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AV14" t="n">
         <v>6.2</v>
       </c>
-      <c r="AV14" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AW14" t="n">
-        <v>38</v>
+        <v>1.34</v>
       </c>
       <c r="AX14" t="n">
-        <v>16.5</v>
+        <v>1.34</v>
       </c>
       <c r="AY14" t="n">
-        <v>12</v>
+        <v>6.6</v>
       </c>
       <c r="AZ14" t="n">
-        <v>15.5</v>
+        <v>1.33</v>
       </c>
       <c r="BA14" t="n">
-        <v>34</v>
+        <v>1.35</v>
       </c>
       <c r="BB14" t="n">
-        <v>46</v>
+        <v>1.35</v>
       </c>
       <c r="BC14" t="n">
-        <v>38</v>
+        <v>1.34</v>
       </c>
       <c r="BD14" t="n">
-        <v>48</v>
+        <v>1.35</v>
       </c>
       <c r="BE14" t="n">
-        <v>10.5</v>
+        <v>1.36</v>
       </c>
       <c r="BF14" t="n">
-        <v>25</v>
+        <v>1.55</v>
       </c>
       <c r="BG14" t="n">
-        <v>10</v>
+        <v>1.55</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-07 08:55:50</t>
+          <t>2026-05-07 11:21:53</t>
         </is>
       </c>
     </row>
@@ -3279,25 +3279,25 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="G15" t="n">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="H15" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="I15" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="J15" t="n">
         <v>4.5</v>
       </c>
       <c r="K15" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L15" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M15" t="n">
         <v>1.04</v>
@@ -3309,140 +3309,140 @@
         <v>1.21</v>
       </c>
       <c r="P15" t="n">
-        <v>2.52</v>
+        <v>2.44</v>
       </c>
       <c r="Q15" t="n">
         <v>1.65</v>
       </c>
       <c r="R15" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S15" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W15" t="n">
         <v>2.68</v>
       </c>
-      <c r="T15" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="W15" t="n">
-        <v>2.52</v>
-      </c>
       <c r="X15" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="Y15" t="n">
-        <v>500</v>
+        <v>28</v>
       </c>
       <c r="Z15" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="AA15" t="n">
-        <v>900</v>
+        <v>180</v>
       </c>
       <c r="AB15" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC15" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD15" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE15" t="n">
-        <v>320</v>
+        <v>80</v>
       </c>
       <c r="AF15" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="AG15" t="n">
         <v>10</v>
       </c>
       <c r="AH15" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AI15" t="n">
-        <v>250</v>
+        <v>75</v>
       </c>
       <c r="AJ15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AL15" t="n">
         <v>28</v>
       </c>
-      <c r="AK15" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>75</v>
-      </c>
       <c r="AM15" t="n">
-        <v>580</v>
+        <v>140</v>
       </c>
       <c r="AN15" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AO15" t="n">
-        <v>700</v>
+        <v>70</v>
       </c>
       <c r="AP15" t="n">
         <v>20</v>
       </c>
       <c r="AQ15" t="n">
-        <v>11.5</v>
+        <v>23</v>
       </c>
       <c r="AR15" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="AS15" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="AT15" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AU15" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AV15" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AW15" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="AX15" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AY15" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AZ15" t="n">
-        <v>11.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA15" t="n">
         <v>36</v>
       </c>
       <c r="BB15" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BD15" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="BE15" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="BF15" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="BG15" t="n">
-        <v>9.800000000000001</v>
+        <v>50</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-07 08:55:50</t>
+          <t>2026-05-07 11:21:53</t>
         </is>
       </c>
     </row>
@@ -3473,25 +3473,25 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="G16" t="n">
-        <v>5.9</v>
+        <v>4.8</v>
       </c>
       <c r="H16" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="I16" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="J16" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="K16" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="L16" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M16" t="n">
         <v>1.07</v>
@@ -3500,143 +3500,143 @@
         <v>3.6</v>
       </c>
       <c r="O16" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P16" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="Q16" t="n">
         <v>2.02</v>
       </c>
       <c r="R16" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S16" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="T16" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="U16" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="V16" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="X16" t="n">
-        <v>28</v>
+        <v>14.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="Z16" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="AA16" t="n">
-        <v>900</v>
+        <v>23</v>
       </c>
       <c r="AB16" t="n">
-        <v>950</v>
+        <v>17</v>
       </c>
       <c r="AC16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>42</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>130</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>80</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>80</v>
+      </c>
+      <c r="AO16" t="n">
         <v>14</v>
       </c>
-      <c r="AD16" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>500</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>950</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>700</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>700</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>700</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>29</v>
-      </c>
       <c r="AP16" t="n">
-        <v>6.8</v>
+        <v>12</v>
       </c>
       <c r="AQ16" t="n">
-        <v>4.5</v>
+        <v>7.8</v>
       </c>
       <c r="AR16" t="n">
-        <v>5.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS16" t="n">
-        <v>6.6</v>
+        <v>19</v>
       </c>
       <c r="AT16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AU16" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AU16" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AV16" t="n">
-        <v>5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW16" t="n">
-        <v>6.6</v>
+        <v>13</v>
       </c>
       <c r="AX16" t="n">
-        <v>8.199999999999999</v>
+        <v>16.5</v>
       </c>
       <c r="AY16" t="n">
-        <v>7</v>
+        <v>15.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>6.6</v>
+        <v>10.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>4.8</v>
+        <v>30</v>
       </c>
       <c r="BB16" t="n">
-        <v>9</v>
+        <v>16.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>8.800000000000001</v>
+        <v>23</v>
       </c>
       <c r="BD16" t="n">
-        <v>8.800000000000001</v>
+        <v>16.5</v>
       </c>
       <c r="BE16" t="n">
-        <v>4.2</v>
+        <v>21</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.84</v>
+        <v>15</v>
       </c>
       <c r="BG16" t="n">
-        <v>5.4</v>
+        <v>12</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-07 08:55:50</t>
+          <t>2026-05-07 11:21:53</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="G17" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="H17" t="n">
         <v>6.2</v>
       </c>
       <c r="I17" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J17" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K17" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="L17" t="n">
         <v>1.35</v>
@@ -3691,34 +3691,34 @@
         <v>1.05</v>
       </c>
       <c r="N17" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O17" t="n">
         <v>1.25</v>
       </c>
       <c r="P17" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="R17" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="S17" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="T17" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="U17" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="V17" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="W17" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="X17" t="n">
         <v>950</v>
@@ -3727,16 +3727,16 @@
         <v>950</v>
       </c>
       <c r="Z17" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AA17" t="n">
         <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AC17" t="n">
-        <v>950</v>
+        <v>42</v>
       </c>
       <c r="AD17" t="n">
         <v>950</v>
@@ -3745,10 +3745,10 @@
         <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>11</v>
+        <v>500</v>
       </c>
       <c r="AG17" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AH17" t="n">
         <v>950</v>
@@ -3757,80 +3757,80 @@
         <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>16</v>
+        <v>900</v>
       </c>
       <c r="AK17" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AL17" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AM17" t="n">
         <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>8.6</v>
+        <v>29</v>
       </c>
       <c r="AO17" t="n">
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>4.1</v>
+        <v>1.92</v>
       </c>
       <c r="AQ17" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AR17" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="AT17" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="AU17" t="n">
-        <v>3.65</v>
+        <v>2.92</v>
       </c>
       <c r="AV17" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AW17" t="n">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="AX17" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AY17" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="AZ17" t="n">
-        <v>4.3</v>
+        <v>1.82</v>
       </c>
       <c r="BA17" t="n">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="BB17" t="n">
-        <v>3.85</v>
+        <v>2.08</v>
       </c>
       <c r="BC17" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.5</v>
+        <v>2.2</v>
       </c>
       <c r="BE17" t="n">
-        <v>2.5</v>
+        <v>1.93</v>
       </c>
       <c r="BF17" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="BG17" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-07 08:55:50</t>
+          <t>2026-05-07 11:21:53</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="G18" t="n">
         <v>1.91</v>
@@ -3885,13 +3885,13 @@
         <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="O18" t="n">
         <v>1.24</v>
       </c>
       <c r="P18" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="Q18" t="n">
         <v>1.72</v>
@@ -3900,25 +3900,25 @@
         <v>1.49</v>
       </c>
       <c r="S18" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="T18" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U18" t="n">
         <v>2.18</v>
       </c>
       <c r="V18" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W18" t="n">
         <v>2.1</v>
       </c>
       <c r="X18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y18" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Z18" t="n">
         <v>36</v>
@@ -3930,7 +3930,7 @@
         <v>11.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD18" t="n">
         <v>19</v>
@@ -3963,31 +3963,31 @@
         <v>580</v>
       </c>
       <c r="AN18" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AO18" t="n">
         <v>48</v>
       </c>
       <c r="AP18" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AQ18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR18" t="n">
-        <v>21</v>
+        <v>7.8</v>
       </c>
       <c r="AS18" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AT18" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AU18" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV18" t="n">
-        <v>6.6</v>
+        <v>15.5</v>
       </c>
       <c r="AW18" t="n">
         <v>40</v>
@@ -3999,10 +3999,10 @@
         <v>9</v>
       </c>
       <c r="AZ18" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA18" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BB18" t="n">
         <v>16</v>
@@ -4014,17 +4014,17 @@
         <v>11</v>
       </c>
       <c r="BE18" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BF18" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BG18" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-07 08:55:50</t>
+          <t>2026-05-07 11:21:53</t>
         </is>
       </c>
     </row>
@@ -4055,70 +4055,70 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="G19" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="H19" t="n">
         <v>3.3</v>
       </c>
       <c r="I19" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="J19" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K19" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L19" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M19" t="n">
         <v>1.07</v>
       </c>
       <c r="N19" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O19" t="n">
         <v>1.33</v>
       </c>
       <c r="P19" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R19" t="n">
         <v>1.35</v>
       </c>
       <c r="S19" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="T19" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="U19" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V19" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W19" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="X19" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y19" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA19" t="n">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="AB19" t="n">
         <v>10.5</v>
@@ -4130,7 +4130,7 @@
         <v>15</v>
       </c>
       <c r="AE19" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="AF19" t="n">
         <v>15.5</v>
@@ -4145,7 +4145,7 @@
         <v>85</v>
       </c>
       <c r="AJ19" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AK19" t="n">
         <v>27</v>
@@ -4157,10 +4157,10 @@
         <v>150</v>
       </c>
       <c r="AN19" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AO19" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AP19" t="n">
         <v>12</v>
@@ -4169,13 +4169,13 @@
         <v>11</v>
       </c>
       <c r="AR19" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="AT19" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU19" t="n">
         <v>7.2</v>
@@ -4193,10 +4193,10 @@
         <v>10</v>
       </c>
       <c r="AZ19" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA19" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="BB19" t="n">
         <v>19.5</v>
@@ -4211,14 +4211,14 @@
         <v>10</v>
       </c>
       <c r="BF19" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BG19" t="n">
         <v>12</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-07 08:55:50</t>
+          <t>2026-05-07 11:21:53</t>
         </is>
       </c>
     </row>
@@ -4249,64 +4249,64 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="G20" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="H20" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="I20" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="J20" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K20" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="L20" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="M20" t="n">
         <v>1.05</v>
       </c>
       <c r="N20" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="O20" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="P20" t="n">
-        <v>2.16</v>
+        <v>2.34</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="R20" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="T20" t="n">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="U20" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="V20" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="W20" t="n">
         <v>2.28</v>
       </c>
       <c r="X20" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="Y20" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="Z20" t="n">
         <v>120</v>
@@ -4315,85 +4315,85 @@
         <v>900</v>
       </c>
       <c r="AB20" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD20" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="AE20" t="n">
-        <v>700</v>
+        <v>170</v>
       </c>
       <c r="AF20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG20" t="n">
         <v>9.6</v>
       </c>
       <c r="AH20" t="n">
-        <v>25</v>
+        <v>17.5</v>
       </c>
       <c r="AI20" t="n">
-        <v>700</v>
+        <v>55</v>
       </c>
       <c r="AJ20" t="n">
-        <v>29</v>
+        <v>18.5</v>
       </c>
       <c r="AK20" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="AL20" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AO20" t="n">
         <v>55</v>
       </c>
-      <c r="AM20" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>310</v>
-      </c>
       <c r="AP20" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AQ20" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AR20" t="n">
         <v>27</v>
       </c>
       <c r="AS20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB20" t="n">
         <v>16</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>18</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>14</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>14</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>14.5</v>
       </c>
       <c r="BC20" t="n">
         <v>15</v>
@@ -4402,17 +4402,17 @@
         <v>21</v>
       </c>
       <c r="BE20" t="n">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="BF20" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="BG20" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-07 08:55:50</t>
+          <t>2026-05-07 11:21:53</t>
         </is>
       </c>
     </row>
@@ -4443,37 +4443,37 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="G21" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="H21" t="n">
         <v>4.5</v>
       </c>
       <c r="I21" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J21" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K21" t="n">
         <v>3.3</v>
       </c>
-      <c r="K21" t="n">
-        <v>3.35</v>
-      </c>
       <c r="L21" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="M21" t="n">
         <v>1.13</v>
       </c>
       <c r="N21" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="O21" t="n">
         <v>1.57</v>
       </c>
       <c r="P21" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q21" t="n">
         <v>2.78</v>
@@ -4485,16 +4485,16 @@
         <v>5.9</v>
       </c>
       <c r="T21" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="U21" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V21" t="n">
         <v>1.27</v>
       </c>
       <c r="W21" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="X21" t="n">
         <v>8.199999999999999</v>
@@ -4503,7 +4503,7 @@
         <v>11.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AA21" t="n">
         <v>130</v>
@@ -4527,16 +4527,16 @@
         <v>11.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI21" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ21" t="n">
         <v>32</v>
       </c>
       <c r="AK21" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AL21" t="n">
         <v>65</v>
@@ -4545,22 +4545,22 @@
         <v>230</v>
       </c>
       <c r="AN21" t="n">
+        <v>29</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>140</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR21" t="n">
         <v>27</v>
       </c>
-      <c r="AO21" t="n">
-        <v>130</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>8</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>28</v>
-      </c>
       <c r="AS21" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AT21" t="n">
         <v>6</v>
@@ -4569,10 +4569,10 @@
         <v>7</v>
       </c>
       <c r="AV21" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AX21" t="n">
         <v>10</v>
@@ -4599,14 +4599,14 @@
         <v>46</v>
       </c>
       <c r="BF21" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="BG21" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-07 08:55:50</t>
+          <t>2026-05-07 11:21:53</t>
         </is>
       </c>
     </row>
@@ -4637,100 +4637,100 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="G22" t="n">
-        <v>1.94</v>
+        <v>1.71</v>
       </c>
       <c r="H22" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="I22" t="n">
-        <v>5.8</v>
+        <v>7.8</v>
       </c>
       <c r="J22" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="K22" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="L22" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="M22" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="N22" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="O22" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="P22" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="R22" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="T22" t="n">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="U22" t="n">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="V22" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="W22" t="n">
-        <v>2.06</v>
+        <v>2.42</v>
       </c>
       <c r="X22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Y22" t="n">
-        <v>14.5</v>
+        <v>21</v>
       </c>
       <c r="Z22" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="AA22" t="n">
-        <v>170</v>
+        <v>290</v>
       </c>
       <c r="AB22" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="AE22" t="n">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="AF22" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AG22" t="n">
         <v>11</v>
       </c>
       <c r="AH22" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AI22" t="n">
-        <v>260</v>
+        <v>700</v>
       </c>
       <c r="AJ22" t="n">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="AK22" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AL22" t="n">
         <v>55</v>
@@ -4739,68 +4739,68 @@
         <v>500</v>
       </c>
       <c r="AN22" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="AO22" t="n">
-        <v>170</v>
+        <v>260</v>
       </c>
       <c r="AP22" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AQ22" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AR22" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AS22" t="n">
-        <v>15.5</v>
+        <v>28</v>
       </c>
       <c r="AT22" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AU22" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AV22" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="AW22" t="n">
-        <v>18</v>
+        <v>13.5</v>
       </c>
       <c r="AX22" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="AY22" t="n">
         <v>10</v>
       </c>
       <c r="AZ22" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BA22" t="n">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="BB22" t="n">
-        <v>18.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC22" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="BD22" t="n">
         <v>32</v>
       </c>
       <c r="BE22" t="n">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="BF22" t="n">
-        <v>17.5</v>
+        <v>12</v>
       </c>
       <c r="BG22" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-07 08:55:50</t>
+          <t>2026-05-07 11:21:53</t>
         </is>
       </c>
     </row>
@@ -4831,10 +4831,10 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="G23" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="H23" t="n">
         <v>8.6</v>
@@ -4843,10 +4843,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="K23" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L23" t="n">
         <v>1.38</v>
@@ -4855,49 +4855,49 @@
         <v>1.06</v>
       </c>
       <c r="N23" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O23" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P23" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="R23" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S23" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="T23" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U23" t="n">
         <v>1.84</v>
       </c>
       <c r="V23" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="W23" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="X23" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="Y23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Z23" t="n">
         <v>80</v>
       </c>
       <c r="AA23" t="n">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="AB23" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC23" t="n">
         <v>10.5</v>
@@ -4906,16 +4906,16 @@
         <v>36</v>
       </c>
       <c r="AE23" t="n">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="AF23" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AG23" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AI23" t="n">
         <v>260</v>
@@ -4927,46 +4927,46 @@
         <v>16.5</v>
       </c>
       <c r="AL23" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM23" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AN23" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AO23" t="n">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="AP23" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AQ23" t="n">
         <v>23</v>
       </c>
       <c r="AR23" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AS23" t="n">
         <v>14</v>
       </c>
       <c r="AT23" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU23" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV23" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AW23" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AX23" t="n">
         <v>7</v>
       </c>
       <c r="AY23" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AZ23" t="n">
         <v>24</v>
@@ -4975,7 +4975,7 @@
         <v>29</v>
       </c>
       <c r="BB23" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BC23" t="n">
         <v>13.5</v>
@@ -4984,17 +4984,17 @@
         <v>26</v>
       </c>
       <c r="BE23" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BF23" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BG23" t="n">
         <v>15</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-07 08:55:50</t>
+          <t>2026-05-07 11:21:53</t>
         </is>
       </c>
     </row>
@@ -5025,22 +5025,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="G24" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="H24" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="I24" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="J24" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="K24" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="L24" t="n">
         <v>1.46</v>
@@ -5058,137 +5058,137 @@
         <v>1.77</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="R24" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T24" t="n">
-        <v>2.42</v>
+        <v>2.22</v>
       </c>
       <c r="U24" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="V24" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W24" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="X24" t="n">
-        <v>90</v>
+        <v>12</v>
       </c>
       <c r="Y24" t="n">
-        <v>950</v>
+        <v>24</v>
       </c>
       <c r="Z24" t="n">
-        <v>110</v>
+        <v>170</v>
       </c>
       <c r="AA24" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="AB24" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AC24" t="n">
-        <v>19</v>
+        <v>9.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>950</v>
+        <v>38</v>
       </c>
       <c r="AE24" t="n">
-        <v>270</v>
+        <v>200</v>
       </c>
       <c r="AF24" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AG24" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH24" t="n">
         <v>950</v>
       </c>
       <c r="AI24" t="n">
-        <v>230</v>
+        <v>190</v>
       </c>
       <c r="AJ24" t="n">
-        <v>160</v>
+        <v>13</v>
       </c>
       <c r="AK24" t="n">
-        <v>150</v>
+        <v>19</v>
       </c>
       <c r="AL24" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AM24" t="n">
         <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="AO24" t="n">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AP24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AT24" t="n">
         <v>6</v>
       </c>
-      <c r="AQ24" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AR24" t="n">
+      <c r="AU24" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>25</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY24" t="n">
         <v>9.6</v>
       </c>
-      <c r="AS24" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AU24" t="n">
+      <c r="AZ24" t="n">
+        <v>24</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>42</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>15</v>
+      </c>
+      <c r="BF24" t="n">
         <v>9</v>
       </c>
-      <c r="AV24" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>9</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BG24" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-07 08:55:50</t>
+          <t>2026-05-07 11:21:53</t>
         </is>
       </c>
     </row>
@@ -5219,22 +5219,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="G25" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="H25" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="I25" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="J25" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="K25" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="L25" t="n">
         <v>1.22</v>
@@ -5243,70 +5243,70 @@
         <v>1.02</v>
       </c>
       <c r="N25" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O25" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="P25" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="R25" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="S25" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="T25" t="n">
         <v>1.67</v>
       </c>
       <c r="U25" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V25" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="W25" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X25" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="Y25" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="Z25" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AC25" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AF25" t="n">
-        <v>110</v>
+        <v>160</v>
       </c>
       <c r="AG25" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AH25" t="n">
         <v>23</v>
       </c>
       <c r="AI25" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AJ25" t="n">
         <v>360</v>
@@ -5315,10 +5315,10 @@
         <v>110</v>
       </c>
       <c r="AL25" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AM25" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AN25" t="n">
         <v>110</v>
@@ -5327,7 +5327,7 @@
         <v>3.6</v>
       </c>
       <c r="AP25" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AQ25" t="n">
         <v>14</v>
@@ -5339,10 +5339,10 @@
         <v>11.5</v>
       </c>
       <c r="AT25" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="AU25" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AV25" t="n">
         <v>10</v>
@@ -5351,10 +5351,10 @@
         <v>11.5</v>
       </c>
       <c r="AX25" t="n">
+        <v>90</v>
+      </c>
+      <c r="AY25" t="n">
         <v>30</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>29</v>
       </c>
       <c r="AZ25" t="n">
         <v>20</v>
@@ -5366,23 +5366,23 @@
         <v>15.5</v>
       </c>
       <c r="BC25" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="BD25" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="BE25" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BF25" t="n">
-        <v>36</v>
+        <v>14.5</v>
       </c>
       <c r="BG25" t="n">
         <v>3.4</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-07 08:55:50</t>
+          <t>2026-05-07 11:21:53</t>
         </is>
       </c>
     </row>
@@ -5419,16 +5419,16 @@
         <v>1.5</v>
       </c>
       <c r="H26" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="I26" t="n">
         <v>11.5</v>
       </c>
       <c r="J26" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K26" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L26" t="n">
         <v>1.51</v>
@@ -5443,22 +5443,22 @@
         <v>1.45</v>
       </c>
       <c r="P26" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="Q26" t="n">
         <v>2.38</v>
       </c>
       <c r="R26" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S26" t="n">
         <v>4.8</v>
       </c>
       <c r="T26" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="U26" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="V26" t="n">
         <v>1.09</v>
@@ -5524,7 +5524,7 @@
         <v>5.7</v>
       </c>
       <c r="AQ26" t="n">
-        <v>12</v>
+        <v>4.2</v>
       </c>
       <c r="AR26" t="n">
         <v>4.2</v>
@@ -5536,10 +5536,10 @@
         <v>4.2</v>
       </c>
       <c r="AU26" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="AV26" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="AW26" t="n">
         <v>4.2</v>
@@ -5551,7 +5551,7 @@
         <v>6.4</v>
       </c>
       <c r="AZ26" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BA26" t="n">
         <v>4.2</v>
@@ -5560,23 +5560,23 @@
         <v>5.7</v>
       </c>
       <c r="BC26" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BD26" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="BE26" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="BF26" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="BG26" t="n">
         <v>8</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-07 08:55:50</t>
+          <t>2026-05-07 11:21:53</t>
         </is>
       </c>
     </row>
@@ -5607,52 +5607,52 @@
         </is>
       </c>
       <c r="F27" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="G27" t="n">
         <v>1.68</v>
       </c>
-      <c r="G27" t="n">
-        <v>1.69</v>
-      </c>
       <c r="H27" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="I27" t="n">
         <v>5.8</v>
       </c>
-      <c r="I27" t="n">
-        <v>5.9</v>
-      </c>
       <c r="J27" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K27" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L27" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M27" t="n">
         <v>1.06</v>
       </c>
       <c r="N27" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O27" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P27" t="n">
         <v>2.04</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="R27" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="S27" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T27" t="n">
         <v>1.97</v>
       </c>
       <c r="U27" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V27" t="n">
         <v>1.2</v>
@@ -5664,19 +5664,19 @@
         <v>16</v>
       </c>
       <c r="Y27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Z27" t="n">
         <v>48</v>
       </c>
       <c r="AA27" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AB27" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC27" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD27" t="n">
         <v>22</v>
@@ -5685,7 +5685,7 @@
         <v>80</v>
       </c>
       <c r="AF27" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AG27" t="n">
         <v>10</v>
@@ -5694,13 +5694,13 @@
         <v>22</v>
       </c>
       <c r="AI27" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ27" t="n">
         <v>16.5</v>
       </c>
       <c r="AK27" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AL27" t="n">
         <v>36</v>
@@ -5709,7 +5709,7 @@
         <v>120</v>
       </c>
       <c r="AN27" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AO27" t="n">
         <v>120</v>
@@ -5718,28 +5718,28 @@
         <v>15</v>
       </c>
       <c r="AQ27" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AR27" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AS27" t="n">
-        <v>95</v>
+        <v>36</v>
       </c>
       <c r="AT27" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AU27" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW27" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AX27" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY27" t="n">
         <v>9.6</v>
@@ -5751,26 +5751,26 @@
         <v>65</v>
       </c>
       <c r="BB27" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BC27" t="n">
         <v>16</v>
       </c>
       <c r="BD27" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BE27" t="n">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="BF27" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG27" t="n">
         <v>85</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-07 08:55:50</t>
+          <t>2026-05-07 11:21:53</t>
         </is>
       </c>
     </row>
@@ -5801,28 +5801,28 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G28" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H28" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I28" t="n">
         <v>4.1</v>
       </c>
       <c r="J28" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K28" t="n">
         <v>3.85</v>
-      </c>
-      <c r="K28" t="n">
-        <v>3.9</v>
       </c>
       <c r="L28" t="n">
         <v>1.4</v>
       </c>
       <c r="M28" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N28" t="n">
         <v>4.1</v>
@@ -5831,19 +5831,19 @@
         <v>1.3</v>
       </c>
       <c r="P28" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="R28" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S28" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="T28" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U28" t="n">
         <v>2.2</v>
@@ -5852,10 +5852,10 @@
         <v>1.32</v>
       </c>
       <c r="W28" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="X28" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y28" t="n">
         <v>16</v>
@@ -5867,13 +5867,13 @@
         <v>80</v>
       </c>
       <c r="AB28" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AC28" t="n">
         <v>8.6</v>
       </c>
       <c r="AD28" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE28" t="n">
         <v>46</v>
@@ -5891,16 +5891,16 @@
         <v>55</v>
       </c>
       <c r="AJ28" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK28" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AL28" t="n">
         <v>34</v>
       </c>
       <c r="AM28" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN28" t="n">
         <v>14</v>
@@ -5918,28 +5918,28 @@
         <v>26</v>
       </c>
       <c r="AS28" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="AT28" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AU28" t="n">
         <v>8</v>
       </c>
       <c r="AV28" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AW28" t="n">
         <v>42</v>
       </c>
       <c r="AX28" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY28" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ28" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA28" t="n">
         <v>48</v>
@@ -5957,14 +5957,14 @@
         <v>75</v>
       </c>
       <c r="BF28" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BG28" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-07 08:55:50</t>
+          <t>2026-05-07 11:21:53</t>
         </is>
       </c>
     </row>
@@ -5995,10 +5995,10 @@
         </is>
       </c>
       <c r="F29" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="G29" t="n">
         <v>1.79</v>
-      </c>
-      <c r="G29" t="n">
-        <v>1.8</v>
       </c>
       <c r="H29" t="n">
         <v>5</v>
@@ -6007,31 +6007,31 @@
         <v>5.1</v>
       </c>
       <c r="J29" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K29" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L29" t="n">
         <v>1.41</v>
       </c>
       <c r="M29" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N29" t="n">
         <v>4.1</v>
       </c>
       <c r="O29" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P29" t="n">
         <v>2.06</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="R29" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S29" t="n">
         <v>3.35</v>
@@ -6040,34 +6040,34 @@
         <v>1.88</v>
       </c>
       <c r="U29" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V29" t="n">
         <v>1.24</v>
       </c>
       <c r="W29" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="X29" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Y29" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z29" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA29" t="n">
         <v>110</v>
       </c>
       <c r="AB29" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AC29" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD29" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AE29" t="n">
         <v>60</v>
@@ -6076,7 +6076,7 @@
         <v>10.5</v>
       </c>
       <c r="AG29" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AH29" t="n">
         <v>19</v>
@@ -6085,7 +6085,7 @@
         <v>60</v>
       </c>
       <c r="AJ29" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AK29" t="n">
         <v>17.5</v>
@@ -6094,31 +6094,31 @@
         <v>34</v>
       </c>
       <c r="AM29" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AN29" t="n">
         <v>11.5</v>
       </c>
       <c r="AO29" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AP29" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AQ29" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AR29" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AS29" t="n">
         <v>95</v>
       </c>
       <c r="AT29" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU29" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV29" t="n">
         <v>18.5</v>
@@ -6127,13 +6127,13 @@
         <v>50</v>
       </c>
       <c r="AX29" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY29" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ29" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BA29" t="n">
         <v>55</v>
@@ -6142,23 +6142,23 @@
         <v>17.5</v>
       </c>
       <c r="BC29" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BD29" t="n">
         <v>32</v>
       </c>
       <c r="BE29" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BF29" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BG29" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-07 08:55:50</t>
+          <t>2026-05-07 11:21:53</t>
         </is>
       </c>
     </row>
@@ -6201,40 +6201,40 @@
         <v>5.4</v>
       </c>
       <c r="J30" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K30" t="n">
         <v>4</v>
       </c>
       <c r="L30" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="M30" t="n">
         <v>1.07</v>
       </c>
       <c r="N30" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O30" t="n">
         <v>1.34</v>
       </c>
       <c r="P30" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="Q30" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U30" t="n">
         <v>2.04</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S30" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T30" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="U30" t="n">
-        <v>2</v>
       </c>
       <c r="V30" t="n">
         <v>1.22</v>
@@ -6252,16 +6252,16 @@
         <v>40</v>
       </c>
       <c r="AA30" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AB30" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AC30" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE30" t="n">
         <v>75</v>
@@ -6273,7 +6273,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AH30" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI30" t="n">
         <v>85</v>
@@ -6285,40 +6285,40 @@
         <v>18.5</v>
       </c>
       <c r="AL30" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM30" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN30" t="n">
         <v>12</v>
       </c>
       <c r="AO30" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AP30" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ30" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AR30" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AS30" t="n">
         <v>120</v>
       </c>
       <c r="AT30" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU30" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV30" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AX30" t="n">
         <v>9.4</v>
@@ -6336,23 +6336,23 @@
         <v>17.5</v>
       </c>
       <c r="BC30" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BD30" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BE30" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="BF30" t="n">
         <v>11</v>
       </c>
       <c r="BG30" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-05-07 08:55:50</t>
+          <t>2026-05-07 11:21:53</t>
         </is>
       </c>
     </row>
@@ -6383,67 +6383,67 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="G31" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="H31" t="n">
         <v>10.5</v>
       </c>
       <c r="I31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J31" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K31" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L31" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="M31" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N31" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="O31" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="P31" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="R31" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S31" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="T31" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="U31" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="V31" t="n">
         <v>1.1</v>
       </c>
       <c r="W31" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="X31" t="n">
-        <v>90</v>
+        <v>14.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>950</v>
+        <v>40</v>
       </c>
       <c r="Z31" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AA31" t="n">
         <v>1000</v>
@@ -6452,64 +6452,64 @@
         <v>6.8</v>
       </c>
       <c r="AC31" t="n">
-        <v>19</v>
+        <v>11.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>950</v>
+        <v>60</v>
       </c>
       <c r="AE31" t="n">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AF31" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AG31" t="n">
         <v>11</v>
       </c>
-      <c r="AG31" t="n">
-        <v>970</v>
-      </c>
       <c r="AH31" t="n">
-        <v>950</v>
+        <v>60</v>
       </c>
       <c r="AI31" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AJ31" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AK31" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AL31" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AM31" t="n">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AN31" t="n">
-        <v>15</v>
+        <v>8.6</v>
       </c>
       <c r="AO31" t="n">
-        <v>1000</v>
+        <v>550</v>
       </c>
       <c r="AP31" t="n">
-        <v>5.9</v>
+        <v>11.5</v>
       </c>
       <c r="AQ31" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AR31" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AS31" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT31" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AU31" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AV31" t="n">
-        <v>8.800000000000001</v>
+        <v>25</v>
       </c>
       <c r="AW31" t="n">
         <v>9.6</v>
@@ -6518,35 +6518,35 @@
         <v>6.2</v>
       </c>
       <c r="AY31" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ31" t="n">
-        <v>8.6</v>
+        <v>22</v>
       </c>
       <c r="BA31" t="n">
-        <v>6.6</v>
+        <v>9.6</v>
       </c>
       <c r="BB31" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BC31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="BD31" t="n">
-        <v>8.4</v>
+        <v>28</v>
       </c>
       <c r="BE31" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BF31" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BG31" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-05-07 08:55:50</t>
+          <t>2026-05-07 11:21:53</t>
         </is>
       </c>
     </row>
@@ -6577,7 +6577,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="G32" t="n">
         <v>2.42</v>
@@ -6595,19 +6595,19 @@
         <v>3.15</v>
       </c>
       <c r="L32" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="M32" t="n">
         <v>1.14</v>
       </c>
       <c r="N32" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="O32" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="P32" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="Q32" t="n">
         <v>2.84</v>
@@ -6619,31 +6619,31 @@
         <v>5.9</v>
       </c>
       <c r="T32" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="U32" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="V32" t="n">
         <v>1.33</v>
       </c>
       <c r="W32" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="X32" t="n">
         <v>8.4</v>
       </c>
       <c r="Y32" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z32" t="n">
         <v>120</v>
       </c>
       <c r="AA32" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB32" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AC32" t="n">
         <v>7.4</v>
@@ -6655,7 +6655,7 @@
         <v>500</v>
       </c>
       <c r="AF32" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG32" t="n">
         <v>12.5</v>
@@ -6667,10 +6667,10 @@
         <v>500</v>
       </c>
       <c r="AJ32" t="n">
-        <v>900</v>
+        <v>250</v>
       </c>
       <c r="AK32" t="n">
-        <v>190</v>
+        <v>75</v>
       </c>
       <c r="AL32" t="n">
         <v>500</v>
@@ -6679,7 +6679,7 @@
         <v>500</v>
       </c>
       <c r="AN32" t="n">
-        <v>48</v>
+        <v>600</v>
       </c>
       <c r="AO32" t="n">
         <v>600</v>
@@ -6688,16 +6688,16 @@
         <v>7.2</v>
       </c>
       <c r="AQ32" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR32" t="n">
         <v>17.5</v>
       </c>
       <c r="AS32" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="AT32" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU32" t="n">
         <v>6.4</v>
@@ -6715,32 +6715,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ32" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA32" t="n">
-        <v>11.5</v>
+        <v>18</v>
       </c>
       <c r="BB32" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="BC32" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="BD32" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="BE32" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="BF32" t="n">
-        <v>10</v>
+        <v>17.5</v>
       </c>
       <c r="BG32" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-05-07 08:55:50</t>
+          <t>2026-05-07 11:21:53</t>
         </is>
       </c>
     </row>
@@ -6771,25 +6771,25 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="G33" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="H33" t="n">
         <v>7.4</v>
       </c>
       <c r="I33" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J33" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K33" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L33" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M33" t="n">
         <v>1.08</v>
@@ -6804,28 +6804,28 @@
         <v>1.82</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R33" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S33" t="n">
         <v>4</v>
       </c>
       <c r="T33" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="U33" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="V33" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="W33" t="n">
         <v>2.74</v>
       </c>
       <c r="X33" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Y33" t="n">
         <v>20</v>
@@ -6834,16 +6834,16 @@
         <v>65</v>
       </c>
       <c r="AA33" t="n">
-        <v>330</v>
+        <v>350</v>
       </c>
       <c r="AB33" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AC33" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AD33" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE33" t="n">
         <v>150</v>
@@ -6852,10 +6852,10 @@
         <v>7.8</v>
       </c>
       <c r="AG33" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AH33" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI33" t="n">
         <v>700</v>
@@ -6864,7 +6864,7 @@
         <v>14</v>
       </c>
       <c r="AK33" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AL33" t="n">
         <v>48</v>
@@ -6873,19 +6873,19 @@
         <v>580</v>
       </c>
       <c r="AN33" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AO33" t="n">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="AP33" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ33" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AR33" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AS33" t="n">
         <v>19.5</v>
@@ -6894,47 +6894,47 @@
         <v>6.2</v>
       </c>
       <c r="AU33" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AV33" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AW33" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AX33" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AY33" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ33" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA33" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="BB33" t="n">
         <v>13</v>
       </c>
       <c r="BC33" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BD33" t="n">
         <v>40</v>
       </c>
       <c r="BE33" t="n">
-        <v>20</v>
+        <v>95</v>
       </c>
       <c r="BF33" t="n">
         <v>11</v>
       </c>
       <c r="BG33" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-05-07 08:55:50</t>
+          <t>2026-05-07 11:21:53</t>
         </is>
       </c>
     </row>
@@ -6965,61 +6965,61 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="G34" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="H34" t="n">
         <v>3.75</v>
       </c>
       <c r="I34" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J34" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K34" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="L34" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="M34" t="n">
         <v>1.12</v>
       </c>
       <c r="N34" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="O34" t="n">
         <v>1.52</v>
       </c>
       <c r="P34" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="R34" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S34" t="n">
         <v>5.3</v>
       </c>
       <c r="T34" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U34" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="V34" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W34" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="X34" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Y34" t="n">
         <v>11</v>
@@ -7037,7 +7037,7 @@
         <v>7.4</v>
       </c>
       <c r="AD34" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE34" t="n">
         <v>60</v>
@@ -7049,7 +7049,7 @@
         <v>12</v>
       </c>
       <c r="AH34" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI34" t="n">
         <v>80</v>
@@ -7073,7 +7073,7 @@
         <v>80</v>
       </c>
       <c r="AP34" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ34" t="n">
         <v>9.199999999999999</v>
@@ -7082,19 +7082,19 @@
         <v>21</v>
       </c>
       <c r="AS34" t="n">
-        <v>8.800000000000001</v>
+        <v>29</v>
       </c>
       <c r="AT34" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AU34" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV34" t="n">
         <v>14</v>
       </c>
       <c r="AW34" t="n">
-        <v>9.199999999999999</v>
+        <v>23</v>
       </c>
       <c r="AX34" t="n">
         <v>11.5</v>
@@ -7103,7 +7103,7 @@
         <v>10</v>
       </c>
       <c r="AZ34" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA34" t="n">
         <v>8.6</v>
@@ -7115,7 +7115,7 @@
         <v>26</v>
       </c>
       <c r="BD34" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BE34" t="n">
         <v>9.199999999999999</v>
@@ -7124,11 +7124,11 @@
         <v>26</v>
       </c>
       <c r="BG34" t="n">
-        <v>8.6</v>
+        <v>24</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-05-07 08:55:50</t>
+          <t>2026-05-07 11:21:53</t>
         </is>
       </c>
     </row>
@@ -7159,25 +7159,25 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="G35" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="H35" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="I35" t="n">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="J35" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K35" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="L35" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="M35" t="n">
         <v>1.09</v>
@@ -7189,140 +7189,140 @@
         <v>1.41</v>
       </c>
       <c r="P35" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="R35" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S35" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="T35" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U35" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="V35" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="W35" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="X35" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Y35" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="Z35" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA35" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AB35" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AC35" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD35" t="n">
         <v>10.5</v>
       </c>
       <c r="AE35" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF35" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AG35" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AH35" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AI35" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AJ35" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="AK35" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AL35" t="n">
         <v>110</v>
       </c>
       <c r="AM35" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AN35" t="n">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="AO35" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AP35" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ35" t="n">
         <v>6.6</v>
       </c>
       <c r="AR35" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AS35" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT35" t="n">
         <v>14.5</v>
       </c>
       <c r="AU35" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV35" t="n">
         <v>9.4</v>
       </c>
       <c r="AW35" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AX35" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AY35" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AZ35" t="n">
         <v>21</v>
       </c>
       <c r="BA35" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="BB35" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC35" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BE35" t="n">
         <v>14</v>
       </c>
-      <c r="BD35" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BE35" t="n">
-        <v>15</v>
-      </c>
       <c r="BF35" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BG35" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-05-07 08:55:50</t>
+          <t>2026-05-07 11:21:53</t>
         </is>
       </c>
     </row>
@@ -7356,10 +7356,10 @@
         <v>2.08</v>
       </c>
       <c r="G36" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="H36" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I36" t="n">
         <v>4.5</v>
@@ -7371,7 +7371,7 @@
         <v>3.5</v>
       </c>
       <c r="L36" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="M36" t="n">
         <v>1.11</v>
@@ -7383,7 +7383,7 @@
         <v>1.49</v>
       </c>
       <c r="P36" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="Q36" t="n">
         <v>2.54</v>
@@ -7404,7 +7404,7 @@
         <v>1.29</v>
       </c>
       <c r="W36" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="X36" t="n">
         <v>1000</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-05-07 08:55:50</t>
+          <t>2026-05-07 11:21:53</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH6"/>
+  <dimension ref="A1:BH4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -743,184 +743,184 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CA Platense</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Penarol</t>
+          <t>Universitario de Deportes</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.22</v>
+        <v>5.7</v>
       </c>
       <c r="G2" t="n">
-        <v>2.24</v>
+        <v>75</v>
       </c>
       <c r="H2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="V2" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>980</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>440</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AQ2" t="n">
         <v>4.7</v>
       </c>
-      <c r="I2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="K2" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="N2" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="S2" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="X2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>190</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>130</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>38</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>200</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK2" t="n">
+      <c r="AR2" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>29</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>27</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>55</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD2" t="n">
         <v>44</v>
       </c>
-      <c r="AL2" t="n">
-        <v>110</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN2" t="n">
+      <c r="BE2" t="n">
+        <v>95</v>
+      </c>
+      <c r="BF2" t="n">
         <v>55</v>
       </c>
-      <c r="AO2" t="n">
-        <v>240</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>27</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>95</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>95</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>32</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>140</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>27</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>34</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>85</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>280</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>38</v>
-      </c>
       <c r="BG2" t="n">
-        <v>140</v>
+        <v>44</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-07 19:31:31</t>
+          <t>2026-05-07 22:04:37</t>
         </is>
       </c>
     </row>
@@ -937,184 +937,184 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Ind Medellin</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>LDU</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.69</v>
+        <v>5.1</v>
       </c>
       <c r="G3" t="n">
-        <v>1.71</v>
+        <v>5.6</v>
       </c>
       <c r="H3" t="n">
-        <v>6.4</v>
+        <v>1.89</v>
       </c>
       <c r="I3" t="n">
-        <v>6.6</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="L3" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="M3" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N3" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O3" t="n">
         <v>1.44</v>
       </c>
       <c r="P3" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="R3" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S3" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="T3" t="n">
-        <v>2.28</v>
+        <v>2.04</v>
       </c>
       <c r="U3" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="V3" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>2.42</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Y3" t="n">
-        <v>17</v>
+        <v>7.2</v>
       </c>
       <c r="Z3" t="n">
-        <v>48</v>
+        <v>15.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
+        <v>26</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>120</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>130</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ3" t="n">
         <v>6.4</v>
       </c>
-      <c r="AC3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>120</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ3" t="n">
+      <c r="AR3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>28</v>
+      </c>
+      <c r="AY3" t="n">
         <v>18</v>
       </c>
-      <c r="AK3" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>210</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>170</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>40</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>140</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>80</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AZ3" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="BB3" t="n">
-        <v>15.5</v>
+        <v>46</v>
       </c>
       <c r="BC3" t="n">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="BD3" t="n">
         <v>44</v>
       </c>
       <c r="BE3" t="n">
-        <v>150</v>
+        <v>44</v>
       </c>
       <c r="BF3" t="n">
+        <v>80</v>
+      </c>
+      <c r="BG3" t="n">
         <v>14.5</v>
       </c>
-      <c r="BG3" t="n">
-        <v>120</v>
-      </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-07 19:31:31</t>
+          <t>2026-05-07 22:04:37</t>
         </is>
       </c>
     </row>
@@ -1131,572 +1131,184 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>23:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Junior FC Barranquilla</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Universitario de Deportes</t>
+          <t>Cerro Porteno</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.4</v>
+        <v>2.02</v>
       </c>
       <c r="G4" t="n">
-        <v>2.46</v>
+        <v>2.08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="I4" t="n">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="J4" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="K4" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="L4" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="M4" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N4" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="O4" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="P4" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.6</v>
+        <v>2.42</v>
       </c>
       <c r="R4" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="S4" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="T4" t="n">
-        <v>2.1</v>
+        <v>1.11</v>
       </c>
       <c r="U4" t="n">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="V4" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="W4" t="n">
-        <v>1.69</v>
+        <v>1.92</v>
       </c>
       <c r="X4" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y4" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="AA4" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE4" t="n">
         <v>75</v>
       </c>
-      <c r="AB4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>60</v>
-      </c>
       <c r="AF4" t="n">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="AG4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH4" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="AI4" t="n">
         <v>95</v>
       </c>
       <c r="AJ4" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AK4" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AL4" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM4" t="n">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="AN4" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="AO4" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AP4" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AQ4" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AR4" t="n">
         <v>20</v>
       </c>
       <c r="AS4" t="n">
-        <v>65</v>
+        <v>12.5</v>
       </c>
       <c r="AT4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU4" t="n">
         <v>7.2</v>
       </c>
-      <c r="AU4" t="n">
-        <v>6.8</v>
-      </c>
       <c r="AV4" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="AX4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AY4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ4" t="n">
         <v>21</v>
       </c>
       <c r="BA4" t="n">
-        <v>65</v>
+        <v>12.5</v>
       </c>
       <c r="BB4" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="BC4" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="BD4" t="n">
-        <v>48</v>
+        <v>11.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="BF4" t="n">
-        <v>23</v>
+        <v>9.6</v>
       </c>
       <c r="BG4" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-07 19:31:31</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>CONMEBOL Copa Libertadores</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>21:30:00</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Ind Medellin</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Flamengo</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="G5" t="n">
-        <v>5</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="V5" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>36</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>19</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>120</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>75</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>980</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>19</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>32</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>38</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>23</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>60</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>50</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>22</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>75</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>14</v>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>2026-05-07 19:31:31</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>CONMEBOL Copa Libertadores</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>23:00:00</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Junior FC Barranquilla</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Cerro Porteno</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="G6" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="H6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="X6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>30</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>120</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>28</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>27</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>100</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>6</v>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>2026-05-07 19:31:31</t>
+          <t>2026-05-07 22:04:37</t>
         </is>
       </c>
     </row>
